--- a/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
+++ b/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="核心卡位龙头全景深度分析" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="买卖决策速查面板" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="核心卡位龙头全景深度分析" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="买卖决策速查面板" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -631,7 +631,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>定盘时间: 2026-09-11 19:39:04 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
+          <t>定盘时间: 2026-09-13 16:53:36 | 数据源: Shioaji Snapshot | 包含三大法人买卖超、财报发布日及主力资金分析</t>
         </is>
       </c>
     </row>
@@ -738,10 +738,10 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>• 毛利率：65.0% - 67.0%
-• 净利率：&gt;43.0%
-• ROE：40.5%
-• EPS：22.08 元 (26Q1)</t>
+          <t>• 毛利率：67.03% (2026Q2)
+• 净利率：53.22% (2026Q2)
+• ROE：79.5% (單季年化, 2026Q2)
+• EPS：49.33 元 (2026Q2)</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -751,15 +751,15 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>外资: +3031 张
-投信: -1765 张
-[2026-08-28 官方结算] 外资主力大幅回流 (+3,031 张)，投信阶段获利减仓 (-1,765 张)。</t>
+          <t>外资: -8252 张
+投信: -181 张
+[2026-09-11 官方结算] 三大法人同步卖超 (-8,833 张)，短线筹码面临清洗。</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 1,243 张 (占量 9.2%)
-[2026-08-28 筹码] 主力机构呈净买入 (+1,243 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 8,833 张 (占量 48.8%)
+[2026-09-11 筹码] 主力机构呈净卖出 (-8,833 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
@@ -825,10 +825,10 @@
       </c>
       <c r="E5" s="15" t="inlineStr">
         <is>
-          <t>• 毛利率：87.0%
-• 净利率：&gt;52.0%
-• ROE：21.72%
-• EPS：74.38 元 (26Q2)</t>
+          <t>• 毛利率：84.18% (2026Q2)
+• 净利率：64.95% (2026Q2)
+• ROE：125.3% (單季年化, 2026Q2)
+• EPS：110.96 元 (2026Q2)</t>
         </is>
       </c>
       <c r="F5" s="16" t="inlineStr">
@@ -838,15 +838,15 @@
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>外资: +102 张
-投信: -59 张
-[2026-08-28 官方结算] 外资主力大幅回流 (+102 张)，投信阶段获利减仓 (-59 张)。</t>
+          <t>外资: +60 张
+投信: -36 张
+[2026-09-11 官方结算] 外资主力大幅回流 (+60 张)，投信阶段获利减仓 (-36 张)。</t>
         </is>
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 34 张 (占量 8.8%)
-[2026-08-28 筹码] 主力机构呈净买入 (+34 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 16 张 (占量 4.6%)
+[2026-09-11 筹码] 主力机构呈净买入 (+16 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -912,10 +912,10 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>• 毛利率：33.8%
-• 净利率：~19.5%
-• ROE：18.58%
-• EPS：27.55 元 (26Q2)</t>
+          <t>• 毛利率：32.03% (2026Q2)
+• 净利率：18.93% (2026Q2)
+• ROE：104.3% (單季年化, 2026Q2)
+• EPS：42.46 元 (2026Q2)</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -925,15 +925,15 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>外资: +45 张
-投信: -172 张
-[2026-08-28 官方结算] 外资主力大幅回流 (+45 张)，投信阶段获利减仓 (-172 张)。</t>
+          <t>外资: -23 张
+投信: +110 张
+[2026-09-11 官方结算] 投信内资买超 (+110 张) 逢低承接，外资高档调节 (-23 张)。</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 152 张 (占量 8.2%)
-[2026-08-28 筹码] 主力机构呈净卖出 (-152 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 69 张 (占量 6.7%)
+[2026-09-11 筹码] 主力机构呈净买入 (+69 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
@@ -999,10 +999,10 @@
       </c>
       <c r="E7" s="15" t="inlineStr">
         <is>
-          <t>• 毛利率：33.8% - 35.0%
-• 净利率：~14.2%
-• ROE：17.03%
-• EPS：20.17 元 (26Q1)</t>
+          <t>• 毛利率：31.17% (2026Q2)
+• 净利率：19.31% (2026Q2)
+• ROE：126.7% (單季年化, 2026Q2)
+• EPS：44.54 元 (2026Q2)</t>
         </is>
       </c>
       <c r="F7" s="16" t="inlineStr">
@@ -1012,15 +1012,15 @@
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>外资: -34 张
-投信: +626 张
-[2026-08-28 官方结算] 投信内资买超 (+626 张) 逢低承接，外资高档调节 (-34 张)。</t>
+          <t>外资: -99 张
+投信: +45 张
+[2026-09-11 官方结算] 投信内资买超 (+45 张) 逢低承接，外资高档调节 (-99 张)。</t>
         </is>
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 503 张 (占量 13.2%)
-[2026-08-28 筹码] 主力机构呈净买入 (+503 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 94 张 (占量 4.7%)
+[2026-09-11 筹码] 主力机构呈净卖出 (-94 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I7" s="15" t="inlineStr">
@@ -1086,28 +1086,28 @@
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>• 毛利率：6.2% - 6.8%
-• 净利率：~2.8%
-• ROE：11.25%
-• EPS：3.23 元 (25Q4)</t>
+          <t>• 毛利率：6.15% (2026Q2)
+• 净利率：2.73% (2026Q2)
+• ROE：23.0% (單季年化, 2026Q2)
+• EPS：7.84 元 (2026Q2)</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14 (26Q2 法说会 - 本周五) | 每月 5 日发布营收</t>
+          <t>2026-08-14 (26Q2 法說會已舉行)；下一次財報/法說會日期待公司公告 | 每月 5 日发布营收</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>外资: +1192 张
-投信: +307 张
-[2026-08-28 官方结算] 外资与投信联手买超 (+776 张)，内外部机构共振做多。</t>
+          <t>外资: -3751 张
+投信: +410 张
+[2026-09-11 官方结算] 投信内资买超 (+410 张) 逢低承接，外资高档调节 (-3,751 张)。</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 776 张 (占量 2.5%)
-[2026-08-28 筹码] 主力机构呈净买入 (+776 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 3,386 张 (占量 14.4%)
+[2026-09-11 筹码] 主力机构呈净卖出 (-3,386 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -1173,10 +1173,10 @@
       </c>
       <c r="E9" s="15" t="inlineStr">
         <is>
-          <t>• 毛利率：35.6% (26Q2)
-• 净利率：13.7% (26Q2)
-• ROE：待更新
-• EPS：9.68 元 (26Q2)</t>
+          <t>• 毛利率：36.27% (2026Q2)
+• 净利率：14.89% (2026Q2)
+• ROE：62.2% (單季年化, 2026Q2)
+• EPS：17.59 元 (2026Q2)</t>
         </is>
       </c>
       <c r="F9" s="16" t="inlineStr">
@@ -1186,15 +1186,15 @@
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
-          <t>外资: +1163 张
-投信: -732 张
-[2026-08-28 官方结算] 外资主力大幅回流 (+1,163 张)，投信阶段获利减仓 (-732 张)。</t>
+          <t>外资: -3573 张
+投信: -536 张
+[2026-09-11 官方结算] 外资与投信偏空调节 (-3,805 张)，机构筹码阶段获利了结。</t>
         </is>
       </c>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 546 张 (占量 4.4%)
-[2026-08-28 筹码] 主力机构呈净买入 (+546 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 3,805 张 (占量 27.6%)
+[2026-09-11 筹码] 主力机构呈净卖出 (-3,805 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I9" s="15" t="inlineStr">
@@ -1260,10 +1260,10 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>• 毛利率：19.7% (26Q2)
-• 净利率：約 11.6% (26Q2)
-• ROE：待更新
-• EPS：19.78 元 (26Q2)</t>
+          <t>• 毛利率：19.63% (2026Q2)
+• 净利率：11.70% (2026Q2)
+• ROE：112.4% (單季年化, 2026Q2)
+• EPS：34.70 元 (2026Q2)</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -1273,15 +1273,15 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>外资: -532 张
-投信: -18 张
-[2026-08-28 官方结算] 三大法人同步卖超 (-554 张)，短线筹码面临清洗。</t>
+          <t>外资: +572 张
+投信: -652 张
+[2026-09-11 官方结算] 外资主力大幅回流 (+572 张)，投信阶段获利减仓 (-652 张)。</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 554 张 (占量 24.7%)
-[2026-08-28 筹码] 主力机构呈净卖出 (-554 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 87 张 (占量 2.6%)
+[2026-09-11 筹码] 主力机构呈净卖出 (-87 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1347,10 +1347,10 @@
       </c>
       <c r="E11" s="15" t="inlineStr">
         <is>
-          <t>• 毛利率：約 60.5% (26Q2)
-• 净利率：約 37.9% (26Q2)
-• ROE：待更新
-• EPS：約 12.15 元 (26Q2)</t>
+          <t>• 毛利率：61.48% (2026Q2)
+• 净利率：36.15% (2026Q2)
+• ROE：109.0% (單季年化, 2026Q2)
+• EPS：21.27 元 (2026Q2)</t>
         </is>
       </c>
       <c r="F11" s="16" t="inlineStr">
@@ -1360,15 +1360,15 @@
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>外资: +57 张
-投信: -33 张
-[2026-08-28 官方结算] 外资主力大幅回流 (+57 张)，投信阶段获利减仓 (-33 张)。</t>
+          <t>外资: +143 张
+投信: +92 张
+[2026-09-11 官方结算] 外资与投信联手买超 (+225 张)，内外部机构共振做多。</t>
         </is>
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 12 张 (占量 0.8%)
-[2026-08-28 筹码] 主力机构呈净买入 (+12 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 225 张 (占量 10.2%)
+[2026-09-11 筹码] 主力机构呈净买入 (+225 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I11" s="15" t="inlineStr">
@@ -1434,10 +1434,10 @@
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>• 毛利率：待更新
-• 净利率：約 11.0% (26Q2)
-• ROE：18.2% 年化 (26H1)
-• EPS：4.80 元 (26Q2)</t>
+          <t>• 毛利率：20.55% (2026Q2)
+• 净利率：9.89% (2026Q2)
+• ROE：36.2% (單季年化, 2026Q2)
+• EPS：8.04 元 (2026Q2)</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -1447,15 +1447,15 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>外资: -568 张
-投信: +61 张
-[2026-08-28 官方结算] 投信内资买超 (+61 张) 逢低承接，外资高档调节 (-568 张)。</t>
+          <t>外资: -8053 张
+投信: +679 张
+[2026-09-11 官方结算] 投信内资买超 (+679 张) 逢低承接，外资高档调节 (-8,053 张)。</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 440 张 (占量 2.5%)
-[2026-08-28 筹码] 主力机构呈净买入 (+440 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 7,819 张 (占量 36.3%)
+[2026-09-11 筹码] 主力机构呈净卖出 (-7,819 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -1521,10 +1521,10 @@
       </c>
       <c r="E13" s="15" t="inlineStr">
         <is>
-          <t>• 毛利率：46.2% (26Q2)
-• 净利率：約 16.2% (26Q2)
-• ROE：待更新
-• EPS：15.28 元 (26Q2)</t>
+          <t>• 毛利率：46.25% (2026Q2)
+• 净利率：16.25% (2026Q2)
+• ROE：45.7% (單季年化, 2026Q2)
+• EPS：30.44 元 (2026Q2)</t>
         </is>
       </c>
       <c r="F13" s="16" t="inlineStr">
@@ -1534,15 +1534,15 @@
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>外资: +1096 张
-投信: -118 张
-[2026-08-28 官方结算] 外资主力大幅回流 (+1,096 张)，投信阶段获利减仓 (-118 张)。</t>
+          <t>外资: -743 张
+投信: +108 张
+[2026-09-11 官方结算] 投信内资买超 (+108 张) 逢低承接，外资高档调节 (-743 张)。</t>
         </is>
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 996 张 (占量 23.8%)
-[2026-08-28 筹码] 主力机构呈净买入 (+996 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 656 张 (占量 9.6%)
+[2026-09-11 筹码] 主力机构呈净卖出 (-656 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I13" s="15" t="inlineStr">
@@ -1621,7 +1621,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-09-11 19:39:04 | 策略: 3-3-4 分批建仓</t>
+          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-09-13 16:53:36 | 策略: 3-3-4 分批建仓</t>
         </is>
       </c>
     </row>

--- a/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
+++ b/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="核心卡位龙头全景深度分析" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="买卖决策速查面板" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="核心卡位龙头全景深度分析" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="买卖决策速查面板" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -631,7 +631,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>定盘时间: 2026-09-13 16:53:36 | 数据源: Shioaji Snapshot | 包含三大法人买卖超、财报发布日及主力资金分析</t>
+          <t>定盘时间: 2026-09-14 21:08:55 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
         </is>
       </c>
     </row>
@@ -730,10 +730,10 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>开盘: 2430.0
-最高: 2430.0
-最低: 2405.0
-收盘: 2410.0</t>
+          <t>开盘: 2385.0
+最高: 2395.0
+最低: 2380.0
+收盘: 2380.0</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2410.0</t>
+          <t>NT$ 2380.0</t>
         </is>
       </c>
       <c r="K4" s="9" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>18,106 张</t>
+          <t>18,180 张</t>
         </is>
       </c>
     </row>
@@ -817,10 +817,10 @@
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>开盘: 12300.0
-最高: 12300.0
-最低: 11950.0
-收盘: 12080.0</t>
+          <t>开盘: 11900.0
+最高: 12025.0
+最低: 11785.0
+收盘: 11990.0</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 12080.0</t>
+          <t>NT$ 11990.0</t>
         </is>
       </c>
       <c r="K5" s="18" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="O5" s="16" t="inlineStr">
         <is>
-          <t>348 张</t>
+          <t>217 张</t>
         </is>
       </c>
     </row>
@@ -905,9 +905,9 @@
       <c r="D6" s="7" t="inlineStr">
         <is>
           <t>开盘: 5270.0
-最高: 5420.0
-最低: 5210.0
-收盘: 5365.0</t>
+最高: 5395.0
+最低: 5230.0
+收盘: 5345.0</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 5365.0</t>
+          <t>NT$ 5345.0</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>1,026 张</t>
+          <t>1,151 张</t>
         </is>
       </c>
     </row>
@@ -991,10 +991,10 @@
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>开盘: 3360.0
-最高: 3390.0
-最低: 3300.0
-收盘: 3370.0</t>
+          <t>开盘: 3255.0
+最高: 3360.0
+最低: 3210.0
+收盘: 3310.0</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="J7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3370.0</t>
+          <t>NT$ 3310.0</t>
         </is>
       </c>
       <c r="K7" s="18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="O7" s="16" t="inlineStr">
         <is>
-          <t>2,004 张</t>
+          <t>2,115 张</t>
         </is>
       </c>
     </row>
@@ -1078,10 +1078,10 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>开盘: 247.5
+          <t>开盘: 244.5
 最高: 249.5
-最低: 247.0
-收盘: 248.0</t>
+最低: 243.5
+收盘: 248.5</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>NT$ 248.0</t>
+          <t>NT$ 248.5</t>
         </is>
       </c>
       <c r="K8" s="9" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="O8" s="7" t="inlineStr">
         <is>
-          <t>23,483 张</t>
+          <t>21,644 张</t>
         </is>
       </c>
     </row>
@@ -1165,9 +1165,9 @@
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>开盘: 1595.0
-最高: 1635.0
-最低: 1595.0
+          <t>开盘: 1560.0
+最高: 1630.0
+最低: 1560.0
 收盘: 1620.0</t>
         </is>
       </c>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="O9" s="16" t="inlineStr">
         <is>
-          <t>13,777 张</t>
+          <t>7,944 张</t>
         </is>
       </c>
     </row>
@@ -1252,10 +1252,10 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>开盘: 1910.0
-最高: 1925.0
-最低: 1870.0
-收盘: 1885.0</t>
+          <t>开盘: 1840.0
+最高: 1895.0
+最低: 1830.0
+收盘: 1875.0</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 1885.0</t>
+          <t>NT$ 1875.0</t>
         </is>
       </c>
       <c r="K10" s="9" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>3,344 张</t>
+          <t>2,928 张</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>开盘: 2175.0
-最高: 2235.0
-最低: 2120.0
-收盘: 2160.0</t>
+          <t>开盘: 2105.0
+最高: 2180.0
+最低: 2080.0
+收盘: 2140.0</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="J11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2160.0</t>
+          <t>NT$ 2140.0</t>
         </is>
       </c>
       <c r="K11" s="18" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="O11" s="16" t="inlineStr">
         <is>
-          <t>2,196 张</t>
+          <t>1,146 张</t>
         </is>
       </c>
     </row>
@@ -1426,10 +1426,10 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>开盘: 630.0
-最高: 630.0
-最低: 605.0
-收盘: 618.0</t>
+          <t>开盘: 599.0
+最高: 620.0
+最低: 596.0
+收盘: 612.0</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 618.0</t>
+          <t>NT$ 612.0</t>
         </is>
       </c>
       <c r="K12" s="9" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>21,532 张</t>
+          <t>9,146 张</t>
         </is>
       </c>
     </row>
@@ -1513,10 +1513,10 @@
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>开盘: 4635.0
-最高: 4655.0
-最低: 4535.0
-收盘: 4585.0</t>
+          <t>开盘: 4475.0
+最高: 4650.0
+最低: 4435.0
+收盘: 4560.0</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="J13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 4585.0</t>
+          <t>NT$ 4560.0</t>
         </is>
       </c>
       <c r="K13" s="18" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="O13" s="16" t="inlineStr">
         <is>
-          <t>6,828 张</t>
+          <t>5,637 张</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-09-13 16:53:36 | 策略: 3-3-4 分批建仓</t>
+          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-09-14 21:08:55 | 策略: 3-3-4 分批建仓</t>
         </is>
       </c>
     </row>
@@ -1685,22 +1685,22 @@
       </c>
       <c r="C4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2430.0</t>
+          <t>NT$ 2385.0</t>
         </is>
       </c>
       <c r="D4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2430.0</t>
+          <t>NT$ 2395.0</t>
         </is>
       </c>
       <c r="E4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2405.0</t>
+          <t>NT$ 2380.0</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2410.0</t>
+          <t>NT$ 2380.0</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
@@ -1732,22 +1732,22 @@
       </c>
       <c r="C5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 12300.0</t>
+          <t>NT$ 11900.0</t>
         </is>
       </c>
       <c r="D5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 12300.0</t>
+          <t>NT$ 12025.0</t>
         </is>
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 11950.0</t>
+          <t>NT$ 11785.0</t>
         </is>
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 12080.0</t>
+          <t>NT$ 11990.0</t>
         </is>
       </c>
       <c r="G5" s="29" t="inlineStr">
@@ -1784,17 +1784,17 @@
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5420.0</t>
+          <t>NT$ 5395.0</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5210.0</t>
+          <t>NT$ 5230.0</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 5365.0</t>
+          <t>NT$ 5345.0</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C7" s="28" t="inlineStr">
         <is>
+          <t>NT$ 3255.0</t>
+        </is>
+      </c>
+      <c r="D7" s="28" t="inlineStr">
+        <is>
           <t>NT$ 3360.0</t>
         </is>
       </c>
-      <c r="D7" s="28" t="inlineStr">
-        <is>
-          <t>NT$ 3390.0</t>
-        </is>
-      </c>
       <c r="E7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3300.0</t>
+          <t>NT$ 3210.0</t>
         </is>
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3370.0</t>
+          <t>NT$ 3310.0</t>
         </is>
       </c>
       <c r="G7" s="29" t="inlineStr">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 247.5</t>
+          <t>NT$ 244.5</t>
         </is>
       </c>
       <c r="D8" s="24" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="E8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 247.0</t>
+          <t>NT$ 243.5</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>NT$ 248.0</t>
+          <t>NT$ 248.5</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
@@ -1920,17 +1920,17 @@
       </c>
       <c r="C9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1595.0</t>
+          <t>NT$ 1560.0</t>
         </is>
       </c>
       <c r="D9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1635.0</t>
+          <t>NT$ 1630.0</t>
         </is>
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1595.0</t>
+          <t>NT$ 1560.0</t>
         </is>
       </c>
       <c r="F9" s="17" t="inlineStr">
@@ -1967,22 +1967,22 @@
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1910.0</t>
+          <t>NT$ 1840.0</t>
         </is>
       </c>
       <c r="D10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1925.0</t>
+          <t>NT$ 1895.0</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1870.0</t>
+          <t>NT$ 1830.0</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 1885.0</t>
+          <t>NT$ 1875.0</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
@@ -2014,22 +2014,22 @@
       </c>
       <c r="C11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2175.0</t>
+          <t>NT$ 2105.0</t>
         </is>
       </c>
       <c r="D11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2235.0</t>
+          <t>NT$ 2180.0</t>
         </is>
       </c>
       <c r="E11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2120.0</t>
+          <t>NT$ 2080.0</t>
         </is>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2160.0</t>
+          <t>NT$ 2140.0</t>
         </is>
       </c>
       <c r="G11" s="29" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 630.0</t>
+          <t>NT$ 599.0</t>
         </is>
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 630.0</t>
+          <t>NT$ 620.0</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 605.0</t>
+          <t>NT$ 596.0</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 618.0</t>
+          <t>NT$ 612.0</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
@@ -2108,22 +2108,22 @@
       </c>
       <c r="C13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4635.0</t>
+          <t>NT$ 4475.0</t>
         </is>
       </c>
       <c r="D13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4655.0</t>
+          <t>NT$ 4650.0</t>
         </is>
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4535.0</t>
+          <t>NT$ 4435.0</t>
         </is>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 4585.0</t>
+          <t>NT$ 4560.0</t>
         </is>
       </c>
       <c r="G13" s="29" t="inlineStr">

--- a/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
+++ b/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
@@ -631,7 +631,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>定盘时间: 2026-09-14 21:08:55 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
+          <t>定盘时间: 2026-09-15 19:57:51 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
         </is>
       </c>
     </row>
@@ -730,10 +730,10 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>开盘: 2385.0
-最高: 2395.0
+          <t>开盘: 2405.0
+最高: 2405.0
 最低: 2380.0
-收盘: 2380.0</t>
+收盘: 2385.0</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2380.0</t>
+          <t>NT$ 2385.0</t>
         </is>
       </c>
       <c r="K4" s="9" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>18,180 张</t>
+          <t>13,479 张</t>
         </is>
       </c>
     </row>
@@ -817,10 +817,10 @@
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>开盘: 11900.0
-最高: 12025.0
-最低: 11785.0
-收盘: 11990.0</t>
+          <t>开盘: 11920.0
+最高: 12075.0
+最低: 11665.0
+收盘: 11715.0</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 11990.0</t>
+          <t>NT$ 11715.0</t>
         </is>
       </c>
       <c r="K5" s="18" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="O5" s="16" t="inlineStr">
         <is>
-          <t>217 张</t>
+          <t>183 张</t>
         </is>
       </c>
     </row>
@@ -904,10 +904,10 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>开盘: 5270.0
-最高: 5395.0
-最低: 5230.0
-收盘: 5345.0</t>
+          <t>开盘: 5300.0
+最高: 5365.0
+最低: 5110.0
+收盘: 5115.0</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 5345.0</t>
+          <t>NT$ 5115.0</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>1,151 张</t>
+          <t>1,318 张</t>
         </is>
       </c>
     </row>
@@ -991,10 +991,10 @@
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>开盘: 3255.0
-最高: 3360.0
-最低: 3210.0
-收盘: 3310.0</t>
+          <t>开盘: 3265.0
+最高: 3300.0
+最低: 3100.0
+收盘: 3115.0</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="J7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3310.0</t>
+          <t>NT$ 3115.0</t>
         </is>
       </c>
       <c r="K7" s="18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="O7" s="16" t="inlineStr">
         <is>
-          <t>2,115 张</t>
+          <t>2,964 张</t>
         </is>
       </c>
     </row>
@@ -1078,10 +1078,10 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>开盘: 244.5
-最高: 249.5
-最低: 243.5
-收盘: 248.5</t>
+          <t>开盘: 247.5
+最高: 250.0
+最低: 246.5
+收盘: 246.5</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>NT$ 248.5</t>
+          <t>NT$ 246.5</t>
         </is>
       </c>
       <c r="K8" s="9" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="O8" s="7" t="inlineStr">
         <is>
-          <t>21,644 张</t>
+          <t>15,338 张</t>
         </is>
       </c>
     </row>
@@ -1165,10 +1165,10 @@
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>开盘: 1560.0
-最高: 1630.0
-最低: 1560.0
-收盘: 1620.0</t>
+          <t>开盘: 1590.0
+最高: 1715.0
+最低: 1585.0
+收盘: 1670.0</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="J9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1620.0</t>
+          <t>NT$ 1670.0</t>
         </is>
       </c>
       <c r="K9" s="18" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="O9" s="16" t="inlineStr">
         <is>
-          <t>7,944 张</t>
+          <t>14,027 张</t>
         </is>
       </c>
     </row>
@@ -1252,10 +1252,10 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>开盘: 1840.0
+          <t>开盘: 1870.0
 最高: 1895.0
 最低: 1830.0
-收盘: 1875.0</t>
+收盘: 1840.0</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 1875.0</t>
+          <t>NT$ 1840.0</t>
         </is>
       </c>
       <c r="K10" s="9" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>2,928 张</t>
+          <t>2,068 张</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>开盘: 2105.0
-最高: 2180.0
-最低: 2080.0
-收盘: 2140.0</t>
+          <t>开盘: 2100.0
+最高: 2155.0
+最低: 2075.0
+收盘: 2080.0</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="J11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2140.0</t>
+          <t>NT$ 2080.0</t>
         </is>
       </c>
       <c r="K11" s="18" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="O11" s="16" t="inlineStr">
         <is>
-          <t>1,146 张</t>
+          <t>946 张</t>
         </is>
       </c>
     </row>
@@ -1426,10 +1426,10 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>开盘: 599.0
-最高: 620.0
-最低: 596.0
-收盘: 612.0</t>
+          <t>开盘: 601.0
+最高: 608.0
+最低: 592.0
+收盘: 592.0</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 612.0</t>
+          <t>NT$ 592.0</t>
         </is>
       </c>
       <c r="K12" s="9" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>9,146 张</t>
+          <t>12,532 张</t>
         </is>
       </c>
     </row>
@@ -1513,10 +1513,10 @@
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>开盘: 4475.0
-最高: 4650.0
-最低: 4435.0
-收盘: 4560.0</t>
+          <t>开盘: 4505.0
+最高: 4575.0
+最低: 4430.0
+收盘: 4430.0</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="J13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 4560.0</t>
+          <t>NT$ 4430.0</t>
         </is>
       </c>
       <c r="K13" s="18" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="O13" s="16" t="inlineStr">
         <is>
-          <t>5,637 张</t>
+          <t>5,688 张</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-09-14 21:08:55 | 策略: 3-3-4 分批建仓</t>
+          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-09-15 19:57:51 | 策略: 3-3-4 分批建仓</t>
         </is>
       </c>
     </row>
@@ -1685,22 +1685,22 @@
       </c>
       <c r="C4" s="24" t="inlineStr">
         <is>
+          <t>NT$ 2405.0</t>
+        </is>
+      </c>
+      <c r="D4" s="24" t="inlineStr">
+        <is>
+          <t>NT$ 2405.0</t>
+        </is>
+      </c>
+      <c r="E4" s="24" t="inlineStr">
+        <is>
+          <t>NT$ 2380.0</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
           <t>NT$ 2385.0</t>
-        </is>
-      </c>
-      <c r="D4" s="24" t="inlineStr">
-        <is>
-          <t>NT$ 2395.0</t>
-        </is>
-      </c>
-      <c r="E4" s="24" t="inlineStr">
-        <is>
-          <t>NT$ 2380.0</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>NT$ 2380.0</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
@@ -1732,22 +1732,22 @@
       </c>
       <c r="C5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 11900.0</t>
+          <t>NT$ 11920.0</t>
         </is>
       </c>
       <c r="D5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 12025.0</t>
+          <t>NT$ 12075.0</t>
         </is>
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 11785.0</t>
+          <t>NT$ 11665.0</t>
         </is>
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 11990.0</t>
+          <t>NT$ 11715.0</t>
         </is>
       </c>
       <c r="G5" s="29" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="C6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5270.0</t>
+          <t>NT$ 5300.0</t>
         </is>
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5395.0</t>
+          <t>NT$ 5365.0</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5230.0</t>
+          <t>NT$ 5110.0</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 5345.0</t>
+          <t>NT$ 5115.0</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3255.0</t>
+          <t>NT$ 3265.0</t>
         </is>
       </c>
       <c r="D7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3360.0</t>
+          <t>NT$ 3300.0</t>
         </is>
       </c>
       <c r="E7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3210.0</t>
+          <t>NT$ 3100.0</t>
         </is>
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3310.0</t>
+          <t>NT$ 3115.0</t>
         </is>
       </c>
       <c r="G7" s="29" t="inlineStr">
@@ -1873,22 +1873,22 @@
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 244.5</t>
+          <t>NT$ 247.5</t>
         </is>
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 249.5</t>
+          <t>NT$ 250.0</t>
         </is>
       </c>
       <c r="E8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 243.5</t>
+          <t>NT$ 246.5</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>NT$ 248.5</t>
+          <t>NT$ 246.5</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
@@ -1920,22 +1920,22 @@
       </c>
       <c r="C9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1560.0</t>
+          <t>NT$ 1590.0</t>
         </is>
       </c>
       <c r="D9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1630.0</t>
+          <t>NT$ 1715.0</t>
         </is>
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1560.0</t>
+          <t>NT$ 1585.0</t>
         </is>
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1620.0</t>
+          <t>NT$ 1670.0</t>
         </is>
       </c>
       <c r="G9" s="29" t="inlineStr">
@@ -1967,22 +1967,22 @@
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
+          <t>NT$ 1870.0</t>
+        </is>
+      </c>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t>NT$ 1895.0</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="inlineStr">
+        <is>
+          <t>NT$ 1830.0</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
           <t>NT$ 1840.0</t>
-        </is>
-      </c>
-      <c r="D10" s="24" t="inlineStr">
-        <is>
-          <t>NT$ 1895.0</t>
-        </is>
-      </c>
-      <c r="E10" s="24" t="inlineStr">
-        <is>
-          <t>NT$ 1830.0</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>NT$ 1875.0</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
@@ -2014,22 +2014,22 @@
       </c>
       <c r="C11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2105.0</t>
+          <t>NT$ 2100.0</t>
         </is>
       </c>
       <c r="D11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2180.0</t>
+          <t>NT$ 2155.0</t>
         </is>
       </c>
       <c r="E11" s="28" t="inlineStr">
         <is>
+          <t>NT$ 2075.0</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
           <t>NT$ 2080.0</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t>NT$ 2140.0</t>
         </is>
       </c>
       <c r="G11" s="29" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 599.0</t>
+          <t>NT$ 601.0</t>
         </is>
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 620.0</t>
+          <t>NT$ 608.0</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 596.0</t>
+          <t>NT$ 592.0</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 612.0</t>
+          <t>NT$ 592.0</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
@@ -2108,22 +2108,22 @@
       </c>
       <c r="C13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4475.0</t>
+          <t>NT$ 4505.0</t>
         </is>
       </c>
       <c r="D13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4650.0</t>
+          <t>NT$ 4575.0</t>
         </is>
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4435.0</t>
+          <t>NT$ 4430.0</t>
         </is>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 4560.0</t>
+          <t>NT$ 4430.0</t>
         </is>
       </c>
       <c r="G13" s="29" t="inlineStr">

--- a/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
+++ b/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
@@ -631,7 +631,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>定盘时间: 2026-09-15 19:57:51 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
+          <t>定盘时间: 2026-09-16 19:53:41 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
         </is>
       </c>
     </row>
@@ -730,10 +730,10 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>开盘: 2405.0
-最高: 2405.0
-最低: 2380.0
-收盘: 2385.0</t>
+          <t>开盘: 2375.0
+最高: 2395.0
+最低: 2375.0
+收盘: 2380.0</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2385.0</t>
+          <t>NT$ 2380.0</t>
         </is>
       </c>
       <c r="K4" s="9" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>13,479 张</t>
+          <t>17,955 张</t>
         </is>
       </c>
     </row>
@@ -817,10 +817,10 @@
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>开盘: 11920.0
-最高: 12075.0
-最低: 11665.0
-收盘: 11715.0</t>
+          <t>开盘: 12040.0
+最高: 12445.0
+最低: 11800.0
+收盘: 12045.0</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 11715.0</t>
+          <t>NT$ 12045.0</t>
         </is>
       </c>
       <c r="K5" s="18" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="O5" s="16" t="inlineStr">
         <is>
-          <t>183 张</t>
+          <t>418 张</t>
         </is>
       </c>
     </row>
@@ -904,10 +904,10 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>开盘: 5300.0
-最高: 5365.0
-最低: 5110.0
-收盘: 5115.0</t>
+          <t>开盘: 5060.0
+最高: 5175.0
+最低: 5030.0
+收盘: 5085.0</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 5115.0</t>
+          <t>NT$ 5085.0</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>1,318 张</t>
+          <t>1,522 张</t>
         </is>
       </c>
     </row>
@@ -991,10 +991,10 @@
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>开盘: 3265.0
-最高: 3300.0
+          <t>开盘: 3115.0
+最高: 3225.0
 最低: 3100.0
-收盘: 3115.0</t>
+收盘: 3175.0</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="J7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3115.0</t>
+          <t>NT$ 3175.0</t>
         </is>
       </c>
       <c r="K7" s="18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="O7" s="16" t="inlineStr">
         <is>
-          <t>2,964 张</t>
+          <t>2,629 张</t>
         </is>
       </c>
     </row>
@@ -1079,9 +1079,9 @@
       <c r="D8" s="7" t="inlineStr">
         <is>
           <t>开盘: 247.5
-最高: 250.0
-最低: 246.5
-收盘: 246.5</t>
+最高: 248.5
+最低: 246.0
+收盘: 248.0</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>NT$ 246.5</t>
+          <t>NT$ 248.0</t>
         </is>
       </c>
       <c r="K8" s="9" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="O8" s="7" t="inlineStr">
         <is>
-          <t>15,338 张</t>
+          <t>19,274 张</t>
         </is>
       </c>
     </row>
@@ -1165,10 +1165,10 @@
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>开盘: 1590.0
-最高: 1715.0
-最低: 1585.0
-收盘: 1670.0</t>
+          <t>开盘: 1680.0
+最高: 1730.0
+最低: 1655.0
+收盘: 1710.0</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="J9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1670.0</t>
+          <t>NT$ 1710.0</t>
         </is>
       </c>
       <c r="K9" s="18" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="O9" s="16" t="inlineStr">
         <is>
-          <t>14,027 张</t>
+          <t>10,019 张</t>
         </is>
       </c>
     </row>
@@ -1252,8 +1252,8 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>开盘: 1870.0
-最高: 1895.0
+          <t>开盘: 1840.0
+最高: 1860.0
 最低: 1830.0
 收盘: 1840.0</t>
         </is>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>2,068 张</t>
+          <t>2,310 张</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>开盘: 2100.0
-最高: 2155.0
-最低: 2075.0
-收盘: 2080.0</t>
+          <t>开盘: 2090.0
+最高: 2130.0
+最低: 2070.0
+收盘: 2090.0</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="J11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2080.0</t>
+          <t>NT$ 2090.0</t>
         </is>
       </c>
       <c r="K11" s="18" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="O11" s="16" t="inlineStr">
         <is>
-          <t>946 张</t>
+          <t>1,073 张</t>
         </is>
       </c>
     </row>
@@ -1426,10 +1426,10 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>开盘: 601.0
-最高: 608.0
-最低: 592.0
-收盘: 592.0</t>
+          <t>开盘: 599.0
+最高: 610.0
+最低: 597.0
+收盘: 605.0</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 592.0</t>
+          <t>NT$ 605.0</t>
         </is>
       </c>
       <c r="K12" s="9" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>12,532 张</t>
+          <t>8,978 张</t>
         </is>
       </c>
     </row>
@@ -1513,10 +1513,10 @@
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>开盘: 4505.0
-最高: 4575.0
-最低: 4430.0
-收盘: 4430.0</t>
+          <t>开盘: 4435.0
+最高: 4625.0
+最低: 4435.0
+收盘: 4530.0</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="J13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 4430.0</t>
+          <t>NT$ 4530.0</t>
         </is>
       </c>
       <c r="K13" s="18" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="O13" s="16" t="inlineStr">
         <is>
-          <t>5,688 张</t>
+          <t>5,889 张</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-09-15 19:57:51 | 策略: 3-3-4 分批建仓</t>
+          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-09-16 19:53:41 | 策略: 3-3-4 分批建仓</t>
         </is>
       </c>
     </row>
@@ -1685,22 +1685,22 @@
       </c>
       <c r="C4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2405.0</t>
+          <t>NT$ 2375.0</t>
         </is>
       </c>
       <c r="D4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2405.0</t>
+          <t>NT$ 2395.0</t>
         </is>
       </c>
       <c r="E4" s="24" t="inlineStr">
         <is>
+          <t>NT$ 2375.0</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
           <t>NT$ 2380.0</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>NT$ 2385.0</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
@@ -1732,22 +1732,22 @@
       </c>
       <c r="C5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 11920.0</t>
+          <t>NT$ 12040.0</t>
         </is>
       </c>
       <c r="D5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 12075.0</t>
+          <t>NT$ 12445.0</t>
         </is>
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 11665.0</t>
+          <t>NT$ 11800.0</t>
         </is>
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 11715.0</t>
+          <t>NT$ 12045.0</t>
         </is>
       </c>
       <c r="G5" s="29" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="C6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5300.0</t>
+          <t>NT$ 5060.0</t>
         </is>
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5365.0</t>
+          <t>NT$ 5175.0</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5110.0</t>
+          <t>NT$ 5030.0</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 5115.0</t>
+          <t>NT$ 5085.0</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="C7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3265.0</t>
+          <t>NT$ 3115.0</t>
         </is>
       </c>
       <c r="D7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3300.0</t>
+          <t>NT$ 3225.0</t>
         </is>
       </c>
       <c r="E7" s="28" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3115.0</t>
+          <t>NT$ 3175.0</t>
         </is>
       </c>
       <c r="G7" s="29" t="inlineStr">
@@ -1878,17 +1878,17 @@
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 250.0</t>
+          <t>NT$ 248.5</t>
         </is>
       </c>
       <c r="E8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 246.5</t>
+          <t>NT$ 246.0</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>NT$ 246.5</t>
+          <t>NT$ 248.0</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
@@ -1920,22 +1920,22 @@
       </c>
       <c r="C9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1590.0</t>
+          <t>NT$ 1680.0</t>
         </is>
       </c>
       <c r="D9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1715.0</t>
+          <t>NT$ 1730.0</t>
         </is>
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1585.0</t>
+          <t>NT$ 1655.0</t>
         </is>
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1670.0</t>
+          <t>NT$ 1710.0</t>
         </is>
       </c>
       <c r="G9" s="29" t="inlineStr">
@@ -1967,12 +1967,12 @@
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1870.0</t>
+          <t>NT$ 1840.0</t>
         </is>
       </c>
       <c r="D10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1895.0</t>
+          <t>NT$ 1860.0</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
@@ -2014,22 +2014,22 @@
       </c>
       <c r="C11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2100.0</t>
+          <t>NT$ 2090.0</t>
         </is>
       </c>
       <c r="D11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2155.0</t>
+          <t>NT$ 2130.0</t>
         </is>
       </c>
       <c r="E11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2075.0</t>
+          <t>NT$ 2070.0</t>
         </is>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2080.0</t>
+          <t>NT$ 2090.0</t>
         </is>
       </c>
       <c r="G11" s="29" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 601.0</t>
+          <t>NT$ 599.0</t>
         </is>
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 608.0</t>
+          <t>NT$ 610.0</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 592.0</t>
+          <t>NT$ 597.0</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 592.0</t>
+          <t>NT$ 605.0</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
@@ -2108,22 +2108,22 @@
       </c>
       <c r="C13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4505.0</t>
+          <t>NT$ 4435.0</t>
         </is>
       </c>
       <c r="D13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4575.0</t>
+          <t>NT$ 4625.0</t>
         </is>
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4430.0</t>
+          <t>NT$ 4435.0</t>
         </is>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 4430.0</t>
+          <t>NT$ 4530.0</t>
         </is>
       </c>
       <c r="G13" s="29" t="inlineStr">

--- a/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
+++ b/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="核心卡位龙头全景深度分析" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="买卖决策速查面板" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="核心卡位龙头全景深度分析" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="买卖决策速查面板" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -631,7 +631,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>定盘时间: 2026-09-16 19:53:41 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
+          <t>定盘时间: 2026-09-16 20:18:39 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-09-16 19:53:41 | 策略: 3-3-4 分批建仓</t>
+          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-09-16 20:18:39 | 策略: 3-3-4 分批建仓</t>
         </is>
       </c>
     </row>

--- a/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
+++ b/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
@@ -631,7 +631,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>定盘时间: 2026-09-16 20:18:39 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
+          <t>定盘时间: 2026-09-16 20:27:43 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
         </is>
       </c>
     </row>
@@ -751,15 +751,15 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>外资: -8252 张
-投信: -181 张
-[2026-09-11 官方结算] 三大法人同步卖超 (-8,833 张)，短线筹码面临清洗。</t>
+          <t>外资: -8745 张
+投信: +166 张
+[2026-09-16 官方结算] 投信内资买超 (+166 张) 逢低承接，外资高档调节 (-8,745 张)。</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 8,833 张 (占量 48.8%)
-[2026-09-11 筹码] 主力机构呈净卖出 (-8,833 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 7,816 张 (占量 43.5%)
+[2026-09-16 筹码] 主力机构呈净卖出 (-7,816 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
@@ -838,15 +838,15 @@
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>外资: +60 张
-投信: -36 张
-[2026-09-11 官方结算] 外资主力大幅回流 (+60 张)，投信阶段获利减仓 (-36 张)。</t>
+          <t>外资: -64 张
+投信: +59 张
+[2026-09-16 官方结算] 投信内资买超 (+59 张) 逢低承接，外资高档调节 (-64 张)。</t>
         </is>
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 16 张 (占量 4.6%)
-[2026-09-11 筹码] 主力机构呈净买入 (+16 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 30 张 (占量 7.2%)
+[2026-09-16 筹码] 主力机构呈净卖出 (-30 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -925,15 +925,15 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>外资: -23 张
-投信: +110 张
-[2026-09-11 官方结算] 投信内资买超 (+110 张) 逢低承接，外资高档调节 (-23 张)。</t>
+          <t>外资: +67 张
+投信: -147 张
+[2026-09-16 官方结算] 外资主力大幅回流 (+67 张)，投信阶段获利减仓 (-147 张)。</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 69 张 (占量 6.7%)
-[2026-09-11 筹码] 主力机构呈净买入 (+69 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 154 张 (占量 10.1%)
+[2026-09-16 筹码] 主力机构呈净卖出 (-154 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
@@ -1012,15 +1012,15 @@
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>外资: -99 张
-投信: +45 张
-[2026-09-11 官方结算] 投信内资买超 (+45 张) 逢低承接，外资高档调节 (-99 张)。</t>
+          <t>外资: -201 张
+投信: +80 张
+[2026-09-16 官方结算] 投信内资买超 (+80 张) 逢低承接，外资高档调节 (-201 张)。</t>
         </is>
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 94 张 (占量 4.7%)
-[2026-09-11 筹码] 主力机构呈净卖出 (-94 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 91 张 (占量 3.5%)
+[2026-09-16 筹码] 主力机构呈净卖出 (-91 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I7" s="15" t="inlineStr">
@@ -1099,15 +1099,15 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>外资: -3751 张
-投信: +410 张
-[2026-09-11 官方结算] 投信内资买超 (+410 张) 逢低承接，外资高档调节 (-3,751 张)。</t>
+          <t>外资: -1689 张
+投信: +1281 张
+[2026-09-16 官方结算] 投信内资买超 (+1,281 张) 逢低承接，外资高档调节 (-1,689 张)。</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 3,386 张 (占量 14.4%)
-[2026-09-11 筹码] 主力机构呈净卖出 (-3,386 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 2,590 张 (占量 13.4%)
+[2026-09-16 筹码] 主力机构呈净卖出 (-2,590 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -1186,15 +1186,15 @@
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
-          <t>外资: -3573 张
-投信: -536 张
-[2026-09-11 官方结算] 外资与投信偏空调节 (-3,805 张)，机构筹码阶段获利了结。</t>
+          <t>外资: -845 张
+投信: +551 张
+[2026-09-16 官方结算] 投信内资买超 (+551 张) 逢低承接，外资高档调节 (-845 张)。</t>
         </is>
       </c>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 3,805 张 (占量 27.6%)
-[2026-09-11 筹码] 主力机构呈净卖出 (-3,805 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 567 张 (占量 5.7%)
+[2026-09-16 筹码] 主力机构呈净卖出 (-567 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I9" s="15" t="inlineStr">
@@ -1273,15 +1273,15 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>外资: +572 张
-投信: -652 张
-[2026-09-11 官方结算] 外资主力大幅回流 (+572 张)，投信阶段获利减仓 (-652 张)。</t>
+          <t>外资: -259 张
+投信: -129 张
+[2026-09-16 官方结算] 三大法人同步卖超 (-500 张)，短线筹码面临清洗。</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 87 张 (占量 2.6%)
-[2026-09-11 筹码] 主力机构呈净卖出 (-87 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 500 张 (占量 21.6%)
+[2026-09-16 筹码] 主力机构呈净卖出 (-500 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1360,15 +1360,15 @@
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>外资: +143 张
-投信: +92 张
-[2026-09-11 官方结算] 外资与投信联手买超 (+225 张)，内外部机构共振做多。</t>
+          <t>外资: -104 张
+投信: +25 张
+[2026-09-16 官方结算] 投信内资买超 (+25 张) 逢低承接，外资高档调节 (-104 张)。</t>
         </is>
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 225 张 (占量 10.2%)
-[2026-09-11 筹码] 主力机构呈净买入 (+225 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 76 张 (占量 7.1%)
+[2026-09-16 筹码] 主力机构呈净卖出 (-76 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I11" s="15" t="inlineStr">
@@ -1447,15 +1447,15 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>外资: -8053 张
-投信: +679 张
-[2026-09-11 官方结算] 投信内资买超 (+679 张) 逢低承接，外资高档调节 (-8,053 张)。</t>
+          <t>外资: +2606 张
+投信: -1038 张
+[2026-09-16 官方结算] 外资主力大幅回流 (+2,606 张)，投信阶段获利减仓 (-1,038 张)。</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 7,819 张 (占量 36.3%)
-[2026-09-11 筹码] 主力机构呈净卖出 (-7,819 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 1,663 张 (占量 18.5%)
+[2026-09-16 筹码] 主力机构呈净买入 (+1,663 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -1534,15 +1534,15 @@
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>外资: -743 张
-投信: +108 张
-[2026-09-11 官方结算] 投信内资买超 (+108 张) 逢低承接，外资高档调节 (-743 张)。</t>
+          <t>外资: +997 张
+投信: -484 张
+[2026-09-16 官方结算] 外资主力大幅回流 (+997 张)，投信阶段获利减仓 (-484 张)。</t>
         </is>
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 656 张 (占量 9.6%)
-[2026-09-11 筹码] 主力机构呈净卖出 (-656 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 729 张 (占量 12.4%)
+[2026-09-16 筹码] 主力机构呈净买入 (+729 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I13" s="15" t="inlineStr">
@@ -1621,7 +1621,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-09-16 20:18:39 | 策略: 3-3-4 分批建仓</t>
+          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-09-16 20:27:43 | 策略: 3-3-4 分批建仓</t>
         </is>
       </c>
     </row>

--- a/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
+++ b/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="核心卡位龙头全景深度分析" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="买卖决策速查面板" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="核心卡位龙头全景深度分析" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="买卖决策速查面板" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -631,7 +631,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>定盘时间: 2026-09-16 20:27:43 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
+          <t>定盘时间: 2026-09-17 19:56:37 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
         </is>
       </c>
     </row>
@@ -730,10 +730,10 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>开盘: 2375.0
-最高: 2395.0
-最低: 2375.0
-收盘: 2380.0</t>
+          <t>开盘: 2405.0
+最高: 2445.0
+最低: 2400.0
+收盘: 2425.0</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -751,15 +751,15 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>外资: -8745 张
-投信: +166 张
-[2026-09-16 官方结算] 投信内资买超 (+166 张) 逢低承接，外资高档调节 (-8,745 张)。</t>
+          <t>外资: +4794 张
+投信: -60 张
+[2026-09-17 官方结算] 外资主力大幅回流 (+4,794 张)，投信阶段获利减仓 (-60 张)。</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 7,816 张 (占量 43.5%)
-[2026-09-16 筹码] 主力机构呈净卖出 (-7,816 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 5,243 张 (占量 32.8%)
+[2026-09-17 筹码] 主力机构呈净买入 (+5,243 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2380.0</t>
+          <t>NT$ 2425.0</t>
         </is>
       </c>
       <c r="K4" s="9" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>17,955 张</t>
+          <t>15,976 张</t>
         </is>
       </c>
     </row>
@@ -817,10 +817,10 @@
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>开盘: 12040.0
-最高: 12445.0
-最低: 11800.0
-收盘: 12045.0</t>
+          <t>开盘: 12400.0
+最高: 12730.0
+最低: 12215.0
+收盘: 12295.0</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -838,15 +838,15 @@
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>外资: -64 张
-投信: +59 张
-[2026-09-16 官方结算] 投信内资买超 (+59 张) 逢低承接，外资高档调节 (-64 张)。</t>
+          <t>外资: -125 张
+投信: +68 张
+[2026-09-17 官方结算] 投信内资买超 (+68 张) 逢低承接，外资高档调节 (-125 张)。</t>
         </is>
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 30 张 (占量 7.2%)
-[2026-09-16 筹码] 主力机构呈净卖出 (-30 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 50 张 (占量 11.8%)
+[2026-09-17 筹码] 主力机构呈净卖出 (-50 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 12045.0</t>
+          <t>NT$ 12295.0</t>
         </is>
       </c>
       <c r="K5" s="18" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="O5" s="16" t="inlineStr">
         <is>
-          <t>418 张</t>
+          <t>423 张</t>
         </is>
       </c>
     </row>
@@ -904,10 +904,10 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>开盘: 5060.0
-最高: 5175.0
-最低: 5030.0
-收盘: 5085.0</t>
+          <t>开盘: 5135.0
+最高: 5255.0
+最低: 4635.0
+收盘: 4695.0</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -925,15 +925,15 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>外资: +67 张
-投信: -147 张
-[2026-09-16 官方结算] 外资主力大幅回流 (+67 张)，投信阶段获利减仓 (-147 张)。</t>
+          <t>外资: +275 张
+投信: -743 张
+[2026-09-17 官方结算] 外资主力大幅回流 (+275 张)，投信阶段获利减仓 (-743 张)。</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 154 张 (占量 10.1%)
-[2026-09-16 筹码] 主力机构呈净卖出 (-154 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 174 张 (占量 3.5%)
+[2026-09-17 筹码] 主力机构呈净卖出 (-174 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 5085.0</t>
+          <t>NT$ 4695.0</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>1,522 张</t>
+          <t>5,030 张</t>
         </is>
       </c>
     </row>
@@ -991,10 +991,10 @@
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>开盘: 3115.0
-最高: 3225.0
-最低: 3100.0
-收盘: 3175.0</t>
+          <t>开盘: 3285.0
+最高: 3350.0
+最低: 3175.0
+收盘: 3185.0</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -1012,15 +1012,15 @@
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>外资: -201 张
-投信: +80 张
-[2026-09-16 官方结算] 投信内资买超 (+80 张) 逢低承接，外资高档调节 (-201 张)。</t>
+          <t>外资: -155 张
+投信: +11 张
+[2026-09-17 官方结算] 投信内资买超 (+11 张) 逢低承接，外资高档调节 (-155 张)。</t>
         </is>
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 91 张 (占量 3.5%)
-[2026-09-16 筹码] 主力机构呈净卖出 (-91 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 88 张 (占量 3.1%)
+[2026-09-17 筹码] 主力机构呈净卖出 (-88 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I7" s="15" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="J7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3175.0</t>
+          <t>NT$ 3185.0</t>
         </is>
       </c>
       <c r="K7" s="18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="O7" s="16" t="inlineStr">
         <is>
-          <t>2,629 张</t>
+          <t>2,864 张</t>
         </is>
       </c>
     </row>
@@ -1078,10 +1078,10 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>开盘: 247.5
-最高: 248.5
-最低: 246.0
-收盘: 248.0</t>
+          <t>开盘: 249.5
+最高: 253.5
+最低: 249.5
+收盘: 250.5</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -1099,15 +1099,15 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>外资: -1689 张
-投信: +1281 张
-[2026-09-16 官方结算] 投信内资买超 (+1,281 张) 逢低承接，外资高档调节 (-1,689 张)。</t>
+          <t>外资: +8880 张
+投信: +109 张
+[2026-09-17 官方结算] 三大法人全线买超 (+9,815 张)，外资与投信合力加仓。</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 2,590 张 (占量 13.4%)
-[2026-09-16 筹码] 主力机构呈净卖出 (-2,590 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 9,815 张 (占量 38.0%)
+[2026-09-17 筹码] 主力机构呈净买入 (+9,815 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>NT$ 248.0</t>
+          <t>NT$ 250.5</t>
         </is>
       </c>
       <c r="K8" s="9" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="O8" s="7" t="inlineStr">
         <is>
-          <t>19,274 张</t>
+          <t>25,806 张</t>
         </is>
       </c>
     </row>
@@ -1165,10 +1165,10 @@
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>开盘: 1680.0
-最高: 1730.0
-最低: 1655.0
-收盘: 1710.0</t>
+          <t>开盘: 1730.0
+最高: 1745.0
+最低: 1685.0
+收盘: 1685.0</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -1186,15 +1186,15 @@
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
-          <t>外资: -845 张
-投信: +551 张
-[2026-09-16 官方结算] 投信内资买超 (+551 张) 逢低承接，外资高档调节 (-845 张)。</t>
+          <t>外资: -663 张
+投信: +253 张
+[2026-09-17 官方结算] 投信内资买超 (+253 张) 逢低承接，外资高档调节 (-663 张)。</t>
         </is>
       </c>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 567 张 (占量 5.7%)
-[2026-09-16 筹码] 主力机构呈净卖出 (-567 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 156 张 (占量 1.5%)
+[2026-09-17 筹码] 主力机构呈净卖出 (-156 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I9" s="15" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="J9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1710.0</t>
+          <t>NT$ 1685.0</t>
         </is>
       </c>
       <c r="K9" s="18" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="O9" s="16" t="inlineStr">
         <is>
-          <t>10,019 张</t>
+          <t>10,146 张</t>
         </is>
       </c>
     </row>
@@ -1252,10 +1252,10 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>开盘: 1840.0
-最高: 1860.0
-最低: 1830.0
-收盘: 1840.0</t>
+          <t>开盘: 1865.0
+最高: 1885.0
+最低: 1790.0
+收盘: 1800.0</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -1273,15 +1273,15 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>外资: -259 张
-投信: -129 张
-[2026-09-16 官方结算] 三大法人同步卖超 (-500 张)，短线筹码面临清洗。</t>
+          <t>外资: +480 张
+投信: -1210 张
+[2026-09-17 官方结算] 外资主力大幅回流 (+480 张)，投信阶段获利减仓 (-1,210 张)。</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 500 张 (占量 21.6%)
-[2026-09-16 筹码] 主力机构呈净卖出 (-500 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 695 张 (占量 16.9%)
+[2026-09-17 筹码] 主力机构呈净卖出 (-695 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 1840.0</t>
+          <t>NT$ 1800.0</t>
         </is>
       </c>
       <c r="K10" s="9" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>2,310 张</t>
+          <t>4,121 张</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>开盘: 2090.0
-最高: 2130.0
-最低: 2070.0
-收盘: 2090.0</t>
+          <t>开盘: 2115.0
+最高: 2160.0
+最低: 2085.0
+收盘: 2085.0</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
@@ -1360,15 +1360,15 @@
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>外资: -104 张
-投信: +25 张
-[2026-09-16 官方结算] 投信内资买超 (+25 张) 逢低承接，外资高档调节 (-104 张)。</t>
+          <t>外资: +70 张
+投信: -28 张
+[2026-09-17 官方结算] 外资主力大幅回流 (+70 张)，投信阶段获利减仓 (-28 张)。</t>
         </is>
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 76 张 (占量 7.1%)
-[2026-09-16 筹码] 主力机构呈净卖出 (-76 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 74 张 (占量 6.2%)
+[2026-09-17 筹码] 主力机构呈净买入 (+74 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I11" s="15" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="J11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2090.0</t>
+          <t>NT$ 2085.0</t>
         </is>
       </c>
       <c r="K11" s="18" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="O11" s="16" t="inlineStr">
         <is>
-          <t>1,073 张</t>
+          <t>1,190 张</t>
         </is>
       </c>
     </row>
@@ -1426,10 +1426,10 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>开盘: 599.0
-最高: 610.0
-最低: 597.0
-收盘: 605.0</t>
+          <t>开盘: 615.0
+最高: 628.0
+最低: 612.0
+收盘: 614.0</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -1447,15 +1447,15 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>外资: +2606 张
-投信: -1038 张
-[2026-09-16 官方结算] 外资主力大幅回流 (+2,606 张)，投信阶段获利减仓 (-1,038 张)。</t>
+          <t>外资: +2463 张
+投信: +375 张
+[2026-09-17 官方结算] 三大法人全线买超 (+3,055 张)，外资与投信合力加仓。</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 1,663 张 (占量 18.5%)
-[2026-09-16 筹码] 主力机构呈净买入 (+1,663 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 3,055 张 (占量 29.4%)
+[2026-09-17 筹码] 主力机构呈净买入 (+3,055 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 605.0</t>
+          <t>NT$ 614.0</t>
         </is>
       </c>
       <c r="K12" s="9" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>8,978 张</t>
+          <t>10,388 张</t>
         </is>
       </c>
     </row>
@@ -1513,10 +1513,10 @@
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>开盘: 4435.0
-最高: 4625.0
-最低: 4435.0
-收盘: 4530.0</t>
+          <t>开盘: 4565.0
+最高: 4700.0
+最低: 4500.0
+收盘: 4500.0</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
@@ -1534,15 +1534,15 @@
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>外资: +997 张
-投信: -484 张
-[2026-09-16 官方结算] 外资主力大幅回流 (+997 张)，投信阶段获利减仓 (-484 张)。</t>
+          <t>外资: +300 张
+投信: +37 张
+[2026-09-17 官方结算] 三大法人全线买超 (+419 张)，外资与投信合力加仓。</t>
         </is>
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 729 张 (占量 12.4%)
-[2026-09-16 筹码] 主力机构呈净买入 (+729 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 419 张 (占量 7.1%)
+[2026-09-17 筹码] 主力机构呈净买入 (+419 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I13" s="15" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="J13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 4530.0</t>
+          <t>NT$ 4500.0</t>
         </is>
       </c>
       <c r="K13" s="18" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="O13" s="16" t="inlineStr">
         <is>
-          <t>5,889 张</t>
+          <t>5,942 张</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-09-16 20:27:43 | 策略: 3-3-4 分批建仓</t>
+          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-09-17 19:56:37 | 策略: 3-3-4 分批建仓</t>
         </is>
       </c>
     </row>
@@ -1685,22 +1685,22 @@
       </c>
       <c r="C4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2375.0</t>
+          <t>NT$ 2405.0</t>
         </is>
       </c>
       <c r="D4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2395.0</t>
+          <t>NT$ 2445.0</t>
         </is>
       </c>
       <c r="E4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2375.0</t>
+          <t>NT$ 2400.0</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2380.0</t>
+          <t>NT$ 2425.0</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
@@ -1732,22 +1732,22 @@
       </c>
       <c r="C5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 12040.0</t>
+          <t>NT$ 12400.0</t>
         </is>
       </c>
       <c r="D5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 12445.0</t>
+          <t>NT$ 12730.0</t>
         </is>
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 11800.0</t>
+          <t>NT$ 12215.0</t>
         </is>
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 12045.0</t>
+          <t>NT$ 12295.0</t>
         </is>
       </c>
       <c r="G5" s="29" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="C6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5060.0</t>
+          <t>NT$ 5135.0</t>
         </is>
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5175.0</t>
+          <t>NT$ 5255.0</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5030.0</t>
+          <t>NT$ 4635.0</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 5085.0</t>
+          <t>NT$ 4695.0</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3115.0</t>
+          <t>NT$ 3285.0</t>
         </is>
       </c>
       <c r="D7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3225.0</t>
+          <t>NT$ 3350.0</t>
         </is>
       </c>
       <c r="E7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3100.0</t>
+          <t>NT$ 3175.0</t>
         </is>
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3175.0</t>
+          <t>NT$ 3185.0</t>
         </is>
       </c>
       <c r="G7" s="29" t="inlineStr">
@@ -1873,22 +1873,22 @@
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 247.5</t>
+          <t>NT$ 249.5</t>
         </is>
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 248.5</t>
+          <t>NT$ 253.5</t>
         </is>
       </c>
       <c r="E8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 246.0</t>
+          <t>NT$ 249.5</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>NT$ 248.0</t>
+          <t>NT$ 250.5</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
@@ -1920,22 +1920,22 @@
       </c>
       <c r="C9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1680.0</t>
+          <t>NT$ 1730.0</t>
         </is>
       </c>
       <c r="D9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1730.0</t>
+          <t>NT$ 1745.0</t>
         </is>
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1655.0</t>
+          <t>NT$ 1685.0</t>
         </is>
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1710.0</t>
+          <t>NT$ 1685.0</t>
         </is>
       </c>
       <c r="G9" s="29" t="inlineStr">
@@ -1967,22 +1967,22 @@
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1840.0</t>
+          <t>NT$ 1865.0</t>
         </is>
       </c>
       <c r="D10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1860.0</t>
+          <t>NT$ 1885.0</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1830.0</t>
+          <t>NT$ 1790.0</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 1840.0</t>
+          <t>NT$ 1800.0</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
@@ -2014,22 +2014,22 @@
       </c>
       <c r="C11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2090.0</t>
+          <t>NT$ 2115.0</t>
         </is>
       </c>
       <c r="D11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2130.0</t>
+          <t>NT$ 2160.0</t>
         </is>
       </c>
       <c r="E11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2070.0</t>
+          <t>NT$ 2085.0</t>
         </is>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2090.0</t>
+          <t>NT$ 2085.0</t>
         </is>
       </c>
       <c r="G11" s="29" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 599.0</t>
+          <t>NT$ 615.0</t>
         </is>
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 610.0</t>
+          <t>NT$ 628.0</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 597.0</t>
+          <t>NT$ 612.0</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 605.0</t>
+          <t>NT$ 614.0</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
@@ -2108,22 +2108,22 @@
       </c>
       <c r="C13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4435.0</t>
+          <t>NT$ 4565.0</t>
         </is>
       </c>
       <c r="D13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4625.0</t>
+          <t>NT$ 4700.0</t>
         </is>
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4435.0</t>
+          <t>NT$ 4500.0</t>
         </is>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 4530.0</t>
+          <t>NT$ 4500.0</t>
         </is>
       </c>
       <c r="G13" s="29" t="inlineStr">

--- a/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
+++ b/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
@@ -631,7 +631,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>定盘时间: 2026-09-17 19:56:37 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
+          <t>定盘时间: 2026-09-18 19:34:55 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
         </is>
       </c>
     </row>
@@ -730,10 +730,10 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>开盘: 2405.0
-最高: 2445.0
-最低: 2400.0
-收盘: 2425.0</t>
+          <t>开盘: 2460.0
+最高: 2460.0
+最低: 2435.0
+收盘: 2460.0</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -751,15 +751,15 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>外资: +4794 张
-投信: -60 张
-[2026-09-17 官方结算] 外资主力大幅回流 (+4,794 张)，投信阶段获利减仓 (-60 张)。</t>
+          <t>外资: +6039 张
+投信: -274 张
+[2026-09-18 官方结算] 外资主力大幅回流 (+6,039 张)，投信阶段获利减仓 (-274 张)。</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 5,243 张 (占量 32.8%)
-[2026-09-17 筹码] 主力机构呈净买入 (+5,243 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 7,127 张 (占量 20.2%)
+[2026-09-18 筹码] 主力机构呈净买入 (+7,127 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2425.0</t>
+          <t>NT$ 2460.0</t>
         </is>
       </c>
       <c r="K4" s="9" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>15,976 张</t>
+          <t>35,310 张</t>
         </is>
       </c>
     </row>
@@ -817,10 +817,10 @@
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>开盘: 12400.0
+          <t>开盘: 12600.0
 最高: 12730.0
-最低: 12215.0
-收盘: 12295.0</t>
+最低: 12230.0
+收盘: 12495.0</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -838,15 +838,15 @@
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>外资: -125 张
-投信: +68 张
-[2026-09-17 官方结算] 投信内资买超 (+68 张) 逢低承接，外资高档调节 (-125 张)。</t>
+          <t>外资: -130 张
+投信: +2 张
+[2026-09-18 官方结算] 投信内资买超 (+2 张) 逢低承接，外资高档调节 (-130 张)。</t>
         </is>
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 50 张 (占量 11.8%)
-[2026-09-17 筹码] 主力机构呈净卖出 (-50 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 129 张 (占量 28.8%)
+[2026-09-18 筹码] 主力机构呈净卖出 (-129 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 12295.0</t>
+          <t>NT$ 12495.0</t>
         </is>
       </c>
       <c r="K5" s="18" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="O5" s="16" t="inlineStr">
         <is>
-          <t>423 张</t>
+          <t>448 张</t>
         </is>
       </c>
     </row>
@@ -904,10 +904,10 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>开盘: 5135.0
-最高: 5255.0
-最低: 4635.0
-收盘: 4695.0</t>
+          <t>开盘: 4910.0
+最高: 5000.0
+最低: 4810.0
+收盘: 4890.0</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -925,15 +925,15 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>外资: +275 张
-投信: -743 张
-[2026-09-17 官方结算] 外资主力大幅回流 (+275 张)，投信阶段获利减仓 (-743 张)。</t>
+          <t>外资: +315 张
+投信: -581 张
+[2026-09-18 官方结算] 外资主力大幅回流 (+315 张)，投信阶段获利减仓 (-581 张)。</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 174 张 (占量 3.5%)
-[2026-09-17 筹码] 主力机构呈净卖出 (-174 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 207 张 (占量 6.1%)
+[2026-09-18 筹码] 主力机构呈净卖出 (-207 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 4695.0</t>
+          <t>NT$ 4890.0</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>5,030 张</t>
+          <t>3,391 张</t>
         </is>
       </c>
     </row>
@@ -991,10 +991,10 @@
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>开盘: 3285.0
-最高: 3350.0
-最低: 3175.0
-收盘: 3185.0</t>
+          <t>开盘: 3345.0
+最高: 3450.0
+最低: 3290.0
+收盘: 3430.0</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -1012,15 +1012,15 @@
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>外资: -155 张
-投信: +11 张
-[2026-09-17 官方结算] 投信内资买超 (+11 张) 逢低承接，外资高档调节 (-155 张)。</t>
+          <t>外资: -2 张
+投信: +41 张
+[2026-09-18 官方结算] 投信内资买超 (+41 张) 逢低承接，外资高档调节 (-2 张)。</t>
         </is>
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 88 张 (占量 3.1%)
-[2026-09-17 筹码] 主力机构呈净卖出 (-88 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 205 张 (占量 5.8%)
+[2026-09-18 筹码] 主力机构呈净买入 (+205 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I7" s="15" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="J7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3185.0</t>
+          <t>NT$ 3430.0</t>
         </is>
       </c>
       <c r="K7" s="18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="O7" s="16" t="inlineStr">
         <is>
-          <t>2,864 张</t>
+          <t>3,509 张</t>
         </is>
       </c>
     </row>
@@ -1078,9 +1078,9 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>开盘: 249.5
-最高: 253.5
-最低: 249.5
+          <t>开盘: 252.5
+最高: 253.0
+最低: 249.0
 收盘: 250.5</t>
         </is>
       </c>
@@ -1099,15 +1099,15 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>外资: +8880 张
-投信: +109 张
-[2026-09-17 官方结算] 三大法人全线买超 (+9,815 张)，外资与投信合力加仓。</t>
+          <t>外资: -6698 张
+投信: -545 张
+[2026-09-18 官方结算] 外资与投信偏空调节 (-6,029 张)，机构筹码阶段获利了结。</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 9,815 张 (占量 38.0%)
-[2026-09-17 筹码] 主力机构呈净买入 (+9,815 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 6,029 张 (占量 13.7%)
+[2026-09-18 筹码] 主力机构呈净卖出 (-6,029 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="O8" s="7" t="inlineStr">
         <is>
-          <t>25,806 张</t>
+          <t>43,932 张</t>
         </is>
       </c>
     </row>
@@ -1166,9 +1166,9 @@
       <c r="D9" s="16" t="inlineStr">
         <is>
           <t>开盘: 1730.0
-最高: 1745.0
-最低: 1685.0
-收盘: 1685.0</t>
+最高: 1750.0
+最低: 1715.0
+收盘: 1735.0</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -1186,15 +1186,15 @@
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
-          <t>外资: -663 张
-投信: +253 张
-[2026-09-17 官方结算] 投信内资买超 (+253 张) 逢低承接，外资高档调节 (-663 张)。</t>
+          <t>外资: +2830 张
+投信: -21 张
+[2026-09-18 官方结算] 外资主力大幅回流 (+2,830 张)，投信阶段获利减仓 (-21 张)。</t>
         </is>
       </c>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 156 张 (占量 1.5%)
-[2026-09-17 筹码] 主力机构呈净卖出 (-156 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 3,150 张 (占量 26.1%)
+[2026-09-18 筹码] 主力机构呈净买入 (+3,150 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I9" s="15" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="J9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1685.0</t>
+          <t>NT$ 1735.0</t>
         </is>
       </c>
       <c r="K9" s="18" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="O9" s="16" t="inlineStr">
         <is>
-          <t>10,146 张</t>
+          <t>12,072 张</t>
         </is>
       </c>
     </row>
@@ -1252,10 +1252,10 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>开盘: 1865.0
-最高: 1885.0
-最低: 1790.0
-收盘: 1800.0</t>
+          <t>开盘: 1810.0
+最高: 1855.0
+最低: 1810.0
+收盘: 1855.0</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -1273,15 +1273,15 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>外资: +480 张
-投信: -1210 张
-[2026-09-17 官方结算] 外资主力大幅回流 (+480 张)，投信阶段获利减仓 (-1,210 张)。</t>
+          <t>外资: -256 张
+投信: -667 张
+[2026-09-18 官方结算] 外资与投信偏空调节 (-752 张)，机构筹码阶段获利了结。</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 695 张 (占量 16.9%)
-[2026-09-17 筹码] 主力机构呈净卖出 (-695 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 752 张 (占量 13.4%)
+[2026-09-18 筹码] 主力机构呈净卖出 (-752 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 1800.0</t>
+          <t>NT$ 1855.0</t>
         </is>
       </c>
       <c r="K10" s="9" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>4,121 张</t>
+          <t>5,621 张</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>开盘: 2115.0
-最高: 2160.0
-最低: 2085.0
-收盘: 2085.0</t>
+          <t>开盘: 2135.0
+最高: 2290.0
+最低: 2135.0
+收盘: 2290.0</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
@@ -1360,15 +1360,15 @@
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>外资: +70 张
-投信: -28 张
-[2026-09-17 官方结算] 外资主力大幅回流 (+70 张)，投信阶段获利减仓 (-28 张)。</t>
+          <t>外资: -167 张
+投信: +93 张
+[2026-09-18 官方结算] 投信内资买超 (+93 张) 逢低承接，外资高档调节 (-167 张)。</t>
         </is>
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 74 张 (占量 6.2%)
-[2026-09-17 筹码] 主力机构呈净买入 (+74 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 10 张 (占量 0.4%)
+[2026-09-18 筹码] 主力机构呈净买入 (+10 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I11" s="15" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="J11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2085.0</t>
+          <t>NT$ 2290.0</t>
         </is>
       </c>
       <c r="K11" s="18" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="O11" s="16" t="inlineStr">
         <is>
-          <t>1,190 张</t>
+          <t>2,467 张</t>
         </is>
       </c>
     </row>
@@ -1426,10 +1426,10 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>开盘: 615.0
-最高: 628.0
-最低: 612.0
-收盘: 614.0</t>
+          <t>开盘: 631.0
+最高: 643.0
+最低: 627.0
+收盘: 638.0</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -1447,15 +1447,15 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>外资: +2463 张
-投信: +375 张
-[2026-09-17 官方结算] 三大法人全线买超 (+3,055 张)，外资与投信合力加仓。</t>
+          <t>外资: +7214 张
+投信: -561 张
+[2026-09-18 官方结算] 外资主力大幅回流 (+7,214 张)，投信阶段获利减仓 (-561 张)。</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 3,055 张 (占量 29.4%)
-[2026-09-17 筹码] 主力机构呈净买入 (+3,055 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 7,650 张 (占量 30.7%)
+[2026-09-18 筹码] 主力机构呈净买入 (+7,650 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 614.0</t>
+          <t>NT$ 638.0</t>
         </is>
       </c>
       <c r="K12" s="9" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>10,388 张</t>
+          <t>24,900 张</t>
         </is>
       </c>
     </row>
@@ -1513,10 +1513,10 @@
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>开盘: 4565.0
-最高: 4700.0
-最低: 4500.0
-收盘: 4500.0</t>
+          <t>开盘: 4600.0
+最高: 4735.0
+最低: 4545.0
+收盘: 4710.0</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
@@ -1534,15 +1534,15 @@
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>外资: +300 张
-投信: +37 张
-[2026-09-17 官方结算] 三大法人全线买超 (+419 张)，外资与投信合力加仓。</t>
+          <t>外资: +2886 张
+投信: -120 张
+[2026-09-18 官方结算] 外资主力大幅回流 (+2,886 张)，投信阶段获利减仓 (-120 张)。</t>
         </is>
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 419 张 (占量 7.1%)
-[2026-09-17 筹码] 主力机构呈净买入 (+419 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 3,057 张 (占量 34.0%)
+[2026-09-18 筹码] 主力机构呈净买入 (+3,057 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I13" s="15" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="J13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 4500.0</t>
+          <t>NT$ 4710.0</t>
         </is>
       </c>
       <c r="K13" s="18" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="O13" s="16" t="inlineStr">
         <is>
-          <t>5,942 张</t>
+          <t>9,003 张</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-09-17 19:56:37 | 策略: 3-3-4 分批建仓</t>
+          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-09-18 19:34:55 | 策略: 3-3-4 分批建仓</t>
         </is>
       </c>
     </row>
@@ -1685,22 +1685,22 @@
       </c>
       <c r="C4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2405.0</t>
+          <t>NT$ 2460.0</t>
         </is>
       </c>
       <c r="D4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2445.0</t>
+          <t>NT$ 2460.0</t>
         </is>
       </c>
       <c r="E4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2400.0</t>
+          <t>NT$ 2435.0</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2425.0</t>
+          <t>NT$ 2460.0</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="C5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 12400.0</t>
+          <t>NT$ 12600.0</t>
         </is>
       </c>
       <c r="D5" s="28" t="inlineStr">
@@ -1742,12 +1742,12 @@
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 12215.0</t>
+          <t>NT$ 12230.0</t>
         </is>
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 12295.0</t>
+          <t>NT$ 12495.0</t>
         </is>
       </c>
       <c r="G5" s="29" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="C6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5135.0</t>
+          <t>NT$ 4910.0</t>
         </is>
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5255.0</t>
+          <t>NT$ 5000.0</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 4635.0</t>
+          <t>NT$ 4810.0</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 4695.0</t>
+          <t>NT$ 4890.0</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3285.0</t>
+          <t>NT$ 3345.0</t>
         </is>
       </c>
       <c r="D7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3350.0</t>
+          <t>NT$ 3450.0</t>
         </is>
       </c>
       <c r="E7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3175.0</t>
+          <t>NT$ 3290.0</t>
         </is>
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3185.0</t>
+          <t>NT$ 3430.0</t>
         </is>
       </c>
       <c r="G7" s="29" t="inlineStr">
@@ -1873,17 +1873,17 @@
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 249.5</t>
+          <t>NT$ 252.5</t>
         </is>
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 253.5</t>
+          <t>NT$ 253.0</t>
         </is>
       </c>
       <c r="E8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 249.5</t>
+          <t>NT$ 249.0</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -1925,17 +1925,17 @@
       </c>
       <c r="D9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1745.0</t>
+          <t>NT$ 1750.0</t>
         </is>
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1685.0</t>
+          <t>NT$ 1715.0</t>
         </is>
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1685.0</t>
+          <t>NT$ 1735.0</t>
         </is>
       </c>
       <c r="G9" s="29" t="inlineStr">
@@ -1967,22 +1967,22 @@
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1865.0</t>
+          <t>NT$ 1810.0</t>
         </is>
       </c>
       <c r="D10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1885.0</t>
+          <t>NT$ 1855.0</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1790.0</t>
+          <t>NT$ 1810.0</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 1800.0</t>
+          <t>NT$ 1855.0</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
@@ -2014,22 +2014,22 @@
       </c>
       <c r="C11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2115.0</t>
+          <t>NT$ 2135.0</t>
         </is>
       </c>
       <c r="D11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2160.0</t>
+          <t>NT$ 2290.0</t>
         </is>
       </c>
       <c r="E11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2085.0</t>
+          <t>NT$ 2135.0</t>
         </is>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2085.0</t>
+          <t>NT$ 2290.0</t>
         </is>
       </c>
       <c r="G11" s="29" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 615.0</t>
+          <t>NT$ 631.0</t>
         </is>
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 628.0</t>
+          <t>NT$ 643.0</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 612.0</t>
+          <t>NT$ 627.0</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 614.0</t>
+          <t>NT$ 638.0</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
@@ -2108,22 +2108,22 @@
       </c>
       <c r="C13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4565.0</t>
+          <t>NT$ 4600.0</t>
         </is>
       </c>
       <c r="D13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4700.0</t>
+          <t>NT$ 4735.0</t>
         </is>
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4500.0</t>
+          <t>NT$ 4545.0</t>
         </is>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 4500.0</t>
+          <t>NT$ 4710.0</t>
         </is>
       </c>
       <c r="G13" s="29" t="inlineStr">

--- a/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
+++ b/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
@@ -631,7 +631,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>定盘时间: 2026-09-18 19:34:55 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
+          <t>定盘时间: 2026-09-21 21:06:55 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
         </is>
       </c>
     </row>
@@ -730,10 +730,10 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>开盘: 2460.0
-最高: 2460.0
-最低: 2435.0
-收盘: 2460.0</t>
+          <t>开盘: 2445.0
+最高: 2485.0
+最低: 2445.0
+收盘: 2480.0</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -751,15 +751,15 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>外资: +6039 张
-投信: -274 张
-[2026-09-18 官方结算] 外资主力大幅回流 (+6,039 张)，投信阶段获利减仓 (-274 张)。</t>
+          <t>外资: +2689 张
+投信: +734 张
+[2026-09-21 官方结算] 三大法人全线买超 (+4,038 张)，外资与投信合力加仓。</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 7,127 张 (占量 20.2%)
-[2026-09-18 筹码] 主力机构呈净买入 (+7,127 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 4,038 张 (占量 27.8%)
+[2026-09-21 筹码] 主力机构呈净买入 (+4,038 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2460.0</t>
+          <t>NT$ 2480.0</t>
         </is>
       </c>
       <c r="K4" s="9" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>35,310 张</t>
+          <t>14,507 张</t>
         </is>
       </c>
     </row>
@@ -817,10 +817,10 @@
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>开盘: 12600.0
-最高: 12730.0
-最低: 12230.0
-收盘: 12495.0</t>
+          <t>开盘: 13000.0
+最高: 13050.0
+最低: 12510.0
+收盘: 12800.0</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -838,15 +838,15 @@
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>外资: -130 张
-投信: +2 张
-[2026-09-18 官方结算] 投信内资买超 (+2 张) 逢低承接，外资高档调节 (-130 张)。</t>
+          <t>外资: -115 张
+投信: +14 张
+[2026-09-21 官方结算] 投信内资买超 (+14 张) 逢低承接，外资高档调节 (-115 张)。</t>
         </is>
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 129 张 (占量 28.8%)
-[2026-09-18 筹码] 主力机构呈净卖出 (-129 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 103 张 (占量 20.4%)
+[2026-09-21 筹码] 主力机构呈净卖出 (-103 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 12495.0</t>
+          <t>NT$ 12800.0</t>
         </is>
       </c>
       <c r="K5" s="18" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="O5" s="16" t="inlineStr">
         <is>
-          <t>448 张</t>
+          <t>505 张</t>
         </is>
       </c>
     </row>
@@ -904,10 +904,10 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>开盘: 4910.0
-最高: 5000.0
-最低: 4810.0
-收盘: 4890.0</t>
+          <t>开盘: 4900.0
+最高: 4945.0
+最低: 4795.0
+收盘: 4895.0</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -925,15 +925,15 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>外资: +315 张
-投信: -581 张
-[2026-09-18 官方结算] 外资主力大幅回流 (+315 张)，投信阶段获利减仓 (-581 张)。</t>
+          <t>外资: +369 张
+投信: -773 张
+[2026-09-21 官方结算] 外资主力大幅回流 (+369 张)，投信阶段获利减仓 (-773 张)。</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 207 张 (占量 6.1%)
-[2026-09-18 筹码] 主力机构呈净卖出 (-207 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 312 张 (占量 14.1%)
+[2026-09-21 筹码] 主力机构呈净卖出 (-312 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 4890.0</t>
+          <t>NT$ 4895.0</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>3,391 张</t>
+          <t>2,214 张</t>
         </is>
       </c>
     </row>
@@ -991,10 +991,10 @@
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>开盘: 3345.0
-最高: 3450.0
-最低: 3290.0
-收盘: 3430.0</t>
+          <t>开盘: 3480.0
+最高: 3495.0
+最低: 3365.0
+收盘: 3415.0</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -1012,15 +1012,15 @@
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>外资: -2 张
-投信: +41 张
-[2026-09-18 官方结算] 投信内资买超 (+41 张) 逢低承接，外资高档调节 (-2 张)。</t>
+          <t>外资: -177 张
+投信: +48 张
+[2026-09-21 官方结算] 投信内资买超 (+48 张) 逢低承接，外资高档调节 (-177 张)。</t>
         </is>
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 205 张 (占量 5.8%)
-[2026-09-18 筹码] 主力机构呈净买入 (+205 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 136 张 (占量 8.2%)
+[2026-09-21 筹码] 主力机构呈净卖出 (-136 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I7" s="15" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="J7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3430.0</t>
+          <t>NT$ 3415.0</t>
         </is>
       </c>
       <c r="K7" s="18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="O7" s="16" t="inlineStr">
         <is>
-          <t>3,509 张</t>
+          <t>1,659 张</t>
         </is>
       </c>
     </row>
@@ -1078,10 +1078,10 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>开盘: 252.5
-最高: 253.0
+          <t>开盘: 251.5
+最高: 252.0
 最低: 249.0
-收盘: 250.5</t>
+收盘: 250.0</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -1099,15 +1099,15 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>外资: -6698 张
-投信: -545 张
-[2026-09-18 官方结算] 外资与投信偏空调节 (-6,029 张)，机构筹码阶段获利了结。</t>
+          <t>外资: -5704 张
+投信: +406 张
+[2026-09-21 官方结算] 投信内资买超 (+406 张) 逢低承接，外资高档调节 (-5,704 张)。</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 6,029 张 (占量 13.7%)
-[2026-09-18 筹码] 主力机构呈净卖出 (-6,029 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 5,302 张 (占量 32.7%)
+[2026-09-21 筹码] 主力机构呈净卖出 (-5,302 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>NT$ 250.5</t>
+          <t>NT$ 250.0</t>
         </is>
       </c>
       <c r="K8" s="9" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="O8" s="7" t="inlineStr">
         <is>
-          <t>43,932 张</t>
+          <t>16,223 张</t>
         </is>
       </c>
     </row>
@@ -1165,10 +1165,10 @@
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>开盘: 1730.0
-最高: 1750.0
-最低: 1715.0
-收盘: 1735.0</t>
+          <t>开盘: 1750.0
+最高: 1885.0
+最低: 1740.0
+收盘: 1875.0</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -1186,15 +1186,15 @@
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
-          <t>外资: +2830 张
-投信: -21 张
-[2026-09-18 官方结算] 外资主力大幅回流 (+2,830 张)，投信阶段获利减仓 (-21 张)。</t>
+          <t>外资: +2274 张
+投信: +3392 张
+[2026-09-21 官方结算] 三大法人全线买超 (+6,566 张)，外资与投信合力加仓。</t>
         </is>
       </c>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 3,150 张 (占量 26.1%)
-[2026-09-18 筹码] 主力机构呈净买入 (+3,150 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 6,566 张 (占量 39.6%)
+[2026-09-21 筹码] 主力机构呈净买入 (+6,566 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I9" s="15" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="J9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1735.0</t>
+          <t>NT$ 1875.0</t>
         </is>
       </c>
       <c r="K9" s="18" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="O9" s="16" t="inlineStr">
         <is>
-          <t>12,072 张</t>
+          <t>16,598 张</t>
         </is>
       </c>
     </row>
@@ -1252,10 +1252,10 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>开盘: 1810.0
-最高: 1855.0
+          <t>开盘: 1840.0
+最高: 1880.0
 最低: 1810.0
-收盘: 1855.0</t>
+收盘: 1840.0</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -1273,15 +1273,15 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>外资: -256 张
-投信: -667 张
-[2026-09-18 官方结算] 外资与投信偏空调节 (-752 张)，机构筹码阶段获利了结。</t>
+          <t>外资: +182 张
+投信: -786 张
+[2026-09-21 官方结算] 外资主力大幅回流 (+182 张)，投信阶段获利减仓 (-786 张)。</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 752 张 (占量 13.4%)
-[2026-09-18 筹码] 主力机构呈净卖出 (-752 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 488 张 (占量 15.1%)
+[2026-09-21 筹码] 主力机构呈净卖出 (-488 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 1855.0</t>
+          <t>NT$ 1840.0</t>
         </is>
       </c>
       <c r="K10" s="9" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>5,621 张</t>
+          <t>3,241 张</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>开盘: 2135.0
-最高: 2290.0
-最低: 2135.0
-收盘: 2290.0</t>
+          <t>开盘: 2515.0
+最高: 2515.0
+最低: 2315.0
+收盘: 2375.0</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
@@ -1360,15 +1360,15 @@
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>外资: -167 张
-投信: +93 张
-[2026-09-18 官方结算] 投信内资买超 (+93 张) 逢低承接，外资高档调节 (-167 张)。</t>
+          <t>外资: +594 张
+投信: -265 张
+[2026-09-21 官方结算] 外资主力大幅回流 (+594 张)，投信阶段获利减仓 (-265 张)。</t>
         </is>
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 10 张 (占量 0.4%)
-[2026-09-18 筹码] 主力机构呈净买入 (+10 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 300 张 (占量 8.2%)
+[2026-09-21 筹码] 主力机构呈净买入 (+300 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I11" s="15" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="J11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2290.0</t>
+          <t>NT$ 2375.0</t>
         </is>
       </c>
       <c r="K11" s="18" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="O11" s="16" t="inlineStr">
         <is>
-          <t>2,467 张</t>
+          <t>3,668 张</t>
         </is>
       </c>
     </row>
@@ -1426,10 +1426,10 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>开盘: 631.0
-最高: 643.0
-最低: 627.0
-收盘: 638.0</t>
+          <t>开盘: 655.0
+最高: 674.0
+最低: 655.0
+收盘: 663.0</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -1447,15 +1447,15 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>外资: +7214 张
-投信: -561 张
-[2026-09-18 官方结算] 外资主力大幅回流 (+7,214 张)，投信阶段获利减仓 (-561 张)。</t>
+          <t>外资: +5123 张
+投信: +541 张
+[2026-09-21 官方结算] 三大法人全线买超 (+6,693 张)，外资与投信合力加仓。</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 7,650 张 (占量 30.7%)
-[2026-09-18 筹码] 主力机构呈净买入 (+7,650 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 6,693 张 (占量 42.2%)
+[2026-09-21 筹码] 主力机构呈净买入 (+6,693 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 638.0</t>
+          <t>NT$ 663.0</t>
         </is>
       </c>
       <c r="K12" s="9" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>24,900 张</t>
+          <t>15,873 张</t>
         </is>
       </c>
     </row>
@@ -1513,10 +1513,10 @@
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>开盘: 4600.0
-最高: 4735.0
-最低: 4545.0
-收盘: 4710.0</t>
+          <t>开盘: 4800.0
+最高: 5035.0
+最低: 4780.0
+收盘: 5010.0</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
@@ -1534,15 +1534,15 @@
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>外资: +2886 张
-投信: -120 张
-[2026-09-18 官方结算] 外资主力大幅回流 (+2,886 张)，投信阶段获利减仓 (-120 张)。</t>
+          <t>外资: +3156 张
+投信: +312 张
+[2026-09-21 官方结算] 三大法人全线买超 (+3,816 张)，外资与投信合力加仓。</t>
         </is>
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 3,057 张 (占量 34.0%)
-[2026-09-18 筹码] 主力机构呈净买入 (+3,057 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 3,816 张 (占量 40.1%)
+[2026-09-21 筹码] 主力机构呈净买入 (+3,816 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I13" s="15" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="J13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 4710.0</t>
+          <t>NT$ 5010.0</t>
         </is>
       </c>
       <c r="K13" s="18" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="O13" s="16" t="inlineStr">
         <is>
-          <t>9,003 张</t>
+          <t>9,518 张</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-09-18 19:34:55 | 策略: 3-3-4 分批建仓</t>
+          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-09-21 21:06:55 | 策略: 3-3-4 分批建仓</t>
         </is>
       </c>
     </row>
@@ -1685,22 +1685,22 @@
       </c>
       <c r="C4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2460.0</t>
+          <t>NT$ 2445.0</t>
         </is>
       </c>
       <c r="D4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2460.0</t>
+          <t>NT$ 2485.0</t>
         </is>
       </c>
       <c r="E4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2435.0</t>
+          <t>NT$ 2445.0</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2460.0</t>
+          <t>NT$ 2480.0</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
@@ -1732,22 +1732,22 @@
       </c>
       <c r="C5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 12600.0</t>
+          <t>NT$ 13000.0</t>
         </is>
       </c>
       <c r="D5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 12730.0</t>
+          <t>NT$ 13050.0</t>
         </is>
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 12230.0</t>
+          <t>NT$ 12510.0</t>
         </is>
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 12495.0</t>
+          <t>NT$ 12800.0</t>
         </is>
       </c>
       <c r="G5" s="29" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="C6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 4910.0</t>
+          <t>NT$ 4900.0</t>
         </is>
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5000.0</t>
+          <t>NT$ 4945.0</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 4810.0</t>
+          <t>NT$ 4795.0</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 4890.0</t>
+          <t>NT$ 4895.0</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3345.0</t>
+          <t>NT$ 3480.0</t>
         </is>
       </c>
       <c r="D7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3450.0</t>
+          <t>NT$ 3495.0</t>
         </is>
       </c>
       <c r="E7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3290.0</t>
+          <t>NT$ 3365.0</t>
         </is>
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3430.0</t>
+          <t>NT$ 3415.0</t>
         </is>
       </c>
       <c r="G7" s="29" t="inlineStr">
@@ -1873,12 +1873,12 @@
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 252.5</t>
+          <t>NT$ 251.5</t>
         </is>
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 253.0</t>
+          <t>NT$ 252.0</t>
         </is>
       </c>
       <c r="E8" s="24" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>NT$ 250.5</t>
+          <t>NT$ 250.0</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
@@ -1920,22 +1920,22 @@
       </c>
       <c r="C9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1730.0</t>
+          <t>NT$ 1750.0</t>
         </is>
       </c>
       <c r="D9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1750.0</t>
+          <t>NT$ 1885.0</t>
         </is>
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1715.0</t>
+          <t>NT$ 1740.0</t>
         </is>
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1735.0</t>
+          <t>NT$ 1875.0</t>
         </is>
       </c>
       <c r="G9" s="29" t="inlineStr">
@@ -1967,22 +1967,22 @@
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
+          <t>NT$ 1840.0</t>
+        </is>
+      </c>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t>NT$ 1880.0</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="inlineStr">
+        <is>
           <t>NT$ 1810.0</t>
         </is>
       </c>
-      <c r="D10" s="24" t="inlineStr">
-        <is>
-          <t>NT$ 1855.0</t>
-        </is>
-      </c>
-      <c r="E10" s="24" t="inlineStr">
-        <is>
-          <t>NT$ 1810.0</t>
-        </is>
-      </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 1855.0</t>
+          <t>NT$ 1840.0</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
@@ -2014,22 +2014,22 @@
       </c>
       <c r="C11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2135.0</t>
+          <t>NT$ 2515.0</t>
         </is>
       </c>
       <c r="D11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2290.0</t>
+          <t>NT$ 2515.0</t>
         </is>
       </c>
       <c r="E11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2135.0</t>
+          <t>NT$ 2315.0</t>
         </is>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2290.0</t>
+          <t>NT$ 2375.0</t>
         </is>
       </c>
       <c r="G11" s="29" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 631.0</t>
+          <t>NT$ 655.0</t>
         </is>
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 643.0</t>
+          <t>NT$ 674.0</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 627.0</t>
+          <t>NT$ 655.0</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 638.0</t>
+          <t>NT$ 663.0</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
@@ -2108,22 +2108,22 @@
       </c>
       <c r="C13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4600.0</t>
+          <t>NT$ 4800.0</t>
         </is>
       </c>
       <c r="D13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4735.0</t>
+          <t>NT$ 5035.0</t>
         </is>
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4545.0</t>
+          <t>NT$ 4780.0</t>
         </is>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 4710.0</t>
+          <t>NT$ 5010.0</t>
         </is>
       </c>
       <c r="G13" s="29" t="inlineStr">

--- a/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
+++ b/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
@@ -631,7 +631,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>定盘时间: 2026-09-21 21:06:55 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
+          <t>定盘时间: 2026-09-22 19:55:29 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
         </is>
       </c>
     </row>
@@ -730,10 +730,10 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>开盘: 2445.0
-最高: 2485.0
-最低: 2445.0
-收盘: 2480.0</t>
+          <t>开盘: 2505.0
+最高: 2510.0
+最低: 2460.0
+收盘: 2460.0</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -751,15 +751,15 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>外资: +2689 张
-投信: +734 张
-[2026-09-21 官方结算] 三大法人全线买超 (+4,038 张)，外资与投信合力加仓。</t>
+          <t>外资: -4330 张
+投信: -406 张
+[2026-09-22 官方结算] 外资与投信偏空调节 (-4,268 张)，机构筹码阶段获利了结。</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 4,038 张 (占量 27.8%)
-[2026-09-21 筹码] 主力机构呈净买入 (+4,038 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 4,268 张 (占量 22.6%)
+[2026-09-22 筹码] 主力机构呈净卖出 (-4,268 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2480.0</t>
+          <t>NT$ 2460.0</t>
         </is>
       </c>
       <c r="K4" s="9" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>14,507 张</t>
+          <t>18,900 张</t>
         </is>
       </c>
     </row>
@@ -817,10 +817,10 @@
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>开盘: 13000.0
-最高: 13050.0
-最低: 12510.0
-收盘: 12800.0</t>
+          <t>开盘: 12900.0
+最高: 13305.0
+最低: 12670.0
+收盘: 12670.0</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -838,15 +838,15 @@
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>外资: -115 张
-投信: +14 张
-[2026-09-21 官方结算] 投信内资买超 (+14 张) 逢低承接，外资高档调节 (-115 张)。</t>
+          <t>外资: -69 张
+投信: +23 张
+[2026-09-22 官方结算] 投信内资买超 (+23 张) 逢低承接，外资高档调节 (-69 张)。</t>
         </is>
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 103 张 (占量 20.4%)
-[2026-09-21 筹码] 主力机构呈净卖出 (-103 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 42 张 (占量 10.9%)
+[2026-09-22 筹码] 主力机构呈净卖出 (-42 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 12800.0</t>
+          <t>NT$ 12670.0</t>
         </is>
       </c>
       <c r="K5" s="18" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="O5" s="16" t="inlineStr">
         <is>
-          <t>505 张</t>
+          <t>384 张</t>
         </is>
       </c>
     </row>
@@ -904,10 +904,10 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>开盘: 4900.0
-最高: 4945.0
-最低: 4795.0
-收盘: 4895.0</t>
+          <t>开盘: 5100.0
+最高: 5100.0
+最低: 4855.0
+收盘: 4860.0</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -925,15 +925,15 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>外资: +369 张
-投信: -773 张
-[2026-09-21 官方结算] 外资主力大幅回流 (+369 张)，投信阶段获利减仓 (-773 张)。</t>
+          <t>外资: +331 张
+投信: -654 张
+[2026-09-22 官方结算] 外资主力大幅回流 (+331 张)，投信阶段获利减仓 (-654 张)。</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 312 张 (占量 14.1%)
-[2026-09-21 筹码] 主力机构呈净卖出 (-312 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 273 张 (占量 16.2%)
+[2026-09-22 筹码] 主力机构呈净卖出 (-273 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 4895.0</t>
+          <t>NT$ 4860.0</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>2,214 张</t>
+          <t>1,685 张</t>
         </is>
       </c>
     </row>
@@ -991,10 +991,10 @@
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>开盘: 3480.0
-最高: 3495.0
-最低: 3365.0
-收盘: 3415.0</t>
+          <t>开盘: 3500.0
+最高: 3505.0
+最低: 3385.0
+收盘: 3390.0</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -1012,15 +1012,15 @@
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>外资: -177 张
-投信: +48 张
-[2026-09-21 官方结算] 投信内资买超 (+48 张) 逢低承接，外资高档调节 (-177 张)。</t>
+          <t>外资: -218 张
+投信: -8 张
+[2026-09-22 官方结算] 外资与投信偏空调节 (-195 张)，机构筹码阶段获利了结。</t>
         </is>
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 136 张 (占量 8.2%)
-[2026-09-21 筹码] 主力机构呈净卖出 (-136 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 195 张 (占量 9.0%)
+[2026-09-22 筹码] 主力机构呈净卖出 (-195 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I7" s="15" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="J7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3415.0</t>
+          <t>NT$ 3390.0</t>
         </is>
       </c>
       <c r="K7" s="18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="O7" s="16" t="inlineStr">
         <is>
-          <t>1,659 张</t>
+          <t>2,168 张</t>
         </is>
       </c>
     </row>
@@ -1078,10 +1078,10 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>开盘: 251.5
-最高: 252.0
-最低: 249.0
-收盘: 250.0</t>
+          <t>开盘: 252.0
+最高: 254.0
+最低: 250.5
+收盘: 253.0</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -1099,15 +1099,15 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>外资: -5704 张
-投信: +406 张
-[2026-09-21 官方结算] 投信内资买超 (+406 张) 逢低承接，外资高档调节 (-5,704 张)。</t>
+          <t>外资: +6811 张
+投信: -19 张
+[2026-09-22 官方结算] 外资主力大幅回流 (+6,811 张)，投信阶段获利减仓 (-19 张)。</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 5,302 张 (占量 32.7%)
-[2026-09-21 筹码] 主力机构呈净卖出 (-5,302 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 7,725 张 (占量 20.5%)
+[2026-09-22 筹码] 主力机构呈净买入 (+7,725 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>NT$ 250.0</t>
+          <t>NT$ 253.0</t>
         </is>
       </c>
       <c r="K8" s="9" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="O8" s="7" t="inlineStr">
         <is>
-          <t>16,223 张</t>
+          <t>37,621 张</t>
         </is>
       </c>
     </row>
@@ -1165,10 +1165,10 @@
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>开盘: 1750.0
-最高: 1885.0
-最低: 1740.0
-收盘: 1875.0</t>
+          <t>开盘: 1965.0
+最高: 1965.0
+最低: 1900.0
+收盘: 1900.0</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -1186,15 +1186,15 @@
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
-          <t>外资: +2274 张
-投信: +3392 张
-[2026-09-21 官方结算] 三大法人全线买超 (+6,566 张)，外资与投信合力加仓。</t>
+          <t>外资: -1324 张
+投信: +1642 张
+[2026-09-22 官方结算] 投信内资买超 (+1,642 张) 逢低承接，外资高档调节 (-1,324 张)。</t>
         </is>
       </c>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 6,566 张 (占量 39.6%)
-[2026-09-21 筹码] 主力机构呈净买入 (+6,566 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 311 张 (占量 2.0%)
+[2026-09-22 筹码] 主力机构呈净买入 (+311 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I9" s="15" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="J9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1875.0</t>
+          <t>NT$ 1900.0</t>
         </is>
       </c>
       <c r="K9" s="18" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="O9" s="16" t="inlineStr">
         <is>
-          <t>16,598 张</t>
+          <t>15,381 张</t>
         </is>
       </c>
     </row>
@@ -1252,10 +1252,10 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>开盘: 1840.0
-最高: 1880.0
-最低: 1810.0
-收盘: 1840.0</t>
+          <t>开盘: 1900.0
+最高: 1935.0
+最低: 1865.0
+收盘: 1915.0</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -1273,15 +1273,15 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>外资: +182 张
-投信: -786 张
-[2026-09-21 官方结算] 外资主力大幅回流 (+182 张)，投信阶段获利减仓 (-786 张)。</t>
+          <t>外资: -150 张
+投信: -173 张
+[2026-09-22 官方结算] 外资与投信偏空调节 (-272 张)，机构筹码阶段获利了结。</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 488 张 (占量 15.1%)
-[2026-09-21 筹码] 主力机构呈净卖出 (-488 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 272 张 (占量 7.3%)
+[2026-09-22 筹码] 主力机构呈净卖出 (-272 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 1840.0</t>
+          <t>NT$ 1915.0</t>
         </is>
       </c>
       <c r="K10" s="9" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>3,241 张</t>
+          <t>3,714 张</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>开盘: 2515.0
-最高: 2515.0
-最低: 2315.0
-收盘: 2375.0</t>
+          <t>开盘: 2395.0
+最高: 2540.0
+最低: 2350.0
+收盘: 2440.0</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
@@ -1360,15 +1360,15 @@
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>外资: +594 张
-投信: -265 张
-[2026-09-21 官方结算] 外资主力大幅回流 (+594 张)，投信阶段获利减仓 (-265 张)。</t>
+          <t>外资: -14 张
+投信: -75 张
+[2026-09-22 官方结算] 外资与投信偏空调节 (-72 张)，机构筹码阶段获利了结。</t>
         </is>
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 300 张 (占量 8.2%)
-[2026-09-21 筹码] 主力机构呈净买入 (+300 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 72 张 (占量 2.6%)
+[2026-09-22 筹码] 主力机构呈净卖出 (-72 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I11" s="15" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="J11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2375.0</t>
+          <t>NT$ 2440.0</t>
         </is>
       </c>
       <c r="K11" s="18" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="O11" s="16" t="inlineStr">
         <is>
-          <t>3,668 张</t>
+          <t>2,759 张</t>
         </is>
       </c>
     </row>
@@ -1426,10 +1426,10 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>开盘: 655.0
-最高: 674.0
-最低: 655.0
-收盘: 663.0</t>
+          <t>开盘: 691.0
+最高: 711.0
+最低: 690.0
+收盘: 693.0</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -1447,15 +1447,15 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>外资: +5123 张
-投信: +541 张
-[2026-09-21 官方结算] 三大法人全线买超 (+6,693 张)，外资与投信合力加仓。</t>
+          <t>外资: +8479 张
+投信: +1163 张
+[2026-09-22 官方结算] 三大法人全线买超 (+10,751 张)，外资与投信合力加仓。</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 6,693 张 (占量 42.2%)
-[2026-09-21 筹码] 主力机构呈净买入 (+6,693 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 10,751 张 (占量 47.9%)
+[2026-09-22 筹码] 主力机构呈净买入 (+10,751 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 663.0</t>
+          <t>NT$ 693.0</t>
         </is>
       </c>
       <c r="K12" s="9" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>15,873 张</t>
+          <t>22,466 张</t>
         </is>
       </c>
     </row>
@@ -1513,10 +1513,10 @@
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>开盘: 4800.0
-最高: 5035.0
-最低: 4780.0
-收盘: 5010.0</t>
+          <t>开盘: 5280.0
+最高: 5480.0
+最低: 5150.0
+收盘: 5180.0</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
@@ -1534,15 +1534,15 @@
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>外资: +3156 张
-投信: +312 张
-[2026-09-21 官方结算] 三大法人全线买超 (+3,816 张)，外资与投信合力加仓。</t>
+          <t>外资: +1541 张
+投信: +373 张
+[2026-09-22 官方结算] 三大法人全线买超 (+1,972 张)，外资与投信合力加仓。</t>
         </is>
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 3,816 张 (占量 40.1%)
-[2026-09-21 筹码] 主力机构呈净买入 (+3,816 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 1,972 张 (占量 18.7%)
+[2026-09-22 筹码] 主力机构呈净买入 (+1,972 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I13" s="15" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="J13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 5010.0</t>
+          <t>NT$ 5180.0</t>
         </is>
       </c>
       <c r="K13" s="18" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="O13" s="16" t="inlineStr">
         <is>
-          <t>9,518 张</t>
+          <t>10,528 张</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-09-21 21:06:55 | 策略: 3-3-4 分批建仓</t>
+          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-09-22 19:55:29 | 策略: 3-3-4 分批建仓</t>
         </is>
       </c>
     </row>
@@ -1685,22 +1685,22 @@
       </c>
       <c r="C4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2445.0</t>
+          <t>NT$ 2505.0</t>
         </is>
       </c>
       <c r="D4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2485.0</t>
+          <t>NT$ 2510.0</t>
         </is>
       </c>
       <c r="E4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2445.0</t>
+          <t>NT$ 2460.0</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2480.0</t>
+          <t>NT$ 2460.0</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
@@ -1732,22 +1732,22 @@
       </c>
       <c r="C5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 13000.0</t>
+          <t>NT$ 12900.0</t>
         </is>
       </c>
       <c r="D5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 13050.0</t>
+          <t>NT$ 13305.0</t>
         </is>
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 12510.0</t>
+          <t>NT$ 12670.0</t>
         </is>
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 12800.0</t>
+          <t>NT$ 12670.0</t>
         </is>
       </c>
       <c r="G5" s="29" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="C6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 4900.0</t>
+          <t>NT$ 5100.0</t>
         </is>
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 4945.0</t>
+          <t>NT$ 5100.0</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 4795.0</t>
+          <t>NT$ 4855.0</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 4895.0</t>
+          <t>NT$ 4860.0</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3480.0</t>
+          <t>NT$ 3500.0</t>
         </is>
       </c>
       <c r="D7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3495.0</t>
+          <t>NT$ 3505.0</t>
         </is>
       </c>
       <c r="E7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3365.0</t>
+          <t>NT$ 3385.0</t>
         </is>
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3415.0</t>
+          <t>NT$ 3390.0</t>
         </is>
       </c>
       <c r="G7" s="29" t="inlineStr">
@@ -1873,22 +1873,22 @@
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 251.5</t>
+          <t>NT$ 252.0</t>
         </is>
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 252.0</t>
+          <t>NT$ 254.0</t>
         </is>
       </c>
       <c r="E8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 249.0</t>
+          <t>NT$ 250.5</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>NT$ 250.0</t>
+          <t>NT$ 253.0</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
@@ -1920,22 +1920,22 @@
       </c>
       <c r="C9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1750.0</t>
+          <t>NT$ 1965.0</t>
         </is>
       </c>
       <c r="D9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1885.0</t>
+          <t>NT$ 1965.0</t>
         </is>
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1740.0</t>
+          <t>NT$ 1900.0</t>
         </is>
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1875.0</t>
+          <t>NT$ 1900.0</t>
         </is>
       </c>
       <c r="G9" s="29" t="inlineStr">
@@ -1967,22 +1967,22 @@
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1840.0</t>
+          <t>NT$ 1900.0</t>
         </is>
       </c>
       <c r="D10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1880.0</t>
+          <t>NT$ 1935.0</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1810.0</t>
+          <t>NT$ 1865.0</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 1840.0</t>
+          <t>NT$ 1915.0</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
@@ -2014,22 +2014,22 @@
       </c>
       <c r="C11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2515.0</t>
+          <t>NT$ 2395.0</t>
         </is>
       </c>
       <c r="D11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2515.0</t>
+          <t>NT$ 2540.0</t>
         </is>
       </c>
       <c r="E11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2315.0</t>
+          <t>NT$ 2350.0</t>
         </is>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2375.0</t>
+          <t>NT$ 2440.0</t>
         </is>
       </c>
       <c r="G11" s="29" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 655.0</t>
+          <t>NT$ 691.0</t>
         </is>
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 674.0</t>
+          <t>NT$ 711.0</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 655.0</t>
+          <t>NT$ 690.0</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 663.0</t>
+          <t>NT$ 693.0</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
@@ -2108,22 +2108,22 @@
       </c>
       <c r="C13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4800.0</t>
+          <t>NT$ 5280.0</t>
         </is>
       </c>
       <c r="D13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 5035.0</t>
+          <t>NT$ 5480.0</t>
         </is>
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4780.0</t>
+          <t>NT$ 5150.0</t>
         </is>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 5010.0</t>
+          <t>NT$ 5180.0</t>
         </is>
       </c>
       <c r="G13" s="29" t="inlineStr">

--- a/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
+++ b/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="核心卡位龙头全景深度分析" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="买卖决策速查面板" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="核心卡位龙头全景深度分析" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="买卖决策速查面板" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -624,14 +624,14 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>台股 10 檔 AI 核心卡位龙头深度投资与买卖点筹码量化分析表</t>
+          <t>台股 11 檔 AI 核心卡位龙头深度投资与买卖点筹码量化分析表</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>定盘时间: 2026-09-22 19:55:29 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
+          <t>定盘时间: 2026-09-23 14:11:55 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
         </is>
       </c>
     </row>
@@ -730,10 +730,10 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>开盘: 2505.0
-最高: 2510.0
-最低: 2460.0
-收盘: 2460.0</t>
+          <t>开盘: 2475.0
+最高: 2505.0
+最低: 2475.0
+收盘: 2500.0</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 4,268 张 (占量 22.6%)
+          <t>法人净卖超 4,268 张 (占量 21.0%)
 [2026-09-22 筹码] 主力机构呈净卖出 (-4,268 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
@@ -769,7 +769,7 @@
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2460.0</t>
+          <t>NT$ 2500.0</t>
         </is>
       </c>
       <c r="K4" s="9" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>18,900 张</t>
+          <t>20,325 张</t>
         </is>
       </c>
     </row>
@@ -817,10 +817,10 @@
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>开盘: 12900.0
-最高: 13305.0
-最低: 12670.0
-收盘: 12670.0</t>
+          <t>开盘: 12670.0
+最高: 12725.0
+最低: 12320.0
+收盘: 12390.0</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 42 张 (占量 10.9%)
+          <t>法人净卖超 42 张 (占量 13.6%)
 [2026-09-22 筹码] 主力机构呈净卖出 (-42 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
@@ -856,7 +856,7 @@
       </c>
       <c r="J5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 12670.0</t>
+          <t>NT$ 12390.0</t>
         </is>
       </c>
       <c r="K5" s="18" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="O5" s="16" t="inlineStr">
         <is>
-          <t>384 张</t>
+          <t>309 张</t>
         </is>
       </c>
     </row>
@@ -904,10 +904,10 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>开盘: 5100.0
-最高: 5100.0
-最低: 4855.0
-收盘: 4860.0</t>
+          <t>开盘: 4910.0
+最高: 5110.0
+最低: 4860.0
+收盘: 5020.0</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 273 张 (占量 16.2%)
+          <t>法人净卖超 273 张 (占量 12.2%)
 [2026-09-22 筹码] 主力机构呈净卖出 (-273 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
@@ -943,7 +943,7 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 4860.0</t>
+          <t>NT$ 5020.0</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>1,685 张</t>
+          <t>2,241 张</t>
         </is>
       </c>
     </row>
@@ -991,10 +991,10 @@
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>开盘: 3500.0
-最高: 3505.0
-最低: 3385.0
-收盘: 3390.0</t>
+          <t>开盘: 3425.0
+最高: 3590.0
+最低: 3410.0
+收盘: 3470.0</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 195 张 (占量 9.0%)
+          <t>法人净卖超 195 张 (占量 7.8%)
 [2026-09-22 筹码] 主力机构呈净卖出 (-195 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="J7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3390.0</t>
+          <t>NT$ 3470.0</t>
         </is>
       </c>
       <c r="K7" s="18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="O7" s="16" t="inlineStr">
         <is>
-          <t>2,168 张</t>
+          <t>2,485 张</t>
         </is>
       </c>
     </row>
@@ -1078,10 +1078,10 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>开盘: 252.0
-最高: 254.0
-最低: 250.5
-收盘: 253.0</t>
+          <t>开盘: 255.0
+最高: 257.0
+最低: 255.0
+收盘: 256.0</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 7,725 张 (占量 20.5%)
+          <t>法人净买超 7,725 张 (占量 22.3%)
 [2026-09-22 筹码] 主力机构呈净买入 (+7,725 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>NT$ 253.0</t>
+          <t>NT$ 256.0</t>
         </is>
       </c>
       <c r="K8" s="9" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="O8" s="7" t="inlineStr">
         <is>
-          <t>37,621 张</t>
+          <t>34,627 张</t>
         </is>
       </c>
     </row>
@@ -1165,9 +1165,9 @@
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>开盘: 1965.0
-最高: 1965.0
-最低: 1900.0
+          <t>开盘: 1910.0
+最高: 1920.0
+最低: 1890.0
 收盘: 1900.0</t>
         </is>
       </c>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 311 张 (占量 2.0%)
+          <t>法人净买超 311 张 (占量 3.5%)
 [2026-09-22 筹码] 主力机构呈净买入 (+311 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="O9" s="16" t="inlineStr">
         <is>
-          <t>15,381 张</t>
+          <t>9,000 张</t>
         </is>
       </c>
     </row>
@@ -1252,10 +1252,10 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>开盘: 1900.0
-最高: 1935.0
-最低: 1865.0
-收盘: 1915.0</t>
+          <t>开盘: 1935.0
+最高: 1955.0
+最低: 1845.0
+收盘: 1890.0</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 272 张 (占量 7.3%)
+          <t>法人净卖超 272 张 (占量 7.0%)
 [2026-09-22 筹码] 主力机构呈净卖出 (-272 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 1915.0</t>
+          <t>NT$ 1890.0</t>
         </is>
       </c>
       <c r="K10" s="9" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>3,714 张</t>
+          <t>3,860 张</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>开盘: 2395.0
-最高: 2540.0
-最低: 2350.0
-收盘: 2440.0</t>
+          <t>开盘: 2445.0
+最高: 2470.0
+最低: 2305.0
+收盘: 2325.0</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 72 张 (占量 2.6%)
+          <t>法人净卖超 72 张 (占量 2.9%)
 [2026-09-22 筹码] 主力机构呈净卖出 (-72 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="J11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2440.0</t>
+          <t>NT$ 2325.0</t>
         </is>
       </c>
       <c r="K11" s="18" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="O11" s="16" t="inlineStr">
         <is>
-          <t>2,759 张</t>
+          <t>2,511 张</t>
         </is>
       </c>
     </row>
@@ -1426,9 +1426,9 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>开盘: 691.0
+          <t>开盘: 710.0
 最高: 711.0
-最低: 690.0
+最低: 689.0
 收盘: 693.0</t>
         </is>
       </c>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 10,751 张 (占量 47.9%)
+          <t>法人净买超 10,751 张 (占量 73.8%)
 [2026-09-22 筹码] 主力机构呈净买入 (+10,751 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>22,466 张</t>
+          <t>14,576 张</t>
         </is>
       </c>
     </row>
@@ -1513,10 +1513,10 @@
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>开盘: 5280.0
-最高: 5480.0
-最低: 5150.0
-收盘: 5180.0</t>
+          <t>开盘: 5220.0
+最高: 5265.0
+最低: 5140.0
+收盘: 5185.0</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 1,972 张 (占量 18.7%)
+          <t>法人净买超 1,972 张 (占量 33.4%)
 [2026-09-22 筹码] 主力机构呈净买入 (+1,972 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="J13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 5180.0</t>
+          <t>NT$ 5185.0</t>
         </is>
       </c>
       <c r="K13" s="18" t="inlineStr">
@@ -1578,7 +1578,94 @@
       </c>
       <c r="O13" s="16" t="inlineStr">
         <is>
-          <t>10,528 张</t>
+          <t>5,902 张</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="105" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>3653.TW</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>由封裝端均熱片、VC／微流道蓋板到系統端液冷冷板的垂直熱管理產品鏈</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>开盘: 6005.0
+最高: 6410.0
+最低: 5930.0
+收盘: 6410.0</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>• 毛利率：46.81% (2026Q2)
+• 净利率：32.01% (2026Q2)
+• ROE：63.1% (單季年化, 2026Q2)
+• EPS：15.80 元 (2026Q2)</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>2026Q2 已公告；下一次財報/法說日待公司公告</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>外资: -201 张
+投信: +85 张
+[2026-09-22 官方结算] 投信内资买超 (+85 张) 逢低承接，外资高档调节 (-201 张)。</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>法人净卖超 119 张 (占量 8.5%)
+[2026-09-22 筹码] 主力机构呈净卖出 (-119 张)，散户承接，筹码短期发散。</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>【Chokepoint 88分】卡位最上游铲子卖家，客户切换周期超 12-36 个月，垄断护城河极深。</t>
+        </is>
+      </c>
+      <c r="J14" s="8" t="inlineStr">
+        <is>
+          <t>NT$ 6410.0</t>
+        </is>
+      </c>
+      <c r="K14" s="9" t="inlineStr">
+        <is>
+          <t>建议买点：待估值與技術面複核
+黄金重仓：暫不設定</t>
+        </is>
+      </c>
+      <c r="L14" s="10" t="inlineStr">
+        <is>
+          <t>依獲利與估值重新評估</t>
+        </is>
+      </c>
+      <c r="M14" s="11" t="inlineStr">
+        <is>
+          <t>不預設固定目標</t>
+        </is>
+      </c>
+      <c r="N14" s="12" t="inlineStr">
+        <is>
+          <t>依獲利趨勢與個人風險承受度管理</t>
+        </is>
+      </c>
+      <c r="O14" s="7" t="inlineStr">
+        <is>
+          <t>1,394 张</t>
         </is>
       </c>
     </row>
@@ -1597,7 +1684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1614,14 +1701,14 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>台股 10 檔卡位龙头 Shioaji 实时买卖点与风控决策面板</t>
+          <t>台股 11 檔卡位龙头 Shioaji 实时买卖点与风控决策面板</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-09-22 19:55:29 | 策略: 3-3-4 分批建仓</t>
+          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-09-23 14:11:55 | 策略: 3-3-4 分批建仓</t>
         </is>
       </c>
     </row>
@@ -1685,22 +1772,22 @@
       </c>
       <c r="C4" s="24" t="inlineStr">
         <is>
+          <t>NT$ 2475.0</t>
+        </is>
+      </c>
+      <c r="D4" s="24" t="inlineStr">
+        <is>
           <t>NT$ 2505.0</t>
         </is>
       </c>
-      <c r="D4" s="24" t="inlineStr">
-        <is>
-          <t>NT$ 2510.0</t>
-        </is>
-      </c>
       <c r="E4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2460.0</t>
+          <t>NT$ 2475.0</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2460.0</t>
+          <t>NT$ 2500.0</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
@@ -1732,22 +1819,22 @@
       </c>
       <c r="C5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 12900.0</t>
+          <t>NT$ 12670.0</t>
         </is>
       </c>
       <c r="D5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 13305.0</t>
+          <t>NT$ 12725.0</t>
         </is>
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 12670.0</t>
+          <t>NT$ 12320.0</t>
         </is>
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 12670.0</t>
+          <t>NT$ 12390.0</t>
         </is>
       </c>
       <c r="G5" s="29" t="inlineStr">
@@ -1779,22 +1866,22 @@
       </c>
       <c r="C6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5100.0</t>
+          <t>NT$ 4910.0</t>
         </is>
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5100.0</t>
+          <t>NT$ 5110.0</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 4855.0</t>
+          <t>NT$ 4860.0</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 4860.0</t>
+          <t>NT$ 5020.0</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
@@ -1826,22 +1913,22 @@
       </c>
       <c r="C7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3500.0</t>
+          <t>NT$ 3425.0</t>
         </is>
       </c>
       <c r="D7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3505.0</t>
+          <t>NT$ 3590.0</t>
         </is>
       </c>
       <c r="E7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3385.0</t>
+          <t>NT$ 3410.0</t>
         </is>
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3390.0</t>
+          <t>NT$ 3470.0</t>
         </is>
       </c>
       <c r="G7" s="29" t="inlineStr">
@@ -1873,22 +1960,22 @@
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 252.0</t>
+          <t>NT$ 255.0</t>
         </is>
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 254.0</t>
+          <t>NT$ 257.0</t>
         </is>
       </c>
       <c r="E8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 250.5</t>
+          <t>NT$ 255.0</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>NT$ 253.0</t>
+          <t>NT$ 256.0</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
@@ -1920,17 +2007,17 @@
       </c>
       <c r="C9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1965.0</t>
+          <t>NT$ 1910.0</t>
         </is>
       </c>
       <c r="D9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1965.0</t>
+          <t>NT$ 1920.0</t>
         </is>
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1900.0</t>
+          <t>NT$ 1890.0</t>
         </is>
       </c>
       <c r="F9" s="17" t="inlineStr">
@@ -1967,22 +2054,22 @@
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1900.0</t>
+          <t>NT$ 1935.0</t>
         </is>
       </c>
       <c r="D10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1935.0</t>
+          <t>NT$ 1955.0</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1865.0</t>
+          <t>NT$ 1845.0</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 1915.0</t>
+          <t>NT$ 1890.0</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
@@ -2014,22 +2101,22 @@
       </c>
       <c r="C11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2395.0</t>
+          <t>NT$ 2445.0</t>
         </is>
       </c>
       <c r="D11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2540.0</t>
+          <t>NT$ 2470.0</t>
         </is>
       </c>
       <c r="E11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2350.0</t>
+          <t>NT$ 2305.0</t>
         </is>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2440.0</t>
+          <t>NT$ 2325.0</t>
         </is>
       </c>
       <c r="G11" s="29" t="inlineStr">
@@ -2061,7 +2148,7 @@
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 691.0</t>
+          <t>NT$ 710.0</t>
         </is>
       </c>
       <c r="D12" s="24" t="inlineStr">
@@ -2071,7 +2158,7 @@
       </c>
       <c r="E12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 690.0</t>
+          <t>NT$ 689.0</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
@@ -2108,22 +2195,22 @@
       </c>
       <c r="C13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 5280.0</t>
+          <t>NT$ 5220.0</t>
         </is>
       </c>
       <c r="D13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 5480.0</t>
+          <t>NT$ 5265.0</t>
         </is>
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 5150.0</t>
+          <t>NT$ 5140.0</t>
         </is>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 5180.0</t>
+          <t>NT$ 5185.0</t>
         </is>
       </c>
       <c r="G13" s="29" t="inlineStr">
@@ -2139,6 +2226,53 @@
       <c r="I13" s="17" t="inlineStr">
         <is>
           <t>獲利與 ASIC 時程轉弱即檢視</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>3653.TW</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>NT$ 6005.0</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>NT$ 6410.0</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="inlineStr">
+        <is>
+          <t>NT$ 5930.0</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>NT$ 6410.0</t>
+        </is>
+      </c>
+      <c r="G14" s="25" t="inlineStr">
+        <is>
+          <t>待估值與技術面複核</t>
+        </is>
+      </c>
+      <c r="H14" s="26" t="inlineStr">
+        <is>
+          <t>依獲利與估值重新評估</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>依獲利趨勢與個人風險承受度管理</t>
         </is>
       </c>
     </row>

--- a/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
+++ b/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="核心卡位龙头全景深度分析" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="买卖决策速查面板" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="核心卡位龙头全景深度分析" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="买卖决策速查面板" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -631,7 +631,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>定盘时间: 2026-09-23 14:11:55 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
+          <t>定盘时间: 2026-09-23 19:55:21 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
           <t>• 毛利率：67.03% (2026Q2)
 • 净利率：53.22% (2026Q2)
 • ROE：79.5% (單季年化, 2026Q2)
-• EPS：49.33 元 (2026Q2)</t>
+• EPS：27.25 元 (2026Q2 單季；TSMC 官方財報)</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -751,15 +751,15 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>外资: -4330 张
-投信: -406 张
-[2026-09-22 官方结算] 外资与投信偏空调节 (-4,268 张)，机构筹码阶段获利了结。</t>
+          <t>外资: +7123 张
+投信: -1143 张
+[2026-09-23 官方结算] 外资主力大幅回流 (+7,123 张)，投信阶段获利减仓 (-1,143 张)。</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 4,268 张 (占量 21.0%)
-[2026-09-22 筹码] 主力机构呈净卖出 (-4,268 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 6,304 张 (占量 31.0%)
+[2026-09-23 筹码] 主力机构呈净买入 (+6,304 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>20,325 张</t>
+          <t>20,361 张</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
           <t>• 毛利率：84.18% (2026Q2)
 • 净利率：64.95% (2026Q2)
 • ROE：125.3% (單季年化, 2026Q2)
-• EPS：110.96 元 (2026Q2)</t>
+• EPS：74.38 元 (2026Q2 單季；公司法說資料)</t>
         </is>
       </c>
       <c r="F5" s="16" t="inlineStr">
@@ -838,15 +838,15 @@
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>外资: -69 张
-投信: +23 张
-[2026-09-22 官方结算] 投信内资买超 (+23 张) 逢低承接，外资高档调节 (-69 张)。</t>
+          <t>外资: +60 张
+投信: -42 张
+[2026-09-23 官方结算] 外资主力大幅回流 (+60 张)，投信阶段获利减仓 (-42 张)。</t>
         </is>
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 42 张 (占量 13.6%)
-[2026-09-22 筹码] 主力机构呈净卖出 (-42 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 34 张 (占量 11.0%)
+[2026-09-23 筹码] 主力机构呈净买入 (+34 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="O5" s="16" t="inlineStr">
         <is>
-          <t>309 张</t>
+          <t>310 张</t>
         </is>
       </c>
     </row>
@@ -915,7 +915,7 @@
           <t>• 毛利率：32.03% (2026Q2)
 • 净利率：18.93% (2026Q2)
 • ROE：104.3% (單季年化, 2026Q2)
-• EPS：42.46 元 (2026Q2)</t>
+• EPS：27.55 元 (2026Q2 單季；公司季度財報)</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -925,15 +925,15 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>外资: +331 张
-投信: -654 张
-[2026-09-22 官方结算] 外资主力大幅回流 (+331 张)，投信阶段获利减仓 (-654 张)。</t>
+          <t>外资: -188 张
+投信: -30 张
+[2026-09-23 官方结算] 外资与投信偏空调节 (-188 张)，机构筹码阶段获利了结。</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 273 张 (占量 12.2%)
-[2026-09-22 筹码] 主力机构呈净卖出 (-273 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 188 张 (占量 8.4%)
+[2026-09-23 筹码] 主力机构呈净卖出 (-188 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>2,241 张</t>
+          <t>2,243 张</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
           <t>• 毛利率：31.17% (2026Q2)
 • 净利率：19.31% (2026Q2)
 • ROE：126.7% (單季年化, 2026Q2)
-• EPS：44.54 元 (2026Q2)</t>
+• EPS：24.37 元 (2026Q2 單季；公司季度財報)</t>
         </is>
       </c>
       <c r="F7" s="16" t="inlineStr">
@@ -1012,15 +1012,15 @@
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>外资: -218 张
-投信: -8 张
-[2026-09-22 官方结算] 外资与投信偏空调节 (-195 张)，机构筹码阶段获利了结。</t>
+          <t>外资: +20 张
+投信: +224 张
+[2026-09-23 官方结算] 三大法人全线买超 (+291 张)，外资与投信合力加仓。</t>
         </is>
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 195 张 (占量 7.8%)
-[2026-09-22 筹码] 主力机构呈净卖出 (-195 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 291 张 (占量 11.7%)
+[2026-09-23 筹码] 主力机构呈净买入 (+291 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I7" s="15" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="O7" s="16" t="inlineStr">
         <is>
-          <t>2,485 张</t>
+          <t>2,486 张</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1089,7 @@
           <t>• 毛利率：6.15% (2026Q2)
 • 净利率：2.73% (2026Q2)
 • ROE：23.0% (單季年化, 2026Q2)
-• EPS：7.84 元 (2026Q2)</t>
+• EPS：4.27 元 (2026Q2 單季；鴻海官方公告)</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -1099,15 +1099,15 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>外资: +6811 张
-投信: -19 张
-[2026-09-22 官方结算] 外资主力大幅回流 (+6,811 张)，投信阶段获利减仓 (-19 张)。</t>
+          <t>外资: +5860 张
+投信: +967 张
+[2026-09-23 官方结算] 三大法人全线买超 (+7,773 张)，外资与投信合力加仓。</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 7,725 张 (占量 22.3%)
-[2026-09-22 筹码] 主力机构呈净买入 (+7,725 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 7,773 张 (占量 22.4%)
+[2026-09-23 筹码] 主力机构呈净买入 (+7,773 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="O8" s="7" t="inlineStr">
         <is>
-          <t>34,627 张</t>
+          <t>34,697 张</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
           <t>• 毛利率：36.27% (2026Q2)
 • 净利率：14.89% (2026Q2)
 • ROE：62.2% (單季年化, 2026Q2)
-• EPS：17.59 元 (2026Q2)</t>
+• EPS：9.68 元 (26Q2)</t>
         </is>
       </c>
       <c r="F9" s="16" t="inlineStr">
@@ -1186,15 +1186,15 @@
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
-          <t>外资: -1324 张
-投信: +1642 张
-[2026-09-22 官方结算] 投信内资买超 (+1,642 张) 逢低承接，外资高档调节 (-1,324 张)。</t>
+          <t>外资: -140 张
+投信: +211 张
+[2026-09-23 官方结算] 投信内资买超 (+211 张) 逢低承接，外资高档调节 (-140 张)。</t>
         </is>
       </c>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 311 张 (占量 3.5%)
-[2026-09-22 筹码] 主力机构呈净买入 (+311 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 135 张 (占量 1.5%)
+[2026-09-23 筹码] 主力机构呈净买入 (+135 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I9" s="15" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="O9" s="16" t="inlineStr">
         <is>
-          <t>9,000 张</t>
+          <t>9,011 张</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
           <t>• 毛利率：19.63% (2026Q2)
 • 净利率：11.70% (2026Q2)
 • ROE：112.4% (單季年化, 2026Q2)
-• EPS：34.70 元 (2026Q2)</t>
+• EPS：19.78 元 (26Q2)</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -1273,15 +1273,15 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>外资: -150 张
-投信: -173 张
-[2026-09-22 官方结算] 外资与投信偏空调节 (-272 张)，机构筹码阶段获利了结。</t>
+          <t>外资: -595 张
+投信: -532 张
+[2026-09-23 官方结算] 三大法人同步卖超 (-1,144 张)，短线筹码面临清洗。</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 272 张 (占量 7.0%)
-[2026-09-22 筹码] 主力机构呈净卖出 (-272 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 1,144 张 (占量 29.6%)
+[2026-09-23 筹码] 主力机构呈净卖出 (-1,144 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>3,860 张</t>
+          <t>3,864 张</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
           <t>• 毛利率：61.48% (2026Q2)
 • 净利率：36.15% (2026Q2)
 • ROE：109.0% (單季年化, 2026Q2)
-• EPS：21.27 元 (2026Q2)</t>
+• EPS：約 12.15 元 (26Q2)</t>
         </is>
       </c>
       <c r="F11" s="16" t="inlineStr">
@@ -1360,15 +1360,15 @@
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>外资: -14 张
-投信: -75 张
-[2026-09-22 官方结算] 外资与投信偏空调节 (-72 张)，机构筹码阶段获利了结。</t>
+          <t>外资: +251 张
+投信: -276 张
+[2026-09-23 官方结算] 外资主力大幅回流 (+251 张)，投信阶段获利减仓 (-276 张)。</t>
         </is>
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 72 张 (占量 2.9%)
-[2026-09-22 筹码] 主力机构呈净卖出 (-72 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 61 张 (占量 2.4%)
+[2026-09-23 筹码] 主力机构呈净买入 (+61 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I11" s="15" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="O11" s="16" t="inlineStr">
         <is>
-          <t>2,511 张</t>
+          <t>2,512 张</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
           <t>• 毛利率：20.55% (2026Q2)
 • 净利率：9.89% (2026Q2)
 • ROE：36.2% (單季年化, 2026Q2)
-• EPS：8.04 元 (2026Q2)</t>
+• EPS：4.80 元 (26Q2)</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -1447,15 +1447,15 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>外资: +8479 张
-投信: +1163 张
-[2026-09-22 官方结算] 三大法人全线买超 (+10,751 张)，外资与投信合力加仓。</t>
+          <t>外资: +4008 张
+投信: -2277 张
+[2026-09-23 官方结算] 外资主力大幅回流 (+4,008 张)，投信阶段获利减仓 (-2,277 张)。</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 10,751 张 (占量 73.8%)
-[2026-09-22 筹码] 主力机构呈净买入 (+10,751 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 1,907 张 (占量 13.1%)
+[2026-09-23 筹码] 主力机构呈净买入 (+1,907 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>14,576 张</t>
+          <t>14,604 张</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
           <t>• 毛利率：46.25% (2026Q2)
 • 净利率：16.25% (2026Q2)
 • ROE：45.7% (單季年化, 2026Q2)
-• EPS：30.44 元 (2026Q2)</t>
+• EPS：15.28 元 (26Q2)</t>
         </is>
       </c>
       <c r="F13" s="16" t="inlineStr">
@@ -1534,15 +1534,15 @@
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>外资: +1541 张
-投信: +373 张
-[2026-09-22 官方结算] 三大法人全线买超 (+1,972 张)，外资与投信合力加仓。</t>
+          <t>外资: +496 张
+投信: -18 张
+[2026-09-23 官方结算] 外资主力大幅回流 (+496 张)，投信阶段获利减仓 (-18 张)。</t>
         </is>
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 1,972 张 (占量 33.4%)
-[2026-09-22 筹码] 主力机构呈净买入 (+1,972 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 519 张 (占量 8.8%)
+[2026-09-23 筹码] 主力机构呈净买入 (+519 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I13" s="15" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="O13" s="16" t="inlineStr">
         <is>
-          <t>5,902 张</t>
+          <t>5,909 张</t>
         </is>
       </c>
     </row>
@@ -1621,15 +1621,15 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>外资: -201 张
-投信: +85 张
-[2026-09-22 官方结算] 投信内资买超 (+85 张) 逢低承接，外资高档调节 (-201 张)。</t>
+          <t>外资: +43 张
+投信: -22 张
+[2026-09-23 官方结算] 外资主力大幅回流 (+43 张)，投信阶段获利减仓 (-22 张)。</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 119 张 (占量 8.5%)
-[2026-09-22 筹码] 主力机构呈净卖出 (-119 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 69 张 (占量 4.9%)
+[2026-09-23 筹码] 主力机构呈净买入 (+69 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -1708,7 +1708,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-09-23 14:11:55 | 策略: 3-3-4 分批建仓</t>
+          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-09-23 19:55:21 | 策略: 3-3-4 分批建仓</t>
         </is>
       </c>
     </row>

--- a/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
+++ b/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
@@ -631,7 +631,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>定盘时间: 2026-09-23 19:55:21 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
+          <t>定盘时间: 2026-09-24 20:02:48 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
         </is>
       </c>
     </row>
@@ -730,10 +730,10 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>开盘: 2475.0
-最高: 2505.0
-最低: 2475.0
-收盘: 2500.0</t>
+          <t>开盘: 2480.0
+最高: 2490.0
+最低: 2470.0
+收盘: 2475.0</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -751,15 +751,15 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>外资: +7123 张
-投信: -1143 张
-[2026-09-23 官方结算] 外资主力大幅回流 (+7,123 张)，投信阶段获利减仓 (-1,143 张)。</t>
+          <t>外资: -4668 张
+投信: -1288 张
+[2026-09-24 官方结算] 外资与投信偏空调节 (-5,713 张)，机构筹码阶段获利了结。</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 6,304 张 (占量 31.0%)
-[2026-09-23 筹码] 主力机构呈净买入 (+6,304 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 5,713 张 (占量 43.9%)
+[2026-09-24 筹码] 主力机构呈净卖出 (-5,713 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2500.0</t>
+          <t>NT$ 2475.0</t>
         </is>
       </c>
       <c r="K4" s="9" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>20,361 张</t>
+          <t>13,005 张</t>
         </is>
       </c>
     </row>
@@ -817,10 +817,10 @@
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>开盘: 12670.0
-最高: 12725.0
-最低: 12320.0
-收盘: 12390.0</t>
+          <t>开盘: 12400.0
+最高: 12640.0
+最低: 12185.0
+收盘: 12350.0</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -838,15 +838,15 @@
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>外资: +60 张
+          <t>外资: +109 张
 投信: -42 张
-[2026-09-23 官方结算] 外资主力大幅回流 (+60 张)，投信阶段获利减仓 (-42 张)。</t>
+[2026-09-24 官方结算] 外资主力大幅回流 (+109 张)，投信阶段获利减仓 (-42 张)。</t>
         </is>
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 34 张 (占量 11.0%)
-[2026-09-23 筹码] 主力机构呈净买入 (+34 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 91 张 (占量 23.6%)
+[2026-09-24 筹码] 主力机构呈净买入 (+91 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 12390.0</t>
+          <t>NT$ 12350.0</t>
         </is>
       </c>
       <c r="K5" s="18" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="O5" s="16" t="inlineStr">
         <is>
-          <t>310 张</t>
+          <t>386 张</t>
         </is>
       </c>
     </row>
@@ -904,10 +904,10 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>开盘: 4910.0
-最高: 5110.0
-最低: 4860.0
-收盘: 5020.0</t>
+          <t>开盘: 5025.0
+最高: 5170.0
+最低: 4980.0
+收盘: 5050.0</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -925,15 +925,15 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>外资: -188 张
-投信: -30 张
-[2026-09-23 官方结算] 外资与投信偏空调节 (-188 张)，机构筹码阶段获利了结。</t>
+          <t>外资: +27 张
+投信: -405 张
+[2026-09-24 官方结算] 外资主力大幅回流 (+27 张)，投信阶段获利减仓 (-405 张)。</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 188 张 (占量 8.4%)
-[2026-09-23 筹码] 主力机构呈净卖出 (-188 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 301 张 (占量 13.8%)
+[2026-09-24 筹码] 主力机构呈净卖出 (-301 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 5020.0</t>
+          <t>NT$ 5050.0</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>2,243 张</t>
+          <t>2,187 张</t>
         </is>
       </c>
     </row>
@@ -991,10 +991,10 @@
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>开盘: 3425.0
-最高: 3590.0
-最低: 3410.0
-收盘: 3470.0</t>
+          <t>开盘: 3460.0
+最高: 3600.0
+最低: 3455.0
+收盘: 3555.0</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -1012,15 +1012,15 @@
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>外资: +20 张
-投信: +224 张
-[2026-09-23 官方结算] 三大法人全线买超 (+291 张)，外资与投信合力加仓。</t>
+          <t>外资: +165 张
+投信: +10 张
+[2026-09-24 官方结算] 三大法人全线买超 (+219 张)，外资与投信合力加仓。</t>
         </is>
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 291 张 (占量 11.7%)
-[2026-09-23 筹码] 主力机构呈净买入 (+291 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 219 张 (占量 10.4%)
+[2026-09-24 筹码] 主力机构呈净买入 (+219 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I7" s="15" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="J7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3470.0</t>
+          <t>NT$ 3555.0</t>
         </is>
       </c>
       <c r="K7" s="18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="O7" s="16" t="inlineStr">
         <is>
-          <t>2,486 张</t>
+          <t>2,104 张</t>
         </is>
       </c>
     </row>
@@ -1078,10 +1078,10 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>开盘: 255.0
-最高: 257.0
-最低: 255.0
-收盘: 256.0</t>
+          <t>开盘: 253.0
+最高: 253.0
+最低: 249.5
+收盘: 250.5</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -1099,15 +1099,15 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>外资: +5860 张
-投信: +967 张
-[2026-09-23 官方结算] 三大法人全线买超 (+7,773 张)，外资与投信合力加仓。</t>
+          <t>外资: -23873 张
+投信: -263 张
+[2026-09-24 官方结算] 三大法人同步卖超 (-24,232 张)，短线筹码面临清洗。</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 7,773 张 (占量 22.4%)
-[2026-09-23 筹码] 主力机构呈净买入 (+7,773 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 24,232 张 (占量 73.5%)
+[2026-09-24 筹码] 主力机构呈净卖出 (-24,232 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>NT$ 256.0</t>
+          <t>NT$ 250.5</t>
         </is>
       </c>
       <c r="K8" s="9" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="O8" s="7" t="inlineStr">
         <is>
-          <t>34,697 张</t>
+          <t>32,978 张</t>
         </is>
       </c>
     </row>
@@ -1165,10 +1165,10 @@
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>开盘: 1910.0
-最高: 1920.0
-最低: 1890.0
-收盘: 1900.0</t>
+          <t>开盘: 1875.0
+最高: 1935.0
+最低: 1875.0
+收盘: 1910.0</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -1186,15 +1186,15 @@
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
-          <t>外资: -140 张
-投信: +211 张
-[2026-09-23 官方结算] 投信内资买超 (+211 张) 逢低承接，外资高档调节 (-140 张)。</t>
+          <t>外资: -328 张
+投信: +420 张
+[2026-09-24 官方结算] 投信内资买超 (+420 张) 逢低承接，外资高档调节 (-328 张)。</t>
         </is>
       </c>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 135 张 (占量 1.5%)
-[2026-09-23 筹码] 主力机构呈净买入 (+135 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 234 张 (占量 2.9%)
+[2026-09-24 筹码] 主力机构呈净买入 (+234 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I9" s="15" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="J9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1900.0</t>
+          <t>NT$ 1910.0</t>
         </is>
       </c>
       <c r="K9" s="18" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="O9" s="16" t="inlineStr">
         <is>
-          <t>9,011 张</t>
+          <t>8,175 张</t>
         </is>
       </c>
     </row>
@@ -1252,10 +1252,10 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>开盘: 1935.0
-最高: 1955.0
-最低: 1845.0
-收盘: 1890.0</t>
+          <t>开盘: 1880.0
+最高: 1905.0
+最低: 1855.0
+收盘: 1895.0</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -1273,15 +1273,15 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>外资: -595 张
-投信: -532 张
-[2026-09-23 官方结算] 三大法人同步卖超 (-1,144 张)，短线筹码面临清洗。</t>
+          <t>外资: -5 张
+投信: -486 张
+[2026-09-24 官方结算] 外资与投信偏空调节 (-481 张)，机构筹码阶段获利了结。</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 1,144 张 (占量 29.6%)
-[2026-09-23 筹码] 主力机构呈净卖出 (-1,144 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 481 张 (占量 20.1%)
+[2026-09-24 筹码] 主力机构呈净卖出 (-481 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 1890.0</t>
+          <t>NT$ 1895.0</t>
         </is>
       </c>
       <c r="K10" s="9" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>3,864 张</t>
+          <t>2,399 张</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>开盘: 2445.0
-最高: 2470.0
-最低: 2305.0
-收盘: 2325.0</t>
+          <t>开盘: 2285.0
+最高: 2345.0
+最低: 2270.0
+收盘: 2295.0</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
@@ -1360,15 +1360,15 @@
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>外资: +251 张
-投信: -276 张
-[2026-09-23 官方结算] 外资主力大幅回流 (+251 张)，投信阶段获利减仓 (-276 张)。</t>
+          <t>外资: +680 张
+投信: -237 张
+[2026-09-24 官方结算] 外资主力大幅回流 (+680 张)，投信阶段获利减仓 (-237 张)。</t>
         </is>
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 61 张 (占量 2.4%)
-[2026-09-23 筹码] 主力机构呈净买入 (+61 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 512 张 (占量 26.6%)
+[2026-09-24 筹码] 主力机构呈净买入 (+512 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I11" s="15" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="J11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2325.0</t>
+          <t>NT$ 2295.0</t>
         </is>
       </c>
       <c r="K11" s="18" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="O11" s="16" t="inlineStr">
         <is>
-          <t>2,512 张</t>
+          <t>1,925 张</t>
         </is>
       </c>
     </row>
@@ -1426,10 +1426,10 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>开盘: 710.0
-最高: 711.0
-最低: 689.0
-收盘: 693.0</t>
+          <t>开盘: 685.0
+最高: 699.0
+最低: 680.0
+收盘: 699.0</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -1447,15 +1447,15 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>外资: +4008 张
-投信: -2277 张
-[2026-09-23 官方结算] 外资主力大幅回流 (+4,008 张)，投信阶段获利减仓 (-2,277 张)。</t>
+          <t>外资: +1906 张
+投信: -2167 张
+[2026-09-24 官方结算] 外资主力大幅回流 (+1,906 张)，投信阶段获利减仓 (-2,167 张)。</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 1,907 张 (占量 13.1%)
-[2026-09-23 筹码] 主力机构呈净买入 (+1,907 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 246 张 (占量 2.3%)
+[2026-09-24 筹码] 主力机构呈净卖出 (-246 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 693.0</t>
+          <t>NT$ 699.0</t>
         </is>
       </c>
       <c r="K12" s="9" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>14,604 张</t>
+          <t>10,518 张</t>
         </is>
       </c>
     </row>
@@ -1513,10 +1513,10 @@
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>开盘: 5220.0
-最高: 5265.0
-最低: 5140.0
-收盘: 5185.0</t>
+          <t>开盘: 5105.0
+最高: 5360.0
+最低: 5105.0
+收盘: 5285.0</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
@@ -1534,15 +1534,15 @@
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>外资: +496 张
-投信: -18 张
-[2026-09-23 官方结算] 外资主力大幅回流 (+496 张)，投信阶段获利减仓 (-18 张)。</t>
+          <t>外资: +826 张
+投信: -289 张
+[2026-09-24 官方结算] 外资主力大幅回流 (+826 张)，投信阶段获利减仓 (-289 张)。</t>
         </is>
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 519 张 (占量 8.8%)
-[2026-09-23 筹码] 主力机构呈净买入 (+519 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 670 张 (占量 9.4%)
+[2026-09-24 筹码] 主力机构呈净买入 (+670 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I13" s="15" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="J13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 5185.0</t>
+          <t>NT$ 5285.0</t>
         </is>
       </c>
       <c r="K13" s="18" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="O13" s="16" t="inlineStr">
         <is>
-          <t>5,909 张</t>
+          <t>7,146 张</t>
         </is>
       </c>
     </row>
@@ -1600,10 +1600,10 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>开盘: 6005.0
-最高: 6410.0
-最低: 5930.0
-收盘: 6410.0</t>
+          <t>开盘: 6560.0
+最高: 6920.0
+最低: 6215.0
+收盘: 6920.0</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -1621,15 +1621,15 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>外资: +43 张
-投信: -22 张
-[2026-09-23 官方结算] 外资主力大幅回流 (+43 张)，投信阶段获利减仓 (-22 张)。</t>
+          <t>外资: -339 张
+投信: +247 张
+[2026-09-24 官方结算] 投信内资买超 (+247 张) 逢低承接，外资高档调节 (-339 张)。</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 69 张 (占量 4.9%)
-[2026-09-23 筹码] 主力机构呈净买入 (+69 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 108 张 (占量 4.1%)
+[2026-09-24 筹码] 主力机构呈净卖出 (-108 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>NT$ 6410.0</t>
+          <t>NT$ 6920.0</t>
         </is>
       </c>
       <c r="K14" s="9" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="O14" s="7" t="inlineStr">
         <is>
-          <t>1,394 张</t>
+          <t>2,664 张</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-09-23 19:55:21 | 策略: 3-3-4 分批建仓</t>
+          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-09-24 20:02:48 | 策略: 3-3-4 分批建仓</t>
         </is>
       </c>
     </row>
@@ -1772,22 +1772,22 @@
       </c>
       <c r="C4" s="24" t="inlineStr">
         <is>
+          <t>NT$ 2480.0</t>
+        </is>
+      </c>
+      <c r="D4" s="24" t="inlineStr">
+        <is>
+          <t>NT$ 2490.0</t>
+        </is>
+      </c>
+      <c r="E4" s="24" t="inlineStr">
+        <is>
+          <t>NT$ 2470.0</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
           <t>NT$ 2475.0</t>
-        </is>
-      </c>
-      <c r="D4" s="24" t="inlineStr">
-        <is>
-          <t>NT$ 2505.0</t>
-        </is>
-      </c>
-      <c r="E4" s="24" t="inlineStr">
-        <is>
-          <t>NT$ 2475.0</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>NT$ 2500.0</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
@@ -1819,22 +1819,22 @@
       </c>
       <c r="C5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 12670.0</t>
+          <t>NT$ 12400.0</t>
         </is>
       </c>
       <c r="D5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 12725.0</t>
+          <t>NT$ 12640.0</t>
         </is>
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 12320.0</t>
+          <t>NT$ 12185.0</t>
         </is>
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 12390.0</t>
+          <t>NT$ 12350.0</t>
         </is>
       </c>
       <c r="G5" s="29" t="inlineStr">
@@ -1866,22 +1866,22 @@
       </c>
       <c r="C6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 4910.0</t>
+          <t>NT$ 5025.0</t>
         </is>
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5110.0</t>
+          <t>NT$ 5170.0</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 4860.0</t>
+          <t>NT$ 4980.0</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 5020.0</t>
+          <t>NT$ 5050.0</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
@@ -1913,22 +1913,22 @@
       </c>
       <c r="C7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3425.0</t>
+          <t>NT$ 3460.0</t>
         </is>
       </c>
       <c r="D7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3590.0</t>
+          <t>NT$ 3600.0</t>
         </is>
       </c>
       <c r="E7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3410.0</t>
+          <t>NT$ 3455.0</t>
         </is>
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3470.0</t>
+          <t>NT$ 3555.0</t>
         </is>
       </c>
       <c r="G7" s="29" t="inlineStr">
@@ -1960,22 +1960,22 @@
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 255.0</t>
+          <t>NT$ 253.0</t>
         </is>
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 257.0</t>
+          <t>NT$ 253.0</t>
         </is>
       </c>
       <c r="E8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 255.0</t>
+          <t>NT$ 249.5</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>NT$ 256.0</t>
+          <t>NT$ 250.5</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
@@ -2007,22 +2007,22 @@
       </c>
       <c r="C9" s="28" t="inlineStr">
         <is>
+          <t>NT$ 1875.0</t>
+        </is>
+      </c>
+      <c r="D9" s="28" t="inlineStr">
+        <is>
+          <t>NT$ 1935.0</t>
+        </is>
+      </c>
+      <c r="E9" s="28" t="inlineStr">
+        <is>
+          <t>NT$ 1875.0</t>
+        </is>
+      </c>
+      <c r="F9" s="17" t="inlineStr">
+        <is>
           <t>NT$ 1910.0</t>
-        </is>
-      </c>
-      <c r="D9" s="28" t="inlineStr">
-        <is>
-          <t>NT$ 1920.0</t>
-        </is>
-      </c>
-      <c r="E9" s="28" t="inlineStr">
-        <is>
-          <t>NT$ 1890.0</t>
-        </is>
-      </c>
-      <c r="F9" s="17" t="inlineStr">
-        <is>
-          <t>NT$ 1900.0</t>
         </is>
       </c>
       <c r="G9" s="29" t="inlineStr">
@@ -2054,22 +2054,22 @@
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1935.0</t>
+          <t>NT$ 1880.0</t>
         </is>
       </c>
       <c r="D10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1955.0</t>
+          <t>NT$ 1905.0</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1845.0</t>
+          <t>NT$ 1855.0</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 1890.0</t>
+          <t>NT$ 1895.0</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
@@ -2101,22 +2101,22 @@
       </c>
       <c r="C11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2445.0</t>
+          <t>NT$ 2285.0</t>
         </is>
       </c>
       <c r="D11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2470.0</t>
+          <t>NT$ 2345.0</t>
         </is>
       </c>
       <c r="E11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2305.0</t>
+          <t>NT$ 2270.0</t>
         </is>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2325.0</t>
+          <t>NT$ 2295.0</t>
         </is>
       </c>
       <c r="G11" s="29" t="inlineStr">
@@ -2148,22 +2148,22 @@
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 710.0</t>
+          <t>NT$ 685.0</t>
         </is>
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 711.0</t>
+          <t>NT$ 699.0</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 689.0</t>
+          <t>NT$ 680.0</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 693.0</t>
+          <t>NT$ 699.0</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
@@ -2195,22 +2195,22 @@
       </c>
       <c r="C13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 5220.0</t>
+          <t>NT$ 5105.0</t>
         </is>
       </c>
       <c r="D13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 5265.0</t>
+          <t>NT$ 5360.0</t>
         </is>
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 5140.0</t>
+          <t>NT$ 5105.0</t>
         </is>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 5185.0</t>
+          <t>NT$ 5285.0</t>
         </is>
       </c>
       <c r="G13" s="29" t="inlineStr">
@@ -2242,22 +2242,22 @@
       </c>
       <c r="C14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 6005.0</t>
+          <t>NT$ 6560.0</t>
         </is>
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 6410.0</t>
+          <t>NT$ 6920.0</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5930.0</t>
+          <t>NT$ 6215.0</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>NT$ 6410.0</t>
+          <t>NT$ 6920.0</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">

--- a/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
+++ b/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
@@ -631,7 +631,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>定盘时间: 2026-09-24 20:02:48 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
+          <t>定盘时间: 2026-09-25 20:02:55 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-09-24 20:02:48 | 策略: 3-3-4 分批建仓</t>
+          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-09-25 20:02:55 | 策略: 3-3-4 分批建仓</t>
         </is>
       </c>
     </row>

--- a/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
+++ b/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
@@ -631,7 +631,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>定盘时间: 2026-09-25 20:02:55 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
+          <t>定盘时间: 2026-09-28 22:17:39 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-09-25 20:02:55 | 策略: 3-3-4 分批建仓</t>
+          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-09-28 22:17:39 | 策略: 3-3-4 分批建仓</t>
         </is>
       </c>
     </row>

--- a/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
+++ b/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
@@ -631,7 +631,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>定盘时间: 2026-09-28 22:17:39 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
+          <t>定盘时间: 2026-09-29 21:11:51 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
         </is>
       </c>
     </row>
@@ -730,9 +730,9 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>开盘: 2480.0
-最高: 2490.0
-最低: 2470.0
+          <t>开盘: 2475.0
+最高: 2495.0
+最低: 2475.0
 收盘: 2475.0</t>
         </is>
       </c>
@@ -751,15 +751,15 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>外资: -4668 张
-投信: -1288 张
-[2026-09-24 官方结算] 外资与投信偏空调节 (-5,713 张)，机构筹码阶段获利了结。</t>
+          <t>外资: -3737 张
+投信: +628 张
+[2026-09-29 官方结算] 投信内资买超 (+628 张) 逢低承接，外资高档调节 (-3,737 张)。</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 5,713 张 (占量 43.9%)
-[2026-09-24 筹码] 主力机构呈净卖出 (-5,713 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 2,991 张 (占量 12.2%)
+[2026-09-29 筹码] 主力机构呈净卖出 (-2,991 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>13,005 张</t>
+          <t>24,601 张</t>
         </is>
       </c>
     </row>
@@ -817,10 +817,10 @@
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>开盘: 12400.0
-最高: 12640.0
-最低: 12185.0
-收盘: 12350.0</t>
+          <t>开盘: 12350.0
+最高: 12550.0
+最低: 11900.0
+收盘: 12115.0</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -838,15 +838,15 @@
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>外资: +109 张
-投信: -42 张
-[2026-09-24 官方结算] 外资主力大幅回流 (+109 张)，投信阶段获利减仓 (-42 张)。</t>
+          <t>外资: +68 张
+投信: -20 张
+[2026-09-29 官方结算] 外资主力大幅回流 (+68 张)，投信阶段获利减仓 (-20 张)。</t>
         </is>
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 91 张 (占量 23.6%)
-[2026-09-24 筹码] 主力机构呈净买入 (+91 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 60 张 (占量 14.9%)
+[2026-09-29 筹码] 主力机构呈净买入 (+60 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 12350.0</t>
+          <t>NT$ 12115.0</t>
         </is>
       </c>
       <c r="K5" s="18" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="O5" s="16" t="inlineStr">
         <is>
-          <t>386 张</t>
+          <t>402 张</t>
         </is>
       </c>
     </row>
@@ -904,10 +904,10 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>开盘: 5025.0
-最高: 5170.0
-最低: 4980.0
-收盘: 5050.0</t>
+          <t>开盘: 4910.0
+最高: 5055.0
+最低: 4870.0
+收盘: 4920.0</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -925,15 +925,15 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>外资: +27 张
-投信: -405 张
-[2026-09-24 官方结算] 外资主力大幅回流 (+27 张)，投信阶段获利减仓 (-405 张)。</t>
+          <t>外资: -283 张
+投信: -188 张
+[2026-09-29 官方结算] 三大法人同步卖超 (-480 张)，短线筹码面临清洗。</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 301 张 (占量 13.8%)
-[2026-09-24 筹码] 主力机构呈净卖出 (-301 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 480 张 (占量 25.5%)
+[2026-09-29 筹码] 主力机构呈净卖出 (-480 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 5050.0</t>
+          <t>NT$ 4920.0</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>2,187 张</t>
+          <t>1,883 张</t>
         </is>
       </c>
     </row>
@@ -991,10 +991,10 @@
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>开盘: 3460.0
-最高: 3600.0
-最低: 3455.0
-收盘: 3555.0</t>
+          <t>开盘: 3420.0
+最高: 3460.0
+最低: 3285.0
+收盘: 3400.0</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -1012,15 +1012,15 @@
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>外资: +165 张
-投信: +10 张
-[2026-09-24 官方结算] 三大法人全线买超 (+219 张)，外资与投信合力加仓。</t>
+          <t>外资: -453 张
+投信: -514 张
+[2026-09-29 官方结算] 外资与投信偏空调节 (-920 张)，机构筹码阶段获利了结。</t>
         </is>
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 219 张 (占量 10.4%)
-[2026-09-24 筹码] 主力机构呈净买入 (+219 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 920 张 (占量 26.8%)
+[2026-09-29 筹码] 主力机构呈净卖出 (-920 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I7" s="15" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="J7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3555.0</t>
+          <t>NT$ 3400.0</t>
         </is>
       </c>
       <c r="K7" s="18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="O7" s="16" t="inlineStr">
         <is>
-          <t>2,104 张</t>
+          <t>3,430 张</t>
         </is>
       </c>
     </row>
@@ -1078,9 +1078,9 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>开盘: 253.0
-最高: 253.0
-最低: 249.5
+          <t>开盘: 247.0
+最高: 254.0
+最低: 247.0
 收盘: 250.5</t>
         </is>
       </c>
@@ -1099,15 +1099,15 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>外资: -23873 张
-投信: -263 张
-[2026-09-24 官方结算] 三大法人同步卖超 (-24,232 张)，短线筹码面临清洗。</t>
+          <t>外资: +3091 张
+投信: -29 张
+[2026-09-29 官方结算] 外资主力大幅回流 (+3,091 张)，投信阶段获利减仓 (-29 张)。</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 24,232 张 (占量 73.5%)
-[2026-09-24 筹码] 主力机构呈净卖出 (-24,232 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 2,984 张 (占量 9.9%)
+[2026-09-29 筹码] 主力机构呈净买入 (+2,984 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="O8" s="7" t="inlineStr">
         <is>
-          <t>32,978 张</t>
+          <t>30,180 张</t>
         </is>
       </c>
     </row>
@@ -1165,10 +1165,10 @@
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>开盘: 1875.0
-最高: 1935.0
-最低: 1875.0
-收盘: 1910.0</t>
+          <t>开盘: 1880.0
+最高: 1950.0
+最低: 1810.0
+收盘: 1835.0</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -1186,15 +1186,15 @@
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
-          <t>外资: -328 张
-投信: +420 张
-[2026-09-24 官方结算] 投信内资买超 (+420 张) 逢低承接，外资高档调节 (-328 张)。</t>
+          <t>外资: -2791 张
+投信: +379 张
+[2026-09-29 官方结算] 投信内资买超 (+379 张) 逢低承接，外资高档调节 (-2,791 张)。</t>
         </is>
       </c>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 234 张 (占量 2.9%)
-[2026-09-24 筹码] 主力机构呈净买入 (+234 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 2,415 张 (占量 18.8%)
+[2026-09-29 筹码] 主力机构呈净卖出 (-2,415 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I9" s="15" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="J9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1910.0</t>
+          <t>NT$ 1835.0</t>
         </is>
       </c>
       <c r="K9" s="18" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="O9" s="16" t="inlineStr">
         <is>
-          <t>8,175 张</t>
+          <t>12,861 张</t>
         </is>
       </c>
     </row>
@@ -1252,10 +1252,10 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>开盘: 1880.0
-最高: 1905.0
-最低: 1855.0
-收盘: 1895.0</t>
+          <t>开盘: 1845.0
+最高: 1880.0
+最低: 1800.0
+收盘: 1810.0</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -1273,15 +1273,15 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>外资: -5 张
-投信: -486 张
-[2026-09-24 官方结算] 外资与投信偏空调节 (-481 张)，机构筹码阶段获利了结。</t>
+          <t>外资: -633 张
+投信: -737 张
+[2026-09-29 官方结算] 外资与投信偏空调节 (-1,367 张)，机构筹码阶段获利了结。</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 481 张 (占量 20.1%)
-[2026-09-24 筹码] 主力机构呈净卖出 (-481 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 1,367 张 (占量 36.3%)
+[2026-09-29 筹码] 主力机构呈净卖出 (-1,367 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 1895.0</t>
+          <t>NT$ 1810.0</t>
         </is>
       </c>
       <c r="K10" s="9" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>2,399 张</t>
+          <t>3,765 张</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>开盘: 2285.0
-最高: 2345.0
-最低: 2270.0
-收盘: 2295.0</t>
+          <t>开盘: 2255.0
+最高: 2325.0
+最低: 2160.0
+收盘: 2185.0</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
@@ -1360,15 +1360,15 @@
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>外资: +680 张
-投信: -237 张
-[2026-09-24 官方结算] 外资主力大幅回流 (+680 张)，投信阶段获利减仓 (-237 张)。</t>
+          <t>外资: -26 张
+投信: -446 张
+[2026-09-29 官方结算] 三大法人同步卖超 (-491 张)，短线筹码面临清洗。</t>
         </is>
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 512 张 (占量 26.6%)
-[2026-09-24 筹码] 主力机构呈净买入 (+512 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 491 张 (占量 21.4%)
+[2026-09-29 筹码] 主力机构呈净卖出 (-491 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I11" s="15" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="J11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2295.0</t>
+          <t>NT$ 2185.0</t>
         </is>
       </c>
       <c r="K11" s="18" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="O11" s="16" t="inlineStr">
         <is>
-          <t>1,925 张</t>
+          <t>2,293 张</t>
         </is>
       </c>
     </row>
@@ -1427,9 +1427,9 @@
       <c r="D12" s="7" t="inlineStr">
         <is>
           <t>开盘: 685.0
-最高: 699.0
-最低: 680.0
-收盘: 699.0</t>
+最高: 693.0
+最低: 678.0
+收盘: 687.0</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -1447,15 +1447,15 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>外资: +1906 张
-投信: -2167 张
-[2026-09-24 官方结算] 外资主力大幅回流 (+1,906 张)，投信阶段获利减仓 (-2,167 张)。</t>
+          <t>外资: -724 张
+投信: -927 张
+[2026-09-29 官方结算] 三大法人同步卖超 (-1,691 张)，短线筹码面临清洗。</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 246 张 (占量 2.3%)
-[2026-09-24 筹码] 主力机构呈净卖出 (-246 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 1,691 张 (占量 12.3%)
+[2026-09-29 筹码] 主力机构呈净卖出 (-1,691 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 699.0</t>
+          <t>NT$ 687.0</t>
         </is>
       </c>
       <c r="K12" s="9" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>10,518 张</t>
+          <t>13,777 张</t>
         </is>
       </c>
     </row>
@@ -1513,10 +1513,10 @@
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>开盘: 5105.0
-最高: 5360.0
-最低: 5105.0
-收盘: 5285.0</t>
+          <t>开盘: 5150.0
+最高: 5195.0
+最低: 4890.0
+收盘: 4910.0</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
@@ -1534,15 +1534,15 @@
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>外资: +826 张
-投信: -289 张
-[2026-09-24 官方结算] 外资主力大幅回流 (+826 张)，投信阶段获利减仓 (-289 张)。</t>
+          <t>外资: -4670 张
+投信: -60 张
+[2026-09-29 官方结算] 三大法人同步卖超 (-4,815 张)，短线筹码面临清洗。</t>
         </is>
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 670 张 (占量 9.4%)
-[2026-09-24 筹码] 主力机构呈净买入 (+670 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 4,815 张 (占量 43.6%)
+[2026-09-29 筹码] 主力机构呈净卖出 (-4,815 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I13" s="15" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="J13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 5285.0</t>
+          <t>NT$ 4910.0</t>
         </is>
       </c>
       <c r="K13" s="18" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="O13" s="16" t="inlineStr">
         <is>
-          <t>7,146 张</t>
+          <t>11,033 张</t>
         </is>
       </c>
     </row>
@@ -1600,10 +1600,10 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>开盘: 6560.0
-最高: 6920.0
-最低: 6215.0
-收盘: 6920.0</t>
+          <t>开盘: 7000.0
+最高: 7160.0
+最低: 6850.0
+收盘: 6895.0</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -1621,15 +1621,15 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>外资: -339 张
-投信: +247 张
-[2026-09-24 官方结算] 投信内资买超 (+247 张) 逢低承接，外资高档调节 (-339 张)。</t>
+          <t>外资: -310 张
+投信: +127 张
+[2026-09-29 官方结算] 投信内资买超 (+127 张) 逢低承接，外资高档调节 (-310 张)。</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 108 张 (占量 4.1%)
-[2026-09-24 筹码] 主力机构呈净卖出 (-108 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 176 张 (占量 11.1%)
+[2026-09-29 筹码] 主力机构呈净卖出 (-176 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>NT$ 6920.0</t>
+          <t>NT$ 6895.0</t>
         </is>
       </c>
       <c r="K14" s="9" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="O14" s="7" t="inlineStr">
         <is>
-          <t>2,664 张</t>
+          <t>1,591 张</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-09-28 22:17:39 | 策略: 3-3-4 分批建仓</t>
+          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-09-29 21:11:51 | 策略: 3-3-4 分批建仓</t>
         </is>
       </c>
     </row>
@@ -1772,17 +1772,17 @@
       </c>
       <c r="C4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2480.0</t>
+          <t>NT$ 2475.0</t>
         </is>
       </c>
       <c r="D4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2490.0</t>
+          <t>NT$ 2495.0</t>
         </is>
       </c>
       <c r="E4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2470.0</t>
+          <t>NT$ 2475.0</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
@@ -1819,22 +1819,22 @@
       </c>
       <c r="C5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 12400.0</t>
+          <t>NT$ 12350.0</t>
         </is>
       </c>
       <c r="D5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 12640.0</t>
+          <t>NT$ 12550.0</t>
         </is>
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 12185.0</t>
+          <t>NT$ 11900.0</t>
         </is>
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 12350.0</t>
+          <t>NT$ 12115.0</t>
         </is>
       </c>
       <c r="G5" s="29" t="inlineStr">
@@ -1866,22 +1866,22 @@
       </c>
       <c r="C6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5025.0</t>
+          <t>NT$ 4910.0</t>
         </is>
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5170.0</t>
+          <t>NT$ 5055.0</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 4980.0</t>
+          <t>NT$ 4870.0</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 5050.0</t>
+          <t>NT$ 4920.0</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
@@ -1913,22 +1913,22 @@
       </c>
       <c r="C7" s="28" t="inlineStr">
         <is>
+          <t>NT$ 3420.0</t>
+        </is>
+      </c>
+      <c r="D7" s="28" t="inlineStr">
+        <is>
           <t>NT$ 3460.0</t>
         </is>
       </c>
-      <c r="D7" s="28" t="inlineStr">
-        <is>
-          <t>NT$ 3600.0</t>
-        </is>
-      </c>
       <c r="E7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3455.0</t>
+          <t>NT$ 3285.0</t>
         </is>
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3555.0</t>
+          <t>NT$ 3400.0</t>
         </is>
       </c>
       <c r="G7" s="29" t="inlineStr">
@@ -1960,17 +1960,17 @@
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 253.0</t>
+          <t>NT$ 247.0</t>
         </is>
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 253.0</t>
+          <t>NT$ 254.0</t>
         </is>
       </c>
       <c r="E8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 249.5</t>
+          <t>NT$ 247.0</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -2007,22 +2007,22 @@
       </c>
       <c r="C9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1875.0</t>
+          <t>NT$ 1880.0</t>
         </is>
       </c>
       <c r="D9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1935.0</t>
+          <t>NT$ 1950.0</t>
         </is>
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1875.0</t>
+          <t>NT$ 1810.0</t>
         </is>
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1910.0</t>
+          <t>NT$ 1835.0</t>
         </is>
       </c>
       <c r="G9" s="29" t="inlineStr">
@@ -2054,22 +2054,22 @@
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
+          <t>NT$ 1845.0</t>
+        </is>
+      </c>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
           <t>NT$ 1880.0</t>
         </is>
       </c>
-      <c r="D10" s="24" t="inlineStr">
-        <is>
-          <t>NT$ 1905.0</t>
-        </is>
-      </c>
       <c r="E10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1855.0</t>
+          <t>NT$ 1800.0</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 1895.0</t>
+          <t>NT$ 1810.0</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
@@ -2101,22 +2101,22 @@
       </c>
       <c r="C11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2285.0</t>
+          <t>NT$ 2255.0</t>
         </is>
       </c>
       <c r="D11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2345.0</t>
+          <t>NT$ 2325.0</t>
         </is>
       </c>
       <c r="E11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2270.0</t>
+          <t>NT$ 2160.0</t>
         </is>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2295.0</t>
+          <t>NT$ 2185.0</t>
         </is>
       </c>
       <c r="G11" s="29" t="inlineStr">
@@ -2153,17 +2153,17 @@
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 699.0</t>
+          <t>NT$ 693.0</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 680.0</t>
+          <t>NT$ 678.0</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 699.0</t>
+          <t>NT$ 687.0</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
@@ -2195,22 +2195,22 @@
       </c>
       <c r="C13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 5105.0</t>
+          <t>NT$ 5150.0</t>
         </is>
       </c>
       <c r="D13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 5360.0</t>
+          <t>NT$ 5195.0</t>
         </is>
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 5105.0</t>
+          <t>NT$ 4890.0</t>
         </is>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 5285.0</t>
+          <t>NT$ 4910.0</t>
         </is>
       </c>
       <c r="G13" s="29" t="inlineStr">
@@ -2242,22 +2242,22 @@
       </c>
       <c r="C14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 6560.0</t>
+          <t>NT$ 7000.0</t>
         </is>
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 6920.0</t>
+          <t>NT$ 7160.0</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 6215.0</t>
+          <t>NT$ 6850.0</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>NT$ 6920.0</t>
+          <t>NT$ 6895.0</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">

--- a/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
+++ b/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
@@ -631,7 +631,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>定盘时间: 2026-09-29 21:11:51 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
+          <t>定盘时间: 2026-09-30 20:52:31 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
         </is>
       </c>
     </row>
@@ -730,10 +730,10 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>开盘: 2475.0
-最高: 2495.0
-最低: 2475.0
-收盘: 2475.0</t>
+          <t>开盘: 2495.0
+最高: 2510.0
+最低: 2480.0
+收盘: 2480.0</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -751,15 +751,15 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>外资: -3737 张
-投信: +628 张
-[2026-09-29 官方结算] 投信内资买超 (+628 张) 逢低承接，外资高档调节 (-3,737 张)。</t>
+          <t>外资: +702 张
+投信: +761 张
+[2026-09-30 官方结算] 三大法人全线买超 (+1,864 张)，外资与投信合力加仓。</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 2,991 张 (占量 12.2%)
-[2026-09-29 筹码] 主力机构呈净卖出 (-2,991 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 1,864 张 (占量 6.1%)
+[2026-09-30 筹码] 主力机构呈净买入 (+1,864 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2475.0</t>
+          <t>NT$ 2480.0</t>
         </is>
       </c>
       <c r="K4" s="9" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>24,601 张</t>
+          <t>30,460 张</t>
         </is>
       </c>
     </row>
@@ -818,9 +818,9 @@
       <c r="D5" s="16" t="inlineStr">
         <is>
           <t>开盘: 12350.0
-最高: 12550.0
-最低: 11900.0
-收盘: 12115.0</t>
+最高: 12785.0
+最低: 12055.0
+收盘: 12055.0</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -838,15 +838,15 @@
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>外资: +68 张
-投信: -20 张
-[2026-09-29 官方结算] 外资主力大幅回流 (+68 张)，投信阶段获利减仓 (-20 张)。</t>
+          <t>外资: -24 张
+投信: +6 张
+[2026-09-30 官方结算] 投信内资买超 (+6 张) 逢低承接，外资高档调节 (-24 张)。</t>
         </is>
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 60 张 (占量 14.9%)
-[2026-09-29 筹码] 主力机构呈净买入 (+60 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 6 张 (占量 1.8%)
+[2026-09-30 筹码] 主力机构呈净买入 (+6 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 12115.0</t>
+          <t>NT$ 12055.0</t>
         </is>
       </c>
       <c r="K5" s="18" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="O5" s="16" t="inlineStr">
         <is>
-          <t>402 张</t>
+          <t>340 张</t>
         </is>
       </c>
     </row>
@@ -904,10 +904,10 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>开盘: 4910.0
-最高: 5055.0
-最低: 4870.0
-收盘: 4920.0</t>
+          <t>开盘: 4990.0
+最高: 5030.0
+最低: 4935.0
+收盘: 4935.0</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -925,15 +925,15 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>外资: -283 张
-投信: -188 张
-[2026-09-29 官方结算] 三大法人同步卖超 (-480 张)，短线筹码面临清洗。</t>
+          <t>外资: -162 张
+投信: +163 张
+[2026-09-30 官方结算] 投信内资买超 (+163 张) 逢低承接，外资高档调节 (-162 张)。</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 480 张 (占量 25.5%)
-[2026-09-29 筹码] 主力机构呈净卖出 (-480 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 3 张 (占量 0.2%)
+[2026-09-30 筹码] 主力机构呈净卖出 (-3 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 4920.0</t>
+          <t>NT$ 4935.0</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>1,883 张</t>
+          <t>1,441 张</t>
         </is>
       </c>
     </row>
@@ -991,10 +991,10 @@
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>开盘: 3420.0
-最高: 3460.0
-最低: 3285.0
-收盘: 3400.0</t>
+          <t>开盘: 3455.0
+最高: 3575.0
+最低: 3405.0
+收盘: 3435.0</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -1012,15 +1012,15 @@
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>外资: -453 张
-投信: -514 张
-[2026-09-29 官方结算] 外资与投信偏空调节 (-920 张)，机构筹码阶段获利了结。</t>
+          <t>外资: +84 张
+投信: +184 张
+[2026-09-30 官方结算] 外资与投信联手买超 (+261 张)，内外部机构共振做多。</t>
         </is>
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 920 张 (占量 26.8%)
-[2026-09-29 筹码] 主力机构呈净卖出 (-920 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 261 张 (占量 7.5%)
+[2026-09-30 筹码] 主力机构呈净买入 (+261 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I7" s="15" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="J7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3400.0</t>
+          <t>NT$ 3435.0</t>
         </is>
       </c>
       <c r="K7" s="18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="O7" s="16" t="inlineStr">
         <is>
-          <t>3,430 张</t>
+          <t>3,474 张</t>
         </is>
       </c>
     </row>
@@ -1078,10 +1078,10 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>开盘: 247.0
+          <t>开盘: 253.5
 最高: 254.0
-最低: 247.0
-收盘: 250.5</t>
+最低: 251.5
+收盘: 251.5</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -1099,15 +1099,15 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>外资: +3091 张
-投信: -29 张
-[2026-09-29 官方结算] 外资主力大幅回流 (+3,091 张)，投信阶段获利减仓 (-29 张)。</t>
+          <t>外资: +4632 张
+投信: -236 张
+[2026-09-30 官方结算] 外资主力大幅回流 (+4,632 张)，投信阶段获利减仓 (-236 张)。</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 2,984 张 (占量 9.9%)
-[2026-09-29 筹码] 主力机构呈净买入 (+2,984 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 4,618 张 (占量 17.5%)
+[2026-09-30 筹码] 主力机构呈净买入 (+4,618 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>NT$ 250.5</t>
+          <t>NT$ 251.5</t>
         </is>
       </c>
       <c r="K8" s="9" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="O8" s="7" t="inlineStr">
         <is>
-          <t>30,180 张</t>
+          <t>26,462 张</t>
         </is>
       </c>
     </row>
@@ -1165,10 +1165,10 @@
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>开盘: 1880.0
-最高: 1950.0
-最低: 1810.0
-收盘: 1835.0</t>
+          <t>开盘: 1885.0
+最高: 1930.0
+最低: 1870.0
+收盘: 1890.0</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -1186,15 +1186,15 @@
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
-          <t>外资: -2791 张
-投信: +379 张
-[2026-09-29 官方结算] 投信内资买超 (+379 张) 逢低承接，外资高档调节 (-2,791 张)。</t>
+          <t>外资: +264 张
+投信: +502 张
+[2026-09-30 官方结算] 三大法人全线买超 (+965 张)，外资与投信合力加仓。</t>
         </is>
       </c>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 2,415 张 (占量 18.8%)
-[2026-09-29 筹码] 主力机构呈净卖出 (-2,415 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 965 张 (占量 9.5%)
+[2026-09-30 筹码] 主力机构呈净买入 (+965 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I9" s="15" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="J9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1835.0</t>
+          <t>NT$ 1890.0</t>
         </is>
       </c>
       <c r="K9" s="18" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="O9" s="16" t="inlineStr">
         <is>
-          <t>12,861 张</t>
+          <t>10,190 张</t>
         </is>
       </c>
     </row>
@@ -1252,10 +1252,10 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>开盘: 1845.0
-最高: 1880.0
-最低: 1800.0
-收盘: 1810.0</t>
+          <t>开盘: 1830.0
+最高: 1855.0
+最低: 1770.0
+收盘: 1775.0</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -1273,15 +1273,15 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>外资: -633 张
-投信: -737 张
-[2026-09-29 官方结算] 外资与投信偏空调节 (-1,367 张)，机构筹码阶段获利了结。</t>
+          <t>外资: +1075 张
+投信: -2183 张
+[2026-09-30 官方结算] 外资主力大幅回流 (+1,075 张)，投信阶段获利减仓 (-2,183 张)。</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 1,367 张 (占量 36.3%)
-[2026-09-29 筹码] 主力机构呈净卖出 (-1,367 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 1,021 张 (占量 15.6%)
+[2026-09-30 筹码] 主力机构呈净卖出 (-1,021 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 1810.0</t>
+          <t>NT$ 1775.0</t>
         </is>
       </c>
       <c r="K10" s="9" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>3,765 张</t>
+          <t>6,538 张</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>开盘: 2255.0
-最高: 2325.0
-最低: 2160.0
-收盘: 2185.0</t>
+          <t>开盘: 2245.0
+最高: 2280.0
+最低: 2135.0
+收盘: 2135.0</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
@@ -1360,15 +1360,15 @@
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>外资: -26 张
-投信: -446 张
-[2026-09-29 官方结算] 三大法人同步卖超 (-491 张)，短线筹码面临清洗。</t>
+          <t>外资: +69 张
+投信: -552 张
+[2026-09-30 官方结算] 外资主力大幅回流 (+69 张)，投信阶段获利减仓 (-552 张)。</t>
         </is>
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 491 张 (占量 21.4%)
-[2026-09-29 筹码] 主力机构呈净卖出 (-491 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 441 张 (占量 19.7%)
+[2026-09-30 筹码] 主力机构呈净卖出 (-441 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I11" s="15" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="J11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2185.0</t>
+          <t>NT$ 2135.0</t>
         </is>
       </c>
       <c r="K11" s="18" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="O11" s="16" t="inlineStr">
         <is>
-          <t>2,293 张</t>
+          <t>2,233 张</t>
         </is>
       </c>
     </row>
@@ -1426,10 +1426,10 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>开盘: 685.0
-最高: 693.0
-最低: 678.0
-收盘: 687.0</t>
+          <t>开盘: 716.0
+最高: 723.0
+最低: 703.0
+收盘: 703.0</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -1447,15 +1447,15 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>外资: -724 张
-投信: -927 张
-[2026-09-29 官方结算] 三大法人同步卖超 (-1,691 张)，短线筹码面临清洗。</t>
+          <t>外资: +2964 张
+投信: -401 张
+[2026-09-30 官方结算] 外资主力大幅回流 (+2,964 张)，投信阶段获利减仓 (-401 张)。</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 1,691 张 (占量 12.3%)
-[2026-09-29 筹码] 主力机构呈净卖出 (-1,691 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 2,673 张 (占量 19.3%)
+[2026-09-30 筹码] 主力机构呈净买入 (+2,673 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 687.0</t>
+          <t>NT$ 703.0</t>
         </is>
       </c>
       <c r="K12" s="9" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>13,777 张</t>
+          <t>13,875 张</t>
         </is>
       </c>
     </row>
@@ -1513,10 +1513,10 @@
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>开盘: 5150.0
-最高: 5195.0
-最低: 4890.0
-收盘: 4910.0</t>
+          <t>开盘: 5010.0
+最高: 5100.0
+最低: 4920.0
+收盘: 4920.0</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
@@ -1534,15 +1534,15 @@
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>外资: -4670 张
-投信: -60 张
-[2026-09-29 官方结算] 三大法人同步卖超 (-4,815 张)，短线筹码面临清洗。</t>
+          <t>外资: -987 张
+投信: +154 张
+[2026-09-30 官方结算] 投信内资买超 (+154 张) 逢低承接，外资高档调节 (-987 张)。</t>
         </is>
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 4,815 张 (占量 43.6%)
-[2026-09-29 筹码] 主力机构呈净卖出 (-4,815 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 767 张 (占量 10.1%)
+[2026-09-30 筹码] 主力机构呈净卖出 (-767 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I13" s="15" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="J13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 4910.0</t>
+          <t>NT$ 4920.0</t>
         </is>
       </c>
       <c r="K13" s="18" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="O13" s="16" t="inlineStr">
         <is>
-          <t>11,033 张</t>
+          <t>7,569 张</t>
         </is>
       </c>
     </row>
@@ -1600,10 +1600,10 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>开盘: 7000.0
-最高: 7160.0
-最低: 6850.0
-收盘: 6895.0</t>
+          <t>开盘: 6980.0
+最高: 7080.0
+最低: 6720.0
+收盘: 6800.0</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -1621,15 +1621,15 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>外资: -310 张
-投信: +127 张
-[2026-09-29 官方结算] 投信内资买超 (+127 张) 逢低承接，外资高档调节 (-310 张)。</t>
+          <t>外资: -214 张
+投信: +44 张
+[2026-09-30 官方结算] 投信内资买超 (+44 张) 逢低承接，外资高档调节 (-214 张)。</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 176 张 (占量 11.1%)
-[2026-09-29 筹码] 主力机构呈净卖出 (-176 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 165 张 (占量 13.9%)
+[2026-09-30 筹码] 主力机构呈净卖出 (-165 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>NT$ 6895.0</t>
+          <t>NT$ 6800.0</t>
         </is>
       </c>
       <c r="K14" s="9" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="O14" s="7" t="inlineStr">
         <is>
-          <t>1,591 张</t>
+          <t>1,186 张</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-09-29 21:11:51 | 策略: 3-3-4 分批建仓</t>
+          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-09-30 20:52:31 | 策略: 3-3-4 分批建仓</t>
         </is>
       </c>
     </row>
@@ -1772,22 +1772,22 @@
       </c>
       <c r="C4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2475.0</t>
+          <t>NT$ 2495.0</t>
         </is>
       </c>
       <c r="D4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2495.0</t>
+          <t>NT$ 2510.0</t>
         </is>
       </c>
       <c r="E4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2475.0</t>
+          <t>NT$ 2480.0</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2475.0</t>
+          <t>NT$ 2480.0</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
@@ -1824,17 +1824,17 @@
       </c>
       <c r="D5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 12550.0</t>
+          <t>NT$ 12785.0</t>
         </is>
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 11900.0</t>
+          <t>NT$ 12055.0</t>
         </is>
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 12115.0</t>
+          <t>NT$ 12055.0</t>
         </is>
       </c>
       <c r="G5" s="29" t="inlineStr">
@@ -1866,22 +1866,22 @@
       </c>
       <c r="C6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 4910.0</t>
+          <t>NT$ 4990.0</t>
         </is>
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5055.0</t>
+          <t>NT$ 5030.0</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 4870.0</t>
+          <t>NT$ 4935.0</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 4920.0</t>
+          <t>NT$ 4935.0</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
@@ -1913,22 +1913,22 @@
       </c>
       <c r="C7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3420.0</t>
+          <t>NT$ 3455.0</t>
         </is>
       </c>
       <c r="D7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3460.0</t>
+          <t>NT$ 3575.0</t>
         </is>
       </c>
       <c r="E7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3285.0</t>
+          <t>NT$ 3405.0</t>
         </is>
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3400.0</t>
+          <t>NT$ 3435.0</t>
         </is>
       </c>
       <c r="G7" s="29" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 247.0</t>
+          <t>NT$ 253.5</t>
         </is>
       </c>
       <c r="D8" s="24" t="inlineStr">
@@ -1970,12 +1970,12 @@
       </c>
       <c r="E8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 247.0</t>
+          <t>NT$ 251.5</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>NT$ 250.5</t>
+          <t>NT$ 251.5</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
@@ -2007,22 +2007,22 @@
       </c>
       <c r="C9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1880.0</t>
+          <t>NT$ 1885.0</t>
         </is>
       </c>
       <c r="D9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1950.0</t>
+          <t>NT$ 1930.0</t>
         </is>
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1810.0</t>
+          <t>NT$ 1870.0</t>
         </is>
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1835.0</t>
+          <t>NT$ 1890.0</t>
         </is>
       </c>
       <c r="G9" s="29" t="inlineStr">
@@ -2054,22 +2054,22 @@
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1845.0</t>
+          <t>NT$ 1830.0</t>
         </is>
       </c>
       <c r="D10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1880.0</t>
+          <t>NT$ 1855.0</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1800.0</t>
+          <t>NT$ 1770.0</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 1810.0</t>
+          <t>NT$ 1775.0</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
@@ -2101,22 +2101,22 @@
       </c>
       <c r="C11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2255.0</t>
+          <t>NT$ 2245.0</t>
         </is>
       </c>
       <c r="D11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2325.0</t>
+          <t>NT$ 2280.0</t>
         </is>
       </c>
       <c r="E11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2160.0</t>
+          <t>NT$ 2135.0</t>
         </is>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2185.0</t>
+          <t>NT$ 2135.0</t>
         </is>
       </c>
       <c r="G11" s="29" t="inlineStr">
@@ -2148,22 +2148,22 @@
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 685.0</t>
+          <t>NT$ 716.0</t>
         </is>
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 693.0</t>
+          <t>NT$ 723.0</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 678.0</t>
+          <t>NT$ 703.0</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 687.0</t>
+          <t>NT$ 703.0</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
@@ -2195,22 +2195,22 @@
       </c>
       <c r="C13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 5150.0</t>
+          <t>NT$ 5010.0</t>
         </is>
       </c>
       <c r="D13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 5195.0</t>
+          <t>NT$ 5100.0</t>
         </is>
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4890.0</t>
+          <t>NT$ 4920.0</t>
         </is>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 4910.0</t>
+          <t>NT$ 4920.0</t>
         </is>
       </c>
       <c r="G13" s="29" t="inlineStr">
@@ -2242,22 +2242,22 @@
       </c>
       <c r="C14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 7000.0</t>
+          <t>NT$ 6980.0</t>
         </is>
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 7160.0</t>
+          <t>NT$ 7080.0</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 6850.0</t>
+          <t>NT$ 6720.0</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>NT$ 6895.0</t>
+          <t>NT$ 6800.0</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">

--- a/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
+++ b/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
@@ -631,7 +631,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>定盘时间: 2026-09-30 20:52:31 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
+          <t>定盘时间: 2026-10-01 21:40:25 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
         </is>
       </c>
     </row>
@@ -730,10 +730,10 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>开盘: 2495.0
+          <t>开盘: 2490.0
 最高: 2510.0
-最低: 2480.0
-收盘: 2480.0</t>
+最低: 2485.0
+收盘: 2510.0</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -751,15 +751,15 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>外资: +702 张
-投信: +761 张
-[2026-09-30 官方结算] 三大法人全线买超 (+1,864 张)，外资与投信合力加仓。</t>
+          <t>外资: +3090 张
+投信: +596 张
+[2026-10-01 官方结算] 三大法人全线买超 (+4,289 张)，外资与投信合力加仓。</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 1,864 张 (占量 6.1%)
-[2026-09-30 筹码] 主力机构呈净买入 (+1,864 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 4,289 张 (占量 23.1%)
+[2026-10-01 筹码] 主力机构呈净买入 (+4,289 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2480.0</t>
+          <t>NT$ 2510.0</t>
         </is>
       </c>
       <c r="K4" s="9" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>30,460 张</t>
+          <t>18,539 张</t>
         </is>
       </c>
     </row>
@@ -817,10 +817,10 @@
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>开盘: 12350.0
-最高: 12785.0
-最低: 12055.0
-收盘: 12055.0</t>
+          <t>开盘: 12270.0
+最高: 12270.0
+最低: 11760.0
+收盘: 11835.0</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -838,15 +838,15 @@
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>外资: -24 张
-投信: +6 张
-[2026-09-30 官方结算] 投信内资买超 (+6 张) 逢低承接，外资高档调节 (-24 张)。</t>
+          <t>外资: +23 张
+投信: -29 张
+[2026-10-01 官方结算] 外资主力大幅回流 (+23 张)，投信阶段获利减仓 (-29 张)。</t>
         </is>
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 6 张 (占量 1.8%)
-[2026-09-30 筹码] 主力机构呈净买入 (+6 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 6 张 (占量 2.0%)
+[2026-10-01 筹码] 主力机构呈净卖出 (-6 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 12055.0</t>
+          <t>NT$ 11835.0</t>
         </is>
       </c>
       <c r="K5" s="18" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="O5" s="16" t="inlineStr">
         <is>
-          <t>340 张</t>
+          <t>293 张</t>
         </is>
       </c>
     </row>
@@ -904,10 +904,10 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>开盘: 4990.0
-最高: 5030.0
-最低: 4935.0
-收盘: 4935.0</t>
+          <t>开盘: 4950.0
+最高: 4975.0
+最低: 4855.0
+收盘: 4975.0</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -925,15 +925,15 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>外资: -162 张
-投信: +163 张
-[2026-09-30 官方结算] 投信内资买超 (+163 张) 逢低承接，外资高档调节 (-162 张)。</t>
+          <t>外资: -202 张
+投信: -66 张
+[2026-10-01 官方结算] 外资与投信偏空调节 (-260 张)，机构筹码阶段获利了结。</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 3 张 (占量 0.2%)
-[2026-09-30 筹码] 主力机构呈净卖出 (-3 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 260 张 (占量 21.3%)
+[2026-10-01 筹码] 主力机构呈净卖出 (-260 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 4935.0</t>
+          <t>NT$ 4975.0</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>1,441 张</t>
+          <t>1,218 张</t>
         </is>
       </c>
     </row>
@@ -991,10 +991,10 @@
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>开盘: 3455.0
-最高: 3575.0
-最低: 3405.0
-收盘: 3435.0</t>
+          <t>开盘: 3435.0
+最高: 3520.0
+最低: 3300.0
+收盘: 3510.0</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -1012,15 +1012,15 @@
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>外资: +84 张
-投信: +184 张
-[2026-09-30 官方结算] 外资与投信联手买超 (+261 张)，内外部机构共振做多。</t>
+          <t>外资: -6 张
+投信: -83 张
+[2026-10-01 官方结算] 外资与投信偏空调节 (-48 张)，机构筹码阶段获利了结。</t>
         </is>
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 261 张 (占量 7.5%)
-[2026-09-30 筹码] 主力机构呈净买入 (+261 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 48 张 (占量 1.5%)
+[2026-10-01 筹码] 主力机构呈净卖出 (-48 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I7" s="15" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="J7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3435.0</t>
+          <t>NT$ 3510.0</t>
         </is>
       </c>
       <c r="K7" s="18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="O7" s="16" t="inlineStr">
         <is>
-          <t>3,474 张</t>
+          <t>3,161 张</t>
         </is>
       </c>
     </row>
@@ -1078,10 +1078,10 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>开盘: 253.5
+          <t>开盘: 253.0
 最高: 254.0
-最低: 251.5
-收盘: 251.5</t>
+最低: 250.5
+收盘: 254.0</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -1099,15 +1099,15 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>外资: +4632 张
-投信: -236 张
-[2026-09-30 官方结算] 外资主力大幅回流 (+4,632 张)，投信阶段获利减仓 (-236 张)。</t>
+          <t>外资: +5092 张
+投信: +203 张
+[2026-10-01 官方结算] 三大法人全线买超 (+5,653 张)，外资与投信合力加仓。</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 4,618 张 (占量 17.5%)
-[2026-09-30 筹码] 主力机构呈净买入 (+4,618 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 5,653 张 (占量 21.7%)
+[2026-10-01 筹码] 主力机构呈净买入 (+5,653 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>NT$ 251.5</t>
+          <t>NT$ 254.0</t>
         </is>
       </c>
       <c r="K8" s="9" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="O8" s="7" t="inlineStr">
         <is>
-          <t>26,462 张</t>
+          <t>26,081 张</t>
         </is>
       </c>
     </row>
@@ -1165,10 +1165,10 @@
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>开盘: 1885.0
-最高: 1930.0
-最低: 1870.0
-收盘: 1890.0</t>
+          <t>开盘: 1925.0
+最高: 1935.0
+最低: 1860.0
+收盘: 1905.0</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -1186,15 +1186,15 @@
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
-          <t>外资: +264 张
-投信: +502 张
-[2026-09-30 官方结算] 三大法人全线买超 (+965 张)，外资与投信合力加仓。</t>
+          <t>外资: -726 张
+投信: +117 张
+[2026-10-01 官方结算] 投信内资买超 (+117 张) 逢低承接，外资高档调节 (-726 张)。</t>
         </is>
       </c>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 965 张 (占量 9.5%)
-[2026-09-30 筹码] 主力机构呈净买入 (+965 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 629 张 (占量 11.1%)
+[2026-10-01 筹码] 主力机构呈净卖出 (-629 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I9" s="15" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="J9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1890.0</t>
+          <t>NT$ 1905.0</t>
         </is>
       </c>
       <c r="K9" s="18" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="O9" s="16" t="inlineStr">
         <is>
-          <t>10,190 张</t>
+          <t>5,664 张</t>
         </is>
       </c>
     </row>
@@ -1252,10 +1252,10 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>开盘: 1830.0
-最高: 1855.0
-最低: 1770.0
-收盘: 1775.0</t>
+          <t>开盘: 1795.0
+最高: 1910.0
+最低: 1785.0
+收盘: 1900.0</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -1273,15 +1273,15 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>外资: +1075 张
-投信: -2183 张
-[2026-09-30 官方结算] 外资主力大幅回流 (+1,075 张)，投信阶段获利减仓 (-2,183 张)。</t>
+          <t>外资: +486 张
+投信: -488 张
+[2026-10-01 官方结算] 外资主力大幅回流 (+486 张)，投信阶段获利减仓 (-488 张)。</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 1,021 张 (占量 15.6%)
-[2026-09-30 筹码] 主力机构呈净卖出 (-1,021 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 41 张 (占量 0.7%)
+[2026-10-01 筹码] 主力机构呈净买入 (+41 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 1775.0</t>
+          <t>NT$ 1900.0</t>
         </is>
       </c>
       <c r="K10" s="9" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>6,538 张</t>
+          <t>5,554 张</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>开盘: 2245.0
-最高: 2280.0
-最低: 2135.0
-收盘: 2135.0</t>
+          <t>开盘: 2125.0
+最高: 2150.0
+最低: 2025.0
+收盘: 2080.0</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
@@ -1360,15 +1360,15 @@
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>外资: +69 张
-投信: -552 张
-[2026-09-30 官方结算] 外资主力大幅回流 (+69 张)，投信阶段获利减仓 (-552 张)。</t>
+          <t>外资: +307 张
+投信: -1192 张
+[2026-10-01 官方结算] 外资主力大幅回流 (+307 张)，投信阶段获利减仓 (-1,192 张)。</t>
         </is>
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 441 张 (占量 19.7%)
-[2026-09-30 筹码] 主力机构呈净卖出 (-441 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 808 张 (占量 33.5%)
+[2026-10-01 筹码] 主力机构呈净卖出 (-808 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I11" s="15" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="J11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2135.0</t>
+          <t>NT$ 2080.0</t>
         </is>
       </c>
       <c r="K11" s="18" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="O11" s="16" t="inlineStr">
         <is>
-          <t>2,233 张</t>
+          <t>2,414 张</t>
         </is>
       </c>
     </row>
@@ -1426,10 +1426,10 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>开盘: 716.0
-最高: 723.0
-最低: 703.0
-收盘: 703.0</t>
+          <t>开盘: 700.0
+最高: 710.0
+最低: 693.0
+收盘: 710.0</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -1447,15 +1447,15 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>外资: +2964 张
-投信: -401 张
-[2026-09-30 官方结算] 外资主力大幅回流 (+2,964 张)，投信阶段获利减仓 (-401 张)。</t>
+          <t>外资: +457 张
+投信: +227 张
+[2026-10-01 官方结算] 三大法人全线买超 (+741 张)，外资与投信合力加仓。</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 2,673 张 (占量 19.3%)
-[2026-09-30 筹码] 主力机构呈净买入 (+2,673 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 741 张 (占量 8.8%)
+[2026-10-01 筹码] 主力机构呈净买入 (+741 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 703.0</t>
+          <t>NT$ 710.0</t>
         </is>
       </c>
       <c r="K12" s="9" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>13,875 张</t>
+          <t>8,457 张</t>
         </is>
       </c>
     </row>
@@ -1513,10 +1513,10 @@
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>开盘: 5010.0
-最高: 5100.0
-最低: 4920.0
-收盘: 4920.0</t>
+          <t>开盘: 4875.0
+最高: 4980.0
+最低: 4875.0
+收盘: 4980.0</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
@@ -1534,15 +1534,15 @@
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>外资: -987 张
-投信: +154 张
-[2026-09-30 官方结算] 投信内资买超 (+154 张) 逢低承接，外资高档调节 (-987 张)。</t>
+          <t>外资: -572 张
+投信: +33 张
+[2026-10-01 官方结算] 投信内资买超 (+33 张) 逢低承接，外资高档调节 (-572 张)。</t>
         </is>
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 767 张 (占量 10.1%)
-[2026-09-30 筹码] 主力机构呈净卖出 (-767 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 465 张 (占量 12.0%)
+[2026-10-01 筹码] 主力机构呈净卖出 (-465 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I13" s="15" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="J13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 4920.0</t>
+          <t>NT$ 4980.0</t>
         </is>
       </c>
       <c r="K13" s="18" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="O13" s="16" t="inlineStr">
         <is>
-          <t>7,569 张</t>
+          <t>3,868 张</t>
         </is>
       </c>
     </row>
@@ -1600,10 +1600,10 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>开盘: 6980.0
-最高: 7080.0
-最低: 6720.0
-收盘: 6800.0</t>
+          <t>开盘: 6720.0
+最高: 6895.0
+最低: 6665.0
+收盘: 6875.0</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -1621,15 +1621,15 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>外资: -214 张
-投信: +44 张
-[2026-09-30 官方结算] 投信内资买超 (+44 张) 逢低承接，外资高档调节 (-214 张)。</t>
+          <t>外资: -26 张
+投信: +42 张
+[2026-10-01 官方结算] 投信内资买超 (+42 张) 逢低承接，外资高档调节 (-26 张)。</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 165 张 (占量 13.9%)
-[2026-09-30 筹码] 主力机构呈净卖出 (-165 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 19 张 (占量 3.3%)
+[2026-10-01 筹码] 主力机构呈净买入 (+19 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>NT$ 6800.0</t>
+          <t>NT$ 6875.0</t>
         </is>
       </c>
       <c r="K14" s="9" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="O14" s="7" t="inlineStr">
         <is>
-          <t>1,186 张</t>
+          <t>578 张</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-09-30 20:52:31 | 策略: 3-3-4 分批建仓</t>
+          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-01 21:40:25 | 策略: 3-3-4 分批建仓</t>
         </is>
       </c>
     </row>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="C4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2495.0</t>
+          <t>NT$ 2490.0</t>
         </is>
       </c>
       <c r="D4" s="24" t="inlineStr">
@@ -1782,12 +1782,12 @@
       </c>
       <c r="E4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2480.0</t>
+          <t>NT$ 2485.0</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2480.0</t>
+          <t>NT$ 2510.0</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
@@ -1819,22 +1819,22 @@
       </c>
       <c r="C5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 12350.0</t>
+          <t>NT$ 12270.0</t>
         </is>
       </c>
       <c r="D5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 12785.0</t>
+          <t>NT$ 12270.0</t>
         </is>
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 12055.0</t>
+          <t>NT$ 11760.0</t>
         </is>
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 12055.0</t>
+          <t>NT$ 11835.0</t>
         </is>
       </c>
       <c r="G5" s="29" t="inlineStr">
@@ -1866,22 +1866,22 @@
       </c>
       <c r="C6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 4990.0</t>
+          <t>NT$ 4950.0</t>
         </is>
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5030.0</t>
+          <t>NT$ 4975.0</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 4935.0</t>
+          <t>NT$ 4855.0</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 4935.0</t>
+          <t>NT$ 4975.0</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
@@ -1913,22 +1913,22 @@
       </c>
       <c r="C7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3455.0</t>
+          <t>NT$ 3435.0</t>
         </is>
       </c>
       <c r="D7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3575.0</t>
+          <t>NT$ 3520.0</t>
         </is>
       </c>
       <c r="E7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3405.0</t>
+          <t>NT$ 3300.0</t>
         </is>
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3435.0</t>
+          <t>NT$ 3510.0</t>
         </is>
       </c>
       <c r="G7" s="29" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 253.5</t>
+          <t>NT$ 253.0</t>
         </is>
       </c>
       <c r="D8" s="24" t="inlineStr">
@@ -1970,12 +1970,12 @@
       </c>
       <c r="E8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 251.5</t>
+          <t>NT$ 250.5</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>NT$ 251.5</t>
+          <t>NT$ 254.0</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
@@ -2007,22 +2007,22 @@
       </c>
       <c r="C9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1885.0</t>
+          <t>NT$ 1925.0</t>
         </is>
       </c>
       <c r="D9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1930.0</t>
+          <t>NT$ 1935.0</t>
         </is>
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1870.0</t>
+          <t>NT$ 1860.0</t>
         </is>
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1890.0</t>
+          <t>NT$ 1905.0</t>
         </is>
       </c>
       <c r="G9" s="29" t="inlineStr">
@@ -2054,22 +2054,22 @@
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1830.0</t>
+          <t>NT$ 1795.0</t>
         </is>
       </c>
       <c r="D10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1855.0</t>
+          <t>NT$ 1910.0</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1770.0</t>
+          <t>NT$ 1785.0</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 1775.0</t>
+          <t>NT$ 1900.0</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
@@ -2101,22 +2101,22 @@
       </c>
       <c r="C11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2245.0</t>
+          <t>NT$ 2125.0</t>
         </is>
       </c>
       <c r="D11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2280.0</t>
+          <t>NT$ 2150.0</t>
         </is>
       </c>
       <c r="E11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2135.0</t>
+          <t>NT$ 2025.0</t>
         </is>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2135.0</t>
+          <t>NT$ 2080.0</t>
         </is>
       </c>
       <c r="G11" s="29" t="inlineStr">
@@ -2148,22 +2148,22 @@
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 716.0</t>
+          <t>NT$ 700.0</t>
         </is>
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 723.0</t>
+          <t>NT$ 710.0</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 703.0</t>
+          <t>NT$ 693.0</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 703.0</t>
+          <t>NT$ 710.0</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
@@ -2195,22 +2195,22 @@
       </c>
       <c r="C13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 5010.0</t>
+          <t>NT$ 4875.0</t>
         </is>
       </c>
       <c r="D13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 5100.0</t>
+          <t>NT$ 4980.0</t>
         </is>
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4920.0</t>
+          <t>NT$ 4875.0</t>
         </is>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 4920.0</t>
+          <t>NT$ 4980.0</t>
         </is>
       </c>
       <c r="G13" s="29" t="inlineStr">
@@ -2242,22 +2242,22 @@
       </c>
       <c r="C14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 6980.0</t>
+          <t>NT$ 6720.0</t>
         </is>
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 7080.0</t>
+          <t>NT$ 6895.0</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 6720.0</t>
+          <t>NT$ 6665.0</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>NT$ 6800.0</t>
+          <t>NT$ 6875.0</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">

--- a/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
+++ b/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
@@ -631,7 +631,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>定盘时间: 2026-10-01 21:40:25 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
+          <t>定盘时间: 2026-10-02 20:57:42 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
         </is>
       </c>
     </row>
@@ -730,10 +730,10 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>开盘: 2490.0
-最高: 2510.0
-最低: 2485.0
-收盘: 2510.0</t>
+          <t>开盘: 2505.0
+最高: 2515.0
+最低: 2495.0
+收盘: 2500.0</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -751,15 +751,15 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>外资: +3090 张
-投信: +596 张
-[2026-10-01 官方结算] 三大法人全线买超 (+4,289 张)，外资与投信合力加仓。</t>
+          <t>外资: -5914 张
+投信: +253 张
+[2026-10-02 官方结算] 投信内资买超 (+253 张) 逢低承接，外资高档调节 (-5,914 张)。</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 4,289 张 (占量 23.1%)
-[2026-10-01 筹码] 主力机构呈净买入 (+4,289 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 5,344 张 (占量 38.4%)
+[2026-10-02 筹码] 主力机构呈净卖出 (-5,344 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2510.0</t>
+          <t>NT$ 2500.0</t>
         </is>
       </c>
       <c r="K4" s="9" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>18,539 张</t>
+          <t>13,902 张</t>
         </is>
       </c>
     </row>
@@ -817,10 +817,10 @@
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>开盘: 12270.0
-最高: 12270.0
-最低: 11760.0
-收盘: 11835.0</t>
+          <t>开盘: 12000.0
+最高: 12295.0
+最低: 11700.0
+收盘: 12145.0</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -838,15 +838,15 @@
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>外资: +23 张
-投信: -29 张
-[2026-10-01 官方结算] 外资主力大幅回流 (+23 张)，投信阶段获利减仓 (-29 张)。</t>
+          <t>外资: +0 张
+投信: +24 张
+[2026-10-02 官方结算] 三大法人合计净买超 38 张，多空资金处于换手态势。</t>
         </is>
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 6 张 (占量 2.0%)
-[2026-10-01 筹码] 主力机构呈净卖出 (-6 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 38 张 (占量 8.1%)
+[2026-10-02 筹码] 主力机构呈净买入 (+38 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 11835.0</t>
+          <t>NT$ 12145.0</t>
         </is>
       </c>
       <c r="K5" s="18" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="O5" s="16" t="inlineStr">
         <is>
-          <t>293 张</t>
+          <t>472 张</t>
         </is>
       </c>
     </row>
@@ -904,10 +904,10 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>开盘: 4950.0
-最高: 4975.0
-最低: 4855.0
-收盘: 4975.0</t>
+          <t>开盘: 5040.0
+最高: 5190.0
+最低: 4975.0
+收盘: 5185.0</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -925,15 +925,15 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>外资: -202 张
-投信: -66 张
-[2026-10-01 官方结算] 外资与投信偏空调节 (-260 张)，机构筹码阶段获利了结。</t>
+          <t>外资: +2 张
+投信: +133 张
+[2026-10-02 官方结算] 三大法人全线买超 (+168 张)，外资与投信合力加仓。</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 260 张 (占量 21.3%)
-[2026-10-01 筹码] 主力机构呈净卖出 (-260 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 168 张 (占量 7.8%)
+[2026-10-02 筹码] 主力机构呈净买入 (+168 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 4975.0</t>
+          <t>NT$ 5185.0</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>1,218 张</t>
+          <t>2,159 张</t>
         </is>
       </c>
     </row>
@@ -991,10 +991,10 @@
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>开盘: 3435.0
-最高: 3520.0
-最低: 3300.0
-收盘: 3510.0</t>
+          <t>开盘: 3570.0
+最高: 3570.0
+最低: 3385.0
+收盘: 3440.0</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -1012,15 +1012,15 @@
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>外资: -6 张
-投信: -83 张
-[2026-10-01 官方结算] 外资与投信偏空调节 (-48 张)，机构筹码阶段获利了结。</t>
+          <t>外资: -342 张
+投信: -276 张
+[2026-10-02 官方结算] 外资与投信偏空调节 (-589 张)，机构筹码阶段获利了结。</t>
         </is>
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 48 张 (占量 1.5%)
-[2026-10-01 筹码] 主力机构呈净卖出 (-48 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 589 张 (占量 18.8%)
+[2026-10-02 筹码] 主力机构呈净卖出 (-589 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I7" s="15" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="J7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3510.0</t>
+          <t>NT$ 3440.0</t>
         </is>
       </c>
       <c r="K7" s="18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="O7" s="16" t="inlineStr">
         <is>
-          <t>3,161 张</t>
+          <t>3,130 张</t>
         </is>
       </c>
     </row>
@@ -1079,9 +1079,9 @@
       <c r="D8" s="7" t="inlineStr">
         <is>
           <t>开盘: 253.0
-最高: 254.0
+最高: 253.0
 最低: 250.5
-收盘: 254.0</t>
+收盘: 251.0</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -1099,15 +1099,15 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>外资: +5092 张
-投信: +203 张
-[2026-10-01 官方结算] 三大法人全线买超 (+5,653 张)，外资与投信合力加仓。</t>
+          <t>外资: -15147 张
+投信: +223 张
+[2026-10-02 官方结算] 投信内资买超 (+223 张) 逢低承接，外资高档调节 (-15,147 张)。</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 5,653 张 (占量 21.7%)
-[2026-10-01 筹码] 主力机构呈净买入 (+5,653 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 14,908 张 (占量 52.5%)
+[2026-10-02 筹码] 主力机构呈净卖出 (-14,908 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>NT$ 254.0</t>
+          <t>NT$ 251.0</t>
         </is>
       </c>
       <c r="K8" s="9" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="O8" s="7" t="inlineStr">
         <is>
-          <t>26,081 张</t>
+          <t>28,422 张</t>
         </is>
       </c>
     </row>
@@ -1165,10 +1165,10 @@
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>开盘: 1925.0
-最高: 1935.0
-最低: 1860.0
-收盘: 1905.0</t>
+          <t>开盘: 1895.0
+最高: 1915.0
+最低: 1880.0
+收盘: 1885.0</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -1186,15 +1186,15 @@
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
-          <t>外资: -726 张
-投信: +117 张
-[2026-10-01 官方结算] 投信内资买超 (+117 张) 逢低承接，外资高档调节 (-726 张)。</t>
+          <t>外资: -1541 张
+投信: +84 张
+[2026-10-02 官方结算] 投信内资买超 (+84 张) 逢低承接，外资高档调节 (-1,541 张)。</t>
         </is>
       </c>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 629 张 (占量 11.1%)
-[2026-10-01 筹码] 主力机构呈净卖出 (-629 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 1,436 张 (占量 26.0%)
+[2026-10-02 筹码] 主力机构呈净卖出 (-1,436 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I9" s="15" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="J9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1905.0</t>
+          <t>NT$ 1885.0</t>
         </is>
       </c>
       <c r="K9" s="18" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="O9" s="16" t="inlineStr">
         <is>
-          <t>5,664 张</t>
+          <t>5,519 张</t>
         </is>
       </c>
     </row>
@@ -1252,10 +1252,10 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>开盘: 1795.0
-最高: 1910.0
-最低: 1785.0
-收盘: 1900.0</t>
+          <t>开盘: 1955.0
+最高: 1980.0
+最低: 1920.0
+收盘: 1965.0</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -1273,15 +1273,15 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>外资: +486 张
-投信: -488 张
-[2026-10-01 官方结算] 外资主力大幅回流 (+486 张)，投信阶段获利减仓 (-488 张)。</t>
+          <t>外资: -413 张
+投信: +110 张
+[2026-10-02 官方结算] 投信内资买超 (+110 张) 逢低承接，外资高档调节 (-413 张)。</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 41 张 (占量 0.7%)
-[2026-10-01 筹码] 主力机构呈净买入 (+41 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 328 张 (占量 6.6%)
+[2026-10-02 筹码] 主力机构呈净卖出 (-328 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 1900.0</t>
+          <t>NT$ 1965.0</t>
         </is>
       </c>
       <c r="K10" s="9" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>5,554 张</t>
+          <t>4,993 张</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>开盘: 2125.0
-最高: 2150.0
-最低: 2025.0
-收盘: 2080.0</t>
+          <t>开盘: 2145.0
+最高: 2225.0
+最低: 2135.0
+收盘: 2190.0</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
@@ -1360,15 +1360,15 @@
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>外资: +307 张
-投信: -1192 张
-[2026-10-01 官方结算] 外资主力大幅回流 (+307 张)，投信阶段获利减仓 (-1,192 张)。</t>
+          <t>外资: +1006 张
+投信: -458 张
+[2026-10-02 官方结算] 外资主力大幅回流 (+1,006 张)，投信阶段获利减仓 (-458 张)。</t>
         </is>
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 808 张 (占量 33.5%)
-[2026-10-01 筹码] 主力机构呈净卖出 (-808 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 564 张 (占量 17.9%)
+[2026-10-02 筹码] 主力机构呈净买入 (+564 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I11" s="15" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="J11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2080.0</t>
+          <t>NT$ 2190.0</t>
         </is>
       </c>
       <c r="K11" s="18" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="O11" s="16" t="inlineStr">
         <is>
-          <t>2,414 张</t>
+          <t>3,149 张</t>
         </is>
       </c>
     </row>
@@ -1426,10 +1426,10 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>开盘: 700.0
-最高: 710.0
-最低: 693.0
-收盘: 710.0</t>
+          <t>开盘: 711.0
+最高: 722.0
+最低: 704.0
+收盘: 713.0</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -1447,15 +1447,15 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>外资: +457 张
-投信: +227 张
-[2026-10-01 官方结算] 三大法人全线买超 (+741 张)，外资与投信合力加仓。</t>
+          <t>外资: +3128 张
+投信: -2506 张
+[2026-10-02 官方结算] 外资主力大幅回流 (+3,128 张)，投信阶段获利减仓 (-2,506 张)。</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 741 张 (占量 8.8%)
-[2026-10-01 筹码] 主力机构呈净买入 (+741 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 775 张 (占量 7.0%)
+[2026-10-02 筹码] 主力机构呈净买入 (+775 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 710.0</t>
+          <t>NT$ 713.0</t>
         </is>
       </c>
       <c r="K12" s="9" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>8,457 张</t>
+          <t>11,136 张</t>
         </is>
       </c>
     </row>
@@ -1513,10 +1513,10 @@
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>开盘: 4875.0
-最高: 4980.0
-最低: 4875.0
-收盘: 4980.0</t>
+          <t>开盘: 4950.0
+最高: 4970.0
+最低: 4880.0
+收盘: 4950.0</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
@@ -1534,15 +1534,15 @@
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>外资: -572 张
-投信: +33 张
-[2026-10-01 官方结算] 投信内资买超 (+33 张) 逢低承接，外资高档调节 (-572 张)。</t>
+          <t>外资: -1472 张
+投信: +224 张
+[2026-10-02 官方结算] 投信内资买超 (+224 张) 逢低承接，外资高档调节 (-1,472 张)。</t>
         </is>
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 465 张 (占量 12.0%)
-[2026-10-01 筹码] 主力机构呈净卖出 (-465 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 1,253 张 (占量 32.6%)
+[2026-10-02 筹码] 主力机构呈净卖出 (-1,253 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I13" s="15" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="J13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 4980.0</t>
+          <t>NT$ 4950.0</t>
         </is>
       </c>
       <c r="K13" s="18" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="O13" s="16" t="inlineStr">
         <is>
-          <t>3,868 张</t>
+          <t>3,839 张</t>
         </is>
       </c>
     </row>
@@ -1600,10 +1600,10 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>开盘: 6720.0
-最高: 6895.0
-最低: 6665.0
-收盘: 6875.0</t>
+          <t>开盘: 6790.0
+最高: 7065.0
+最低: 6760.0
+收盘: 6800.0</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -1621,15 +1621,15 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>外资: -26 张
-投信: +42 张
-[2026-10-01 官方结算] 投信内资买超 (+42 张) 逢低承接，外资高档调节 (-26 张)。</t>
+          <t>外资: -220 张
+投信: +63 张
+[2026-10-02 官方结算] 投信内资买超 (+63 张) 逢低承接，外资高档调节 (-220 张)。</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 19 张 (占量 3.3%)
-[2026-10-01 筹码] 主力机构呈净买入 (+19 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 155 张 (占量 15.1%)
+[2026-10-02 筹码] 主力机构呈净卖出 (-155 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>NT$ 6875.0</t>
+          <t>NT$ 6800.0</t>
         </is>
       </c>
       <c r="K14" s="9" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="O14" s="7" t="inlineStr">
         <is>
-          <t>578 张</t>
+          <t>1,025 张</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-01 21:40:25 | 策略: 3-3-4 分批建仓</t>
+          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-02 20:57:42 | 策略: 3-3-4 分批建仓</t>
         </is>
       </c>
     </row>
@@ -1772,22 +1772,22 @@
       </c>
       <c r="C4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2490.0</t>
+          <t>NT$ 2505.0</t>
         </is>
       </c>
       <c r="D4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2510.0</t>
+          <t>NT$ 2515.0</t>
         </is>
       </c>
       <c r="E4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2485.0</t>
+          <t>NT$ 2495.0</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2510.0</t>
+          <t>NT$ 2500.0</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
@@ -1819,22 +1819,22 @@
       </c>
       <c r="C5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 12270.0</t>
+          <t>NT$ 12000.0</t>
         </is>
       </c>
       <c r="D5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 12270.0</t>
+          <t>NT$ 12295.0</t>
         </is>
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 11760.0</t>
+          <t>NT$ 11700.0</t>
         </is>
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 11835.0</t>
+          <t>NT$ 12145.0</t>
         </is>
       </c>
       <c r="G5" s="29" t="inlineStr">
@@ -1866,22 +1866,22 @@
       </c>
       <c r="C6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 4950.0</t>
+          <t>NT$ 5040.0</t>
         </is>
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
+          <t>NT$ 5190.0</t>
+        </is>
+      </c>
+      <c r="E6" s="24" t="inlineStr">
+        <is>
           <t>NT$ 4975.0</t>
         </is>
       </c>
-      <c r="E6" s="24" t="inlineStr">
-        <is>
-          <t>NT$ 4855.0</t>
-        </is>
-      </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 4975.0</t>
+          <t>NT$ 5185.0</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
@@ -1913,22 +1913,22 @@
       </c>
       <c r="C7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3435.0</t>
+          <t>NT$ 3570.0</t>
         </is>
       </c>
       <c r="D7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3520.0</t>
+          <t>NT$ 3570.0</t>
         </is>
       </c>
       <c r="E7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3300.0</t>
+          <t>NT$ 3385.0</t>
         </is>
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3510.0</t>
+          <t>NT$ 3440.0</t>
         </is>
       </c>
       <c r="G7" s="29" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 254.0</t>
+          <t>NT$ 253.0</t>
         </is>
       </c>
       <c r="E8" s="24" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>NT$ 254.0</t>
+          <t>NT$ 251.0</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
@@ -2007,22 +2007,22 @@
       </c>
       <c r="C9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1925.0</t>
+          <t>NT$ 1895.0</t>
         </is>
       </c>
       <c r="D9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1935.0</t>
+          <t>NT$ 1915.0</t>
         </is>
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1860.0</t>
+          <t>NT$ 1880.0</t>
         </is>
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1905.0</t>
+          <t>NT$ 1885.0</t>
         </is>
       </c>
       <c r="G9" s="29" t="inlineStr">
@@ -2054,22 +2054,22 @@
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1795.0</t>
+          <t>NT$ 1955.0</t>
         </is>
       </c>
       <c r="D10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1910.0</t>
+          <t>NT$ 1980.0</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1785.0</t>
+          <t>NT$ 1920.0</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 1900.0</t>
+          <t>NT$ 1965.0</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
@@ -2101,22 +2101,22 @@
       </c>
       <c r="C11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2125.0</t>
+          <t>NT$ 2145.0</t>
         </is>
       </c>
       <c r="D11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2150.0</t>
+          <t>NT$ 2225.0</t>
         </is>
       </c>
       <c r="E11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2025.0</t>
+          <t>NT$ 2135.0</t>
         </is>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2080.0</t>
+          <t>NT$ 2190.0</t>
         </is>
       </c>
       <c r="G11" s="29" t="inlineStr">
@@ -2148,22 +2148,22 @@
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 700.0</t>
+          <t>NT$ 711.0</t>
         </is>
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 710.0</t>
+          <t>NT$ 722.0</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 693.0</t>
+          <t>NT$ 704.0</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 710.0</t>
+          <t>NT$ 713.0</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
@@ -2195,22 +2195,22 @@
       </c>
       <c r="C13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4875.0</t>
+          <t>NT$ 4950.0</t>
         </is>
       </c>
       <c r="D13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4980.0</t>
+          <t>NT$ 4970.0</t>
         </is>
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4875.0</t>
+          <t>NT$ 4880.0</t>
         </is>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 4980.0</t>
+          <t>NT$ 4950.0</t>
         </is>
       </c>
       <c r="G13" s="29" t="inlineStr">
@@ -2242,22 +2242,22 @@
       </c>
       <c r="C14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 6720.0</t>
+          <t>NT$ 6790.0</t>
         </is>
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 6895.0</t>
+          <t>NT$ 7065.0</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 6665.0</t>
+          <t>NT$ 6760.0</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>NT$ 6875.0</t>
+          <t>NT$ 6800.0</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">

--- a/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
+++ b/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
@@ -631,7 +631,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>定盘时间: 2026-10-02 20:57:42 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
+          <t>定盘时间: 2026-10-05 23:06:03 | 数据源: Shioaji Snapshot | 包含三大法人买卖超、财报发布日及主力资金分析</t>
         </is>
       </c>
     </row>
@@ -730,10 +730,10 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>开盘: 2505.0
-最高: 2515.0
-最低: 2495.0
-收盘: 2500.0</t>
+          <t>开盘: 2550.0
+最高: 2580.0
+最低: 2545.0
+收盘: 2575.0</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -751,15 +751,15 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>外资: -5914 张
-投信: +253 张
-[2026-10-02 官方结算] 投信内资买超 (+253 张) 逢低承接，外资高档调节 (-5,914 张)。</t>
+          <t>外资: +9770 张
+投信: +589 张
+[2026-10-05 官方结算] 三大法人全线买超 (+10,851 张)，外资与投信合力加仓。</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 5,344 张 (占量 38.4%)
-[2026-10-02 筹码] 主力机构呈净卖出 (-5,344 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 10,851 张 (占量 53.7%)
+[2026-10-05 筹码] 主力机构呈净买入 (+10,851 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2500.0</t>
+          <t>NT$ 2575.0</t>
         </is>
       </c>
       <c r="K4" s="9" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>13,902 张</t>
+          <t>20,216 张</t>
         </is>
       </c>
     </row>
@@ -817,10 +817,10 @@
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>开盘: 12000.0
-最高: 12295.0
-最低: 11700.0
-收盘: 12145.0</t>
+          <t>开盘: 12500.0
+最高: 13355.0
+最低: 12450.0
+收盘: 13355.0</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -838,15 +838,15 @@
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>外资: +0 张
-投信: +24 张
-[2026-10-02 官方结算] 三大法人合计净买超 38 张，多空资金处于换手态势。</t>
+          <t>外资: +10 张
+投信: +31 张
+[2026-10-05 官方结算] 外资与投信联手买超 (+34 张)，内外部机构共振做多。</t>
         </is>
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 38 张 (占量 8.1%)
-[2026-10-02 筹码] 主力机构呈净买入 (+38 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 34 张 (占量 7.5%)
+[2026-10-05 筹码] 主力机构呈净买入 (+34 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 12145.0</t>
+          <t>NT$ 13355.0</t>
         </is>
       </c>
       <c r="K5" s="18" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="O5" s="16" t="inlineStr">
         <is>
-          <t>472 张</t>
+          <t>456 张</t>
         </is>
       </c>
     </row>
@@ -904,10 +904,10 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>开盘: 5040.0
-最高: 5190.0
-最低: 4975.0
-收盘: 5185.0</t>
+          <t>开盘: 5630.0
+最高: 5700.0
+最低: 5600.0
+收盘: 5700.0</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -925,15 +925,15 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>外资: +2 张
-投信: +133 张
-[2026-10-02 官方结算] 三大法人全线买超 (+168 张)，外资与投信合力加仓。</t>
+          <t>外资: -100 张
+投信: -18 张
+[2026-10-05 官方结算] 外资与投信偏空调节 (19 张)，机构筹码阶段获利了结。</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 168 张 (占量 7.8%)
-[2026-10-02 筹码] 主力机构呈净买入 (+168 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 19 张 (占量 1.9%)
+[2026-10-05 筹码] 主力机构呈净买入 (+19 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 5185.0</t>
+          <t>NT$ 5700.0</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>2,159 张</t>
+          <t>981 张</t>
         </is>
       </c>
     </row>
@@ -992,9 +992,9 @@
       <c r="D7" s="16" t="inlineStr">
         <is>
           <t>开盘: 3570.0
-最高: 3570.0
-最低: 3385.0
-收盘: 3440.0</t>
+最高: 3690.0
+最低: 3420.0
+收盘: 3585.0</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -1012,15 +1012,15 @@
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>外资: -342 张
-投信: -276 张
-[2026-10-02 官方结算] 外资与投信偏空调节 (-589 张)，机构筹码阶段获利了结。</t>
+          <t>外资: +724 张
+投信: +246 张
+[2026-10-05 官方结算] 外资与投信联手买超 (+938 张)，内外部机构共振做多。</t>
         </is>
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 589 张 (占量 18.8%)
-[2026-10-02 筹码] 主力机构呈净卖出 (-589 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 938 张 (占量 21.7%)
+[2026-10-05 筹码] 主力机构呈净买入 (+938 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I7" s="15" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="J7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3440.0</t>
+          <t>NT$ 3585.0</t>
         </is>
       </c>
       <c r="K7" s="18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="O7" s="16" t="inlineStr">
         <is>
-          <t>3,130 张</t>
+          <t>4,322 张</t>
         </is>
       </c>
     </row>
@@ -1078,10 +1078,10 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>开盘: 253.0
-最高: 253.0
-最低: 250.5
-收盘: 251.0</t>
+          <t>开盘: 254.0
+最高: 256.0
+最低: 253.5
+收盘: 254.0</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -1099,15 +1099,15 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>外资: -15147 张
-投信: +223 张
-[2026-10-02 官方结算] 投信内资买超 (+223 张) 逢低承接，外资高档调节 (-15,147 张)。</t>
+          <t>外资: +13072 张
+投信: -64 张
+[2026-10-05 官方结算] 外资主力大幅回流 (+13,072 张)，投信阶段获利减仓 (-64 张)。</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 14,908 张 (占量 52.5%)
-[2026-10-02 筹码] 主力机构呈净卖出 (-14,908 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 13,383 张 (占量 29.6%)
+[2026-10-05 筹码] 主力机构呈净买入 (+13,383 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>NT$ 251.0</t>
+          <t>NT$ 254.0</t>
         </is>
       </c>
       <c r="K8" s="9" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="O8" s="7" t="inlineStr">
         <is>
-          <t>28,422 张</t>
+          <t>45,279 张</t>
         </is>
       </c>
     </row>
@@ -1165,10 +1165,10 @@
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>开盘: 1895.0
-最高: 1915.0
-最低: 1880.0
-收盘: 1885.0</t>
+          <t>开盘: 1920.0
+最高: 2010.0
+最低: 1920.0
+收盘: 2005.0</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -1186,15 +1186,15 @@
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
-          <t>外资: -1541 张
-投信: +84 张
-[2026-10-02 官方结算] 投信内资买超 (+84 张) 逢低承接，外资高档调节 (-1,541 张)。</t>
+          <t>外资: +7962 张
+投信: +29 张
+[2026-10-05 官方结算] 三大法人全线买超 (+8,351 张)，外资与投信合力加仓。</t>
         </is>
       </c>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 1,436 张 (占量 26.0%)
-[2026-10-02 筹码] 主力机构呈净卖出 (-1,436 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 8,351 张 (占量 55.4%)
+[2026-10-05 筹码] 主力机构呈净买入 (+8,351 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I9" s="15" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="J9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1885.0</t>
+          <t>NT$ 2005.0</t>
         </is>
       </c>
       <c r="K9" s="18" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="O9" s="16" t="inlineStr">
         <is>
-          <t>5,519 张</t>
+          <t>15,084 张</t>
         </is>
       </c>
     </row>
@@ -1252,10 +1252,10 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>开盘: 1955.0
-最高: 1980.0
-最低: 1920.0
-收盘: 1965.0</t>
+          <t>开盘: 2070.0
+最高: 2110.0
+最低: 2015.0
+收盘: 2075.0</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -1273,15 +1273,15 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>外资: -413 张
-投信: +110 张
-[2026-10-02 官方结算] 投信内资买超 (+110 张) 逢低承接，外资高档调节 (-413 张)。</t>
+          <t>外资: +213 张
+投信: -189 张
+[2026-10-05 官方结算] 外资主力大幅回流 (+213 张)，投信阶段获利减仓 (-189 张)。</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 328 张 (占量 6.6%)
-[2026-10-02 筹码] 主力机构呈净卖出 (-328 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 132 张 (占量 2.3%)
+[2026-10-05 筹码] 主力机构呈净买入 (+132 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 1965.0</t>
+          <t>NT$ 2075.0</t>
         </is>
       </c>
       <c r="K10" s="9" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>4,993 张</t>
+          <t>5,800 张</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>开盘: 2145.0
-最高: 2225.0
-最低: 2135.0
-收盘: 2190.0</t>
+          <t>开盘: 2225.0
+最高: 2355.0
+最低: 2215.0
+收盘: 2325.0</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
@@ -1360,15 +1360,15 @@
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>外资: +1006 张
-投信: -458 张
-[2026-10-02 官方结算] 外资主力大幅回流 (+1,006 张)，投信阶段获利减仓 (-458 张)。</t>
+          <t>外资: +578 张
+投信: -20 张
+[2026-10-05 官方结算] 外资主力大幅回流 (+578 张)，投信阶段获利减仓 (-20 张)。</t>
         </is>
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 564 张 (占量 17.9%)
-[2026-10-02 筹码] 主力机构呈净买入 (+564 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 492 张 (占量 17.3%)
+[2026-10-05 筹码] 主力机构呈净买入 (+492 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I11" s="15" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="J11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2190.0</t>
+          <t>NT$ 2325.0</t>
         </is>
       </c>
       <c r="K11" s="18" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="O11" s="16" t="inlineStr">
         <is>
-          <t>3,149 张</t>
+          <t>2,836 张</t>
         </is>
       </c>
     </row>
@@ -1426,10 +1426,10 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>开盘: 711.0
-最高: 722.0
-最低: 704.0
-收盘: 713.0</t>
+          <t>开盘: 747.0
+最高: 758.0
+最低: 729.0
+收盘: 742.0</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -1447,15 +1447,15 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>外资: +3128 张
-投信: -2506 张
-[2026-10-02 官方结算] 外资主力大幅回流 (+3,128 张)，投信阶段获利减仓 (-2,506 张)。</t>
+          <t>外资: +3081 张
+投信: -880 张
+[2026-10-05 官方结算] 外资主力大幅回流 (+3,081 张)，投信阶段获利减仓 (-880 张)。</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 775 张 (占量 7.0%)
-[2026-10-02 筹码] 主力机构呈净买入 (+775 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 2,376 张 (占量 14.2%)
+[2026-10-05 筹码] 主力机构呈净买入 (+2,376 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 713.0</t>
+          <t>NT$ 742.0</t>
         </is>
       </c>
       <c r="K12" s="9" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>11,136 张</t>
+          <t>16,774 张</t>
         </is>
       </c>
     </row>
@@ -1513,10 +1513,10 @@
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>开盘: 4950.0
-最高: 4970.0
-最低: 4880.0
-收盘: 4950.0</t>
+          <t>开盘: 4980.0
+最高: 5165.0
+最低: 4980.0
+收盘: 5165.0</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
@@ -1534,15 +1534,15 @@
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>外资: -1472 张
-投信: +224 张
-[2026-10-02 官方结算] 投信内资买超 (+224 张) 逢低承接，外资高档调节 (-1,472 张)。</t>
+          <t>外资: +1297 张
+投信: -62 张
+[2026-10-05 官方结算] 外资主力大幅回流 (+1,297 张)，投信阶段获利减仓 (-62 张)。</t>
         </is>
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 1,253 张 (占量 32.6%)
-[2026-10-02 筹码] 主力机构呈净卖出 (-1,253 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 1,357 张 (占量 20.1%)
+[2026-10-05 筹码] 主力机构呈净买入 (+1,357 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I13" s="15" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="J13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 4950.0</t>
+          <t>NT$ 5165.0</t>
         </is>
       </c>
       <c r="K13" s="18" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="O13" s="16" t="inlineStr">
         <is>
-          <t>3,839 张</t>
+          <t>6,758 张</t>
         </is>
       </c>
     </row>
@@ -1600,10 +1600,10 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>开盘: 6790.0
-最高: 7065.0
+          <t>开盘: 6800.0
+最高: 7440.0
 最低: 6760.0
-收盘: 6800.0</t>
+收盘: 7205.0</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -1621,15 +1621,15 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>外资: -220 张
-投信: +63 张
-[2026-10-02 官方结算] 投信内资买超 (+63 张) 逢低承接，外资高档调节 (-220 张)。</t>
+          <t>外资: -100 张
+投信: +18 张
+[2026-10-05 官方结算] 投信内资买超 (+18 张) 逢低承接，外资高档调节 (-100 张)。</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 155 张 (占量 15.1%)
-[2026-10-02 筹码] 主力机构呈净卖出 (-155 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 82 张 (占量 7.7%)
+[2026-10-05 筹码] 主力机构呈净卖出 (-82 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>NT$ 6800.0</t>
+          <t>NT$ 7205.0</t>
         </is>
       </c>
       <c r="K14" s="9" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="O14" s="7" t="inlineStr">
         <is>
-          <t>1,025 张</t>
+          <t>1,069 张</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-02 20:57:42 | 策略: 3-3-4 分批建仓</t>
+          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-05 23:06:03 | 策略: 3-3-4 分批建仓</t>
         </is>
       </c>
     </row>
@@ -1772,22 +1772,22 @@
       </c>
       <c r="C4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2505.0</t>
+          <t>NT$ 2550.0</t>
         </is>
       </c>
       <c r="D4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2515.0</t>
+          <t>NT$ 2580.0</t>
         </is>
       </c>
       <c r="E4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2495.0</t>
+          <t>NT$ 2545.0</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2500.0</t>
+          <t>NT$ 2575.0</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
@@ -1819,22 +1819,22 @@
       </c>
       <c r="C5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 12000.0</t>
+          <t>NT$ 12500.0</t>
         </is>
       </c>
       <c r="D5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 12295.0</t>
+          <t>NT$ 13355.0</t>
         </is>
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 11700.0</t>
+          <t>NT$ 12450.0</t>
         </is>
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 12145.0</t>
+          <t>NT$ 13355.0</t>
         </is>
       </c>
       <c r="G5" s="29" t="inlineStr">
@@ -1866,22 +1866,22 @@
       </c>
       <c r="C6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5040.0</t>
+          <t>NT$ 5630.0</t>
         </is>
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5190.0</t>
+          <t>NT$ 5700.0</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 4975.0</t>
+          <t>NT$ 5600.0</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 5185.0</t>
+          <t>NT$ 5700.0</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
@@ -1918,17 +1918,17 @@
       </c>
       <c r="D7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3570.0</t>
+          <t>NT$ 3690.0</t>
         </is>
       </c>
       <c r="E7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3385.0</t>
+          <t>NT$ 3420.0</t>
         </is>
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3440.0</t>
+          <t>NT$ 3585.0</t>
         </is>
       </c>
       <c r="G7" s="29" t="inlineStr">
@@ -1960,22 +1960,22 @@
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 253.0</t>
+          <t>NT$ 254.0</t>
         </is>
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 253.0</t>
+          <t>NT$ 256.0</t>
         </is>
       </c>
       <c r="E8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 250.5</t>
+          <t>NT$ 253.5</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>NT$ 251.0</t>
+          <t>NT$ 254.0</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
@@ -2007,22 +2007,22 @@
       </c>
       <c r="C9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1895.0</t>
+          <t>NT$ 1920.0</t>
         </is>
       </c>
       <c r="D9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1915.0</t>
+          <t>NT$ 2010.0</t>
         </is>
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1880.0</t>
+          <t>NT$ 1920.0</t>
         </is>
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1885.0</t>
+          <t>NT$ 2005.0</t>
         </is>
       </c>
       <c r="G9" s="29" t="inlineStr">
@@ -2054,22 +2054,22 @@
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1955.0</t>
+          <t>NT$ 2070.0</t>
         </is>
       </c>
       <c r="D10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1980.0</t>
+          <t>NT$ 2110.0</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1920.0</t>
+          <t>NT$ 2015.0</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 1965.0</t>
+          <t>NT$ 2075.0</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
@@ -2101,22 +2101,22 @@
       </c>
       <c r="C11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2145.0</t>
+          <t>NT$ 2225.0</t>
         </is>
       </c>
       <c r="D11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2225.0</t>
+          <t>NT$ 2355.0</t>
         </is>
       </c>
       <c r="E11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2135.0</t>
+          <t>NT$ 2215.0</t>
         </is>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2190.0</t>
+          <t>NT$ 2325.0</t>
         </is>
       </c>
       <c r="G11" s="29" t="inlineStr">
@@ -2148,22 +2148,22 @@
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 711.0</t>
+          <t>NT$ 747.0</t>
         </is>
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 722.0</t>
+          <t>NT$ 758.0</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 704.0</t>
+          <t>NT$ 729.0</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 713.0</t>
+          <t>NT$ 742.0</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
@@ -2195,22 +2195,22 @@
       </c>
       <c r="C13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4950.0</t>
+          <t>NT$ 4980.0</t>
         </is>
       </c>
       <c r="D13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4970.0</t>
+          <t>NT$ 5165.0</t>
         </is>
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4880.0</t>
+          <t>NT$ 4980.0</t>
         </is>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 4950.0</t>
+          <t>NT$ 5165.0</t>
         </is>
       </c>
       <c r="G13" s="29" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="C14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 6790.0</t>
+          <t>NT$ 6800.0</t>
         </is>
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 7065.0</t>
+          <t>NT$ 7440.0</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>NT$ 6800.0</t>
+          <t>NT$ 7205.0</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">

--- a/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
+++ b/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
@@ -631,7 +631,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>定盘时间: 2026-10-05 23:06:03 | 数据源: Shioaji Snapshot | 包含三大法人买卖超、财报发布日及主力资金分析</t>
+          <t>定盘时间: 2026-10-06 21:29:40 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
         </is>
       </c>
     </row>
@@ -730,10 +730,10 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>开盘: 2550.0
-最高: 2580.0
-最低: 2545.0
-收盘: 2575.0</t>
+          <t>开盘: 2575.0
+最高: 2590.0
+最低: 2565.0
+收盘: 2585.0</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -751,15 +751,15 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>外资: +9770 张
-投信: +589 张
-[2026-10-05 官方结算] 三大法人全线买超 (+10,851 张)，外资与投信合力加仓。</t>
+          <t>外资: -1673 张
+投信: +154 张
+[2026-10-06 官方结算] 投信内资买超 (+154 张) 逢低承接，外资高档调节 (-1,673 张)。</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 10,851 张 (占量 53.7%)
-[2026-10-05 筹码] 主力机构呈净买入 (+10,851 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 1,122 张 (占量 6.1%)
+[2026-10-06 筹码] 主力机构呈净卖出 (-1,122 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2575.0</t>
+          <t>NT$ 2585.0</t>
         </is>
       </c>
       <c r="K4" s="9" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>20,216 张</t>
+          <t>18,438 张</t>
         </is>
       </c>
     </row>
@@ -817,10 +817,10 @@
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>开盘: 12500.0
-最高: 13355.0
-最低: 12450.0
-收盘: 13355.0</t>
+          <t>开盘: 13500.0
+最高: 13500.0
+最低: 12845.0
+收盘: 13100.0</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -838,15 +838,15 @@
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>外资: +10 张
-投信: +31 张
-[2026-10-05 官方结算] 外资与投信联手买超 (+34 张)，内外部机构共振做多。</t>
+          <t>外资: -113 张
+投信: -19 张
+[2026-10-06 官方结算] 外资与投信偏空调节 (-109 张)，机构筹码阶段获利了结。</t>
         </is>
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 34 张 (占量 7.5%)
-[2026-10-05 筹码] 主力机构呈净买入 (+34 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 109 张 (占量 15.5%)
+[2026-10-06 筹码] 主力机构呈净卖出 (-109 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 13355.0</t>
+          <t>NT$ 13100.0</t>
         </is>
       </c>
       <c r="K5" s="18" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="O5" s="16" t="inlineStr">
         <is>
-          <t>456 张</t>
+          <t>701 张</t>
         </is>
       </c>
     </row>
@@ -904,10 +904,10 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>开盘: 5630.0
-最高: 5700.0
-最低: 5600.0
-收盘: 5700.0</t>
+          <t>开盘: 6040.0
+最高: 6115.0
+最低: 5820.0
+收盘: 5995.0</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -925,15 +925,15 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>外资: -100 张
-投信: -18 张
-[2026-10-05 官方结算] 外资与投信偏空调节 (19 张)，机构筹码阶段获利了结。</t>
+          <t>外资: +654 张
+投信: +595 张
+[2026-10-06 官方结算] 外资与投信联手买超 (+1,218 张)，内外部机构共振做多。</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 19 张 (占量 1.9%)
-[2026-10-05 筹码] 主力机构呈净买入 (+19 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 1,218 张 (占量 26.2%)
+[2026-10-06 筹码] 主力机构呈净买入 (+1,218 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 5700.0</t>
+          <t>NT$ 5995.0</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>981 张</t>
+          <t>4,646 张</t>
         </is>
       </c>
     </row>
@@ -991,10 +991,10 @@
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>开盘: 3570.0
-最高: 3690.0
-最低: 3420.0
-收盘: 3585.0</t>
+          <t>开盘: 3650.0
+最高: 3700.0
+最低: 3515.0
+收盘: 3685.0</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -1012,15 +1012,15 @@
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>外资: +724 张
-投信: +246 张
-[2026-10-05 官方结算] 外资与投信联手买超 (+938 张)，内外部机构共振做多。</t>
+          <t>外资: +146 张
+投信: +258 张
+[2026-10-06 官方结算] 三大法人全线买超 (+459 张)，外资与投信合力加仓。</t>
         </is>
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 938 张 (占量 21.7%)
-[2026-10-05 筹码] 主力机构呈净买入 (+938 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 459 张 (占量 15.0%)
+[2026-10-06 筹码] 主力机构呈净买入 (+459 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I7" s="15" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="J7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3585.0</t>
+          <t>NT$ 3685.0</t>
         </is>
       </c>
       <c r="K7" s="18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="O7" s="16" t="inlineStr">
         <is>
-          <t>4,322 张</t>
+          <t>3,065 张</t>
         </is>
       </c>
     </row>
@@ -1078,10 +1078,10 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>开盘: 254.0
-最高: 256.0
+          <t>开盘: 263.0
+最高: 266.5
 最低: 253.5
-收盘: 254.0</t>
+收盘: 256.0</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -1099,15 +1099,15 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>外资: +13072 张
-投信: -64 张
-[2026-10-05 官方结算] 外资主力大幅回流 (+13,072 张)，投信阶段获利减仓 (-64 张)。</t>
+          <t>外资: -19983 张
+投信: -1141 张
+[2026-10-06 官方结算] 外资与投信偏空调节 (-20,730 张)，机构筹码阶段获利了结。</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 13,383 张 (占量 29.6%)
-[2026-10-05 筹码] 主力机构呈净买入 (+13,383 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 20,730 张 (占量 21.9%)
+[2026-10-06 筹码] 主力机构呈净卖出 (-20,730 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>NT$ 254.0</t>
+          <t>NT$ 256.0</t>
         </is>
       </c>
       <c r="K8" s="9" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="O8" s="7" t="inlineStr">
         <is>
-          <t>45,279 张</t>
+          <t>94,815 张</t>
         </is>
       </c>
     </row>
@@ -1165,10 +1165,10 @@
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>开盘: 1920.0
-最高: 2010.0
-最低: 1920.0
-收盘: 2005.0</t>
+          <t>开盘: 2045.0
+最高: 2115.0
+最低: 2010.0
+收盘: 2050.0</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -1186,15 +1186,15 @@
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
-          <t>外资: +7962 张
-投信: +29 张
-[2026-10-05 官方结算] 三大法人全线买超 (+8,351 张)，外资与投信合力加仓。</t>
+          <t>外资: +644 张
+投信: +649 张
+[2026-10-06 官方结算] 外资与投信联手买超 (+1,180 张)，内外部机构共振做多。</t>
         </is>
       </c>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 8,351 张 (占量 55.4%)
-[2026-10-05 筹码] 主力机构呈净买入 (+8,351 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 1,180 张 (占量 8.7%)
+[2026-10-06 筹码] 主力机构呈净买入 (+1,180 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I9" s="15" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="J9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2005.0</t>
+          <t>NT$ 2050.0</t>
         </is>
       </c>
       <c r="K9" s="18" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="O9" s="16" t="inlineStr">
         <is>
-          <t>15,084 张</t>
+          <t>13,591 张</t>
         </is>
       </c>
     </row>
@@ -1252,10 +1252,10 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>开盘: 2070.0
-最高: 2110.0
-最低: 2015.0
-收盘: 2075.0</t>
+          <t>开盘: 2080.0
+最高: 2105.0
+最低: 2035.0
+收盘: 2050.0</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -1273,15 +1273,15 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>外资: +213 张
-投信: -189 张
-[2026-10-05 官方结算] 外资主力大幅回流 (+213 张)，投信阶段获利减仓 (-189 张)。</t>
+          <t>外资: +31 张
+投信: -322 张
+[2026-10-06 官方结算] 外资主力大幅回流 (+31 张)，投信阶段获利减仓 (-322 张)。</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 132 张 (占量 2.3%)
-[2026-10-05 筹码] 主力机构呈净买入 (+132 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 297 张 (占量 8.7%)
+[2026-10-06 筹码] 主力机构呈净卖出 (-297 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2075.0</t>
+          <t>NT$ 2050.0</t>
         </is>
       </c>
       <c r="K10" s="9" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>5,800 张</t>
+          <t>3,423 张</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>开盘: 2225.0
-最高: 2355.0
-最低: 2215.0
-收盘: 2325.0</t>
+          <t>开盘: 2330.0
+最高: 2370.0
+最低: 2275.0
+收盘: 2350.0</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
@@ -1360,15 +1360,15 @@
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>外资: +578 张
-投信: -20 张
-[2026-10-05 官方结算] 外资主力大幅回流 (+578 张)，投信阶段获利减仓 (-20 张)。</t>
+          <t>外资: +166 张
+投信: -48 张
+[2026-10-06 官方结算] 外资主力大幅回流 (+166 张)，投信阶段获利减仓 (-48 张)。</t>
         </is>
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 492 张 (占量 17.3%)
-[2026-10-05 筹码] 主力机构呈净买入 (+492 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 92 张 (占量 4.9%)
+[2026-10-06 筹码] 主力机构呈净买入 (+92 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I11" s="15" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="J11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2325.0</t>
+          <t>NT$ 2350.0</t>
         </is>
       </c>
       <c r="K11" s="18" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="O11" s="16" t="inlineStr">
         <is>
-          <t>2,836 张</t>
+          <t>1,859 张</t>
         </is>
       </c>
     </row>
@@ -1426,10 +1426,10 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>开盘: 747.0
-最高: 758.0
-最低: 729.0
-收盘: 742.0</t>
+          <t>开盘: 743.0
+最高: 755.0
+最低: 733.0
+收盘: 744.0</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -1447,15 +1447,15 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>外资: +3081 张
-投信: -880 张
-[2026-10-05 官方结算] 外资主力大幅回流 (+3,081 张)，投信阶段获利减仓 (-880 张)。</t>
+          <t>外资: +1699 张
+投信: -1526 张
+[2026-10-06 官方结算] 外资主力大幅回流 (+1,699 张)，投信阶段获利减仓 (-1,526 张)。</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 2,376 张 (占量 14.2%)
-[2026-10-05 筹码] 主力机构呈净买入 (+2,376 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 276 张 (占量 3.0%)
+[2026-10-06 筹码] 主力机构呈净买入 (+276 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 742.0</t>
+          <t>NT$ 744.0</t>
         </is>
       </c>
       <c r="K12" s="9" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>16,774 张</t>
+          <t>9,224 张</t>
         </is>
       </c>
     </row>
@@ -1513,10 +1513,10 @@
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>开盘: 4980.0
-最高: 5165.0
-最低: 4980.0
-收盘: 5165.0</t>
+          <t>开盘: 5080.0
+最高: 5085.0
+最低: 4915.0
+收盘: 4920.0</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
@@ -1534,15 +1534,15 @@
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>外资: +1297 张
-投信: -62 张
-[2026-10-05 官方结算] 外资主力大幅回流 (+1,297 张)，投信阶段获利减仓 (-62 张)。</t>
+          <t>外资: -3913 张
+投信: -864 张
+[2026-10-06 官方结算] 外资与投信偏空调节 (-4,744 张)，机构筹码阶段获利了结。</t>
         </is>
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 1,357 张 (占量 20.1%)
-[2026-10-05 筹码] 主力机构呈净买入 (+1,357 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 4,744 张 (占量 57.4%)
+[2026-10-06 筹码] 主力机构呈净卖出 (-4,744 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I13" s="15" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="J13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 5165.0</t>
+          <t>NT$ 4920.0</t>
         </is>
       </c>
       <c r="K13" s="18" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="O13" s="16" t="inlineStr">
         <is>
-          <t>6,758 张</t>
+          <t>8,268 张</t>
         </is>
       </c>
     </row>
@@ -1600,10 +1600,10 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>开盘: 6800.0
-最高: 7440.0
-最低: 6760.0
-收盘: 7205.0</t>
+          <t>开盘: 7185.0
+最高: 7280.0
+最低: 7050.0
+收盘: 7080.0</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -1621,15 +1621,15 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>外资: -100 张
-投信: +18 张
-[2026-10-05 官方结算] 投信内资买超 (+18 张) 逢低承接，外资高档调节 (-100 张)。</t>
+          <t>外资: +70 张
+投信: -15 张
+[2026-10-06 官方结算] 外资主力大幅回流 (+70 张)，投信阶段获利减仓 (-15 张)。</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 82 张 (占量 7.7%)
-[2026-10-05 筹码] 主力机构呈净卖出 (-82 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 54 张 (占量 10.1%)
+[2026-10-06 筹码] 主力机构呈净买入 (+54 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>NT$ 7205.0</t>
+          <t>NT$ 7080.0</t>
         </is>
       </c>
       <c r="K14" s="9" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="O14" s="7" t="inlineStr">
         <is>
-          <t>1,069 张</t>
+          <t>533 张</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-05 23:06:03 | 策略: 3-3-4 分批建仓</t>
+          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-06 21:29:40 | 策略: 3-3-4 分批建仓</t>
         </is>
       </c>
     </row>
@@ -1772,22 +1772,22 @@
       </c>
       <c r="C4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2550.0</t>
+          <t>NT$ 2575.0</t>
         </is>
       </c>
       <c r="D4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2580.0</t>
+          <t>NT$ 2590.0</t>
         </is>
       </c>
       <c r="E4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2545.0</t>
+          <t>NT$ 2565.0</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2575.0</t>
+          <t>NT$ 2585.0</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
@@ -1819,22 +1819,22 @@
       </c>
       <c r="C5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 12500.0</t>
+          <t>NT$ 13500.0</t>
         </is>
       </c>
       <c r="D5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 13355.0</t>
+          <t>NT$ 13500.0</t>
         </is>
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 12450.0</t>
+          <t>NT$ 12845.0</t>
         </is>
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 13355.0</t>
+          <t>NT$ 13100.0</t>
         </is>
       </c>
       <c r="G5" s="29" t="inlineStr">
@@ -1866,22 +1866,22 @@
       </c>
       <c r="C6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5630.0</t>
+          <t>NT$ 6040.0</t>
         </is>
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5700.0</t>
+          <t>NT$ 6115.0</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5600.0</t>
+          <t>NT$ 5820.0</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 5700.0</t>
+          <t>NT$ 5995.0</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
@@ -1913,22 +1913,22 @@
       </c>
       <c r="C7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3570.0</t>
+          <t>NT$ 3650.0</t>
         </is>
       </c>
       <c r="D7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3690.0</t>
+          <t>NT$ 3700.0</t>
         </is>
       </c>
       <c r="E7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3420.0</t>
+          <t>NT$ 3515.0</t>
         </is>
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3585.0</t>
+          <t>NT$ 3685.0</t>
         </is>
       </c>
       <c r="G7" s="29" t="inlineStr">
@@ -1960,22 +1960,22 @@
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 254.0</t>
+          <t>NT$ 263.0</t>
         </is>
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
+          <t>NT$ 266.5</t>
+        </is>
+      </c>
+      <c r="E8" s="24" t="inlineStr">
+        <is>
+          <t>NT$ 253.5</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
           <t>NT$ 256.0</t>
-        </is>
-      </c>
-      <c r="E8" s="24" t="inlineStr">
-        <is>
-          <t>NT$ 253.5</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>NT$ 254.0</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
@@ -2007,22 +2007,22 @@
       </c>
       <c r="C9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1920.0</t>
+          <t>NT$ 2045.0</t>
         </is>
       </c>
       <c r="D9" s="28" t="inlineStr">
         <is>
+          <t>NT$ 2115.0</t>
+        </is>
+      </c>
+      <c r="E9" s="28" t="inlineStr">
+        <is>
           <t>NT$ 2010.0</t>
         </is>
       </c>
-      <c r="E9" s="28" t="inlineStr">
-        <is>
-          <t>NT$ 1920.0</t>
-        </is>
-      </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2005.0</t>
+          <t>NT$ 2050.0</t>
         </is>
       </c>
       <c r="G9" s="29" t="inlineStr">
@@ -2054,22 +2054,22 @@
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2070.0</t>
+          <t>NT$ 2080.0</t>
         </is>
       </c>
       <c r="D10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2110.0</t>
+          <t>NT$ 2105.0</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2015.0</t>
+          <t>NT$ 2035.0</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2075.0</t>
+          <t>NT$ 2050.0</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
@@ -2101,22 +2101,22 @@
       </c>
       <c r="C11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2225.0</t>
+          <t>NT$ 2330.0</t>
         </is>
       </c>
       <c r="D11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2355.0</t>
+          <t>NT$ 2370.0</t>
         </is>
       </c>
       <c r="E11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2215.0</t>
+          <t>NT$ 2275.0</t>
         </is>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2325.0</t>
+          <t>NT$ 2350.0</t>
         </is>
       </c>
       <c r="G11" s="29" t="inlineStr">
@@ -2148,22 +2148,22 @@
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 747.0</t>
+          <t>NT$ 743.0</t>
         </is>
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 758.0</t>
+          <t>NT$ 755.0</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 729.0</t>
+          <t>NT$ 733.0</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 742.0</t>
+          <t>NT$ 744.0</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
@@ -2195,22 +2195,22 @@
       </c>
       <c r="C13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4980.0</t>
+          <t>NT$ 5080.0</t>
         </is>
       </c>
       <c r="D13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 5165.0</t>
+          <t>NT$ 5085.0</t>
         </is>
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4980.0</t>
+          <t>NT$ 4915.0</t>
         </is>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 5165.0</t>
+          <t>NT$ 4920.0</t>
         </is>
       </c>
       <c r="G13" s="29" t="inlineStr">
@@ -2242,22 +2242,22 @@
       </c>
       <c r="C14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 6800.0</t>
+          <t>NT$ 7185.0</t>
         </is>
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 7440.0</t>
+          <t>NT$ 7280.0</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 6760.0</t>
+          <t>NT$ 7050.0</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>NT$ 7205.0</t>
+          <t>NT$ 7080.0</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">

--- a/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
+++ b/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
@@ -631,7 +631,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>定盘时间: 2026-10-06 21:29:40 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
+          <t>定盘时间: 2026-10-07 21:41:31 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
         </is>
       </c>
     </row>
@@ -730,9 +730,9 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>开盘: 2575.0
-最高: 2590.0
-最低: 2565.0
+          <t>开盘: 2565.0
+最高: 2585.0
+最低: 2560.0
 收盘: 2585.0</t>
         </is>
       </c>
@@ -751,15 +751,15 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>外资: -1673 张
-投信: +154 张
-[2026-10-06 官方结算] 投信内资买超 (+154 张) 逢低承接，外资高档调节 (-1,673 张)。</t>
+          <t>外资: -1164 张
+投信: +66 张
+[2026-10-07 官方结算] 投信内资买超 (+66 张) 逢低承接，外资高档调节 (-1,164 张)。</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 1,122 张 (占量 6.1%)
-[2026-10-06 筹码] 主力机构呈净卖出 (-1,122 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 650 张 (占量 4.5%)
+[2026-10-07 筹码] 主力机构呈净卖出 (-650 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>18,438 张</t>
+          <t>14,406 张</t>
         </is>
       </c>
     </row>
@@ -817,10 +817,10 @@
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>开盘: 13500.0
-最高: 13500.0
-最低: 12845.0
-收盘: 13100.0</t>
+          <t>开盘: 11790.0
+最高: 11790.0
+最低: 11790.0
+收盘: 11790.0</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -838,15 +838,15 @@
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>外资: -113 张
-投信: -19 张
-[2026-10-06 官方结算] 外资与投信偏空调节 (-109 张)，机构筹码阶段获利了结。</t>
+          <t>外资: +51 张
+投信: +27 张
+[2026-10-07 官方结算] 外资与投信联手买超 (+45 张)，内外部机构共振做多。</t>
         </is>
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 109 张 (占量 15.5%)
-[2026-10-06 筹码] 主力机构呈净卖出 (-109 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 45 张 (占量 19.0%)
+[2026-10-07 筹码] 主力机构呈净买入 (+45 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 13100.0</t>
+          <t>NT$ 11790.0</t>
         </is>
       </c>
       <c r="K5" s="18" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="O5" s="16" t="inlineStr">
         <is>
-          <t>701 张</t>
+          <t>237 张</t>
         </is>
       </c>
     </row>
@@ -904,10 +904,10 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>开盘: 6040.0
-最高: 6115.0
-最低: 5820.0
-收盘: 5995.0</t>
+          <t>开盘: 6015.0
+最高: 6325.0
+最低: 5950.0
+收盘: 5950.0</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -925,15 +925,15 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>外资: +654 张
-投信: +595 张
-[2026-10-06 官方结算] 外资与投信联手买超 (+1,218 张)，内外部机构共振做多。</t>
+          <t>外资: +388 张
+投信: +38 张
+[2026-10-07 官方结算] 三大法人全线买超 (+434 张)，外资与投信合力加仓。</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 1,218 张 (占量 26.2%)
-[2026-10-06 筹码] 主力机构呈净买入 (+1,218 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 434 张 (占量 16.7%)
+[2026-10-07 筹码] 主力机构呈净买入 (+434 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 5995.0</t>
+          <t>NT$ 5950.0</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>4,646 张</t>
+          <t>2,598 张</t>
         </is>
       </c>
     </row>
@@ -992,9 +992,9 @@
       <c r="D7" s="16" t="inlineStr">
         <is>
           <t>开盘: 3650.0
-最高: 3700.0
-最低: 3515.0
-收盘: 3685.0</t>
+最高: 3655.0
+最低: 3505.0
+收盘: 3545.0</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -1012,15 +1012,15 @@
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>外资: +146 张
-投信: +258 张
-[2026-10-06 官方结算] 三大法人全线买超 (+459 张)，外资与投信合力加仓。</t>
+          <t>外资: -1059 张
+投信: +54 张
+[2026-10-07 官方结算] 投信内资买超 (+54 张) 逢低承接，外资高档调节 (-1,059 张)。</t>
         </is>
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 459 张 (占量 15.0%)
-[2026-10-06 筹码] 主力机构呈净买入 (+459 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 1,107 张 (占量 38.6%)
+[2026-10-07 筹码] 主力机构呈净卖出 (-1,107 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I7" s="15" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="J7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3685.0</t>
+          <t>NT$ 3545.0</t>
         </is>
       </c>
       <c r="K7" s="18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="O7" s="16" t="inlineStr">
         <is>
-          <t>3,065 张</t>
+          <t>2,867 张</t>
         </is>
       </c>
     </row>
@@ -1078,10 +1078,10 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>开盘: 263.0
-最高: 266.5
-最低: 253.5
-收盘: 256.0</t>
+          <t>开盘: 254.0
+最高: 254.5
+最低: 251.5
+收盘: 252.0</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -1099,15 +1099,15 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>外资: -19983 张
-投信: -1141 张
-[2026-10-06 官方结算] 外资与投信偏空调节 (-20,730 张)，机构筹码阶段获利了结。</t>
+          <t>外资: -11743 张
+投信: -626 张
+[2026-10-07 官方结算] 三大法人同步卖超 (-12,639 张)，短线筹码面临清洗。</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 20,730 张 (占量 21.9%)
-[2026-10-06 筹码] 主力机构呈净卖出 (-20,730 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 12,639 张 (占量 36.1%)
+[2026-10-07 筹码] 主力机构呈净卖出 (-12,639 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>NT$ 256.0</t>
+          <t>NT$ 252.0</t>
         </is>
       </c>
       <c r="K8" s="9" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="O8" s="7" t="inlineStr">
         <is>
-          <t>94,815 张</t>
+          <t>35,015 张</t>
         </is>
       </c>
     </row>
@@ -1165,10 +1165,10 @@
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>开盘: 2045.0
-最高: 2115.0
-最低: 2010.0
-收盘: 2050.0</t>
+          <t>开盘: 2025.0
+最高: 2045.0
+最低: 1975.0
+收盘: 1990.0</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -1186,15 +1186,15 @@
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
-          <t>外资: +644 张
-投信: +649 张
-[2026-10-06 官方结算] 外资与投信联手买超 (+1,180 张)，内外部机构共振做多。</t>
+          <t>外资: -2068 张
+投信: +196 张
+[2026-10-07 官方结算] 投信内资买超 (+196 张) 逢低承接，外资高档调节 (-2,068 张)。</t>
         </is>
       </c>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 1,180 张 (占量 8.7%)
-[2026-10-06 筹码] 主力机构呈净买入 (+1,180 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 1,981 张 (占量 22.0%)
+[2026-10-07 筹码] 主力机构呈净卖出 (-1,981 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I9" s="15" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="J9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2050.0</t>
+          <t>NT$ 1990.0</t>
         </is>
       </c>
       <c r="K9" s="18" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="O9" s="16" t="inlineStr">
         <is>
-          <t>13,591 张</t>
+          <t>8,997 张</t>
         </is>
       </c>
     </row>
@@ -1252,10 +1252,10 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>开盘: 2080.0
-最高: 2105.0
-最低: 2035.0
-收盘: 2050.0</t>
+          <t>开盘: 2050.0
+最高: 2140.0
+最低: 2005.0
+收盘: 2015.0</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -1273,15 +1273,15 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>外资: +31 张
-投信: -322 张
-[2026-10-06 官方结算] 外资主力大幅回流 (+31 张)，投信阶段获利减仓 (-322 张)。</t>
+          <t>外资: -216 张
+投信: -74 张
+[2026-10-07 官方结算] 三大法人同步卖超 (-343 张)，短线筹码面临清洗。</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 297 张 (占量 8.7%)
-[2026-10-06 筹码] 主力机构呈净卖出 (-297 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 343 张 (占量 7.0%)
+[2026-10-07 筹码] 主力机构呈净卖出 (-343 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2050.0</t>
+          <t>NT$ 2015.0</t>
         </is>
       </c>
       <c r="K10" s="9" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>3,423 张</t>
+          <t>4,892 张</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>开盘: 2330.0
-最高: 2370.0
-最低: 2275.0
-收盘: 2350.0</t>
+          <t>开盘: 2480.0
+最高: 2560.0
+最低: 2385.0
+收盘: 2400.0</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
@@ -1360,15 +1360,15 @@
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>外资: +166 张
-投信: -48 张
-[2026-10-06 官方结算] 外资主力大幅回流 (+166 张)，投信阶段获利减仓 (-48 张)。</t>
+          <t>外资: +789 张
+投信: +20 张
+[2026-10-07 官方结算] 外资与投信联手买超 (+636 张)，内外部机构共振做多。</t>
         </is>
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 92 张 (占量 4.9%)
-[2026-10-06 筹码] 主力机构呈净买入 (+92 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 636 张 (占量 12.9%)
+[2026-10-07 筹码] 主力机构呈净买入 (+636 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I11" s="15" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="J11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2350.0</t>
+          <t>NT$ 2400.0</t>
         </is>
       </c>
       <c r="K11" s="18" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="O11" s="16" t="inlineStr">
         <is>
-          <t>1,859 张</t>
+          <t>4,933 张</t>
         </is>
       </c>
     </row>
@@ -1426,10 +1426,10 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>开盘: 743.0
-最高: 755.0
-最低: 733.0
-收盘: 744.0</t>
+          <t>开盘: 735.0
+最高: 748.0
+最低: 728.0
+收盘: 732.0</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -1447,15 +1447,15 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>外资: +1699 张
-投信: -1526 张
-[2026-10-06 官方结算] 外资主力大幅回流 (+1,699 张)，投信阶段获利减仓 (-1,526 张)。</t>
+          <t>外资: -1410 张
+投信: +31 张
+[2026-10-07 官方结算] 投信内资买超 (+31 张) 逢低承接，外资高档调节 (-1,410 张)。</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 276 张 (占量 3.0%)
-[2026-10-06 筹码] 主力机构呈净买入 (+276 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 1,352 张 (占量 17.6%)
+[2026-10-07 筹码] 主力机构呈净卖出 (-1,352 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 744.0</t>
+          <t>NT$ 732.0</t>
         </is>
       </c>
       <c r="K12" s="9" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>9,224 张</t>
+          <t>7,688 张</t>
         </is>
       </c>
     </row>
@@ -1513,10 +1513,10 @@
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>开盘: 5080.0
-最高: 5085.0
-最低: 4915.0
-收盘: 4920.0</t>
+          <t>开盘: 4920.0
+最高: 4940.0
+最低: 4835.0
+收盘: 4835.0</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
@@ -1534,15 +1534,15 @@
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>外资: -3913 张
-投信: -864 张
-[2026-10-06 官方结算] 外资与投信偏空调节 (-4,744 张)，机构筹码阶段获利了结。</t>
+          <t>外资: -2770 张
+投信: -286 张
+[2026-10-07 官方结算] 三大法人同步卖超 (-3,186 张)，短线筹码面临清洗。</t>
         </is>
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 4,744 张 (占量 57.4%)
-[2026-10-06 筹码] 主力机构呈净卖出 (-4,744 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 3,186 张 (占量 56.4%)
+[2026-10-07 筹码] 主力机构呈净卖出 (-3,186 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I13" s="15" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="J13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 4920.0</t>
+          <t>NT$ 4835.0</t>
         </is>
       </c>
       <c r="K13" s="18" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="O13" s="16" t="inlineStr">
         <is>
-          <t>8,268 张</t>
+          <t>5,645 张</t>
         </is>
       </c>
     </row>
@@ -1600,10 +1600,10 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>开盘: 7185.0
-最高: 7280.0
-最低: 7050.0
-收盘: 7080.0</t>
+          <t>开盘: 6970.0
+最高: 7020.0
+最低: 6760.0
+收盘: 6805.0</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -1621,15 +1621,15 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>外资: +70 张
-投信: -15 张
-[2026-10-06 官方结算] 外资主力大幅回流 (+70 张)，投信阶段获利减仓 (-15 张)。</t>
+          <t>外资: +62 张
+投信: -160 张
+[2026-10-07 官方结算] 外资主力大幅回流 (+62 张)，投信阶段获利减仓 (-160 张)。</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 54 张 (占量 10.1%)
-[2026-10-06 筹码] 主力机构呈净买入 (+54 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 94 张 (占量 10.0%)
+[2026-10-07 筹码] 主力机构呈净卖出 (-94 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>NT$ 7080.0</t>
+          <t>NT$ 6805.0</t>
         </is>
       </c>
       <c r="K14" s="9" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="O14" s="7" t="inlineStr">
         <is>
-          <t>533 张</t>
+          <t>939 张</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-06 21:29:40 | 策略: 3-3-4 分批建仓</t>
+          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-07 21:41:31 | 策略: 3-3-4 分批建仓</t>
         </is>
       </c>
     </row>
@@ -1772,17 +1772,17 @@
       </c>
       <c r="C4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2575.0</t>
+          <t>NT$ 2565.0</t>
         </is>
       </c>
       <c r="D4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2590.0</t>
+          <t>NT$ 2585.0</t>
         </is>
       </c>
       <c r="E4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2565.0</t>
+          <t>NT$ 2560.0</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
@@ -1819,22 +1819,22 @@
       </c>
       <c r="C5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 13500.0</t>
+          <t>NT$ 11790.0</t>
         </is>
       </c>
       <c r="D5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 13500.0</t>
+          <t>NT$ 11790.0</t>
         </is>
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 12845.0</t>
+          <t>NT$ 11790.0</t>
         </is>
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 13100.0</t>
+          <t>NT$ 11790.0</t>
         </is>
       </c>
       <c r="G5" s="29" t="inlineStr">
@@ -1866,22 +1866,22 @@
       </c>
       <c r="C6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 6040.0</t>
+          <t>NT$ 6015.0</t>
         </is>
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 6115.0</t>
+          <t>NT$ 6325.0</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5820.0</t>
+          <t>NT$ 5950.0</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 5995.0</t>
+          <t>NT$ 5950.0</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
@@ -1918,17 +1918,17 @@
       </c>
       <c r="D7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3700.0</t>
+          <t>NT$ 3655.0</t>
         </is>
       </c>
       <c r="E7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3515.0</t>
+          <t>NT$ 3505.0</t>
         </is>
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3685.0</t>
+          <t>NT$ 3545.0</t>
         </is>
       </c>
       <c r="G7" s="29" t="inlineStr">
@@ -1960,22 +1960,22 @@
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 263.0</t>
+          <t>NT$ 254.0</t>
         </is>
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 266.5</t>
+          <t>NT$ 254.5</t>
         </is>
       </c>
       <c r="E8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 253.5</t>
+          <t>NT$ 251.5</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>NT$ 256.0</t>
+          <t>NT$ 252.0</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
@@ -2007,22 +2007,22 @@
       </c>
       <c r="C9" s="28" t="inlineStr">
         <is>
+          <t>NT$ 2025.0</t>
+        </is>
+      </c>
+      <c r="D9" s="28" t="inlineStr">
+        <is>
           <t>NT$ 2045.0</t>
         </is>
       </c>
-      <c r="D9" s="28" t="inlineStr">
-        <is>
-          <t>NT$ 2115.0</t>
-        </is>
-      </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2010.0</t>
+          <t>NT$ 1975.0</t>
         </is>
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2050.0</t>
+          <t>NT$ 1990.0</t>
         </is>
       </c>
       <c r="G9" s="29" t="inlineStr">
@@ -2054,22 +2054,22 @@
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2080.0</t>
+          <t>NT$ 2050.0</t>
         </is>
       </c>
       <c r="D10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2105.0</t>
+          <t>NT$ 2140.0</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2035.0</t>
+          <t>NT$ 2005.0</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2050.0</t>
+          <t>NT$ 2015.0</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
@@ -2101,22 +2101,22 @@
       </c>
       <c r="C11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2330.0</t>
+          <t>NT$ 2480.0</t>
         </is>
       </c>
       <c r="D11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2370.0</t>
+          <t>NT$ 2560.0</t>
         </is>
       </c>
       <c r="E11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2275.0</t>
+          <t>NT$ 2385.0</t>
         </is>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2350.0</t>
+          <t>NT$ 2400.0</t>
         </is>
       </c>
       <c r="G11" s="29" t="inlineStr">
@@ -2148,22 +2148,22 @@
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 743.0</t>
+          <t>NT$ 735.0</t>
         </is>
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 755.0</t>
+          <t>NT$ 748.0</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 733.0</t>
+          <t>NT$ 728.0</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 744.0</t>
+          <t>NT$ 732.0</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
@@ -2195,22 +2195,22 @@
       </c>
       <c r="C13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 5080.0</t>
+          <t>NT$ 4920.0</t>
         </is>
       </c>
       <c r="D13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 5085.0</t>
+          <t>NT$ 4940.0</t>
         </is>
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4915.0</t>
+          <t>NT$ 4835.0</t>
         </is>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 4920.0</t>
+          <t>NT$ 4835.0</t>
         </is>
       </c>
       <c r="G13" s="29" t="inlineStr">
@@ -2242,22 +2242,22 @@
       </c>
       <c r="C14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 7185.0</t>
+          <t>NT$ 6970.0</t>
         </is>
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 7280.0</t>
+          <t>NT$ 7020.0</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 7050.0</t>
+          <t>NT$ 6760.0</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>NT$ 7080.0</t>
+          <t>NT$ 6805.0</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">

--- a/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
+++ b/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
@@ -631,7 +631,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>定盘时间: 2026-10-07 21:41:31 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
+          <t>定盘时间: 2026-10-08 21:50:06 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
         </is>
       </c>
     </row>
@@ -730,10 +730,10 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>开盘: 2565.0
-最高: 2585.0
-最低: 2560.0
-收盘: 2585.0</t>
+          <t>开盘: 2550.0
+最高: 2575.0
+最低: 2550.0
+收盘: 2550.0</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -751,15 +751,15 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>外资: -1164 张
-投信: +66 张
-[2026-10-07 官方结算] 投信内资买超 (+66 张) 逢低承接，外资高档调节 (-1,164 张)。</t>
+          <t>外资: -12303 张
+投信: +792 张
+[2026-10-08 官方结算] 投信内资买超 (+792 张) 逢低承接，外资高档调节 (-12,303 张)。</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 650 张 (占量 4.5%)
-[2026-10-07 筹码] 主力机构呈净卖出 (-650 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 11,001 张 (占量 54.3%)
+[2026-10-08 筹码] 主力机构呈净卖出 (-11,001 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2585.0</t>
+          <t>NT$ 2550.0</t>
         </is>
       </c>
       <c r="K4" s="9" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>14,406 张</t>
+          <t>20,245 张</t>
         </is>
       </c>
     </row>
@@ -817,10 +817,10 @@
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>开盘: 11790.0
-最高: 11790.0
-最低: 11790.0
-收盘: 11790.0</t>
+          <t>开盘: 10935.0
+最高: 10965.0
+最低: 10615.0
+收盘: 10615.0</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -838,15 +838,15 @@
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>外资: +51 张
-投信: +27 张
-[2026-10-07 官方结算] 外资与投信联手买超 (+45 张)，内外部机构共振做多。</t>
+          <t>外资: -296 张
+投信: -252 张
+[2026-10-08 官方结算] 外资与投信偏空调节 (-510 张)，机构筹码阶段获利了结。</t>
         </is>
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 45 张 (占量 19.0%)
-[2026-10-07 筹码] 主力机构呈净买入 (+45 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 510 张 (占量 29.3%)
+[2026-10-08 筹码] 主力机构呈净卖出 (-510 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 11790.0</t>
+          <t>NT$ 10615.0</t>
         </is>
       </c>
       <c r="K5" s="18" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="O5" s="16" t="inlineStr">
         <is>
-          <t>237 张</t>
+          <t>1,741 张</t>
         </is>
       </c>
     </row>
@@ -904,10 +904,10 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>开盘: 6015.0
-最高: 6325.0
-最低: 5950.0
-收盘: 5950.0</t>
+          <t>开盘: 5910.0
+最高: 6065.0
+最低: 5745.0
+收盘: 6000.0</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -925,15 +925,15 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>外资: +388 张
-投信: +38 张
-[2026-10-07 官方结算] 三大法人全线买超 (+434 张)，外资与投信合力加仓。</t>
+          <t>外资: -17 张
+投信: +59 张
+[2026-10-08 官方结算] 投信内资买超 (+59 张) 逢低承接，外资高档调节 (-17 张)。</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 434 张 (占量 16.7%)
-[2026-10-07 筹码] 主力机构呈净买入 (+434 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 32 张 (占量 1.9%)
+[2026-10-08 筹码] 主力机构呈净买入 (+32 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 5950.0</t>
+          <t>NT$ 6000.0</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>2,598 张</t>
+          <t>1,663 张</t>
         </is>
       </c>
     </row>
@@ -991,10 +991,10 @@
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>开盘: 3650.0
-最高: 3655.0
-最低: 3505.0
-收盘: 3545.0</t>
+          <t>开盘: 3445.0
+最高: 3515.0
+最低: 3410.0
+收盘: 3440.0</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -1012,15 +1012,15 @@
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>外资: -1059 张
-投信: +54 张
-[2026-10-07 官方结算] 投信内资买超 (+54 张) 逢低承接，外资高档调节 (-1,059 张)。</t>
+          <t>外资: -423 张
+投信: -183 张
+[2026-10-08 官方结算] 外资与投信偏空调节 (-552 张)，机构筹码阶段获利了结。</t>
         </is>
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 1,107 张 (占量 38.6%)
-[2026-10-07 筹码] 主力机构呈净卖出 (-1,107 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 552 张 (占量 18.6%)
+[2026-10-08 筹码] 主力机构呈净卖出 (-552 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I7" s="15" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="J7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3545.0</t>
+          <t>NT$ 3440.0</t>
         </is>
       </c>
       <c r="K7" s="18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="O7" s="16" t="inlineStr">
         <is>
-          <t>2,867 张</t>
+          <t>2,971 张</t>
         </is>
       </c>
     </row>
@@ -1078,10 +1078,10 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>开盘: 254.0
-最高: 254.5
-最低: 251.5
-收盘: 252.0</t>
+          <t>开盘: 251.0
+最高: 251.0
+最低: 249.0
+收盘: 249.0</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -1099,15 +1099,15 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>外资: -11743 张
-投信: -626 张
-[2026-10-07 官方结算] 三大法人同步卖超 (-12,639 张)，短线筹码面临清洗。</t>
+          <t>外资: -25606 张
+投信: +147 张
+[2026-10-08 官方结算] 投信内资买超 (+147 张) 逢低承接，外资高档调节 (-25,606 张)。</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 12,639 张 (占量 36.1%)
-[2026-10-07 筹码] 主力机构呈净卖出 (-12,639 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 25,528 张 (占量 66.3%)
+[2026-10-08 筹码] 主力机构呈净卖出 (-25,528 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>NT$ 252.0</t>
+          <t>NT$ 249.0</t>
         </is>
       </c>
       <c r="K8" s="9" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="O8" s="7" t="inlineStr">
         <is>
-          <t>35,015 张</t>
+          <t>38,492 张</t>
         </is>
       </c>
     </row>
@@ -1165,10 +1165,10 @@
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>开盘: 2025.0
-最高: 2045.0
-最低: 1975.0
-收盘: 1990.0</t>
+          <t>开盘: 1980.0
+最高: 1990.0
+最低: 1950.0
+收盘: 1965.0</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -1186,15 +1186,15 @@
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
-          <t>外资: -2068 张
-投信: +196 张
-[2026-10-07 官方结算] 投信内资买超 (+196 张) 逢低承接，外资高档调节 (-2,068 张)。</t>
+          <t>外资: -1169 张
+投信: +358 张
+[2026-10-08 官方结算] 投信内资买超 (+358 张) 逢低承接，外资高档调节 (-1,169 张)。</t>
         </is>
       </c>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 1,981 张 (占量 22.0%)
-[2026-10-07 筹码] 主力机构呈净卖出 (-1,981 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 806 张 (占量 16.6%)
+[2026-10-08 筹码] 主力机构呈净卖出 (-806 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I9" s="15" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="J9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1990.0</t>
+          <t>NT$ 1965.0</t>
         </is>
       </c>
       <c r="K9" s="18" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="O9" s="16" t="inlineStr">
         <is>
-          <t>8,997 张</t>
+          <t>4,846 张</t>
         </is>
       </c>
     </row>
@@ -1252,10 +1252,10 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>开盘: 2050.0
-最高: 2140.0
-最低: 2005.0
-收盘: 2015.0</t>
+          <t>开盘: 1990.0
+最高: 2100.0
+最低: 1970.0
+收盘: 2070.0</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -1273,15 +1273,15 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>外资: -216 张
-投信: -74 张
-[2026-10-07 官方结算] 三大法人同步卖超 (-343 张)，短线筹码面临清洗。</t>
+          <t>外资: +141 张
+投信: +455 张
+[2026-10-08 官方结算] 三大法人全线买超 (+675 张)，外资与投信合力加仓。</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 343 张 (占量 7.0%)
-[2026-10-07 筹码] 主力机构呈净卖出 (-343 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 675 张 (占量 16.0%)
+[2026-10-08 筹码] 主力机构呈净买入 (+675 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2015.0</t>
+          <t>NT$ 2070.0</t>
         </is>
       </c>
       <c r="K10" s="9" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>4,892 张</t>
+          <t>4,214 张</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>开盘: 2480.0
-最高: 2560.0
-最低: 2385.0
-收盘: 2400.0</t>
+          <t>开盘: 2365.0
+最高: 2390.0
+最低: 2315.0
+收盘: 2330.0</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
@@ -1360,15 +1360,15 @@
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>外资: +789 张
-投信: +20 张
-[2026-10-07 官方结算] 外资与投信联手买超 (+636 张)，内外部机构共振做多。</t>
+          <t>外资: -52 张
+投信: +22 张
+[2026-10-08 官方结算] 投信内资买超 (+22 张) 逢低承接，外资高档调节 (-52 张)。</t>
         </is>
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 636 张 (占量 12.9%)
-[2026-10-07 筹码] 主力机构呈净买入 (+636 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 51 张 (占量 3.1%)
+[2026-10-08 筹码] 主力机构呈净卖出 (-51 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I11" s="15" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="J11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2400.0</t>
+          <t>NT$ 2330.0</t>
         </is>
       </c>
       <c r="K11" s="18" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="O11" s="16" t="inlineStr">
         <is>
-          <t>4,933 张</t>
+          <t>1,670 张</t>
         </is>
       </c>
     </row>
@@ -1426,10 +1426,10 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>开盘: 735.0
-最高: 748.0
-最低: 728.0
-收盘: 732.0</t>
+          <t>开盘: 732.0
+最高: 752.0
+最低: 715.0
+收盘: 744.0</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -1447,15 +1447,15 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>外资: -1410 张
-投信: +31 张
-[2026-10-07 官方结算] 投信内资买超 (+31 张) 逢低承接，外资高档调节 (-1,410 张)。</t>
+          <t>外资: +1049 张
+投信: -234 张
+[2026-10-08 官方结算] 外资主力大幅回流 (+1,049 张)，投信阶段获利减仓 (-234 张)。</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 1,352 张 (占量 17.6%)
-[2026-10-07 筹码] 主力机构呈净卖出 (-1,352 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 1,251 张 (占量 8.3%)
+[2026-10-08 筹码] 主力机构呈净买入 (+1,251 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 732.0</t>
+          <t>NT$ 744.0</t>
         </is>
       </c>
       <c r="K12" s="9" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>7,688 张</t>
+          <t>15,115 张</t>
         </is>
       </c>
     </row>
@@ -1513,10 +1513,10 @@
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>开盘: 4920.0
-最高: 4940.0
-最低: 4835.0
-收盘: 4835.0</t>
+          <t>开盘: 4800.0
+最高: 4850.0
+最低: 4690.0
+收盘: 4690.0</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
@@ -1534,15 +1534,15 @@
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>外资: -2770 张
-投信: -286 张
-[2026-10-07 官方结算] 三大法人同步卖超 (-3,186 张)，短线筹码面临清洗。</t>
+          <t>外资: -3022 张
+投信: -158 张
+[2026-10-08 官方结算] 三大法人同步卖超 (-3,268 张)，短线筹码面临清洗。</t>
         </is>
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 3,186 张 (占量 56.4%)
-[2026-10-07 筹码] 主力机构呈净卖出 (-3,186 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 3,268 张 (占量 51.1%)
+[2026-10-08 筹码] 主力机构呈净卖出 (-3,268 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I13" s="15" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="J13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 4835.0</t>
+          <t>NT$ 4690.0</t>
         </is>
       </c>
       <c r="K13" s="18" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="O13" s="16" t="inlineStr">
         <is>
-          <t>5,645 张</t>
+          <t>6,394 张</t>
         </is>
       </c>
     </row>
@@ -1600,10 +1600,10 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>开盘: 6970.0
-最高: 7020.0
-最低: 6760.0
-收盘: 6805.0</t>
+          <t>开盘: 6800.0
+最高: 7245.0
+最低: 6775.0
+收盘: 7165.0</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -1621,15 +1621,15 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>外资: +62 张
-投信: -160 张
-[2026-10-07 官方结算] 外资主力大幅回流 (+62 张)，投信阶段获利减仓 (-160 张)。</t>
+          <t>外资: +247 张
+投信: -53 张
+[2026-10-08 官方结算] 外资主力大幅回流 (+247 张)，投信阶段获利减仓 (-53 张)。</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 94 张 (占量 10.0%)
-[2026-10-07 筹码] 主力机构呈净卖出 (-94 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 145 张 (占量 9.3%)
+[2026-10-08 筹码] 主力机构呈净买入 (+145 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>NT$ 6805.0</t>
+          <t>NT$ 7165.0</t>
         </is>
       </c>
       <c r="K14" s="9" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="O14" s="7" t="inlineStr">
         <is>
-          <t>939 张</t>
+          <t>1,552 张</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-07 21:41:31 | 策略: 3-3-4 分批建仓</t>
+          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-08 21:50:06 | 策略: 3-3-4 分批建仓</t>
         </is>
       </c>
     </row>
@@ -1772,22 +1772,22 @@
       </c>
       <c r="C4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2565.0</t>
+          <t>NT$ 2550.0</t>
         </is>
       </c>
       <c r="D4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2585.0</t>
+          <t>NT$ 2575.0</t>
         </is>
       </c>
       <c r="E4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2560.0</t>
+          <t>NT$ 2550.0</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2585.0</t>
+          <t>NT$ 2550.0</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
@@ -1819,22 +1819,22 @@
       </c>
       <c r="C5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 11790.0</t>
+          <t>NT$ 10935.0</t>
         </is>
       </c>
       <c r="D5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 11790.0</t>
+          <t>NT$ 10965.0</t>
         </is>
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 11790.0</t>
+          <t>NT$ 10615.0</t>
         </is>
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 11790.0</t>
+          <t>NT$ 10615.0</t>
         </is>
       </c>
       <c r="G5" s="29" t="inlineStr">
@@ -1866,22 +1866,22 @@
       </c>
       <c r="C6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 6015.0</t>
+          <t>NT$ 5910.0</t>
         </is>
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 6325.0</t>
+          <t>NT$ 6065.0</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5950.0</t>
+          <t>NT$ 5745.0</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 5950.0</t>
+          <t>NT$ 6000.0</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
@@ -1913,22 +1913,22 @@
       </c>
       <c r="C7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3650.0</t>
+          <t>NT$ 3445.0</t>
         </is>
       </c>
       <c r="D7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3655.0</t>
+          <t>NT$ 3515.0</t>
         </is>
       </c>
       <c r="E7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3505.0</t>
+          <t>NT$ 3410.0</t>
         </is>
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3545.0</t>
+          <t>NT$ 3440.0</t>
         </is>
       </c>
       <c r="G7" s="29" t="inlineStr">
@@ -1960,22 +1960,22 @@
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 254.0</t>
+          <t>NT$ 251.0</t>
         </is>
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 254.5</t>
+          <t>NT$ 251.0</t>
         </is>
       </c>
       <c r="E8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 251.5</t>
+          <t>NT$ 249.0</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>NT$ 252.0</t>
+          <t>NT$ 249.0</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
@@ -2007,22 +2007,22 @@
       </c>
       <c r="C9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2025.0</t>
+          <t>NT$ 1980.0</t>
         </is>
       </c>
       <c r="D9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2045.0</t>
+          <t>NT$ 1990.0</t>
         </is>
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1975.0</t>
+          <t>NT$ 1950.0</t>
         </is>
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1990.0</t>
+          <t>NT$ 1965.0</t>
         </is>
       </c>
       <c r="G9" s="29" t="inlineStr">
@@ -2054,22 +2054,22 @@
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2050.0</t>
+          <t>NT$ 1990.0</t>
         </is>
       </c>
       <c r="D10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2140.0</t>
+          <t>NT$ 2100.0</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2005.0</t>
+          <t>NT$ 1970.0</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2015.0</t>
+          <t>NT$ 2070.0</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
@@ -2101,22 +2101,22 @@
       </c>
       <c r="C11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2480.0</t>
+          <t>NT$ 2365.0</t>
         </is>
       </c>
       <c r="D11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2560.0</t>
+          <t>NT$ 2390.0</t>
         </is>
       </c>
       <c r="E11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2385.0</t>
+          <t>NT$ 2315.0</t>
         </is>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2400.0</t>
+          <t>NT$ 2330.0</t>
         </is>
       </c>
       <c r="G11" s="29" t="inlineStr">
@@ -2148,22 +2148,22 @@
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 735.0</t>
+          <t>NT$ 732.0</t>
         </is>
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 748.0</t>
+          <t>NT$ 752.0</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 728.0</t>
+          <t>NT$ 715.0</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 732.0</t>
+          <t>NT$ 744.0</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
@@ -2195,22 +2195,22 @@
       </c>
       <c r="C13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4920.0</t>
+          <t>NT$ 4800.0</t>
         </is>
       </c>
       <c r="D13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4940.0</t>
+          <t>NT$ 4850.0</t>
         </is>
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4835.0</t>
+          <t>NT$ 4690.0</t>
         </is>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 4835.0</t>
+          <t>NT$ 4690.0</t>
         </is>
       </c>
       <c r="G13" s="29" t="inlineStr">
@@ -2242,22 +2242,22 @@
       </c>
       <c r="C14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 6970.0</t>
+          <t>NT$ 6800.0</t>
         </is>
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 7020.0</t>
+          <t>NT$ 7245.0</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 6760.0</t>
+          <t>NT$ 6775.0</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>NT$ 6805.0</t>
+          <t>NT$ 7165.0</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">

--- a/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
+++ b/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
@@ -631,7 +631,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>定盘时间: 2026-10-08 21:50:06 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
+          <t>定盘时间: 2026-10-09 21:34:12 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-08 21:50:06 | 策略: 3-3-4 分批建仓</t>
+          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-09 21:34:12 | 策略: 3-3-4 分批建仓</t>
         </is>
       </c>
     </row>

--- a/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
+++ b/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
@@ -631,7 +631,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>定盘时间: 2026-10-09 21:34:12 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
+          <t>定盘时间: 2026-10-12 23:51:16 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
         </is>
       </c>
     </row>
@@ -730,10 +730,10 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>开盘: 2550.0
-最高: 2575.0
-最低: 2550.0
-收盘: 2550.0</t>
+          <t>开盘: 2510.0
+最高: 2550.0
+最低: 2510.0
+收盘: 2540.0</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -751,15 +751,15 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>外资: -12303 张
-投信: +792 张
-[2026-10-08 官方结算] 投信内资买超 (+792 张) 逢低承接，外资高档调节 (-12,303 张)。</t>
+          <t>外资: -9423 张
+投信: +588 张
+[2026-10-12 官方结算] 投信内资买超 (+588 张) 逢低承接，外资高档调节 (-9,423 张)。</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 11,001 张 (占量 54.3%)
-[2026-10-08 筹码] 主力机构呈净卖出 (-11,001 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 7,464 张 (占量 36.6%)
+[2026-10-12 筹码] 主力机构呈净卖出 (-7,464 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2550.0</t>
+          <t>NT$ 2540.0</t>
         </is>
       </c>
       <c r="K4" s="9" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>20,245 张</t>
+          <t>20,391 张</t>
         </is>
       </c>
     </row>
@@ -817,10 +817,10 @@
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>开盘: 10935.0
-最高: 10965.0
-最低: 10615.0
-收盘: 10615.0</t>
+          <t>开盘: 10320.0
+最高: 10625.0
+最低: 10120.0
+收盘: 10580.0</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -838,15 +838,15 @@
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>外资: -296 张
-投信: -252 张
-[2026-10-08 官方结算] 外资与投信偏空调节 (-510 张)，机构筹码阶段获利了结。</t>
+          <t>外资: -104 张
+投信: -98 张
+[2026-10-12 官方结算] 外资与投信偏空调节 (-179 张)，机构筹码阶段获利了结。</t>
         </is>
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 510 张 (占量 29.3%)
-[2026-10-08 筹码] 主力机构呈净卖出 (-510 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 179 张 (占量 19.5%)
+[2026-10-12 筹码] 主力机构呈净卖出 (-179 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 10615.0</t>
+          <t>NT$ 10580.0</t>
         </is>
       </c>
       <c r="K5" s="18" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="O5" s="16" t="inlineStr">
         <is>
-          <t>1,741 张</t>
+          <t>918 张</t>
         </is>
       </c>
     </row>
@@ -904,10 +904,10 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>开盘: 5910.0
-最高: 6065.0
-最低: 5745.0
-收盘: 6000.0</t>
+          <t>开盘: 5885.0
+最高: 6190.0
+最低: 5815.0
+收盘: 6150.0</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -925,15 +925,15 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>外资: -17 张
-投信: +59 张
-[2026-10-08 官方结算] 投信内资买超 (+59 张) 逢低承接，外资高档调节 (-17 张)。</t>
+          <t>外资: -7 张
+投信: +136 张
+[2026-10-12 官方结算] 投信内资买超 (+136 张) 逢低承接，外资高档调节 (-7 张)。</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 32 张 (占量 1.9%)
-[2026-10-08 筹码] 主力机构呈净买入 (+32 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 215 张 (占量 10.0%)
+[2026-10-12 筹码] 主力机构呈净买入 (+215 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 6000.0</t>
+          <t>NT$ 6150.0</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>1,663 张</t>
+          <t>2,150 张</t>
         </is>
       </c>
     </row>
@@ -991,10 +991,10 @@
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>开盘: 3445.0
-最高: 3515.0
-最低: 3410.0
-收盘: 3440.0</t>
+          <t>开盘: 3380.0
+最高: 3410.0
+最低: 3330.0
+收盘: 3385.0</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -1012,15 +1012,15 @@
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>外资: -423 张
-投信: -183 张
-[2026-10-08 官方结算] 外资与投信偏空调节 (-552 张)，机构筹码阶段获利了结。</t>
+          <t>外资: +311 张
+投信: -205 张
+[2026-10-12 官方结算] 外资主力大幅回流 (+311 张)，投信阶段获利减仓 (-205 张)。</t>
         </is>
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 552 张 (占量 18.6%)
-[2026-10-08 筹码] 主力机构呈净卖出 (-552 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 98 张 (占量 4.4%)
+[2026-10-12 筹码] 主力机构呈净买入 (+98 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I7" s="15" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="J7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3440.0</t>
+          <t>NT$ 3385.0</t>
         </is>
       </c>
       <c r="K7" s="18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="O7" s="16" t="inlineStr">
         <is>
-          <t>2,971 张</t>
+          <t>2,205 张</t>
         </is>
       </c>
     </row>
@@ -1078,10 +1078,10 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>开盘: 251.0
-最高: 251.0
-最低: 249.0
-收盘: 249.0</t>
+          <t>开盘: 245.0
+最高: 246.0
+最低: 243.5
+收盘: 244.5</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -1099,15 +1099,15 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>外资: -25606 张
-投信: +147 张
-[2026-10-08 官方结算] 投信内资买超 (+147 张) 逢低承接，外资高档调节 (-25,606 张)。</t>
+          <t>外资: -25349 张
+投信: +78 张
+[2026-10-12 官方结算] 投信内资买超 (+78 张) 逢低承接，外资高档调节 (-25,349 张)。</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 25,528 张 (占量 66.3%)
-[2026-10-08 筹码] 主力机构呈净卖出 (-25,528 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 25,242 张 (占量 50.6%)
+[2026-10-12 筹码] 主力机构呈净卖出 (-25,242 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>NT$ 249.0</t>
+          <t>NT$ 244.5</t>
         </is>
       </c>
       <c r="K8" s="9" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="O8" s="7" t="inlineStr">
         <is>
-          <t>38,492 张</t>
+          <t>49,909 张</t>
         </is>
       </c>
     </row>
@@ -1165,10 +1165,10 @@
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>开盘: 1980.0
-最高: 1990.0
-最低: 1950.0
-收盘: 1965.0</t>
+          <t>开盘: 1940.0
+最高: 1940.0
+最低: 1855.0
+收盘: 1900.0</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -1186,15 +1186,15 @@
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
-          <t>外资: -1169 张
-投信: +358 张
-[2026-10-08 官方结算] 投信内资买超 (+358 张) 逢低承接，外资高档调节 (-1,169 张)。</t>
+          <t>外资: -1865 张
+投信: -846 张
+[2026-10-12 官方结算] 外资与投信偏空调节 (-2,704 张)，机构筹码阶段获利了结。</t>
         </is>
       </c>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 806 张 (占量 16.6%)
-[2026-10-08 筹码] 主力机构呈净卖出 (-806 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 2,704 张 (占量 25.3%)
+[2026-10-12 筹码] 主力机构呈净卖出 (-2,704 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I9" s="15" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="J9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1965.0</t>
+          <t>NT$ 1900.0</t>
         </is>
       </c>
       <c r="K9" s="18" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="O9" s="16" t="inlineStr">
         <is>
-          <t>4,846 张</t>
+          <t>10,676 张</t>
         </is>
       </c>
     </row>
@@ -1252,10 +1252,10 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>开盘: 1990.0
-最高: 2100.0
-最低: 1970.0
-收盘: 2070.0</t>
+          <t>开盘: 2120.0
+最高: 2130.0
+最低: 2020.0
+收盘: 2130.0</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -1273,15 +1273,15 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>外资: +141 张
-投信: +455 张
-[2026-10-08 官方结算] 三大法人全线买超 (+675 张)，外资与投信合力加仓。</t>
+          <t>外资: -628 张
+投信: +121 张
+[2026-10-12 官方结算] 投信内资买超 (+121 张) 逢低承接，外资高档调节 (-628 张)。</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 675 张 (占量 16.0%)
-[2026-10-08 筹码] 主力机构呈净买入 (+675 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 490 张 (占量 11.4%)
+[2026-10-12 筹码] 主力机构呈净卖出 (-490 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2070.0</t>
+          <t>NT$ 2130.0</t>
         </is>
       </c>
       <c r="K10" s="9" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>4,214 张</t>
+          <t>4,299 张</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>开盘: 2365.0
-最高: 2390.0
-最低: 2315.0
-收盘: 2330.0</t>
+          <t>开盘: 2370.0
+最高: 2385.0
+最低: 2265.0
+收盘: 2365.0</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
@@ -1360,15 +1360,15 @@
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>外资: -52 张
-投信: +22 张
-[2026-10-08 官方结算] 投信内资买超 (+22 张) 逢低承接，外资高档调节 (-52 张)。</t>
+          <t>外资: -193 张
+投信: +51 张
+[2026-10-12 官方结算] 投信内资买超 (+51 张) 逢低承接，外资高档调节 (-193 张)。</t>
         </is>
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 51 张 (占量 3.1%)
-[2026-10-08 筹码] 主力机构呈净卖出 (-51 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 112 张 (占量 6.6%)
+[2026-10-12 筹码] 主力机构呈净卖出 (-112 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I11" s="15" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="J11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2330.0</t>
+          <t>NT$ 2365.0</t>
         </is>
       </c>
       <c r="K11" s="18" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="O11" s="16" t="inlineStr">
         <is>
-          <t>1,670 张</t>
+          <t>1,701 张</t>
         </is>
       </c>
     </row>
@@ -1426,10 +1426,10 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>开盘: 732.0
-最高: 752.0
-最低: 715.0
-收盘: 744.0</t>
+          <t>开盘: 745.0
+最高: 765.0
+最低: 736.0
+收盘: 762.0</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -1447,15 +1447,15 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>外资: +1049 张
-投信: -234 张
-[2026-10-08 官方结算] 外资主力大幅回流 (+1,049 张)，投信阶段获利减仓 (-234 张)。</t>
+          <t>外资: +2158 张
+投信: +813 张
+[2026-10-12 官方结算] 三大法人全线买超 (+3,222 张)，外资与投信合力加仓。</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 1,251 张 (占量 8.3%)
-[2026-10-08 筹码] 主力机构呈净买入 (+1,251 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 3,222 张 (占量 21.3%)
+[2026-10-12 筹码] 主力机构呈净买入 (+3,222 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 744.0</t>
+          <t>NT$ 762.0</t>
         </is>
       </c>
       <c r="K12" s="9" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>15,115 张</t>
+          <t>15,099 张</t>
         </is>
       </c>
     </row>
@@ -1513,10 +1513,10 @@
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>开盘: 4800.0
-最高: 4850.0
-最低: 4690.0
-收盘: 4690.0</t>
+          <t>开盘: 4615.0
+最高: 4660.0
+最低: 4545.0
+收盘: 4625.0</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
@@ -1534,15 +1534,15 @@
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>外资: -3022 张
-投信: -158 张
-[2026-10-08 官方结算] 三大法人同步卖超 (-3,268 张)，短线筹码面临清洗。</t>
+          <t>外资: -2107 张
+投信: +16 张
+[2026-10-12 官方结算] 投信内资买超 (+16 张) 逢低承接，外资高档调节 (-2,107 张)。</t>
         </is>
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 3,268 张 (占量 51.1%)
-[2026-10-08 筹码] 主力机构呈净卖出 (-3,268 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 1,955 张 (占量 30.8%)
+[2026-10-12 筹码] 主力机构呈净卖出 (-1,955 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I13" s="15" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="J13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 4690.0</t>
+          <t>NT$ 4625.0</t>
         </is>
       </c>
       <c r="K13" s="18" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="O13" s="16" t="inlineStr">
         <is>
-          <t>6,394 张</t>
+          <t>6,357 张</t>
         </is>
       </c>
     </row>
@@ -1600,10 +1600,10 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>开盘: 6800.0
-最高: 7245.0
-最低: 6775.0
-收盘: 7165.0</t>
+          <t>开盘: 7165.0
+最高: 7190.0
+最低: 6920.0
+收盘: 7160.0</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -1621,15 +1621,15 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>外资: +247 张
-投信: -53 张
-[2026-10-08 官方结算] 外资主力大幅回流 (+247 张)，投信阶段获利减仓 (-53 张)。</t>
+          <t>外资: -127 张
+投信: +48 张
+[2026-10-12 官方结算] 投信内资买超 (+48 张) 逢低承接，外资高档调节 (-127 张)。</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 145 张 (占量 9.3%)
-[2026-10-08 筹码] 主力机构呈净买入 (+145 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 72 张 (占量 10.8%)
+[2026-10-12 筹码] 主力机构呈净卖出 (-72 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>NT$ 7165.0</t>
+          <t>NT$ 7160.0</t>
         </is>
       </c>
       <c r="K14" s="9" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="O14" s="7" t="inlineStr">
         <is>
-          <t>1,552 张</t>
+          <t>667 张</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-09 21:34:12 | 策略: 3-3-4 分批建仓</t>
+          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-12 23:51:16 | 策略: 3-3-4 分批建仓</t>
         </is>
       </c>
     </row>
@@ -1772,22 +1772,22 @@
       </c>
       <c r="C4" s="24" t="inlineStr">
         <is>
+          <t>NT$ 2510.0</t>
+        </is>
+      </c>
+      <c r="D4" s="24" t="inlineStr">
+        <is>
           <t>NT$ 2550.0</t>
         </is>
       </c>
-      <c r="D4" s="24" t="inlineStr">
-        <is>
-          <t>NT$ 2575.0</t>
-        </is>
-      </c>
       <c r="E4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2550.0</t>
+          <t>NT$ 2510.0</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2550.0</t>
+          <t>NT$ 2540.0</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
@@ -1819,22 +1819,22 @@
       </c>
       <c r="C5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 10935.0</t>
+          <t>NT$ 10320.0</t>
         </is>
       </c>
       <c r="D5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 10965.0</t>
+          <t>NT$ 10625.0</t>
         </is>
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 10615.0</t>
+          <t>NT$ 10120.0</t>
         </is>
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 10615.0</t>
+          <t>NT$ 10580.0</t>
         </is>
       </c>
       <c r="G5" s="29" t="inlineStr">
@@ -1866,22 +1866,22 @@
       </c>
       <c r="C6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5910.0</t>
+          <t>NT$ 5885.0</t>
         </is>
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 6065.0</t>
+          <t>NT$ 6190.0</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5745.0</t>
+          <t>NT$ 5815.0</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 6000.0</t>
+          <t>NT$ 6150.0</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
@@ -1913,22 +1913,22 @@
       </c>
       <c r="C7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3445.0</t>
+          <t>NT$ 3380.0</t>
         </is>
       </c>
       <c r="D7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3515.0</t>
+          <t>NT$ 3410.0</t>
         </is>
       </c>
       <c r="E7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3410.0</t>
+          <t>NT$ 3330.0</t>
         </is>
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3440.0</t>
+          <t>NT$ 3385.0</t>
         </is>
       </c>
       <c r="G7" s="29" t="inlineStr">
@@ -1960,22 +1960,22 @@
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 251.0</t>
+          <t>NT$ 245.0</t>
         </is>
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 251.0</t>
+          <t>NT$ 246.0</t>
         </is>
       </c>
       <c r="E8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 249.0</t>
+          <t>NT$ 243.5</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>NT$ 249.0</t>
+          <t>NT$ 244.5</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
@@ -2007,22 +2007,22 @@
       </c>
       <c r="C9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1980.0</t>
+          <t>NT$ 1940.0</t>
         </is>
       </c>
       <c r="D9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1990.0</t>
+          <t>NT$ 1940.0</t>
         </is>
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1950.0</t>
+          <t>NT$ 1855.0</t>
         </is>
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1965.0</t>
+          <t>NT$ 1900.0</t>
         </is>
       </c>
       <c r="G9" s="29" t="inlineStr">
@@ -2054,22 +2054,22 @@
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1990.0</t>
+          <t>NT$ 2120.0</t>
         </is>
       </c>
       <c r="D10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2100.0</t>
+          <t>NT$ 2130.0</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1970.0</t>
+          <t>NT$ 2020.0</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2070.0</t>
+          <t>NT$ 2130.0</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
@@ -2101,22 +2101,22 @@
       </c>
       <c r="C11" s="28" t="inlineStr">
         <is>
+          <t>NT$ 2370.0</t>
+        </is>
+      </c>
+      <c r="D11" s="28" t="inlineStr">
+        <is>
+          <t>NT$ 2385.0</t>
+        </is>
+      </c>
+      <c r="E11" s="28" t="inlineStr">
+        <is>
+          <t>NT$ 2265.0</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
           <t>NT$ 2365.0</t>
-        </is>
-      </c>
-      <c r="D11" s="28" t="inlineStr">
-        <is>
-          <t>NT$ 2390.0</t>
-        </is>
-      </c>
-      <c r="E11" s="28" t="inlineStr">
-        <is>
-          <t>NT$ 2315.0</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t>NT$ 2330.0</t>
         </is>
       </c>
       <c r="G11" s="29" t="inlineStr">
@@ -2148,22 +2148,22 @@
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 732.0</t>
+          <t>NT$ 745.0</t>
         </is>
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 752.0</t>
+          <t>NT$ 765.0</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 715.0</t>
+          <t>NT$ 736.0</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 744.0</t>
+          <t>NT$ 762.0</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
@@ -2195,22 +2195,22 @@
       </c>
       <c r="C13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4800.0</t>
+          <t>NT$ 4615.0</t>
         </is>
       </c>
       <c r="D13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4850.0</t>
+          <t>NT$ 4660.0</t>
         </is>
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4690.0</t>
+          <t>NT$ 4545.0</t>
         </is>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 4690.0</t>
+          <t>NT$ 4625.0</t>
         </is>
       </c>
       <c r="G13" s="29" t="inlineStr">
@@ -2242,22 +2242,22 @@
       </c>
       <c r="C14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 6800.0</t>
+          <t>NT$ 7165.0</t>
         </is>
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 7245.0</t>
+          <t>NT$ 7190.0</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 6775.0</t>
+          <t>NT$ 6920.0</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>NT$ 7165.0</t>
+          <t>NT$ 7160.0</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">

--- a/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
+++ b/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
@@ -631,7 +631,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>定盘时间: 2026-10-12 23:51:16 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
+          <t>定盘时间: 2026-10-13 22:27:40 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
         </is>
       </c>
     </row>
@@ -730,10 +730,10 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>开盘: 2510.0
-最高: 2550.0
-最低: 2510.0
-收盘: 2540.0</t>
+          <t>开盘: 2500.0
+最高: 2510.0
+最低: 2490.0
+收盘: 2490.0</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -751,15 +751,15 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>外资: -9423 张
-投信: +588 张
-[2026-10-12 官方结算] 投信内资买超 (+588 张) 逢低承接，外资高档调节 (-9,423 张)。</t>
+          <t>外资: -25642 张
+投信: +3005 张
+[2026-10-13 官方结算] 投信内资买超 (+3,005 张) 逢低承接，外资高档调节 (-25,642 张)。</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 7,464 张 (占量 36.6%)
-[2026-10-12 筹码] 主力机构呈净卖出 (-7,464 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 20,145 张 (占量 58.4%)
+[2026-10-13 筹码] 主力机构呈净卖出 (-20,145 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2540.0</t>
+          <t>NT$ 2490.0</t>
         </is>
       </c>
       <c r="K4" s="9" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>20,391 张</t>
+          <t>34,480 张</t>
         </is>
       </c>
     </row>
@@ -817,10 +817,10 @@
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>开盘: 10320.0
-最高: 10625.0
-最低: 10120.0
-收盘: 10580.0</t>
+          <t>开盘: 10200.0
+最高: 10490.0
+最低: 10015.0
+收盘: 10060.0</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -838,15 +838,15 @@
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>外资: -104 张
-投信: -98 张
-[2026-10-12 官方结算] 外资与投信偏空调节 (-179 张)，机构筹码阶段获利了结。</t>
+          <t>外资: +137 张
+投信: -213 张
+[2026-10-13 官方结算] 外资主力大幅回流 (+137 张)，投信阶段获利减仓 (-213 张)。</t>
         </is>
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 179 张 (占量 19.5%)
-[2026-10-12 筹码] 主力机构呈净卖出 (-179 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 72 张 (占量 8.7%)
+[2026-10-13 筹码] 主力机构呈净卖出 (-72 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 10580.0</t>
+          <t>NT$ 10060.0</t>
         </is>
       </c>
       <c r="K5" s="18" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="O5" s="16" t="inlineStr">
         <is>
-          <t>918 张</t>
+          <t>832 张</t>
         </is>
       </c>
     </row>
@@ -904,10 +904,10 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>开盘: 5885.0
-最高: 6190.0
-最低: 5815.0
-收盘: 6150.0</t>
+          <t>开盘: 5915.0
+最高: 5930.0
+最低: 5535.0
+收盘: 5545.0</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -925,15 +925,15 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>外资: -7 张
-投信: +136 张
-[2026-10-12 官方结算] 投信内资买超 (+136 张) 逢低承接，外资高档调节 (-7 张)。</t>
+          <t>外资: -927 张
+投信: -170 张
+[2026-10-13 官方结算] 外资与投信偏空调节 (-1,026 张)，机构筹码阶段获利了结。</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 215 张 (占量 10.0%)
-[2026-10-12 筹码] 主力机构呈净买入 (+215 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 1,026 张 (占量 24.8%)
+[2026-10-13 筹码] 主力机构呈净卖出 (-1,026 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 6150.0</t>
+          <t>NT$ 5545.0</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>2,150 张</t>
+          <t>4,129 张</t>
         </is>
       </c>
     </row>
@@ -991,10 +991,10 @@
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>开盘: 3380.0
-最高: 3410.0
-最低: 3330.0
-收盘: 3385.0</t>
+          <t>开盘: 3310.0
+最高: 3420.0
+最低: 3275.0
+收盘: 3280.0</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -1012,15 +1012,15 @@
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>外资: +311 张
-投信: -205 张
-[2026-10-12 官方结算] 外资主力大幅回流 (+311 张)，投信阶段获利减仓 (-205 张)。</t>
+          <t>外资: -571 张
+投信: +234 张
+[2026-10-13 官方结算] 投信内资买超 (+234 张) 逢低承接，外资高档调节 (-571 张)。</t>
         </is>
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 98 张 (占量 4.4%)
-[2026-10-12 筹码] 主力机构呈净买入 (+98 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 372 张 (占量 14.5%)
+[2026-10-13 筹码] 主力机构呈净卖出 (-372 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I7" s="15" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="J7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3385.0</t>
+          <t>NT$ 3280.0</t>
         </is>
       </c>
       <c r="K7" s="18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="O7" s="16" t="inlineStr">
         <is>
-          <t>2,205 张</t>
+          <t>2,573 张</t>
         </is>
       </c>
     </row>
@@ -1078,10 +1078,10 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>开盘: 245.0
-最高: 246.0
-最低: 243.5
-收盘: 244.5</t>
+          <t>开盘: 243.5
+最高: 243.5
+最低: 239.0
+收盘: 240.0</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -1099,15 +1099,15 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>外资: -25349 张
-投信: +78 张
-[2026-10-12 官方结算] 投信内资买超 (+78 张) 逢低承接，外资高档调节 (-25,349 张)。</t>
+          <t>外资: -19578 张
+投信: +765 张
+[2026-10-13 官方结算] 投信内资买超 (+765 张) 逢低承接，外资高档调节 (-19,578 张)。</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 25,242 张 (占量 50.6%)
-[2026-10-12 筹码] 主力机构呈净卖出 (-25,242 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 18,442 张 (占量 43.1%)
+[2026-10-13 筹码] 主力机构呈净卖出 (-18,442 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>NT$ 244.5</t>
+          <t>NT$ 240.0</t>
         </is>
       </c>
       <c r="K8" s="9" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="O8" s="7" t="inlineStr">
         <is>
-          <t>49,909 张</t>
+          <t>42,745 张</t>
         </is>
       </c>
     </row>
@@ -1165,10 +1165,10 @@
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>开盘: 1940.0
-最高: 1940.0
-最低: 1855.0
-收盘: 1900.0</t>
+          <t>开盘: 1830.0
+最高: 1855.0
+最低: 1770.0
+收盘: 1775.0</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -1186,15 +1186,15 @@
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
-          <t>外资: -1865 张
-投信: -846 张
-[2026-10-12 官方结算] 外资与投信偏空调节 (-2,704 张)，机构筹码阶段获利了结。</t>
+          <t>外资: -5830 张
+投信: -1458 张
+[2026-10-13 官方结算] 三大法人同步卖超 (-7,482 张)，短线筹码面临清洗。</t>
         </is>
       </c>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 2,704 张 (占量 25.3%)
-[2026-10-12 筹码] 主力机构呈净卖出 (-2,704 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 7,482 张 (占量 60.7%)
+[2026-10-13 筹码] 主力机构呈净卖出 (-7,482 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I9" s="15" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="J9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1900.0</t>
+          <t>NT$ 1775.0</t>
         </is>
       </c>
       <c r="K9" s="18" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="O9" s="16" t="inlineStr">
         <is>
-          <t>10,676 张</t>
+          <t>12,317 张</t>
         </is>
       </c>
     </row>
@@ -1252,10 +1252,10 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>开盘: 2120.0
-最高: 2130.0
-最低: 2020.0
-收盘: 2130.0</t>
+          <t>开盘: 2090.0
+最高: 2145.0
+最低: 2015.0
+收盘: 2040.0</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -1273,15 +1273,15 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>外资: -628 张
-投信: +121 张
-[2026-10-12 官方结算] 投信内资买超 (+121 张) 逢低承接，外资高档调节 (-628 张)。</t>
+          <t>外资: -1033 张
+投信: +643 张
+[2026-10-13 官方结算] 投信内资买超 (+643 张) 逢低承接，外资高档调节 (-1,033 张)。</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 490 张 (占量 11.4%)
-[2026-10-12 筹码] 主力机构呈净卖出 (-490 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 450 张 (占量 8.6%)
+[2026-10-13 筹码] 主力机构呈净卖出 (-450 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2130.0</t>
+          <t>NT$ 2040.0</t>
         </is>
       </c>
       <c r="K10" s="9" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>4,299 张</t>
+          <t>5,204 张</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>开盘: 2370.0
-最高: 2385.0
-最低: 2265.0
-收盘: 2365.0</t>
+          <t>开盘: 2285.0
+最高: 2320.0
+最低: 2180.0
+收盘: 2200.0</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
@@ -1360,15 +1360,15 @@
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>外资: -193 张
-投信: +51 张
-[2026-10-12 官方结算] 投信内资买超 (+51 张) 逢低承接，外资高档调节 (-193 张)。</t>
+          <t>外资: -536 张
+投信: -208 张
+[2026-10-13 官方结算] 外资与投信偏空调节 (-668 张)，机构筹码阶段获利了结。</t>
         </is>
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 112 张 (占量 6.6%)
-[2026-10-12 筹码] 主力机构呈净卖出 (-112 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 668 张 (占量 25.3%)
+[2026-10-13 筹码] 主力机构呈净卖出 (-668 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I11" s="15" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="J11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2365.0</t>
+          <t>NT$ 2200.0</t>
         </is>
       </c>
       <c r="K11" s="18" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="O11" s="16" t="inlineStr">
         <is>
-          <t>1,701 张</t>
+          <t>2,638 张</t>
         </is>
       </c>
     </row>
@@ -1426,10 +1426,10 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>开盘: 745.0
-最高: 765.0
-最低: 736.0
-收盘: 762.0</t>
+          <t>开盘: 749.0
+最高: 751.0
+最低: 731.0
+收盘: 740.0</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -1447,15 +1447,15 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>外资: +2158 张
-投信: +813 张
-[2026-10-12 官方结算] 三大法人全线买超 (+3,222 张)，外资与投信合力加仓。</t>
+          <t>外资: -4265 张
+投信: +1884 张
+[2026-10-13 官方结算] 投信内资买超 (+1,884 张) 逢低承接，外资高档调节 (-4,265 张)。</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 3,222 张 (占量 21.3%)
-[2026-10-12 筹码] 主力机构呈净买入 (+3,222 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 2,546 张 (占量 16.4%)
+[2026-10-13 筹码] 主力机构呈净卖出 (-2,546 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 762.0</t>
+          <t>NT$ 740.0</t>
         </is>
       </c>
       <c r="K12" s="9" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>15,099 张</t>
+          <t>15,526 张</t>
         </is>
       </c>
     </row>
@@ -1513,10 +1513,10 @@
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>开盘: 4615.0
-最高: 4660.0
-最低: 4545.0
-收盘: 4625.0</t>
+          <t>开盘: 4485.0
+最高: 4575.0
+最低: 4460.0
+收盘: 4525.0</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
@@ -1534,15 +1534,15 @@
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>外资: -2107 张
-投信: +16 张
-[2026-10-12 官方结算] 投信内资买超 (+16 张) 逢低承接，外资高档调节 (-2,107 张)。</t>
+          <t>外资: -3010 张
+投信: +227 张
+[2026-10-13 官方结算] 投信内资买超 (+227 张) 逢低承接，外资高档调节 (-3,010 张)。</t>
         </is>
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 1,955 张 (占量 30.8%)
-[2026-10-12 筹码] 主力机构呈净卖出 (-1,955 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 2,652 张 (占量 40.3%)
+[2026-10-13 筹码] 主力机构呈净卖出 (-2,652 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I13" s="15" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="J13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 4625.0</t>
+          <t>NT$ 4525.0</t>
         </is>
       </c>
       <c r="K13" s="18" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="O13" s="16" t="inlineStr">
         <is>
-          <t>6,357 张</t>
+          <t>6,575 张</t>
         </is>
       </c>
     </row>
@@ -1600,10 +1600,10 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>开盘: 7165.0
-最高: 7190.0
-最低: 6920.0
-收盘: 7160.0</t>
+          <t>开盘: 7020.0
+最高: 7215.0
+最低: 6940.0
+收盘: 6990.0</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -1621,15 +1621,15 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>外资: -127 张
-投信: +48 张
-[2026-10-12 官方结算] 投信内资买超 (+48 张) 逢低承接，外资高档调节 (-127 张)。</t>
+          <t>外资: +82 张
+投信: -43 张
+[2026-10-13 官方结算] 外资主力大幅回流 (+82 张)，投信阶段获利减仓 (-43 张)。</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 72 张 (占量 10.8%)
-[2026-10-12 筹码] 主力机构呈净卖出 (-72 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 43 张 (占量 4.6%)
+[2026-10-13 筹码] 主力机构呈净买入 (+43 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>NT$ 7160.0</t>
+          <t>NT$ 6990.0</t>
         </is>
       </c>
       <c r="K14" s="9" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="O14" s="7" t="inlineStr">
         <is>
-          <t>667 张</t>
+          <t>926 张</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-12 23:51:16 | 策略: 3-3-4 分批建仓</t>
+          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-13 22:27:40 | 策略: 3-3-4 分批建仓</t>
         </is>
       </c>
     </row>
@@ -1772,22 +1772,22 @@
       </c>
       <c r="C4" s="24" t="inlineStr">
         <is>
+          <t>NT$ 2500.0</t>
+        </is>
+      </c>
+      <c r="D4" s="24" t="inlineStr">
+        <is>
           <t>NT$ 2510.0</t>
         </is>
       </c>
-      <c r="D4" s="24" t="inlineStr">
-        <is>
-          <t>NT$ 2550.0</t>
-        </is>
-      </c>
       <c r="E4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2510.0</t>
+          <t>NT$ 2490.0</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2540.0</t>
+          <t>NT$ 2490.0</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
@@ -1819,22 +1819,22 @@
       </c>
       <c r="C5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 10320.0</t>
+          <t>NT$ 10200.0</t>
         </is>
       </c>
       <c r="D5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 10625.0</t>
+          <t>NT$ 10490.0</t>
         </is>
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 10120.0</t>
+          <t>NT$ 10015.0</t>
         </is>
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 10580.0</t>
+          <t>NT$ 10060.0</t>
         </is>
       </c>
       <c r="G5" s="29" t="inlineStr">
@@ -1866,22 +1866,22 @@
       </c>
       <c r="C6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5885.0</t>
+          <t>NT$ 5915.0</t>
         </is>
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 6190.0</t>
+          <t>NT$ 5930.0</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5815.0</t>
+          <t>NT$ 5535.0</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 6150.0</t>
+          <t>NT$ 5545.0</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
@@ -1913,22 +1913,22 @@
       </c>
       <c r="C7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3380.0</t>
+          <t>NT$ 3310.0</t>
         </is>
       </c>
       <c r="D7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3410.0</t>
+          <t>NT$ 3420.0</t>
         </is>
       </c>
       <c r="E7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3330.0</t>
+          <t>NT$ 3275.0</t>
         </is>
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3385.0</t>
+          <t>NT$ 3280.0</t>
         </is>
       </c>
       <c r="G7" s="29" t="inlineStr">
@@ -1960,22 +1960,22 @@
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 245.0</t>
+          <t>NT$ 243.5</t>
         </is>
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 246.0</t>
+          <t>NT$ 243.5</t>
         </is>
       </c>
       <c r="E8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 243.5</t>
+          <t>NT$ 239.0</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>NT$ 244.5</t>
+          <t>NT$ 240.0</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
@@ -2007,22 +2007,22 @@
       </c>
       <c r="C9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1940.0</t>
+          <t>NT$ 1830.0</t>
         </is>
       </c>
       <c r="D9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1940.0</t>
+          <t>NT$ 1855.0</t>
         </is>
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1855.0</t>
+          <t>NT$ 1770.0</t>
         </is>
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1900.0</t>
+          <t>NT$ 1775.0</t>
         </is>
       </c>
       <c r="G9" s="29" t="inlineStr">
@@ -2054,22 +2054,22 @@
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2120.0</t>
+          <t>NT$ 2090.0</t>
         </is>
       </c>
       <c r="D10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2130.0</t>
+          <t>NT$ 2145.0</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2020.0</t>
+          <t>NT$ 2015.0</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2130.0</t>
+          <t>NT$ 2040.0</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
@@ -2101,22 +2101,22 @@
       </c>
       <c r="C11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2370.0</t>
+          <t>NT$ 2285.0</t>
         </is>
       </c>
       <c r="D11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2385.0</t>
+          <t>NT$ 2320.0</t>
         </is>
       </c>
       <c r="E11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2265.0</t>
+          <t>NT$ 2180.0</t>
         </is>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2365.0</t>
+          <t>NT$ 2200.0</t>
         </is>
       </c>
       <c r="G11" s="29" t="inlineStr">
@@ -2148,22 +2148,22 @@
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 745.0</t>
+          <t>NT$ 749.0</t>
         </is>
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 765.0</t>
+          <t>NT$ 751.0</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 736.0</t>
+          <t>NT$ 731.0</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 762.0</t>
+          <t>NT$ 740.0</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
@@ -2195,22 +2195,22 @@
       </c>
       <c r="C13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4615.0</t>
+          <t>NT$ 4485.0</t>
         </is>
       </c>
       <c r="D13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4660.0</t>
+          <t>NT$ 4575.0</t>
         </is>
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4545.0</t>
+          <t>NT$ 4460.0</t>
         </is>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 4625.0</t>
+          <t>NT$ 4525.0</t>
         </is>
       </c>
       <c r="G13" s="29" t="inlineStr">
@@ -2242,22 +2242,22 @@
       </c>
       <c r="C14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 7165.0</t>
+          <t>NT$ 7020.0</t>
         </is>
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 7190.0</t>
+          <t>NT$ 7215.0</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 6920.0</t>
+          <t>NT$ 6940.0</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>NT$ 7160.0</t>
+          <t>NT$ 6990.0</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">

--- a/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
+++ b/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
@@ -631,7 +631,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>定盘时间: 2026-10-13 22:27:40 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
+          <t>定盘时间: 2026-10-14 20:13:00 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
         </is>
       </c>
     </row>
@@ -730,8 +730,8 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>开盘: 2500.0
-最高: 2510.0
+          <t>开盘: 2505.0
+最高: 2535.0
 最低: 2490.0
 收盘: 2490.0</t>
         </is>
@@ -751,15 +751,15 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>外资: -25642 张
-投信: +3005 张
-[2026-10-13 官方结算] 投信内资买超 (+3,005 张) 逢低承接，外资高档调节 (-25,642 张)。</t>
+          <t>外资: -6753 张
+投信: +800 张
+[2026-10-14 官方结算] 投信内资买超 (+800 张) 逢低承接，外资高档调节 (-6,753 张)。</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 20,145 张 (占量 58.4%)
-[2026-10-13 筹码] 主力机构呈净卖出 (-20,145 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 5,417 张 (占量 23.4%)
+[2026-10-14 筹码] 主力机构呈净卖出 (-5,417 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>34,480 张</t>
+          <t>23,175 张</t>
         </is>
       </c>
     </row>
@@ -817,10 +817,10 @@
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>开盘: 10200.0
-最高: 10490.0
-最低: 10015.0
-收盘: 10060.0</t>
+          <t>开盘: 10155.0
+最高: 10295.0
+最低: 9950.0
+收盘: 10005.0</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -838,15 +838,15 @@
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>外资: +137 张
-投信: -213 张
-[2026-10-13 官方结算] 外资主力大幅回流 (+137 张)，投信阶段获利减仓 (-213 张)。</t>
+          <t>外资: -76 张
+投信: -70 张
+[2026-10-14 官方结算] 三大法人同步卖超 (-158 张)，短线筹码面临清洗。</t>
         </is>
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 72 张 (占量 8.7%)
-[2026-10-13 筹码] 主力机构呈净卖出 (-72 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 158 张 (占量 27.2%)
+[2026-10-14 筹码] 主力机构呈净卖出 (-158 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 10060.0</t>
+          <t>NT$ 10005.0</t>
         </is>
       </c>
       <c r="K5" s="18" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="O5" s="16" t="inlineStr">
         <is>
-          <t>832 张</t>
+          <t>580 张</t>
         </is>
       </c>
     </row>
@@ -904,10 +904,10 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>开盘: 5915.0
-最高: 5930.0
-最低: 5535.0
-收盘: 5545.0</t>
+          <t>开盘: 5545.0
+最高: 5645.0
+最低: 5510.0
+收盘: 5520.0</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -925,15 +925,15 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>外资: -927 张
-投信: -170 张
-[2026-10-13 官方结算] 外资与投信偏空调节 (-1,026 张)，机构筹码阶段获利了结。</t>
+          <t>外资: -107 张
+投信: +172 张
+[2026-10-14 官方结算] 投信内资买超 (+172 张) 逢低承接，外资高档调节 (-107 张)。</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 1,026 张 (占量 24.8%)
-[2026-10-13 筹码] 主力机构呈净卖出 (-1,026 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 39 张 (占量 1.8%)
+[2026-10-14 筹码] 主力机构呈净买入 (+39 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 5545.0</t>
+          <t>NT$ 5520.0</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>4,129 张</t>
+          <t>2,143 张</t>
         </is>
       </c>
     </row>
@@ -991,10 +991,10 @@
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>开盘: 3310.0
-最高: 3420.0
+          <t>开盘: 3330.0
+最高: 3350.0
 最低: 3275.0
-收盘: 3280.0</t>
+收盘: 3315.0</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -1012,15 +1012,15 @@
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>外资: -571 张
-投信: +234 张
-[2026-10-13 官方结算] 投信内资买超 (+234 张) 逢低承接，外资高档调节 (-571 张)。</t>
+          <t>外资: -548 张
+投信: +92 张
+[2026-10-14 官方结算] 投信内资买超 (+92 张) 逢低承接，外资高档调节 (-548 张)。</t>
         </is>
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 372 张 (占量 14.5%)
-[2026-10-13 筹码] 主力机构呈净卖出 (-372 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 499 张 (占量 22.4%)
+[2026-10-14 筹码] 主力机构呈净卖出 (-499 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I7" s="15" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="J7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3280.0</t>
+          <t>NT$ 3315.0</t>
         </is>
       </c>
       <c r="K7" s="18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="O7" s="16" t="inlineStr">
         <is>
-          <t>2,573 张</t>
+          <t>2,226 张</t>
         </is>
       </c>
     </row>
@@ -1078,10 +1078,10 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>开盘: 243.5
-最高: 243.5
-最低: 239.0
-收盘: 240.0</t>
+          <t>开盘: 241.5
+最高: 246.0
+最低: 241.0
+收盘: 243.0</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -1099,15 +1099,15 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>外资: -19578 张
-投信: +765 张
-[2026-10-13 官方结算] 投信内资买超 (+765 张) 逢低承接，外资高档调节 (-19,578 张)。</t>
+          <t>外资: +2170 张
+投信: +557 张
+[2026-10-14 官方结算] 三大法人全线买超 (+3,334 张)，外资与投信合力加仓。</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 18,442 张 (占量 43.1%)
-[2026-10-13 筹码] 主力机构呈净卖出 (-18,442 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 3,334 张 (占量 10.0%)
+[2026-10-14 筹码] 主力机构呈净买入 (+3,334 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>NT$ 240.0</t>
+          <t>NT$ 243.0</t>
         </is>
       </c>
       <c r="K8" s="9" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="O8" s="7" t="inlineStr">
         <is>
-          <t>42,745 张</t>
+          <t>33,296 张</t>
         </is>
       </c>
     </row>
@@ -1165,10 +1165,10 @@
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>开盘: 1830.0
-最高: 1855.0
-最低: 1770.0
-收盘: 1775.0</t>
+          <t>开盘: 1790.0
+最高: 1820.0
+最低: 1775.0
+收盘: 1785.0</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -1186,15 +1186,15 @@
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
-          <t>外资: -5830 张
-投信: -1458 张
-[2026-10-13 官方结算] 三大法人同步卖超 (-7,482 张)，短线筹码面临清洗。</t>
+          <t>外资: -1237 张
+投信: -176 张
+[2026-10-14 官方结算] 三大法人同步卖超 (-1,444 张)，短线筹码面临清洗。</t>
         </is>
       </c>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 7,482 张 (占量 60.7%)
-[2026-10-13 筹码] 主力机构呈净卖出 (-7,482 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 1,444 张 (占量 16.0%)
+[2026-10-14 筹码] 主力机构呈净卖出 (-1,444 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I9" s="15" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="J9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1775.0</t>
+          <t>NT$ 1785.0</t>
         </is>
       </c>
       <c r="K9" s="18" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="O9" s="16" t="inlineStr">
         <is>
-          <t>12,317 张</t>
+          <t>9,021 张</t>
         </is>
       </c>
     </row>
@@ -1252,10 +1252,10 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>开盘: 2090.0
-最高: 2145.0
-最低: 2015.0
-收盘: 2040.0</t>
+          <t>开盘: 2075.0
+最高: 2110.0
+最低: 2050.0
+收盘: 2050.0</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -1273,15 +1273,15 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>外资: -1033 张
-投信: +643 张
-[2026-10-13 官方结算] 投信内资买超 (+643 张) 逢低承接，外资高档调节 (-1,033 张)。</t>
+          <t>外资: -596 张
+投信: +413 张
+[2026-10-14 官方结算] 投信内资买超 (+413 张) 逢低承接，外资高档调节 (-596 张)。</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 450 张 (占量 8.6%)
-[2026-10-13 筹码] 主力机构呈净卖出 (-450 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 216 张 (占量 5.1%)
+[2026-10-14 筹码] 主力机构呈净卖出 (-216 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2040.0</t>
+          <t>NT$ 2050.0</t>
         </is>
       </c>
       <c r="K10" s="9" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>5,204 张</t>
+          <t>4,209 张</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>开盘: 2285.0
-最高: 2320.0
-最低: 2180.0
-收盘: 2200.0</t>
+          <t>开盘: 2255.0
+最高: 2350.0
+最低: 2230.0
+收盘: 2250.0</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
@@ -1360,15 +1360,15 @@
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>外资: -536 张
-投信: -208 张
-[2026-10-13 官方结算] 外资与投信偏空调节 (-668 张)，机构筹码阶段获利了结。</t>
+          <t>外资: -205 张
+投信: -16 张
+[2026-10-14 官方结算] 外资与投信偏空调节 (-203 张)，机构筹码阶段获利了结。</t>
         </is>
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 668 张 (占量 25.3%)
-[2026-10-13 筹码] 主力机构呈净卖出 (-668 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 203 张 (占量 8.3%)
+[2026-10-14 筹码] 主力机构呈净卖出 (-203 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I11" s="15" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="J11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2200.0</t>
+          <t>NT$ 2250.0</t>
         </is>
       </c>
       <c r="K11" s="18" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="O11" s="16" t="inlineStr">
         <is>
-          <t>2,638 张</t>
+          <t>2,444 张</t>
         </is>
       </c>
     </row>
@@ -1426,10 +1426,10 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>开盘: 749.0
-最高: 751.0
-最低: 731.0
-收盘: 740.0</t>
+          <t>开盘: 755.0
+最高: 763.0
+最低: 742.0
+收盘: 747.0</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -1447,15 +1447,15 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>外资: -4265 张
-投信: +1884 张
-[2026-10-13 官方结算] 投信内资买超 (+1,884 张) 逢低承接，外资高档调节 (-4,265 张)。</t>
+          <t>外资: +497 张
+投信: +561 张
+[2026-10-14 官方结算] 三大法人全线买超 (+1,116 张)，外资与投信合力加仓。</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 2,546 张 (占量 16.4%)
-[2026-10-13 筹码] 主力机构呈净卖出 (-2,546 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 1,116 张 (占量 8.9%)
+[2026-10-14 筹码] 主力机构呈净买入 (+1,116 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 740.0</t>
+          <t>NT$ 747.0</t>
         </is>
       </c>
       <c r="K12" s="9" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>15,526 张</t>
+          <t>12,572 张</t>
         </is>
       </c>
     </row>
@@ -1513,10 +1513,10 @@
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>开盘: 4485.0
-最高: 4575.0
-最低: 4460.0
-收盘: 4525.0</t>
+          <t>开盘: 4525.0
+最高: 4600.0
+最低: 4475.0
+收盘: 4475.0</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
@@ -1534,15 +1534,15 @@
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>外资: -3010 张
-投信: +227 张
-[2026-10-13 官方结算] 投信内资买超 (+227 张) 逢低承接，外资高档调节 (-3,010 张)。</t>
+          <t>外资: -3513 张
+投信: +239 张
+[2026-10-14 官方结算] 投信内资买超 (+239 张) 逢低承接，外资高档调节 (-3,513 张)。</t>
         </is>
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 2,652 张 (占量 40.3%)
-[2026-10-13 筹码] 主力机构呈净卖出 (-2,652 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 3,257 张 (占量 49.4%)
+[2026-10-14 筹码] 主力机构呈净卖出 (-3,257 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I13" s="15" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="J13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 4525.0</t>
+          <t>NT$ 4475.0</t>
         </is>
       </c>
       <c r="K13" s="18" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="O13" s="16" t="inlineStr">
         <is>
-          <t>6,575 张</t>
+          <t>6,587 张</t>
         </is>
       </c>
     </row>
@@ -1600,10 +1600,10 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>开盘: 7020.0
-最高: 7215.0
-最低: 6940.0
-收盘: 6990.0</t>
+          <t>开盘: 7120.0
+最高: 7330.0
+最低: 6965.0
+收盘: 7070.0</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -1621,15 +1621,15 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>外资: +82 张
-投信: -43 张
-[2026-10-13 官方结算] 外资主力大幅回流 (+82 张)，投信阶段获利减仓 (-43 张)。</t>
+          <t>外资: -340 张
+投信: +252 张
+[2026-10-14 官方结算] 投信内资买超 (+252 张) 逢低承接，外资高档调节 (-340 张)。</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 43 张 (占量 4.6%)
-[2026-10-13 筹码] 主力机构呈净买入 (+43 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 156 张 (占量 13.9%)
+[2026-10-14 筹码] 主力机构呈净卖出 (-156 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>NT$ 6990.0</t>
+          <t>NT$ 7070.0</t>
         </is>
       </c>
       <c r="K14" s="9" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="O14" s="7" t="inlineStr">
         <is>
-          <t>926 张</t>
+          <t>1,122 张</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-13 22:27:40 | 策略: 3-3-4 分批建仓</t>
+          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-14 20:13:00 | 策略: 3-3-4 分批建仓</t>
         </is>
       </c>
     </row>
@@ -1772,12 +1772,12 @@
       </c>
       <c r="C4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2500.0</t>
+          <t>NT$ 2505.0</t>
         </is>
       </c>
       <c r="D4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2510.0</t>
+          <t>NT$ 2535.0</t>
         </is>
       </c>
       <c r="E4" s="24" t="inlineStr">
@@ -1819,22 +1819,22 @@
       </c>
       <c r="C5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 10200.0</t>
+          <t>NT$ 10155.0</t>
         </is>
       </c>
       <c r="D5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 10490.0</t>
+          <t>NT$ 10295.0</t>
         </is>
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 10015.0</t>
+          <t>NT$ 9950.0</t>
         </is>
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 10060.0</t>
+          <t>NT$ 10005.0</t>
         </is>
       </c>
       <c r="G5" s="29" t="inlineStr">
@@ -1866,22 +1866,22 @@
       </c>
       <c r="C6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5915.0</t>
+          <t>NT$ 5545.0</t>
         </is>
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5930.0</t>
+          <t>NT$ 5645.0</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5535.0</t>
+          <t>NT$ 5510.0</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 5545.0</t>
+          <t>NT$ 5520.0</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
@@ -1913,12 +1913,12 @@
       </c>
       <c r="C7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3310.0</t>
+          <t>NT$ 3330.0</t>
         </is>
       </c>
       <c r="D7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3420.0</t>
+          <t>NT$ 3350.0</t>
         </is>
       </c>
       <c r="E7" s="28" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3280.0</t>
+          <t>NT$ 3315.0</t>
         </is>
       </c>
       <c r="G7" s="29" t="inlineStr">
@@ -1960,22 +1960,22 @@
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 243.5</t>
+          <t>NT$ 241.5</t>
         </is>
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 243.5</t>
+          <t>NT$ 246.0</t>
         </is>
       </c>
       <c r="E8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 239.0</t>
+          <t>NT$ 241.0</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>NT$ 240.0</t>
+          <t>NT$ 243.0</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
@@ -2007,22 +2007,22 @@
       </c>
       <c r="C9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1830.0</t>
+          <t>NT$ 1790.0</t>
         </is>
       </c>
       <c r="D9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1855.0</t>
+          <t>NT$ 1820.0</t>
         </is>
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1770.0</t>
+          <t>NT$ 1775.0</t>
         </is>
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1775.0</t>
+          <t>NT$ 1785.0</t>
         </is>
       </c>
       <c r="G9" s="29" t="inlineStr">
@@ -2054,22 +2054,22 @@
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2090.0</t>
+          <t>NT$ 2075.0</t>
         </is>
       </c>
       <c r="D10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2145.0</t>
+          <t>NT$ 2110.0</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2015.0</t>
+          <t>NT$ 2050.0</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2040.0</t>
+          <t>NT$ 2050.0</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
@@ -2101,22 +2101,22 @@
       </c>
       <c r="C11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2285.0</t>
+          <t>NT$ 2255.0</t>
         </is>
       </c>
       <c r="D11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2320.0</t>
+          <t>NT$ 2350.0</t>
         </is>
       </c>
       <c r="E11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2180.0</t>
+          <t>NT$ 2230.0</t>
         </is>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2200.0</t>
+          <t>NT$ 2250.0</t>
         </is>
       </c>
       <c r="G11" s="29" t="inlineStr">
@@ -2148,22 +2148,22 @@
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 749.0</t>
+          <t>NT$ 755.0</t>
         </is>
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 751.0</t>
+          <t>NT$ 763.0</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 731.0</t>
+          <t>NT$ 742.0</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 740.0</t>
+          <t>NT$ 747.0</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
@@ -2195,22 +2195,22 @@
       </c>
       <c r="C13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4485.0</t>
+          <t>NT$ 4525.0</t>
         </is>
       </c>
       <c r="D13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4575.0</t>
+          <t>NT$ 4600.0</t>
         </is>
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4460.0</t>
+          <t>NT$ 4475.0</t>
         </is>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 4525.0</t>
+          <t>NT$ 4475.0</t>
         </is>
       </c>
       <c r="G13" s="29" t="inlineStr">
@@ -2242,22 +2242,22 @@
       </c>
       <c r="C14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 7020.0</t>
+          <t>NT$ 7120.0</t>
         </is>
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 7215.0</t>
+          <t>NT$ 7330.0</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 6940.0</t>
+          <t>NT$ 6965.0</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>NT$ 6990.0</t>
+          <t>NT$ 7070.0</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">

--- a/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
+++ b/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
@@ -631,7 +631,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>定盘时间: 2026-10-14 20:13:00 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
+          <t>定盘时间: 2026-10-15 19:52:13 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
         </is>
       </c>
     </row>
@@ -730,10 +730,10 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>开盘: 2505.0
-最高: 2535.0
-最低: 2490.0
-收盘: 2490.0</t>
+          <t>开盘: 2420.0
+最高: 2450.0
+最低: 2420.0
+收盘: 2440.0</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -751,15 +751,15 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>外资: -6753 张
-投信: +800 张
-[2026-10-14 官方结算] 投信内资买超 (+800 张) 逢低承接，外资高档调节 (-6,753 张)。</t>
+          <t>外资: -34112 张
+投信: +3222 张
+[2026-10-15 官方结算] 投信内资买超 (+3,222 张) 逢低承接，外资高档调节 (-34,112 张)。</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 5,417 张 (占量 23.4%)
-[2026-10-14 筹码] 主力机构呈净卖出 (-5,417 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 23,474 张 (占量 48.9%)
+[2026-10-15 筹码] 主力机构呈净卖出 (-23,474 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2490.0</t>
+          <t>NT$ 2440.0</t>
         </is>
       </c>
       <c r="K4" s="9" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>23,175 张</t>
+          <t>48,032 张</t>
         </is>
       </c>
     </row>
@@ -817,10 +817,10 @@
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>开盘: 10155.0
-最高: 10295.0
-最低: 9950.0
-收盘: 10005.0</t>
+          <t>开盘: 9700.0
+最高: 9920.0
+最低: 9500.0
+收盘: 9720.0</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -838,15 +838,15 @@
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>外资: -76 张
-投信: -70 张
-[2026-10-14 官方结算] 三大法人同步卖超 (-158 张)，短线筹码面临清洗。</t>
+          <t>外资: -86 张
+投信: -13 张
+[2026-10-15 官方结算] 三大法人同步卖超 (-107 张)，短线筹码面临清洗。</t>
         </is>
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 158 张 (占量 27.2%)
-[2026-10-14 筹码] 主力机构呈净卖出 (-158 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 107 张 (占量 17.0%)
+[2026-10-15 筹码] 主力机构呈净卖出 (-107 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 10005.0</t>
+          <t>NT$ 9720.0</t>
         </is>
       </c>
       <c r="K5" s="18" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="O5" s="16" t="inlineStr">
         <is>
-          <t>580 张</t>
+          <t>628 张</t>
         </is>
       </c>
     </row>
@@ -904,10 +904,10 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>开盘: 5545.0
-最高: 5645.0
-最低: 5510.0
-收盘: 5520.0</t>
+          <t>开盘: 5010.0
+最高: 5330.0
+最低: 4980.0
+收盘: 5120.0</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -925,15 +925,15 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>外资: -107 张
-投信: +172 张
-[2026-10-14 官方结算] 投信内资买超 (+172 张) 逢低承接，外资高档调节 (-107 张)。</t>
+          <t>外资: -963 张
+投信: +267 张
+[2026-10-15 官方结算] 投信内资买超 (+267 张) 逢低承接，外资高档调节 (-963 张)。</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 39 张 (占量 1.8%)
-[2026-10-14 筹码] 主力机构呈净买入 (+39 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 634 张 (占量 11.7%)
+[2026-10-15 筹码] 主力机构呈净卖出 (-634 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 5520.0</t>
+          <t>NT$ 5120.0</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>2,143 张</t>
+          <t>5,439 张</t>
         </is>
       </c>
     </row>
@@ -991,10 +991,10 @@
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>开盘: 3330.0
-最高: 3350.0
-最低: 3275.0
-收盘: 3315.0</t>
+          <t>开盘: 3200.0
+最高: 3220.0
+最低: 3050.0
+收盘: 3085.0</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -1012,15 +1012,15 @@
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>外资: -548 张
-投信: +92 张
-[2026-10-14 官方结算] 投信内资买超 (+92 张) 逢低承接，外资高档调节 (-548 张)。</t>
+          <t>外资: -1360 张
+投信: +266 张
+[2026-10-15 官方结算] 投信内资买超 (+266 张) 逢低承接，外资高档调节 (-1,360 张)。</t>
         </is>
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 499 张 (占量 22.4%)
-[2026-10-14 筹码] 主力机构呈净卖出 (-499 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 1,126 张 (占量 30.4%)
+[2026-10-15 筹码] 主力机构呈净卖出 (-1,126 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I7" s="15" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="J7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3315.0</t>
+          <t>NT$ 3085.0</t>
         </is>
       </c>
       <c r="K7" s="18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="O7" s="16" t="inlineStr">
         <is>
-          <t>2,226 张</t>
+          <t>3,705 张</t>
         </is>
       </c>
     </row>
@@ -1078,10 +1078,10 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>开盘: 241.5
-最高: 246.0
-最低: 241.0
-收盘: 243.0</t>
+          <t>开盘: 240.0
+最高: 240.0
+最低: 238.0
+收盘: 239.5</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -1099,15 +1099,15 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>外资: +2170 张
-投信: +557 张
-[2026-10-14 官方结算] 三大法人全线买超 (+3,334 张)，外资与投信合力加仓。</t>
+          <t>外资: -13279 张
+投信: +1239 张
+[2026-10-15 官方结算] 投信内资买超 (+1,239 张) 逢低承接，外资高档调节 (-13,279 张)。</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 3,334 张 (占量 10.0%)
-[2026-10-14 筹码] 主力机构呈净买入 (+3,334 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 10,172 张 (占量 21.9%)
+[2026-10-15 筹码] 主力机构呈净卖出 (-10,172 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>NT$ 243.0</t>
+          <t>NT$ 239.5</t>
         </is>
       </c>
       <c r="K8" s="9" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="O8" s="7" t="inlineStr">
         <is>
-          <t>33,296 张</t>
+          <t>46,466 张</t>
         </is>
       </c>
     </row>
@@ -1165,10 +1165,10 @@
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>开盘: 1790.0
-最高: 1820.0
-最低: 1775.0
-收盘: 1785.0</t>
+          <t>开盘: 1690.0
+最高: 1700.0
+最低: 1610.0
+收盘: 1630.0</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -1186,15 +1186,15 @@
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
-          <t>外资: -1237 张
-投信: -176 张
-[2026-10-14 官方结算] 三大法人同步卖超 (-1,444 张)，短线筹码面临清洗。</t>
+          <t>外资: -10831 张
+投信: +580 张
+[2026-10-15 官方结算] 投信内资买超 (+580 张) 逢低承接，外资高档调节 (-10,831 张)。</t>
         </is>
       </c>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 1,444 张 (占量 16.0%)
-[2026-10-14 筹码] 主力机构呈净卖出 (-1,444 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 10,346 张 (占量 51.6%)
+[2026-10-15 筹码] 主力机构呈净卖出 (-10,346 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I9" s="15" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="J9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1785.0</t>
+          <t>NT$ 1630.0</t>
         </is>
       </c>
       <c r="K9" s="18" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="O9" s="16" t="inlineStr">
         <is>
-          <t>9,021 张</t>
+          <t>20,034 张</t>
         </is>
       </c>
     </row>
@@ -1252,10 +1252,10 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>开盘: 2075.0
-最高: 2110.0
-最低: 2050.0
-收盘: 2050.0</t>
+          <t>开盘: 1915.0
+最高: 2005.0
+最低: 1910.0
+收盘: 1950.0</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -1273,15 +1273,15 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>外资: -596 张
-投信: +413 张
-[2026-10-14 官方结算] 投信内资买超 (+413 张) 逢低承接，外资高档调节 (-596 张)。</t>
+          <t>外资: -811 张
+投信: +371 张
+[2026-10-15 官方结算] 投信内资买超 (+371 张) 逢低承接，外资高档调节 (-811 张)。</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 216 张 (占量 5.1%)
-[2026-10-14 筹码] 主力机构呈净卖出 (-216 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 327 张 (占量 7.7%)
+[2026-10-15 筹码] 主力机构呈净卖出 (-327 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2050.0</t>
+          <t>NT$ 1950.0</t>
         </is>
       </c>
       <c r="K10" s="9" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>4,209 张</t>
+          <t>4,267 张</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>开盘: 2255.0
-最高: 2350.0
-最低: 2230.0
-收盘: 2250.0</t>
+          <t>开盘: 2125.0
+最高: 2160.0
+最低: 2025.0
+收盘: 2025.0</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
@@ -1360,15 +1360,15 @@
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>外资: -205 张
-投信: -16 张
-[2026-10-14 官方结算] 外资与投信偏空调节 (-203 张)，机构筹码阶段获利了结。</t>
+          <t>外资: -1391 张
+投信: -7 张
+[2026-10-15 官方结算] 外资与投信偏空调节 (-1,266 张)，机构筹码阶段获利了结。</t>
         </is>
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 203 张 (占量 8.3%)
-[2026-10-14 筹码] 主力机构呈净卖出 (-203 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 1,266 张 (占量 35.1%)
+[2026-10-15 筹码] 主力机构呈净卖出 (-1,266 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I11" s="15" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="J11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2250.0</t>
+          <t>NT$ 2025.0</t>
         </is>
       </c>
       <c r="K11" s="18" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="O11" s="16" t="inlineStr">
         <is>
-          <t>2,444 张</t>
+          <t>3,607 张</t>
         </is>
       </c>
     </row>
@@ -1426,10 +1426,10 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>开盘: 755.0
-最高: 763.0
-最低: 742.0
-收盘: 747.0</t>
+          <t>开盘: 696.0
+最高: 699.0
+最低: 673.0
+收盘: 673.0</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -1447,15 +1447,15 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>外资: +497 张
-投信: +561 张
-[2026-10-14 官方结算] 三大法人全线买超 (+1,116 张)，外资与投信合力加仓。</t>
+          <t>外资: -21307 张
+投信: +2529 张
+[2026-10-15 官方结算] 投信内资买超 (+2,529 张) 逢低承接，外资高档调节 (-21,307 张)。</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 1,116 张 (占量 8.9%)
-[2026-10-14 筹码] 主力机构呈净买入 (+1,116 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 18,822 张 (占量 54.7%)
+[2026-10-15 筹码] 主力机构呈净卖出 (-18,822 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 747.0</t>
+          <t>NT$ 673.0</t>
         </is>
       </c>
       <c r="K12" s="9" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>12,572 张</t>
+          <t>34,430 张</t>
         </is>
       </c>
     </row>
@@ -1513,10 +1513,10 @@
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>开盘: 4525.0
-最高: 4600.0
-最低: 4475.0
-收盘: 4475.0</t>
+          <t>开盘: 4195.0
+最高: 4295.0
+最低: 4145.0
+收盘: 4165.0</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
@@ -1534,15 +1534,15 @@
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>外资: -3513 张
-投信: +239 张
-[2026-10-14 官方结算] 投信内资买超 (+239 张) 逢低承接，外资高档调节 (-3,513 张)。</t>
+          <t>外资: -6885 张
+投信: +259 张
+[2026-10-15 官方结算] 投信内资买超 (+259 张) 逢低承接，外资高档调节 (-6,885 张)。</t>
         </is>
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 3,257 张 (占量 49.4%)
-[2026-10-14 筹码] 主力机构呈净卖出 (-3,257 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 6,313 张 (占量 43.5%)
+[2026-10-15 筹码] 主力机构呈净卖出 (-6,313 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I13" s="15" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="J13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 4475.0</t>
+          <t>NT$ 4165.0</t>
         </is>
       </c>
       <c r="K13" s="18" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="O13" s="16" t="inlineStr">
         <is>
-          <t>6,587 张</t>
+          <t>14,496 张</t>
         </is>
       </c>
     </row>
@@ -1600,10 +1600,10 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>开盘: 7120.0
-最高: 7330.0
-最低: 6965.0
-收盘: 7070.0</t>
+          <t>开盘: 6720.0
+最高: 7070.0
+最低: 6660.0
+收盘: 6765.0</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -1621,15 +1621,15 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>外资: -340 张
-投信: +252 张
-[2026-10-14 官方结算] 投信内资买超 (+252 张) 逢低承接，外资高档调节 (-340 张)。</t>
+          <t>外资: -402 张
+投信: +277 张
+[2026-10-15 官方结算] 投信内资买超 (+277 张) 逢低承接，外资高档调节 (-402 张)。</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 156 张 (占量 13.9%)
-[2026-10-14 筹码] 主力机构呈净卖出 (-156 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 12 张 (占量 0.7%)
+[2026-10-15 筹码] 主力机构呈净卖出 (-12 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>NT$ 7070.0</t>
+          <t>NT$ 6765.0</t>
         </is>
       </c>
       <c r="K14" s="9" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="O14" s="7" t="inlineStr">
         <is>
-          <t>1,122 张</t>
+          <t>1,656 张</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-14 20:13:00 | 策略: 3-3-4 分批建仓</t>
+          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-15 19:52:13 | 策略: 3-3-4 分批建仓</t>
         </is>
       </c>
     </row>
@@ -1772,22 +1772,22 @@
       </c>
       <c r="C4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2505.0</t>
+          <t>NT$ 2420.0</t>
         </is>
       </c>
       <c r="D4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2535.0</t>
+          <t>NT$ 2450.0</t>
         </is>
       </c>
       <c r="E4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2490.0</t>
+          <t>NT$ 2420.0</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2490.0</t>
+          <t>NT$ 2440.0</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
@@ -1819,22 +1819,22 @@
       </c>
       <c r="C5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 10155.0</t>
+          <t>NT$ 9700.0</t>
         </is>
       </c>
       <c r="D5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 10295.0</t>
+          <t>NT$ 9920.0</t>
         </is>
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 9950.0</t>
+          <t>NT$ 9500.0</t>
         </is>
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 10005.0</t>
+          <t>NT$ 9720.0</t>
         </is>
       </c>
       <c r="G5" s="29" t="inlineStr">
@@ -1866,22 +1866,22 @@
       </c>
       <c r="C6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5545.0</t>
+          <t>NT$ 5010.0</t>
         </is>
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5645.0</t>
+          <t>NT$ 5330.0</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5510.0</t>
+          <t>NT$ 4980.0</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 5520.0</t>
+          <t>NT$ 5120.0</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
@@ -1913,22 +1913,22 @@
       </c>
       <c r="C7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3330.0</t>
+          <t>NT$ 3200.0</t>
         </is>
       </c>
       <c r="D7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3350.0</t>
+          <t>NT$ 3220.0</t>
         </is>
       </c>
       <c r="E7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3275.0</t>
+          <t>NT$ 3050.0</t>
         </is>
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3315.0</t>
+          <t>NT$ 3085.0</t>
         </is>
       </c>
       <c r="G7" s="29" t="inlineStr">
@@ -1960,22 +1960,22 @@
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 241.5</t>
+          <t>NT$ 240.0</t>
         </is>
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 246.0</t>
+          <t>NT$ 240.0</t>
         </is>
       </c>
       <c r="E8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 241.0</t>
+          <t>NT$ 238.0</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>NT$ 243.0</t>
+          <t>NT$ 239.5</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
@@ -2007,22 +2007,22 @@
       </c>
       <c r="C9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1790.0</t>
+          <t>NT$ 1690.0</t>
         </is>
       </c>
       <c r="D9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1820.0</t>
+          <t>NT$ 1700.0</t>
         </is>
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1775.0</t>
+          <t>NT$ 1610.0</t>
         </is>
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1785.0</t>
+          <t>NT$ 1630.0</t>
         </is>
       </c>
       <c r="G9" s="29" t="inlineStr">
@@ -2054,22 +2054,22 @@
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2075.0</t>
+          <t>NT$ 1915.0</t>
         </is>
       </c>
       <c r="D10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2110.0</t>
+          <t>NT$ 2005.0</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2050.0</t>
+          <t>NT$ 1910.0</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2050.0</t>
+          <t>NT$ 1950.0</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
@@ -2101,22 +2101,22 @@
       </c>
       <c r="C11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2255.0</t>
+          <t>NT$ 2125.0</t>
         </is>
       </c>
       <c r="D11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2350.0</t>
+          <t>NT$ 2160.0</t>
         </is>
       </c>
       <c r="E11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2230.0</t>
+          <t>NT$ 2025.0</t>
         </is>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2250.0</t>
+          <t>NT$ 2025.0</t>
         </is>
       </c>
       <c r="G11" s="29" t="inlineStr">
@@ -2148,22 +2148,22 @@
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 755.0</t>
+          <t>NT$ 696.0</t>
         </is>
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 763.0</t>
+          <t>NT$ 699.0</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 742.0</t>
+          <t>NT$ 673.0</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 747.0</t>
+          <t>NT$ 673.0</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
@@ -2195,22 +2195,22 @@
       </c>
       <c r="C13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4525.0</t>
+          <t>NT$ 4195.0</t>
         </is>
       </c>
       <c r="D13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4600.0</t>
+          <t>NT$ 4295.0</t>
         </is>
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4475.0</t>
+          <t>NT$ 4145.0</t>
         </is>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 4475.0</t>
+          <t>NT$ 4165.0</t>
         </is>
       </c>
       <c r="G13" s="29" t="inlineStr">
@@ -2242,22 +2242,22 @@
       </c>
       <c r="C14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 7120.0</t>
+          <t>NT$ 6720.0</t>
         </is>
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 7330.0</t>
+          <t>NT$ 7070.0</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 6965.0</t>
+          <t>NT$ 6660.0</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>NT$ 7070.0</t>
+          <t>NT$ 6765.0</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">

--- a/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
+++ b/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
@@ -631,7 +631,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>定盘时间: 2026-10-15 19:52:13 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
+          <t>定盘时间: 2026-10-16 19:43:44 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
         </is>
       </c>
     </row>
@@ -730,10 +730,10 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>开盘: 2420.0
-最高: 2450.0
+          <t>开盘: 2430.0
+最高: 2445.0
 最低: 2420.0
-收盘: 2440.0</t>
+收盘: 2420.0</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -746,20 +746,20 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15 (26Q3 法说会) | 每月 10 日发布营收</t>
+          <t>2026-10-15 (26Q3 法說會已舉行)；下一次財報/法說會日期待公司公告 | 每月 10 日发布营收</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>外资: -34112 张
-投信: +3222 张
-[2026-10-15 官方结算] 投信内资买超 (+3,222 张) 逢低承接，外资高档调节 (-34,112 张)。</t>
+          <t>外资: -22047 张
+投信: +710 张
+[2026-10-16 官方结算] 投信内资买超 (+710 张) 逢低承接，外资高档调节 (-22,047 张)。</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 23,474 张 (占量 48.9%)
-[2026-10-15 筹码] 主力机构呈净卖出 (-23,474 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 22,372 张 (占量 67.0%)
+[2026-10-16 筹码] 主力机构呈净卖出 (-22,372 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2440.0</t>
+          <t>NT$ 2420.0</t>
         </is>
       </c>
       <c r="K4" s="9" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>48,032 张</t>
+          <t>33,389 张</t>
         </is>
       </c>
     </row>
@@ -817,10 +817,10 @@
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>开盘: 9700.0
-最高: 9920.0
-最低: 9500.0
-收盘: 9720.0</t>
+          <t>开盘: 10140.0
+最高: 10175.0
+最低: 9775.0
+收盘: 9955.0</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -838,15 +838,15 @@
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>外资: -86 张
-投信: -13 张
-[2026-10-15 官方结算] 三大法人同步卖超 (-107 张)，短线筹码面临清洗。</t>
+          <t>外资: -141 张
+投信: +47 张
+[2026-10-16 官方结算] 投信内资买超 (+47 张) 逢低承接，外资高档调节 (-141 张)。</t>
         </is>
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 107 张 (占量 17.0%)
-[2026-10-15 筹码] 主力机构呈净卖出 (-107 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 109 张 (占量 20.8%)
+[2026-10-16 筹码] 主力机构呈净卖出 (-109 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 9720.0</t>
+          <t>NT$ 9955.0</t>
         </is>
       </c>
       <c r="K5" s="18" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="O5" s="16" t="inlineStr">
         <is>
-          <t>628 张</t>
+          <t>523 张</t>
         </is>
       </c>
     </row>
@@ -904,10 +904,10 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>开盘: 5010.0
-最高: 5330.0
-最低: 4980.0
-收盘: 5120.0</t>
+          <t>开盘: 5155.0
+最高: 5260.0
+最低: 5005.0
+收盘: 5165.0</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -925,15 +925,15 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>外资: -963 张
-投信: +267 张
-[2026-10-15 官方结算] 投信内资买超 (+267 张) 逢低承接，外资高档调节 (-963 张)。</t>
+          <t>外资: +196 张
+投信: -186 张
+[2026-10-16 官方结算] 外资主力大幅回流 (+196 张)，投信阶段获利减仓 (-186 张)。</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 634 张 (占量 11.7%)
-[2026-10-15 筹码] 主力机构呈净卖出 (-634 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 63 张 (占量 2.5%)
+[2026-10-16 筹码] 主力机构呈净卖出 (-63 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 5120.0</t>
+          <t>NT$ 5165.0</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>5,439 张</t>
+          <t>2,552 张</t>
         </is>
       </c>
     </row>
@@ -991,10 +991,10 @@
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>开盘: 3200.0
-最高: 3220.0
-最低: 3050.0
-收盘: 3085.0</t>
+          <t>开盘: 3115.0
+最高: 3355.0
+最低: 3080.0
+收盘: 3315.0</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -1012,15 +1012,15 @@
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>外资: -1360 张
-投信: +266 张
-[2026-10-15 官方结算] 投信内资买超 (+266 张) 逢低承接，外资高档调节 (-1,360 张)。</t>
+          <t>外资: -725 张
+投信: +591 张
+[2026-10-16 官方结算] 投信内资买超 (+591 张) 逢低承接，外资高档调节 (-725 张)。</t>
         </is>
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 1,126 张 (占量 30.4%)
-[2026-10-15 筹码] 主力机构呈净卖出 (-1,126 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 154 张 (占量 4.3%)
+[2026-10-16 筹码] 主力机构呈净卖出 (-154 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I7" s="15" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="J7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3085.0</t>
+          <t>NT$ 3315.0</t>
         </is>
       </c>
       <c r="K7" s="18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="O7" s="16" t="inlineStr">
         <is>
-          <t>3,705 张</t>
+          <t>3,568 张</t>
         </is>
       </c>
     </row>
@@ -1078,10 +1078,10 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>开盘: 240.0
-最高: 240.0
-最低: 238.0
-收盘: 239.5</t>
+          <t>开盘: 241.5
+最高: 247.0
+最低: 240.5
+收盘: 244.0</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -1099,15 +1099,15 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>外资: -13279 张
-投信: +1239 张
-[2026-10-15 官方结算] 投信内资买超 (+1,239 张) 逢低承接，外资高档调节 (-13,279 张)。</t>
+          <t>外资: +22670 张
+投信: -239 张
+[2026-10-16 官方结算] 外资主力大幅回流 (+22,670 张)，投信阶段获利减仓 (-239 张)。</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 10,172 张 (占量 21.9%)
-[2026-10-15 筹码] 主力机构呈净卖出 (-10,172 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 23,159 张 (占量 47.0%)
+[2026-10-16 筹码] 主力机构呈净买入 (+23,159 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>NT$ 239.5</t>
+          <t>NT$ 244.0</t>
         </is>
       </c>
       <c r="K8" s="9" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="O8" s="7" t="inlineStr">
         <is>
-          <t>46,466 张</t>
+          <t>49,268 张</t>
         </is>
       </c>
     </row>
@@ -1165,10 +1165,10 @@
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>开盘: 1690.0
-最高: 1700.0
-最低: 1610.0
-收盘: 1630.0</t>
+          <t>开盘: 1650.0
+最高: 1665.0
+最低: 1630.0
+收盘: 1635.0</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -1186,15 +1186,15 @@
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
-          <t>外资: -10831 张
-投信: +580 张
-[2026-10-15 官方结算] 投信内资买超 (+580 张) 逢低承接，外资高档调节 (-10,831 张)。</t>
+          <t>外资: -2134 张
+投信: +268 张
+[2026-10-16 官方结算] 投信内资买超 (+268 张) 逢低承接，外资高档调节 (-2,134 张)。</t>
         </is>
       </c>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 10,346 张 (占量 51.6%)
-[2026-10-15 筹码] 主力机构呈净卖出 (-10,346 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 2,005 张 (占量 27.1%)
+[2026-10-16 筹码] 主力机构呈净卖出 (-2,005 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I9" s="15" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="J9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1630.0</t>
+          <t>NT$ 1635.0</t>
         </is>
       </c>
       <c r="K9" s="18" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="O9" s="16" t="inlineStr">
         <is>
-          <t>20,034 张</t>
+          <t>7,388 张</t>
         </is>
       </c>
     </row>
@@ -1252,10 +1252,10 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>开盘: 1915.0
-最高: 2005.0
-最低: 1910.0
-收盘: 1950.0</t>
+          <t>开盘: 1965.0
+最高: 2030.0
+最低: 1935.0
+收盘: 1980.0</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -1273,15 +1273,15 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>外资: -811 张
-投信: +371 张
-[2026-10-15 官方结算] 投信内资买超 (+371 张) 逢低承接，外资高档调节 (-811 张)。</t>
+          <t>外资: -63 张
+投信: +354 张
+[2026-10-16 官方结算] 投信内资买超 (+354 张) 逢低承接，外资高档调节 (-63 张)。</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 327 张 (占量 7.7%)
-[2026-10-15 筹码] 主力机构呈净卖出 (-327 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 305 张 (占量 9.0%)
+[2026-10-16 筹码] 主力机构呈净买入 (+305 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 1950.0</t>
+          <t>NT$ 1980.0</t>
         </is>
       </c>
       <c r="K10" s="9" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>4,267 张</t>
+          <t>3,397 张</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>开盘: 2125.0
-最高: 2160.0
-最低: 2025.0
-收盘: 2025.0</t>
+          <t>开盘: 1985.0
+最高: 2045.0
+最低: 1960.0
+收盘: 2000.0</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
@@ -1360,15 +1360,15 @@
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>外资: -1391 张
-投信: -7 张
-[2026-10-15 官方结算] 外资与投信偏空调节 (-1,266 张)，机构筹码阶段获利了结。</t>
+          <t>外资: -717 张
+投信: +134 张
+[2026-10-16 官方结算] 投信内资买超 (+134 张) 逢低承接，外资高档调节 (-717 张)。</t>
         </is>
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 1,266 张 (占量 35.1%)
-[2026-10-15 筹码] 主力机构呈净卖出 (-1,266 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 534 张 (占量 15.5%)
+[2026-10-16 筹码] 主力机构呈净卖出 (-534 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I11" s="15" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="J11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2025.0</t>
+          <t>NT$ 2000.0</t>
         </is>
       </c>
       <c r="K11" s="18" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="O11" s="16" t="inlineStr">
         <is>
-          <t>3,607 张</t>
+          <t>3,436 张</t>
         </is>
       </c>
     </row>
@@ -1426,10 +1426,10 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>开盘: 696.0
-最高: 699.0
-最低: 673.0
-收盘: 673.0</t>
+          <t>开盘: 652.0
+最高: 678.0
+最低: 652.0
+收盘: 671.0</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -1447,15 +1447,15 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>外资: -21307 张
-投信: +2529 张
-[2026-10-15 官方结算] 投信内资买超 (+2,529 张) 逢低承接，外资高档调节 (-21,307 张)。</t>
+          <t>外资: -1531 张
+投信: -1815 张
+[2026-10-16 官方结算] 外资与投信偏空调节 (-3,188 张)，机构筹码阶段获利了结。</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 18,822 张 (占量 54.7%)
-[2026-10-15 筹码] 主力机构呈净卖出 (-18,822 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 3,188 张 (占量 17.4%)
+[2026-10-16 筹码] 主力机构呈净卖出 (-3,188 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 673.0</t>
+          <t>NT$ 671.0</t>
         </is>
       </c>
       <c r="K12" s="9" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>34,430 张</t>
+          <t>18,308 张</t>
         </is>
       </c>
     </row>
@@ -1513,10 +1513,10 @@
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>开盘: 4195.0
-最高: 4295.0
-最低: 4145.0
-收盘: 4165.0</t>
+          <t>开盘: 4275.0
+最高: 4360.0
+最低: 4240.0
+收盘: 4250.0</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
@@ -1534,15 +1534,15 @@
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>外资: -6885 张
-投信: +259 张
-[2026-10-15 官方结算] 投信内资买超 (+259 张) 逢低承接，外资高档调节 (-6,885 张)。</t>
+          <t>外资: -1623 张
+投信: +471 张
+[2026-10-16 官方结算] 投信内资买超 (+471 张) 逢低承接，外资高档调节 (-1,623 张)。</t>
         </is>
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 6,313 张 (占量 43.5%)
-[2026-10-15 筹码] 主力机构呈净卖出 (-6,313 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 1,384 张 (占量 17.9%)
+[2026-10-16 筹码] 主力机构呈净卖出 (-1,384 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I13" s="15" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="J13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 4165.0</t>
+          <t>NT$ 4250.0</t>
         </is>
       </c>
       <c r="K13" s="18" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="O13" s="16" t="inlineStr">
         <is>
-          <t>14,496 张</t>
+          <t>7,748 张</t>
         </is>
       </c>
     </row>
@@ -1600,10 +1600,10 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>开盘: 6720.0
-最高: 7070.0
-最低: 6660.0
-收盘: 6765.0</t>
+          <t>开盘: 6765.0
+最高: 6950.0
+最低: 6675.0
+收盘: 6730.0</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -1621,15 +1621,15 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>外资: -402 张
-投信: +277 张
-[2026-10-15 官方结算] 投信内资买超 (+277 张) 逢低承接，外资高档调节 (-402 张)。</t>
+          <t>外资: -110 张
+投信: +50 张
+[2026-10-16 官方结算] 投信内资买超 (+50 张) 逢低承接，外资高档调节 (-110 张)。</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 12 张 (占量 0.7%)
-[2026-10-15 筹码] 主力机构呈净卖出 (-12 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 93 张 (占量 8.5%)
+[2026-10-16 筹码] 主力机构呈净卖出 (-93 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>NT$ 6765.0</t>
+          <t>NT$ 6730.0</t>
         </is>
       </c>
       <c r="K14" s="9" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="O14" s="7" t="inlineStr">
         <is>
-          <t>1,656 张</t>
+          <t>1,099 张</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-15 19:52:13 | 策略: 3-3-4 分批建仓</t>
+          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-16 19:43:44 | 策略: 3-3-4 分批建仓</t>
         </is>
       </c>
     </row>
@@ -1772,22 +1772,22 @@
       </c>
       <c r="C4" s="24" t="inlineStr">
         <is>
+          <t>NT$ 2430.0</t>
+        </is>
+      </c>
+      <c r="D4" s="24" t="inlineStr">
+        <is>
+          <t>NT$ 2445.0</t>
+        </is>
+      </c>
+      <c r="E4" s="24" t="inlineStr">
+        <is>
           <t>NT$ 2420.0</t>
         </is>
       </c>
-      <c r="D4" s="24" t="inlineStr">
-        <is>
-          <t>NT$ 2450.0</t>
-        </is>
-      </c>
-      <c r="E4" s="24" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>NT$ 2420.0</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>NT$ 2440.0</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
@@ -1819,22 +1819,22 @@
       </c>
       <c r="C5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 9700.0</t>
+          <t>NT$ 10140.0</t>
         </is>
       </c>
       <c r="D5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 9920.0</t>
+          <t>NT$ 10175.0</t>
         </is>
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 9500.0</t>
+          <t>NT$ 9775.0</t>
         </is>
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 9720.0</t>
+          <t>NT$ 9955.0</t>
         </is>
       </c>
       <c r="G5" s="29" t="inlineStr">
@@ -1866,22 +1866,22 @@
       </c>
       <c r="C6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5010.0</t>
+          <t>NT$ 5155.0</t>
         </is>
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5330.0</t>
+          <t>NT$ 5260.0</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 4980.0</t>
+          <t>NT$ 5005.0</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 5120.0</t>
+          <t>NT$ 5165.0</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
@@ -1913,22 +1913,22 @@
       </c>
       <c r="C7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3200.0</t>
+          <t>NT$ 3115.0</t>
         </is>
       </c>
       <c r="D7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3220.0</t>
+          <t>NT$ 3355.0</t>
         </is>
       </c>
       <c r="E7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3050.0</t>
+          <t>NT$ 3080.0</t>
         </is>
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3085.0</t>
+          <t>NT$ 3315.0</t>
         </is>
       </c>
       <c r="G7" s="29" t="inlineStr">
@@ -1960,22 +1960,22 @@
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 240.0</t>
+          <t>NT$ 241.5</t>
         </is>
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 240.0</t>
+          <t>NT$ 247.0</t>
         </is>
       </c>
       <c r="E8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 238.0</t>
+          <t>NT$ 240.5</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>NT$ 239.5</t>
+          <t>NT$ 244.0</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
@@ -2007,22 +2007,22 @@
       </c>
       <c r="C9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1690.0</t>
+          <t>NT$ 1650.0</t>
         </is>
       </c>
       <c r="D9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1700.0</t>
+          <t>NT$ 1665.0</t>
         </is>
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1610.0</t>
+          <t>NT$ 1630.0</t>
         </is>
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1630.0</t>
+          <t>NT$ 1635.0</t>
         </is>
       </c>
       <c r="G9" s="29" t="inlineStr">
@@ -2054,22 +2054,22 @@
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1915.0</t>
+          <t>NT$ 1965.0</t>
         </is>
       </c>
       <c r="D10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2005.0</t>
+          <t>NT$ 2030.0</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1910.0</t>
+          <t>NT$ 1935.0</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 1950.0</t>
+          <t>NT$ 1980.0</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
@@ -2101,22 +2101,22 @@
       </c>
       <c r="C11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2125.0</t>
+          <t>NT$ 1985.0</t>
         </is>
       </c>
       <c r="D11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2160.0</t>
+          <t>NT$ 2045.0</t>
         </is>
       </c>
       <c r="E11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2025.0</t>
+          <t>NT$ 1960.0</t>
         </is>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2025.0</t>
+          <t>NT$ 2000.0</t>
         </is>
       </c>
       <c r="G11" s="29" t="inlineStr">
@@ -2148,22 +2148,22 @@
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 696.0</t>
+          <t>NT$ 652.0</t>
         </is>
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 699.0</t>
+          <t>NT$ 678.0</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 673.0</t>
+          <t>NT$ 652.0</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 673.0</t>
+          <t>NT$ 671.0</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
@@ -2195,22 +2195,22 @@
       </c>
       <c r="C13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4195.0</t>
+          <t>NT$ 4275.0</t>
         </is>
       </c>
       <c r="D13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4295.0</t>
+          <t>NT$ 4360.0</t>
         </is>
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4145.0</t>
+          <t>NT$ 4240.0</t>
         </is>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 4165.0</t>
+          <t>NT$ 4250.0</t>
         </is>
       </c>
       <c r="G13" s="29" t="inlineStr">
@@ -2242,22 +2242,22 @@
       </c>
       <c r="C14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 6720.0</t>
+          <t>NT$ 6765.0</t>
         </is>
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 7070.0</t>
+          <t>NT$ 6950.0</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 6660.0</t>
+          <t>NT$ 6675.0</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>NT$ 6765.0</t>
+          <t>NT$ 6730.0</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">

--- a/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
+++ b/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="核心卡位龙头全景深度分析" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="买卖决策速查面板" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="核心卡位龙头全景深度分析" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="买卖决策速查面板" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -631,7 +631,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>定盘时间: 2026-10-16 19:43:44 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
+          <t>定盘时间: 2026-10-19 20:33:54 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
         </is>
       </c>
     </row>
@@ -730,9 +730,9 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>开盘: 2430.0
-最高: 2445.0
-最低: 2420.0
+          <t>开盘: 2395.0
+最高: 2420.0
+最低: 2390.0
 收盘: 2420.0</t>
         </is>
       </c>
@@ -740,7 +740,7 @@
         <is>
           <t>• 毛利率：67.03% (2026Q2)
 • 净利率：53.22% (2026Q2)
-• ROE：79.5% (單季年化, 2026Q2)
+• ROE：39.8% (年初累計年化, 2026Q2)
 • EPS：27.25 元 (2026Q2 單季；TSMC 官方財報)</t>
         </is>
       </c>
@@ -751,15 +751,15 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>外资: -22047 张
-投信: +710 张
-[2026-10-16 官方结算] 投信内资买超 (+710 张) 逢低承接，外资高档调节 (-22,047 张)。</t>
+          <t>外资: -9835 张
+投信: +3884 张
+[2026-10-19 官方结算] 投信内资买超 (+3,884 张) 逢低承接，外资高档调节 (-9,835 张)。</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 22,372 张 (占量 67.0%)
-[2026-10-16 筹码] 主力机构呈净卖出 (-22,372 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 4,604 张 (占量 19.5%)
+[2026-10-19 筹码] 主力机构呈净卖出 (-4,604 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>33,389 张</t>
+          <t>23,643 张</t>
         </is>
       </c>
     </row>
@@ -817,17 +817,17 @@
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>开盘: 10140.0
-最高: 10175.0
-最低: 9775.0
-收盘: 9955.0</t>
+          <t>开盘: 9785.0
+最高: 10040.0
+最低: 9690.0
+收盘: 9920.0</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
         <is>
           <t>• 毛利率：84.18% (2026Q2)
 • 净利率：64.95% (2026Q2)
-• ROE：125.3% (單季年化, 2026Q2)
+• ROE：62.7% (年初累計年化, 2026Q2)
 • EPS：74.38 元 (2026Q2 單季；公司法說資料)</t>
         </is>
       </c>
@@ -838,15 +838,15 @@
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>外资: -141 张
-投信: +47 张
-[2026-10-16 官方结算] 投信内资买超 (+47 张) 逢低承接，外资高档调节 (-141 张)。</t>
+          <t>外资: -60 张
+投信: +9 张
+[2026-10-19 官方结算] 投信内资买超 (+9 张) 逢低承接，外资高档调节 (-60 张)。</t>
         </is>
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 109 张 (占量 20.8%)
-[2026-10-16 筹码] 主力机构呈净卖出 (-109 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 52 张 (占量 13.9%)
+[2026-10-19 筹码] 主力机构呈净卖出 (-52 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 9955.0</t>
+          <t>NT$ 9920.0</t>
         </is>
       </c>
       <c r="K5" s="18" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="O5" s="16" t="inlineStr">
         <is>
-          <t>523 张</t>
+          <t>373 张</t>
         </is>
       </c>
     </row>
@@ -904,17 +904,17 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>开盘: 5155.0
-最高: 5260.0
-最低: 5005.0
-收盘: 5165.0</t>
+          <t>开盘: 5010.0
+最高: 5165.0
+最低: 4955.0
+收盘: 5125.0</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
           <t>• 毛利率：32.03% (2026Q2)
 • 净利率：18.93% (2026Q2)
-• ROE：104.3% (單季年化, 2026Q2)
+• ROE：52.2% (年初累計年化, 2026Q2)
 • EPS：27.55 元 (2026Q2 單季；公司季度財報)</t>
         </is>
       </c>
@@ -925,15 +925,15 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>外资: +196 张
-投信: -186 张
-[2026-10-16 官方结算] 外资主力大幅回流 (+196 张)，投信阶段获利减仓 (-186 张)。</t>
+          <t>外资: +16 张
+投信: +15 张
+[2026-10-19 官方结算] 外资与投信联手买超 (+-80 张)，内外部机构共振做多。</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 63 张 (占量 2.5%)
-[2026-10-16 筹码] 主力机构呈净卖出 (-63 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 80 张 (占量 5.0%)
+[2026-10-19 筹码] 主力机构呈净卖出 (-80 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 5165.0</t>
+          <t>NT$ 5125.0</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>2,552 张</t>
+          <t>1,604 张</t>
         </is>
       </c>
     </row>
@@ -991,17 +991,17 @@
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>开盘: 3115.0
-最高: 3355.0
-最低: 3080.0
-收盘: 3315.0</t>
+          <t>开盘: 3220.0
+最高: 3350.0
+最低: 3180.0
+收盘: 3320.0</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
         <is>
           <t>• 毛利率：31.17% (2026Q2)
 • 净利率：19.31% (2026Q2)
-• ROE：126.7% (單季年化, 2026Q2)
+• ROE：63.3% (年初累計年化, 2026Q2)
 • EPS：24.37 元 (2026Q2 單季；公司季度財報)</t>
         </is>
       </c>
@@ -1012,15 +1012,15 @@
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>外资: -725 张
-投信: +591 张
-[2026-10-16 官方结算] 投信内资买超 (+591 张) 逢低承接，外资高档调节 (-725 张)。</t>
+          <t>外资: -527 张
+投信: +509 张
+[2026-10-19 官方结算] 投信内资买超 (+509 张) 逢低承接，外资高档调节 (-527 张)。</t>
         </is>
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 154 张 (占量 4.3%)
-[2026-10-16 筹码] 主力机构呈净卖出 (-154 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 24 张 (占量 1.0%)
+[2026-10-19 筹码] 主力机构呈净卖出 (-24 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I7" s="15" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="J7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3315.0</t>
+          <t>NT$ 3320.0</t>
         </is>
       </c>
       <c r="K7" s="18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="O7" s="16" t="inlineStr">
         <is>
-          <t>3,568 张</t>
+          <t>2,319 张</t>
         </is>
       </c>
     </row>
@@ -1078,17 +1078,17 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>开盘: 241.5
-最高: 247.0
-最低: 240.5
-收盘: 244.0</t>
+          <t>开盘: 242.0
+最高: 242.5
+最低: 238.5
+收盘: 239.5</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
           <t>• 毛利率：6.15% (2026Q2)
 • 净利率：2.73% (2026Q2)
-• ROE：23.0% (單季年化, 2026Q2)
+• ROE：11.5% (年初累計年化, 2026Q2)
 • EPS：4.27 元 (2026Q2 單季；鴻海官方公告)</t>
         </is>
       </c>
@@ -1099,15 +1099,15 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>外资: +22670 张
-投信: -239 张
-[2026-10-16 官方结算] 外资主力大幅回流 (+22,670 张)，投信阶段获利减仓 (-239 张)。</t>
+          <t>外资: -14885 张
+投信: +817 张
+[2026-10-19 官方结算] 投信内资买超 (+817 张) 逢低承接，外资高档调节 (-14,885 张)。</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 23,159 张 (占量 47.0%)
-[2026-10-16 筹码] 主力机构呈净买入 (+23,159 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 13,522 张 (占量 46.2%)
+[2026-10-19 筹码] 主力机构呈净卖出 (-13,522 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>NT$ 244.0</t>
+          <t>NT$ 239.5</t>
         </is>
       </c>
       <c r="K8" s="9" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="O8" s="7" t="inlineStr">
         <is>
-          <t>49,268 张</t>
+          <t>29,293 张</t>
         </is>
       </c>
     </row>
@@ -1165,17 +1165,17 @@
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>开盘: 1650.0
-最高: 1665.0
-最低: 1630.0
-收盘: 1635.0</t>
+          <t>开盘: 1600.0
+最高: 1655.0
+最低: 1590.0
+收盘: 1640.0</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
         <is>
           <t>• 毛利率：36.27% (2026Q2)
 • 净利率：14.89% (2026Q2)
-• ROE：62.2% (單季年化, 2026Q2)
+• ROE：31.1% (年初累計年化, 2026Q2)
 • EPS：9.68 元 (26Q2)</t>
         </is>
       </c>
@@ -1186,15 +1186,15 @@
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
-          <t>外资: -2134 张
-投信: +268 张
-[2026-10-16 官方结算] 投信内资买超 (+268 张) 逢低承接，外资高档调节 (-2,134 张)。</t>
+          <t>外资: -835 张
+投信: +632 张
+[2026-10-19 官方结算] 投信内资买超 (+632 张) 逢低承接，外资高档调节 (-835 张)。</t>
         </is>
       </c>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 2,005 张 (占量 27.1%)
-[2026-10-16 筹码] 主力机构呈净卖出 (-2,005 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 782 张 (占量 11.2%)
+[2026-10-19 筹码] 主力机构呈净卖出 (-782 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I9" s="15" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="J9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1635.0</t>
+          <t>NT$ 1640.0</t>
         </is>
       </c>
       <c r="K9" s="18" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="O9" s="16" t="inlineStr">
         <is>
-          <t>7,388 张</t>
+          <t>6,954 张</t>
         </is>
       </c>
     </row>
@@ -1252,17 +1252,17 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>开盘: 1965.0
-最高: 2030.0
-最低: 1935.0
-收盘: 1980.0</t>
+          <t>开盘: 1925.0
+最高: 2055.0
+最低: 1910.0
+收盘: 2005.0</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
           <t>• 毛利率：19.63% (2026Q2)
 • 净利率：11.70% (2026Q2)
-• ROE：112.4% (單季年化, 2026Q2)
+• ROE：56.2% (年初累計年化, 2026Q2)
 • EPS：19.78 元 (26Q2)</t>
         </is>
       </c>
@@ -1273,15 +1273,15 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>外资: -63 张
-投信: +354 张
-[2026-10-16 官方结算] 投信内资买超 (+354 张) 逢低承接，外资高档调节 (-63 张)。</t>
+          <t>外资: +1008 张
+投信: -62 张
+[2026-10-19 官方结算] 外资主力大幅回流 (+1,008 张)，投信阶段获利减仓 (-62 张)。</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 305 张 (占量 9.0%)
-[2026-10-16 筹码] 主力机构呈净买入 (+305 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 918 张 (占量 20.1%)
+[2026-10-19 筹码] 主力机构呈净买入 (+918 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 1980.0</t>
+          <t>NT$ 2005.0</t>
         </is>
       </c>
       <c r="K10" s="9" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>3,397 张</t>
+          <t>4,576 张</t>
         </is>
       </c>
     </row>
@@ -1341,15 +1341,15 @@
         <is>
           <t>开盘: 1985.0
 最高: 2045.0
-最低: 1960.0
-收盘: 2000.0</t>
+最低: 1945.0
+收盘: 2005.0</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
         <is>
           <t>• 毛利率：61.48% (2026Q2)
 • 净利率：36.15% (2026Q2)
-• ROE：109.0% (單季年化, 2026Q2)
+• ROE：54.5% (年初累計年化, 2026Q2)
 • EPS：約 12.15 元 (26Q2)</t>
         </is>
       </c>
@@ -1360,15 +1360,15 @@
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>外资: -717 张
-投信: +134 张
-[2026-10-16 官方结算] 投信内资买超 (+134 张) 逢低承接，外资高档调节 (-717 张)。</t>
+          <t>外资: -292 张
+投信: +3 张
+[2026-10-19 官方结算] 投信内资买超 (+3 张) 逢低承接，外资高档调节 (-292 张)。</t>
         </is>
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 534 张 (占量 15.5%)
-[2026-10-16 筹码] 主力机构呈净卖出 (-534 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 282 张 (占量 14.4%)
+[2026-10-19 筹码] 主力机构呈净卖出 (-282 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I11" s="15" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="J11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2000.0</t>
+          <t>NT$ 2005.0</t>
         </is>
       </c>
       <c r="K11" s="18" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="O11" s="16" t="inlineStr">
         <is>
-          <t>3,436 张</t>
+          <t>1,953 张</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>开盘: 652.0
-最高: 678.0
-最低: 652.0
-收盘: 671.0</t>
+          <t>开盘: 640.0
+最高: 675.0
+最低: 639.0
+收盘: 670.0</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
           <t>• 毛利率：20.55% (2026Q2)
 • 净利率：9.89% (2026Q2)
-• ROE：36.2% (單季年化, 2026Q2)
+• ROE：18.1% (年初累計年化, 2026Q2)
 • EPS：4.80 元 (26Q2)</t>
         </is>
       </c>
@@ -1447,15 +1447,15 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>外资: -1531 张
-投信: -1815 张
-[2026-10-16 官方结算] 外资与投信偏空调节 (-3,188 张)，机构筹码阶段获利了结。</t>
+          <t>外资: -1627 张
+投信: +1595 张
+[2026-10-19 官方结算] 投信内资买超 (+1,595 张) 逢低承接，外资高档调节 (-1,627 张)。</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 3,188 张 (占量 17.4%)
-[2026-10-16 筹码] 主力机构呈净卖出 (-3,188 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 157 张 (占量 1.1%)
+[2026-10-19 筹码] 主力机构呈净买入 (+157 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 671.0</t>
+          <t>NT$ 670.0</t>
         </is>
       </c>
       <c r="K12" s="9" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>18,308 张</t>
+          <t>13,999 张</t>
         </is>
       </c>
     </row>
@@ -1513,17 +1513,17 @@
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>开盘: 4275.0
-最高: 4360.0
-最低: 4240.0
-收盘: 4250.0</t>
+          <t>开盘: 4150.0
+最高: 4250.0
+最低: 4145.0
+收盘: 4205.0</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
         <is>
           <t>• 毛利率：46.25% (2026Q2)
 • 净利率：16.25% (2026Q2)
-• ROE：45.7% (單季年化, 2026Q2)
+• ROE：22.9% (年初累計年化, 2026Q2)
 • EPS：15.28 元 (26Q2)</t>
         </is>
       </c>
@@ -1534,15 +1534,15 @@
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>外资: -1623 张
-投信: +471 张
-[2026-10-16 官方结算] 投信内资买超 (+471 张) 逢低承接，外资高档调节 (-1,623 张)。</t>
+          <t>外资: -1154 张
+投信: +165 张
+[2026-10-19 官方结算] 投信内资买超 (+165 张) 逢低承接，外资高档调节 (-1,154 张)。</t>
         </is>
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 1,384 张 (占量 17.9%)
-[2026-10-16 筹码] 主力机构呈净卖出 (-1,384 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 1,202 张 (占量 22.5%)
+[2026-10-19 筹码] 主力机构呈净卖出 (-1,202 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I13" s="15" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="J13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 4250.0</t>
+          <t>NT$ 4205.0</t>
         </is>
       </c>
       <c r="K13" s="18" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="O13" s="16" t="inlineStr">
         <is>
-          <t>7,748 张</t>
+          <t>5,350 张</t>
         </is>
       </c>
     </row>
@@ -1600,10 +1600,10 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>开盘: 6765.0
-最高: 6950.0
-最低: 6675.0
-收盘: 6730.0</t>
+          <t>开盘: 6475.0
+最高: 6590.0
+最低: 6330.0
+收盘: 6560.0</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -1621,15 +1621,15 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>外资: -110 张
-投信: +50 张
-[2026-10-16 官方结算] 投信内资买超 (+50 张) 逢低承接，外资高档调节 (-110 张)。</t>
+          <t>外资: -79 张
+投信: +89 张
+[2026-10-19 官方结算] 投信内资买超 (+89 张) 逢低承接，外资高档调节 (-79 张)。</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 93 张 (占量 8.5%)
-[2026-10-16 筹码] 主力机构呈净卖出 (-93 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 15 张 (占量 0.8%)
+[2026-10-19 筹码] 主力机构呈净买入 (+15 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>NT$ 6730.0</t>
+          <t>NT$ 6560.0</t>
         </is>
       </c>
       <c r="K14" s="9" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="O14" s="7" t="inlineStr">
         <is>
-          <t>1,099 张</t>
+          <t>1,857 张</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-16 19:43:44 | 策略: 3-3-4 分批建仓</t>
+          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-19 20:33:54 | 策略: 3-3-4 分批建仓</t>
         </is>
       </c>
     </row>
@@ -1772,17 +1772,17 @@
       </c>
       <c r="C4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2430.0</t>
+          <t>NT$ 2395.0</t>
         </is>
       </c>
       <c r="D4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2445.0</t>
+          <t>NT$ 2420.0</t>
         </is>
       </c>
       <c r="E4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2420.0</t>
+          <t>NT$ 2390.0</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
@@ -1819,22 +1819,22 @@
       </c>
       <c r="C5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 10140.0</t>
+          <t>NT$ 9785.0</t>
         </is>
       </c>
       <c r="D5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 10175.0</t>
+          <t>NT$ 10040.0</t>
         </is>
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 9775.0</t>
+          <t>NT$ 9690.0</t>
         </is>
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 9955.0</t>
+          <t>NT$ 9920.0</t>
         </is>
       </c>
       <c r="G5" s="29" t="inlineStr">
@@ -1866,22 +1866,22 @@
       </c>
       <c r="C6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5155.0</t>
+          <t>NT$ 5010.0</t>
         </is>
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5260.0</t>
+          <t>NT$ 5165.0</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5005.0</t>
+          <t>NT$ 4955.0</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 5165.0</t>
+          <t>NT$ 5125.0</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
@@ -1913,22 +1913,22 @@
       </c>
       <c r="C7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3115.0</t>
+          <t>NT$ 3220.0</t>
         </is>
       </c>
       <c r="D7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3355.0</t>
+          <t>NT$ 3350.0</t>
         </is>
       </c>
       <c r="E7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3080.0</t>
+          <t>NT$ 3180.0</t>
         </is>
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3315.0</t>
+          <t>NT$ 3320.0</t>
         </is>
       </c>
       <c r="G7" s="29" t="inlineStr">
@@ -1960,22 +1960,22 @@
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 241.5</t>
+          <t>NT$ 242.0</t>
         </is>
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 247.0</t>
+          <t>NT$ 242.5</t>
         </is>
       </c>
       <c r="E8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 240.5</t>
+          <t>NT$ 238.5</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>NT$ 244.0</t>
+          <t>NT$ 239.5</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
@@ -2007,22 +2007,22 @@
       </c>
       <c r="C9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1650.0</t>
+          <t>NT$ 1600.0</t>
         </is>
       </c>
       <c r="D9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1665.0</t>
+          <t>NT$ 1655.0</t>
         </is>
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1630.0</t>
+          <t>NT$ 1590.0</t>
         </is>
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1635.0</t>
+          <t>NT$ 1640.0</t>
         </is>
       </c>
       <c r="G9" s="29" t="inlineStr">
@@ -2054,22 +2054,22 @@
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1965.0</t>
+          <t>NT$ 1925.0</t>
         </is>
       </c>
       <c r="D10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2030.0</t>
+          <t>NT$ 2055.0</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1935.0</t>
+          <t>NT$ 1910.0</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 1980.0</t>
+          <t>NT$ 2005.0</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="E11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1960.0</t>
+          <t>NT$ 1945.0</t>
         </is>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2000.0</t>
+          <t>NT$ 2005.0</t>
         </is>
       </c>
       <c r="G11" s="29" t="inlineStr">
@@ -2148,22 +2148,22 @@
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 652.0</t>
+          <t>NT$ 640.0</t>
         </is>
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 678.0</t>
+          <t>NT$ 675.0</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 652.0</t>
+          <t>NT$ 639.0</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 671.0</t>
+          <t>NT$ 670.0</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
@@ -2195,22 +2195,22 @@
       </c>
       <c r="C13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4275.0</t>
+          <t>NT$ 4150.0</t>
         </is>
       </c>
       <c r="D13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4360.0</t>
+          <t>NT$ 4250.0</t>
         </is>
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4240.0</t>
+          <t>NT$ 4145.0</t>
         </is>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 4250.0</t>
+          <t>NT$ 4205.0</t>
         </is>
       </c>
       <c r="G13" s="29" t="inlineStr">
@@ -2242,22 +2242,22 @@
       </c>
       <c r="C14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 6765.0</t>
+          <t>NT$ 6475.0</t>
         </is>
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 6950.0</t>
+          <t>NT$ 6590.0</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 6675.0</t>
+          <t>NT$ 6330.0</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>NT$ 6730.0</t>
+          <t>NT$ 6560.0</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">

--- a/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
+++ b/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
@@ -631,7 +631,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>定盘时间: 2026-10-19 20:33:54 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
+          <t>定盘时间: 2026-10-19 20:41:37 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-19 20:33:54 | 策略: 3-3-4 分批建仓</t>
+          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-19 20:41:37 | 策略: 3-3-4 分批建仓</t>
         </is>
       </c>
     </row>

--- a/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
+++ b/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="核心卡位龙头全景深度分析" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="买卖决策速查面板" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="核心卡位龙头全景深度分析" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="买卖决策速查面板" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -631,7 +631,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>定盘时间: 2026-10-19 20:41:37 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
+          <t>定盘时间: 2026-10-19 21:46:09 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-19 20:41:37 | 策略: 3-3-4 分批建仓</t>
+          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-19 21:46:09 | 策略: 3-3-4 分批建仓</t>
         </is>
       </c>
     </row>

--- a/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
+++ b/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="核心卡位龙头全景深度分析" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="买卖决策速查面板" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="核心卡位龙头全景深度分析" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="买卖决策速查面板" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -631,7 +631,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>定盘时间: 2026-10-19 21:46:09 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
+          <t>定盘时间: 2026-10-20 15:06:07 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
         </is>
       </c>
     </row>
@@ -730,10 +730,10 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>开盘: 2395.0
-最高: 2420.0
-最低: 2390.0
-收盘: 2420.0</t>
+          <t>开盘: 2400.0
+最高: 2415.0
+最低: 2395.0
+收盘: 2405.0</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 4,604 张 (占量 19.5%)
+          <t>法人净卖超 4,604 张 (占量 27.0%)
 [2026-10-19 筹码] 主力机构呈净卖出 (-4,604 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
@@ -769,7 +769,7 @@
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2420.0</t>
+          <t>NT$ 2405.0</t>
         </is>
       </c>
       <c r="K4" s="9" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>23,643 张</t>
+          <t>17,029 张</t>
         </is>
       </c>
     </row>
@@ -817,10 +817,10 @@
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>开盘: 9785.0
-最高: 10040.0
-最低: 9690.0
-收盘: 9920.0</t>
+          <t>开盘: 9985.0
+最高: 10330.0
+最低: 9970.0
+收盘: 10100.0</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 52 张 (占量 13.9%)
+          <t>法人净卖超 52 张 (占量 9.8%)
 [2026-10-19 筹码] 主力机构呈净卖出 (-52 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
@@ -856,7 +856,7 @@
       </c>
       <c r="J5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 9920.0</t>
+          <t>NT$ 10100.0</t>
         </is>
       </c>
       <c r="K5" s="18" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="O5" s="16" t="inlineStr">
         <is>
-          <t>373 张</t>
+          <t>533 张</t>
         </is>
       </c>
     </row>
@@ -904,10 +904,10 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>开盘: 5010.0
-最高: 5165.0
-最低: 4955.0
-收盘: 5125.0</t>
+          <t>开盘: 5050.0
+最高: 5200.0
+最低: 4930.0
+收盘: 4945.0</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 5125.0</t>
+          <t>NT$ 4945.0</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>1,604 张</t>
+          <t>1,585 张</t>
         </is>
       </c>
     </row>
@@ -991,10 +991,10 @@
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>开盘: 3220.0
-最高: 3350.0
-最低: 3180.0
-收盘: 3320.0</t>
+          <t>开盘: 3290.0
+最高: 3420.0
+最低: 3270.0
+收盘: 3325.0</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 24 张 (占量 1.0%)
+          <t>法人净卖超 24 张 (占量 0.9%)
 [2026-10-19 筹码] 主力机构呈净卖出 (-24 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="J7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3320.0</t>
+          <t>NT$ 3325.0</t>
         </is>
       </c>
       <c r="K7" s="18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="O7" s="16" t="inlineStr">
         <is>
-          <t>2,319 张</t>
+          <t>2,637 张</t>
         </is>
       </c>
     </row>
@@ -1078,10 +1078,10 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>开盘: 242.0
-最高: 242.5
-最低: 238.5
-收盘: 239.5</t>
+          <t>开盘: 238.0
+最高: 244.5
+最低: 237.0
+收盘: 241.5</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 13,522 张 (占量 46.2%)
+          <t>法人净卖超 13,522 张 (占量 51.6%)
 [2026-10-19 筹码] 主力机构呈净卖出 (-13,522 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>NT$ 239.5</t>
+          <t>NT$ 241.5</t>
         </is>
       </c>
       <c r="K8" s="9" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="O8" s="7" t="inlineStr">
         <is>
-          <t>29,293 张</t>
+          <t>26,229 张</t>
         </is>
       </c>
     </row>
@@ -1165,10 +1165,10 @@
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>开盘: 1600.0
-最高: 1655.0
-最低: 1590.0
-收盘: 1640.0</t>
+          <t>开盘: 1635.0
+最高: 1645.0
+最低: 1595.0
+收盘: 1605.0</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 782 张 (占量 11.2%)
+          <t>法人净卖超 782 张 (占量 9.8%)
 [2026-10-19 筹码] 主力机构呈净卖出 (-782 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="J9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1640.0</t>
+          <t>NT$ 1605.0</t>
         </is>
       </c>
       <c r="K9" s="18" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="O9" s="16" t="inlineStr">
         <is>
-          <t>6,954 张</t>
+          <t>7,947 张</t>
         </is>
       </c>
     </row>
@@ -1252,10 +1252,10 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>开盘: 1925.0
+          <t>开盘: 2000.0
 最高: 2055.0
-最低: 1910.0
-收盘: 2005.0</t>
+最低: 1950.0
+收盘: 1970.0</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 918 张 (占量 20.1%)
+          <t>法人净买超 918 张 (占量 24.3%)
 [2026-10-19 筹码] 主力机构呈净买入 (+918 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2005.0</t>
+          <t>NT$ 1970.0</t>
         </is>
       </c>
       <c r="K10" s="9" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>4,576 张</t>
+          <t>3,781 张</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>开盘: 1985.0
-最高: 2045.0
-最低: 1945.0
-收盘: 2005.0</t>
+          <t>开盘: 2000.0
+最高: 2075.0
+最低: 1990.0
+收盘: 2000.0</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 282 张 (占量 14.4%)
+          <t>法人净卖超 282 张 (占量 16.3%)
 [2026-10-19 筹码] 主力机构呈净卖出 (-282 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="J11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2005.0</t>
+          <t>NT$ 2000.0</t>
         </is>
       </c>
       <c r="K11" s="18" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="O11" s="16" t="inlineStr">
         <is>
-          <t>1,953 张</t>
+          <t>1,731 张</t>
         </is>
       </c>
     </row>
@@ -1426,10 +1426,10 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>开盘: 640.0
-最高: 675.0
-最低: 639.0
-收盘: 670.0</t>
+          <t>开盘: 669.0
+最高: 680.0
+最低: 655.0
+收盘: 660.0</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 157 张 (占量 1.1%)
+          <t>法人净买超 157 张 (占量 1.3%)
 [2026-10-19 筹码] 主力机构呈净买入 (+157 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 670.0</t>
+          <t>NT$ 660.0</t>
         </is>
       </c>
       <c r="K12" s="9" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>13,999 张</t>
+          <t>11,799 张</t>
         </is>
       </c>
     </row>
@@ -1513,10 +1513,10 @@
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>开盘: 4150.0
-最高: 4250.0
-最低: 4145.0
-收盘: 4205.0</t>
+          <t>开盘: 4260.0
+最高: 4305.0
+最低: 4120.0
+收盘: 4150.0</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 1,202 张 (占量 22.5%)
+          <t>法人净卖超 1,202 张 (占量 21.4%)
 [2026-10-19 筹码] 主力机构呈净卖出 (-1,202 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="J13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 4205.0</t>
+          <t>NT$ 4150.0</t>
         </is>
       </c>
       <c r="K13" s="18" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="O13" s="16" t="inlineStr">
         <is>
-          <t>5,350 张</t>
+          <t>5,612 张</t>
         </is>
       </c>
     </row>
@@ -1601,9 +1601,9 @@
       <c r="D14" s="7" t="inlineStr">
         <is>
           <t>开盘: 6475.0
-最高: 6590.0
-最低: 6330.0
-收盘: 6560.0</t>
+最高: 6720.0
+最低: 6475.0
+收盘: 6650.0</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 15 张 (占量 0.8%)
+          <t>法人净买超 15 张 (占量 1.7%)
 [2026-10-19 筹码] 主力机构呈净买入 (+15 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>NT$ 6560.0</t>
+          <t>NT$ 6650.0</t>
         </is>
       </c>
       <c r="K14" s="9" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="O14" s="7" t="inlineStr">
         <is>
-          <t>1,857 张</t>
+          <t>876 张</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-19 21:46:09 | 策略: 3-3-4 分批建仓</t>
+          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-20 15:06:07 | 策略: 3-3-4 分批建仓</t>
         </is>
       </c>
     </row>
@@ -1772,22 +1772,22 @@
       </c>
       <c r="C4" s="24" t="inlineStr">
         <is>
+          <t>NT$ 2400.0</t>
+        </is>
+      </c>
+      <c r="D4" s="24" t="inlineStr">
+        <is>
+          <t>NT$ 2415.0</t>
+        </is>
+      </c>
+      <c r="E4" s="24" t="inlineStr">
+        <is>
           <t>NT$ 2395.0</t>
         </is>
       </c>
-      <c r="D4" s="24" t="inlineStr">
-        <is>
-          <t>NT$ 2420.0</t>
-        </is>
-      </c>
-      <c r="E4" s="24" t="inlineStr">
-        <is>
-          <t>NT$ 2390.0</t>
-        </is>
-      </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2420.0</t>
+          <t>NT$ 2405.0</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
@@ -1819,22 +1819,22 @@
       </c>
       <c r="C5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 9785.0</t>
+          <t>NT$ 9985.0</t>
         </is>
       </c>
       <c r="D5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 10040.0</t>
+          <t>NT$ 10330.0</t>
         </is>
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 9690.0</t>
+          <t>NT$ 9970.0</t>
         </is>
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 9920.0</t>
+          <t>NT$ 10100.0</t>
         </is>
       </c>
       <c r="G5" s="29" t="inlineStr">
@@ -1866,22 +1866,22 @@
       </c>
       <c r="C6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5010.0</t>
+          <t>NT$ 5050.0</t>
         </is>
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5165.0</t>
+          <t>NT$ 5200.0</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 4955.0</t>
+          <t>NT$ 4930.0</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 5125.0</t>
+          <t>NT$ 4945.0</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
@@ -1913,22 +1913,22 @@
       </c>
       <c r="C7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3220.0</t>
+          <t>NT$ 3290.0</t>
         </is>
       </c>
       <c r="D7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3350.0</t>
+          <t>NT$ 3420.0</t>
         </is>
       </c>
       <c r="E7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3180.0</t>
+          <t>NT$ 3270.0</t>
         </is>
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3320.0</t>
+          <t>NT$ 3325.0</t>
         </is>
       </c>
       <c r="G7" s="29" t="inlineStr">
@@ -1960,22 +1960,22 @@
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 242.0</t>
+          <t>NT$ 238.0</t>
         </is>
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 242.5</t>
+          <t>NT$ 244.5</t>
         </is>
       </c>
       <c r="E8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 238.5</t>
+          <t>NT$ 237.0</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>NT$ 239.5</t>
+          <t>NT$ 241.5</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
@@ -2007,22 +2007,22 @@
       </c>
       <c r="C9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1600.0</t>
+          <t>NT$ 1635.0</t>
         </is>
       </c>
       <c r="D9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1655.0</t>
+          <t>NT$ 1645.0</t>
         </is>
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1590.0</t>
+          <t>NT$ 1595.0</t>
         </is>
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1640.0</t>
+          <t>NT$ 1605.0</t>
         </is>
       </c>
       <c r="G9" s="29" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1925.0</t>
+          <t>NT$ 2000.0</t>
         </is>
       </c>
       <c r="D10" s="24" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="E10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1910.0</t>
+          <t>NT$ 1950.0</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2005.0</t>
+          <t>NT$ 1970.0</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
@@ -2101,22 +2101,22 @@
       </c>
       <c r="C11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1985.0</t>
+          <t>NT$ 2000.0</t>
         </is>
       </c>
       <c r="D11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2045.0</t>
+          <t>NT$ 2075.0</t>
         </is>
       </c>
       <c r="E11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1945.0</t>
+          <t>NT$ 1990.0</t>
         </is>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2005.0</t>
+          <t>NT$ 2000.0</t>
         </is>
       </c>
       <c r="G11" s="29" t="inlineStr">
@@ -2148,22 +2148,22 @@
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 640.0</t>
+          <t>NT$ 669.0</t>
         </is>
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 675.0</t>
+          <t>NT$ 680.0</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 639.0</t>
+          <t>NT$ 655.0</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 670.0</t>
+          <t>NT$ 660.0</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
@@ -2195,22 +2195,22 @@
       </c>
       <c r="C13" s="28" t="inlineStr">
         <is>
+          <t>NT$ 4260.0</t>
+        </is>
+      </c>
+      <c r="D13" s="28" t="inlineStr">
+        <is>
+          <t>NT$ 4305.0</t>
+        </is>
+      </c>
+      <c r="E13" s="28" t="inlineStr">
+        <is>
+          <t>NT$ 4120.0</t>
+        </is>
+      </c>
+      <c r="F13" s="17" t="inlineStr">
+        <is>
           <t>NT$ 4150.0</t>
-        </is>
-      </c>
-      <c r="D13" s="28" t="inlineStr">
-        <is>
-          <t>NT$ 4250.0</t>
-        </is>
-      </c>
-      <c r="E13" s="28" t="inlineStr">
-        <is>
-          <t>NT$ 4145.0</t>
-        </is>
-      </c>
-      <c r="F13" s="17" t="inlineStr">
-        <is>
-          <t>NT$ 4205.0</t>
         </is>
       </c>
       <c r="G13" s="29" t="inlineStr">
@@ -2247,17 +2247,17 @@
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 6590.0</t>
+          <t>NT$ 6720.0</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 6330.0</t>
+          <t>NT$ 6475.0</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>NT$ 6560.0</t>
+          <t>NT$ 6650.0</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">

--- a/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
+++ b/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="核心卡位龙头全景深度分析" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="买卖决策速查面板" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="核心卡位龙头全景深度分析" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="买卖决策速查面板" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -631,7 +631,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>定盘时间: 2026-10-20 15:06:07 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
+          <t>定盘时间: 2026-10-20 19:55:25 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
         </is>
       </c>
     </row>
@@ -751,15 +751,15 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>外资: -9835 张
-投信: +3884 张
-[2026-10-19 官方结算] 投信内资买超 (+3,884 张) 逢低承接，外资高档调节 (-9,835 张)。</t>
+          <t>外资: -9365 张
+投信: +1029 张
+[2026-10-20 官方结算] 投信内资买超 (+1,029 张) 逢低承接，外资高档调节 (-9,365 张)。</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 4,604 张 (占量 27.0%)
-[2026-10-19 筹码] 主力机构呈净卖出 (-4,604 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 8,364 张 (占量 49.1%)
+[2026-10-20 筹码] 主力机构呈净卖出 (-8,364 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
@@ -838,15 +838,15 @@
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>外资: -60 张
-投信: +9 张
-[2026-10-19 官方结算] 投信内资买超 (+9 张) 逢低承接，外资高档调节 (-60 张)。</t>
+          <t>外资: -104 张
+投信: +76 张
+[2026-10-20 官方结算] 投信内资买超 (+76 张) 逢低承接，外资高档调节 (-104 张)。</t>
         </is>
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 52 张 (占量 9.8%)
-[2026-10-19 筹码] 主力机构呈净卖出 (-52 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 37 张 (占量 6.9%)
+[2026-10-20 筹码] 主力机构呈净卖出 (-37 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -925,15 +925,15 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>外资: +16 张
-投信: +15 张
-[2026-10-19 官方结算] 外资与投信联手买超 (+-80 张)，内外部机构共振做多。</t>
+          <t>外资: -157 张
+投信: +60 张
+[2026-10-20 官方结算] 投信内资买超 (+60 张) 逢低承接，外资高档调节 (-157 张)。</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 80 张 (占量 5.0%)
-[2026-10-19 筹码] 主力机构呈净卖出 (-80 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 193 张 (占量 12.2%)
+[2026-10-20 筹码] 主力机构呈净卖出 (-193 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
@@ -1012,15 +1012,15 @@
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>外资: -527 张
-投信: +509 张
-[2026-10-19 官方结算] 投信内资买超 (+509 张) 逢低承接，外资高档调节 (-527 张)。</t>
+          <t>外资: -599 张
+投信: +881 张
+[2026-10-20 官方结算] 投信内资买超 (+881 张) 逢低承接，外资高档调节 (-599 张)。</t>
         </is>
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 24 张 (占量 0.9%)
-[2026-10-19 筹码] 主力机构呈净卖出 (-24 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 209 张 (占量 7.9%)
+[2026-10-20 筹码] 主力机构呈净买入 (+209 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I7" s="15" t="inlineStr">
@@ -1099,15 +1099,15 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>外资: -14885 张
-投信: +817 张
-[2026-10-19 官方结算] 投信内资买超 (+817 张) 逢低承接，外资高档调节 (-14,885 张)。</t>
+          <t>外资: +3853 张
+投信: +967 张
+[2026-10-20 官方结算] 三大法人全线买超 (+5,218 张)，外资与投信合力加仓。</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 13,522 张 (占量 51.6%)
-[2026-10-19 筹码] 主力机构呈净卖出 (-13,522 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 5,218 张 (占量 19.9%)
+[2026-10-20 筹码] 主力机构呈净买入 (+5,218 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -1186,15 +1186,15 @@
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
-          <t>外资: -835 张
-投信: +632 张
-[2026-10-19 官方结算] 投信内资买超 (+632 张) 逢低承接，外资高档调节 (-835 张)。</t>
+          <t>外资: -3501 张
+投信: +603 张
+[2026-10-20 官方结算] 投信内资买超 (+603 张) 逢低承接，外资高档调节 (-3,501 张)。</t>
         </is>
       </c>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 782 张 (占量 9.8%)
-[2026-10-19 筹码] 主力机构呈净卖出 (-782 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 3,275 张 (占量 41.2%)
+[2026-10-20 筹码] 主力机构呈净卖出 (-3,275 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I9" s="15" t="inlineStr">
@@ -1273,15 +1273,15 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>外资: +1008 张
-投信: -62 张
-[2026-10-19 官方结算] 外资主力大幅回流 (+1,008 张)，投信阶段获利减仓 (-62 张)。</t>
+          <t>外资: -553 张
+投信: +926 张
+[2026-10-20 官方结算] 投信内资买超 (+926 张) 逢低承接，外资高档调节 (-553 张)。</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 918 张 (占量 24.3%)
-[2026-10-19 筹码] 主力机构呈净买入 (+918 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 256 张 (占量 6.8%)
+[2026-10-20 筹码] 主力机构呈净买入 (+256 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1360,15 +1360,15 @@
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>外资: -292 张
-投信: +3 张
-[2026-10-19 官方结算] 投信内资买超 (+3 张) 逢低承接，外资高档调节 (-292 张)。</t>
+          <t>外资: -423 张
+投信: +166 张
+[2026-10-20 官方结算] 投信内资买超 (+166 张) 逢低承接，外资高档调节 (-423 张)。</t>
         </is>
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 282 张 (占量 16.3%)
-[2026-10-19 筹码] 主力机构呈净卖出 (-282 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 290 张 (占量 16.8%)
+[2026-10-20 筹码] 主力机构呈净卖出 (-290 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I11" s="15" t="inlineStr">
@@ -1447,15 +1447,15 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>外资: -1627 张
-投信: +1595 张
-[2026-10-19 官方结算] 投信内资买超 (+1,595 张) 逢低承接，外资高档调节 (-1,627 张)。</t>
+          <t>外资: -1958 张
+投信: +599 张
+[2026-10-20 官方结算] 投信内资买超 (+599 张) 逢低承接，外资高档调节 (-1,958 张)。</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 157 张 (占量 1.3%)
-[2026-10-19 筹码] 主力机构呈净买入 (+157 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 2,005 张 (占量 17.0%)
+[2026-10-20 筹码] 主力机构呈净卖出 (-2,005 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -1534,15 +1534,15 @@
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>外资: -1154 张
-投信: +165 张
-[2026-10-19 官方结算] 投信内资买超 (+165 张) 逢低承接，外资高档调节 (-1,154 张)。</t>
+          <t>外资: -1566 张
+投信: +295 张
+[2026-10-20 官方结算] 投信内资买超 (+295 张) 逢低承接，外资高档调节 (-1,566 张)。</t>
         </is>
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 1,202 张 (占量 21.4%)
-[2026-10-19 筹码] 主力机构呈净卖出 (-1,202 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 1,368 张 (占量 24.4%)
+[2026-10-20 筹码] 主力机构呈净卖出 (-1,368 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I13" s="15" t="inlineStr">
@@ -1621,15 +1621,15 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>外资: -79 张
-投信: +89 张
-[2026-10-19 官方结算] 投信内资买超 (+89 张) 逢低承接，外资高档调节 (-79 张)。</t>
+          <t>外资: -80 张
+投信: +78 张
+[2026-10-20 官方结算] 投信内资买超 (+78 张) 逢低承接，外资高档调节 (-80 张)。</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 15 张 (占量 1.7%)
-[2026-10-19 筹码] 主力机构呈净买入 (+15 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 16 张 (占量 1.8%)
+[2026-10-20 筹码] 主力机构呈净卖出 (-16 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -1708,7 +1708,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-20 15:06:07 | 策略: 3-3-4 分批建仓</t>
+          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-20 19:55:25 | 策略: 3-3-4 分批建仓</t>
         </is>
       </c>
     </row>

--- a/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
+++ b/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="核心卡位龙头全景深度分析" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="买卖决策速查面板" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="核心卡位龙头全景深度分析" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="买卖决策速查面板" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -631,7 +631,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>定盘时间: 2026-10-20 19:55:25 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
+          <t>定盘时间: 2026-10-21 15:06:14 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
         </is>
       </c>
     </row>
@@ -730,10 +730,10 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>开盘: 2400.0
-最高: 2415.0
-最低: 2395.0
-收盘: 2405.0</t>
+          <t>开盘: 2425.0
+最高: 2435.0
+最低: 2400.0
+收盘: 2420.0</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 8,364 张 (占量 49.1%)
+          <t>法人净卖超 8,364 张 (占量 37.5%)
 [2026-10-20 筹码] 主力机构呈净卖出 (-8,364 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
@@ -769,7 +769,7 @@
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2405.0</t>
+          <t>NT$ 2420.0</t>
         </is>
       </c>
       <c r="K4" s="9" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>17,029 张</t>
+          <t>22,276 张</t>
         </is>
       </c>
     </row>
@@ -817,10 +817,10 @@
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>开盘: 9985.0
-最高: 10330.0
-最低: 9970.0
-收盘: 10100.0</t>
+          <t>开盘: 10500.0
+最高: 10580.0
+最低: 9985.0
+收盘: 10080.0</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 37 张 (占量 6.9%)
+          <t>法人净卖超 37 张 (占量 6.2%)
 [2026-10-20 筹码] 主力机构呈净卖出 (-37 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
@@ -856,7 +856,7 @@
       </c>
       <c r="J5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 10100.0</t>
+          <t>NT$ 10080.0</t>
         </is>
       </c>
       <c r="K5" s="18" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="O5" s="16" t="inlineStr">
         <is>
-          <t>533 张</t>
+          <t>592 张</t>
         </is>
       </c>
     </row>
@@ -904,10 +904,10 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>开盘: 5050.0
-最高: 5200.0
-最低: 4930.0
-收盘: 4945.0</t>
+          <t>开盘: 5135.0
+最高: 5205.0
+最低: 4965.0
+收盘: 4990.0</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 193 张 (占量 12.2%)
+          <t>法人净卖超 193 张 (占量 7.6%)
 [2026-10-20 筹码] 主力机构呈净卖出 (-193 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
@@ -943,7 +943,7 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 4945.0</t>
+          <t>NT$ 4990.0</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>1,585 张</t>
+          <t>2,537 张</t>
         </is>
       </c>
     </row>
@@ -991,10 +991,10 @@
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>开盘: 3290.0
-最高: 3420.0
-最低: 3270.0
-收盘: 3325.0</t>
+          <t>开盘: 3400.0
+最高: 3450.0
+最低: 3195.0
+收盘: 3235.0</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 209 张 (占量 7.9%)
+          <t>法人净买超 209 张 (占量 5.5%)
 [2026-10-20 筹码] 主力机构呈净买入 (+209 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="J7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3325.0</t>
+          <t>NT$ 3235.0</t>
         </is>
       </c>
       <c r="K7" s="18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="O7" s="16" t="inlineStr">
         <is>
-          <t>2,637 张</t>
+          <t>3,802 张</t>
         </is>
       </c>
     </row>
@@ -1078,10 +1078,10 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>开盘: 238.0
-最高: 244.5
-最低: 237.0
-收盘: 241.5</t>
+          <t>开盘: 244.5
+最高: 250.0
+最低: 244.5
+收盘: 250.0</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 5,218 张 (占量 19.9%)
+          <t>法人净买超 5,218 张 (占量 9.8%)
 [2026-10-20 筹码] 主力机构呈净买入 (+5,218 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>NT$ 241.5</t>
+          <t>NT$ 250.0</t>
         </is>
       </c>
       <c r="K8" s="9" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="O8" s="7" t="inlineStr">
         <is>
-          <t>26,229 张</t>
+          <t>53,380 张</t>
         </is>
       </c>
     </row>
@@ -1165,10 +1165,10 @@
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>开盘: 1635.0
-最高: 1645.0
-最低: 1595.0
-收盘: 1605.0</t>
+          <t>开盘: 1625.0
+最高: 1660.0
+最低: 1600.0
+收盘: 1625.0</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 3,275 张 (占量 41.2%)
+          <t>法人净卖超 3,275 张 (占量 31.1%)
 [2026-10-20 筹码] 主力机构呈净卖出 (-3,275 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="J9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1605.0</t>
+          <t>NT$ 1625.0</t>
         </is>
       </c>
       <c r="K9" s="18" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="O9" s="16" t="inlineStr">
         <is>
-          <t>7,947 张</t>
+          <t>10,519 张</t>
         </is>
       </c>
     </row>
@@ -1252,10 +1252,10 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>开盘: 2000.0
-最高: 2055.0
-最低: 1950.0
-收盘: 1970.0</t>
+          <t>开盘: 2045.0
+最高: 2050.0
+最低: 1805.0
+收盘: 1815.0</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 256 张 (占量 6.8%)
+          <t>法人净买超 256 张 (占量 3.6%)
 [2026-10-20 筹码] 主力机构呈净买入 (+256 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 1970.0</t>
+          <t>NT$ 1815.0</t>
         </is>
       </c>
       <c r="K10" s="9" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>3,781 张</t>
+          <t>7,140 张</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>开盘: 2000.0
-最高: 2075.0
+          <t>开盘: 2030.0
+最高: 2095.0
 最低: 1990.0
-收盘: 2000.0</t>
+收盘: 2010.0</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 290 张 (占量 16.8%)
+          <t>法人净卖超 290 张 (占量 11.2%)
 [2026-10-20 筹码] 主力机构呈净卖出 (-290 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="J11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2000.0</t>
+          <t>NT$ 2010.0</t>
         </is>
       </c>
       <c r="K11" s="18" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="O11" s="16" t="inlineStr">
         <is>
-          <t>1,731 张</t>
+          <t>2,589 张</t>
         </is>
       </c>
     </row>
@@ -1426,10 +1426,10 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>开盘: 669.0
-最高: 680.0
-最低: 655.0
-收盘: 660.0</t>
+          <t>开盘: 684.0
+最高: 687.0
+最低: 668.0
+收盘: 684.0</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 2,005 张 (占量 17.0%)
+          <t>法人净卖超 2,005 张 (占量 19.2%)
 [2026-10-20 筹码] 主力机构呈净卖出 (-2,005 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 660.0</t>
+          <t>NT$ 684.0</t>
         </is>
       </c>
       <c r="K12" s="9" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>11,799 张</t>
+          <t>10,425 张</t>
         </is>
       </c>
     </row>
@@ -1513,10 +1513,10 @@
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>开盘: 4260.0
-最高: 4305.0
-最低: 4120.0
-收盘: 4150.0</t>
+          <t>开盘: 4215.0
+最高: 4295.0
+最低: 4095.0
+收盘: 4140.0</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 1,368 张 (占量 24.4%)
+          <t>法人净卖超 1,368 张 (占量 17.1%)
 [2026-10-20 筹码] 主力机构呈净卖出 (-1,368 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="J13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 4150.0</t>
+          <t>NT$ 4140.0</t>
         </is>
       </c>
       <c r="K13" s="18" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="O13" s="16" t="inlineStr">
         <is>
-          <t>5,612 张</t>
+          <t>8,018 张</t>
         </is>
       </c>
     </row>
@@ -1600,10 +1600,10 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>开盘: 6475.0
-最高: 6720.0
-最低: 6475.0
-收盘: 6650.0</t>
+          <t>开盘: 6835.0
+最高: 6985.0
+最低: 6500.0
+收盘: 6535.0</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 16 张 (占量 1.8%)
+          <t>法人净卖超 16 张 (占量 1.3%)
 [2026-10-20 筹码] 主力机构呈净卖出 (-16 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>NT$ 6650.0</t>
+          <t>NT$ 6535.0</t>
         </is>
       </c>
       <c r="K14" s="9" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="O14" s="7" t="inlineStr">
         <is>
-          <t>876 张</t>
+          <t>1,271 张</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-20 19:55:25 | 策略: 3-3-4 分批建仓</t>
+          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-21 15:06:14 | 策略: 3-3-4 分批建仓</t>
         </is>
       </c>
     </row>
@@ -1772,22 +1772,22 @@
       </c>
       <c r="C4" s="24" t="inlineStr">
         <is>
+          <t>NT$ 2425.0</t>
+        </is>
+      </c>
+      <c r="D4" s="24" t="inlineStr">
+        <is>
+          <t>NT$ 2435.0</t>
+        </is>
+      </c>
+      <c r="E4" s="24" t="inlineStr">
+        <is>
           <t>NT$ 2400.0</t>
         </is>
       </c>
-      <c r="D4" s="24" t="inlineStr">
-        <is>
-          <t>NT$ 2415.0</t>
-        </is>
-      </c>
-      <c r="E4" s="24" t="inlineStr">
-        <is>
-          <t>NT$ 2395.0</t>
-        </is>
-      </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2405.0</t>
+          <t>NT$ 2420.0</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
@@ -1819,22 +1819,22 @@
       </c>
       <c r="C5" s="28" t="inlineStr">
         <is>
+          <t>NT$ 10500.0</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="inlineStr">
+        <is>
+          <t>NT$ 10580.0</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
           <t>NT$ 9985.0</t>
         </is>
       </c>
-      <c r="D5" s="28" t="inlineStr">
-        <is>
-          <t>NT$ 10330.0</t>
-        </is>
-      </c>
-      <c r="E5" s="28" t="inlineStr">
-        <is>
-          <t>NT$ 9970.0</t>
-        </is>
-      </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 10100.0</t>
+          <t>NT$ 10080.0</t>
         </is>
       </c>
       <c r="G5" s="29" t="inlineStr">
@@ -1866,22 +1866,22 @@
       </c>
       <c r="C6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5050.0</t>
+          <t>NT$ 5135.0</t>
         </is>
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5200.0</t>
+          <t>NT$ 5205.0</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 4930.0</t>
+          <t>NT$ 4965.0</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 4945.0</t>
+          <t>NT$ 4990.0</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
@@ -1913,22 +1913,22 @@
       </c>
       <c r="C7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3290.0</t>
+          <t>NT$ 3400.0</t>
         </is>
       </c>
       <c r="D7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3420.0</t>
+          <t>NT$ 3450.0</t>
         </is>
       </c>
       <c r="E7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3270.0</t>
+          <t>NT$ 3195.0</t>
         </is>
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3325.0</t>
+          <t>NT$ 3235.0</t>
         </is>
       </c>
       <c r="G7" s="29" t="inlineStr">
@@ -1960,22 +1960,22 @@
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 238.0</t>
+          <t>NT$ 244.5</t>
         </is>
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
+          <t>NT$ 250.0</t>
+        </is>
+      </c>
+      <c r="E8" s="24" t="inlineStr">
+        <is>
           <t>NT$ 244.5</t>
         </is>
       </c>
-      <c r="E8" s="24" t="inlineStr">
-        <is>
-          <t>NT$ 237.0</t>
-        </is>
-      </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>NT$ 241.5</t>
+          <t>NT$ 250.0</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
@@ -2007,22 +2007,22 @@
       </c>
       <c r="C9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1635.0</t>
+          <t>NT$ 1625.0</t>
         </is>
       </c>
       <c r="D9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1645.0</t>
+          <t>NT$ 1660.0</t>
         </is>
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1595.0</t>
+          <t>NT$ 1600.0</t>
         </is>
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1605.0</t>
+          <t>NT$ 1625.0</t>
         </is>
       </c>
       <c r="G9" s="29" t="inlineStr">
@@ -2054,22 +2054,22 @@
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2000.0</t>
+          <t>NT$ 2045.0</t>
         </is>
       </c>
       <c r="D10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2055.0</t>
+          <t>NT$ 2050.0</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1950.0</t>
+          <t>NT$ 1805.0</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 1970.0</t>
+          <t>NT$ 1815.0</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="C11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2000.0</t>
+          <t>NT$ 2030.0</t>
         </is>
       </c>
       <c r="D11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2075.0</t>
+          <t>NT$ 2095.0</t>
         </is>
       </c>
       <c r="E11" s="28" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2000.0</t>
+          <t>NT$ 2010.0</t>
         </is>
       </c>
       <c r="G11" s="29" t="inlineStr">
@@ -2148,22 +2148,22 @@
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 669.0</t>
+          <t>NT$ 684.0</t>
         </is>
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 680.0</t>
+          <t>NT$ 687.0</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 655.0</t>
+          <t>NT$ 668.0</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 660.0</t>
+          <t>NT$ 684.0</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
@@ -2195,22 +2195,22 @@
       </c>
       <c r="C13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4260.0</t>
+          <t>NT$ 4215.0</t>
         </is>
       </c>
       <c r="D13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4305.0</t>
+          <t>NT$ 4295.0</t>
         </is>
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4120.0</t>
+          <t>NT$ 4095.0</t>
         </is>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 4150.0</t>
+          <t>NT$ 4140.0</t>
         </is>
       </c>
       <c r="G13" s="29" t="inlineStr">
@@ -2242,22 +2242,22 @@
       </c>
       <c r="C14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 6475.0</t>
+          <t>NT$ 6835.0</t>
         </is>
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 6720.0</t>
+          <t>NT$ 6985.0</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 6475.0</t>
+          <t>NT$ 6500.0</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>NT$ 6650.0</t>
+          <t>NT$ 6535.0</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">

--- a/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
+++ b/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="核心卡位龙头全景深度分析" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="买卖决策速查面板" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="核心卡位龙头全景深度分析" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="买卖决策速查面板" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -631,7 +631,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>定盘时间: 2026-10-21 15:06:14 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
+          <t>定盘时间: 2026-10-21 20:09:46 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
         </is>
       </c>
     </row>
@@ -751,15 +751,15 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>外资: -9365 张
-投信: +1029 张
-[2026-10-20 官方结算] 投信内资买超 (+1,029 张) 逢低承接，外资高档调节 (-9,365 张)。</t>
+          <t>外资: -6154 张
+投信: +1397 张
+[2026-10-21 官方结算] 投信内资买超 (+1,397 张) 逢低承接，外资高档调节 (-6,154 张)。</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 8,364 张 (占量 37.5%)
-[2026-10-20 筹码] 主力机构呈净卖出 (-8,364 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 5,805 张 (占量 26.1%)
+[2026-10-21 筹码] 主力机构呈净卖出 (-5,805 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
@@ -838,15 +838,15 @@
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>外资: -104 张
-投信: +76 张
-[2026-10-20 官方结算] 投信内资买超 (+76 张) 逢低承接，外资高档调节 (-104 张)。</t>
+          <t>外资: -48 张
+投信: +40 张
+[2026-10-21 官方结算] 投信内资买超 (+40 张) 逢低承接，外资高档调节 (-48 张)。</t>
         </is>
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 37 张 (占量 6.2%)
-[2026-10-20 筹码] 主力机构呈净卖出 (-37 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 30 张 (占量 5.1%)
+[2026-10-21 筹码] 主力机构呈净卖出 (-30 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -925,15 +925,15 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>外资: -157 张
-投信: +60 张
-[2026-10-20 官方结算] 投信内资买超 (+60 张) 逢低承接，外资高档调节 (-157 张)。</t>
+          <t>外资: -190 张
+投信: +147 张
+[2026-10-21 官方结算] 投信内资买超 (+147 张) 逢低承接，外资高档调节 (-190 张)。</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 193 张 (占量 7.6%)
-[2026-10-20 筹码] 主力机构呈净卖出 (-193 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 185 张 (占量 7.3%)
+[2026-10-21 筹码] 主力机构呈净卖出 (-185 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
@@ -1012,15 +1012,15 @@
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>外资: -599 张
-投信: +881 张
-[2026-10-20 官方结算] 投信内资买超 (+881 张) 逢低承接，外资高档调节 (-599 张)。</t>
+          <t>外资: -1173 张
+投信: +452 张
+[2026-10-21 官方结算] 投信内资买超 (+452 张) 逢低承接，外资高档调节 (-1,173 张)。</t>
         </is>
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 209 张 (占量 5.5%)
-[2026-10-20 筹码] 主力机构呈净买入 (+209 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 847 张 (占量 22.3%)
+[2026-10-21 筹码] 主力机构呈净卖出 (-847 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I7" s="15" t="inlineStr">
@@ -1099,15 +1099,15 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>外资: +3853 张
-投信: +967 张
-[2026-10-20 官方结算] 三大法人全线买超 (+5,218 张)，外资与投信合力加仓。</t>
+          <t>外资: +30172 张
+投信: +397 张
+[2026-10-21 官方结算] 外资与投信联手买超 (+27,794 张)，内外部机构共振做多。</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 5,218 张 (占量 9.8%)
-[2026-10-20 筹码] 主力机构呈净买入 (+5,218 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 27,794 张 (占量 52.1%)
+[2026-10-21 筹码] 主力机构呈净买入 (+27,794 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -1186,15 +1186,15 @@
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
-          <t>外资: -3501 张
-投信: +603 张
-[2026-10-20 官方结算] 投信内资买超 (+603 张) 逢低承接，外资高档调节 (-3,501 张)。</t>
+          <t>外资: -2536 张
+投信: +353 张
+[2026-10-21 官方结算] 投信内资买超 (+353 张) 逢低承接，外资高档调节 (-2,536 张)。</t>
         </is>
       </c>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 3,275 张 (占量 31.1%)
-[2026-10-20 筹码] 主力机构呈净卖出 (-3,275 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 2,336 张 (占量 22.2%)
+[2026-10-21 筹码] 主力机构呈净卖出 (-2,336 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I9" s="15" t="inlineStr">
@@ -1273,15 +1273,15 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>外资: -553 张
-投信: +926 张
-[2026-10-20 官方结算] 投信内资买超 (+926 张) 逢低承接，外资高档调节 (-553 张)。</t>
+          <t>外资: -1544 张
+投信: -121 张
+[2026-10-21 官方结算] 三大法人同步卖超 (-1,864 张)，短线筹码面临清洗。</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 256 张 (占量 3.6%)
-[2026-10-20 筹码] 主力机构呈净买入 (+256 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 1,864 张 (占量 26.1%)
+[2026-10-21 筹码] 主力机构呈净卖出 (-1,864 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1360,15 +1360,15 @@
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>外资: -423 张
-投信: +166 张
-[2026-10-20 官方结算] 投信内资买超 (+166 张) 逢低承接，外资高档调节 (-423 张)。</t>
+          <t>外资: -827 张
+投信: +314 张
+[2026-10-21 官方结算] 投信内资买超 (+314 张) 逢低承接，外资高档调节 (-827 张)。</t>
         </is>
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 290 张 (占量 11.2%)
-[2026-10-20 筹码] 主力机构呈净卖出 (-290 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 542 张 (占量 20.9%)
+[2026-10-21 筹码] 主力机构呈净卖出 (-542 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I11" s="15" t="inlineStr">
@@ -1447,15 +1447,15 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>外资: -1958 张
-投信: +599 张
-[2026-10-20 官方结算] 投信内资买超 (+599 张) 逢低承接，外资高档调节 (-1,958 张)。</t>
+          <t>外资: +65 张
+投信: +267 张
+[2026-10-21 官方结算] 三大法人全线买超 (+467 张)，外资与投信合力加仓。</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 2,005 张 (占量 19.2%)
-[2026-10-20 筹码] 主力机构呈净卖出 (-2,005 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 467 张 (占量 4.5%)
+[2026-10-21 筹码] 主力机构呈净买入 (+467 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -1534,15 +1534,15 @@
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>外资: -1566 张
-投信: +295 张
-[2026-10-20 官方结算] 投信内资买超 (+295 张) 逢低承接，外资高档调节 (-1,566 张)。</t>
+          <t>外资: -1162 张
+投信: +167 张
+[2026-10-21 官方结算] 投信内资买超 (+167 张) 逢低承接，外资高档调节 (-1,162 张)。</t>
         </is>
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 1,368 张 (占量 17.1%)
-[2026-10-20 筹码] 主力机构呈净卖出 (-1,368 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 1,646 张 (占量 20.5%)
+[2026-10-21 筹码] 主力机构呈净卖出 (-1,646 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I13" s="15" t="inlineStr">
@@ -1621,15 +1621,15 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>外资: -80 张
-投信: +78 张
-[2026-10-20 官方结算] 投信内资买超 (+78 张) 逢低承接，外资高档调节 (-80 张)。</t>
+          <t>外资: -180 张
+投信: -3 张
+[2026-10-21 官方结算] 三大法人同步卖超 (-224 张)，短线筹码面临清洗。</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 16 张 (占量 1.3%)
-[2026-10-20 筹码] 主力机构呈净卖出 (-16 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 224 张 (占量 17.6%)
+[2026-10-21 筹码] 主力机构呈净卖出 (-224 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -1708,7 +1708,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-21 15:06:14 | 策略: 3-3-4 分批建仓</t>
+          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-21 20:09:46 | 策略: 3-3-4 分批建仓</t>
         </is>
       </c>
     </row>

--- a/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
+++ b/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
@@ -631,7 +631,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>定盘时间: 2026-10-21 20:09:46 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
+          <t>定盘时间: 2026-10-22 20:13:08 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
         </is>
       </c>
     </row>
@@ -730,10 +730,10 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>开盘: 2425.0
+          <t>开盘: 2435.0
 最高: 2435.0
-最低: 2400.0
-收盘: 2420.0</t>
+最低: 2385.0
+收盘: 2385.0</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -751,15 +751,15 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>外资: -6154 张
-投信: +1397 张
-[2026-10-21 官方结算] 投信内资买超 (+1,397 张) 逢低承接，外资高档调节 (-6,154 张)。</t>
+          <t>外资: -12695 张
+投信: +1349 张
+[2026-10-22 官方结算] 投信内资买超 (+1,349 张) 逢低承接，外资高档调节 (-12,695 张)。</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 5,805 张 (占量 26.1%)
-[2026-10-21 筹码] 主力机构呈净卖出 (-5,805 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 10,150 张 (占量 44.6%)
+[2026-10-22 筹码] 主力机构呈净卖出 (-10,150 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2420.0</t>
+          <t>NT$ 2385.0</t>
         </is>
       </c>
       <c r="K4" s="9" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>22,276 张</t>
+          <t>22,750 张</t>
         </is>
       </c>
     </row>
@@ -817,10 +817,10 @@
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>开盘: 10500.0
-最高: 10580.0
-最低: 9985.0
-收盘: 10080.0</t>
+          <t>开盘: 10100.0
+最高: 10255.0
+最低: 9755.0
+收盘: 9755.0</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -838,15 +838,15 @@
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>外资: -48 张
-投信: +40 张
-[2026-10-21 官方结算] 投信内资买超 (+40 张) 逢低承接，外资高档调节 (-48 张)。</t>
+          <t>外资: +19 张
+投信: +21 张
+[2026-10-22 官方结算] 三大法人全线买超 (+42 张)，外资与投信合力加仓。</t>
         </is>
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 30 张 (占量 5.1%)
-[2026-10-21 筹码] 主力机构呈净卖出 (-30 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 42 张 (占量 10.2%)
+[2026-10-22 筹码] 主力机构呈净买入 (+42 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 10080.0</t>
+          <t>NT$ 9755.0</t>
         </is>
       </c>
       <c r="K5" s="18" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="O5" s="16" t="inlineStr">
         <is>
-          <t>592 张</t>
+          <t>410 张</t>
         </is>
       </c>
     </row>
@@ -904,10 +904,10 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>开盘: 5135.0
-最高: 5205.0
-最低: 4965.0
-收盘: 4990.0</t>
+          <t>开盘: 5335.0
+最高: 5485.0
+最低: 5060.0
+收盘: 5070.0</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -925,15 +925,15 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>外资: -190 张
-投信: +147 张
-[2026-10-21 官方结算] 投信内资买超 (+147 张) 逢低承接，外资高档调节 (-190 张)。</t>
+          <t>外资: +162 张
+投信: +36 张
+[2026-10-22 官方结算] 三大法人全线买超 (+263 张)，外资与投信合力加仓。</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 185 张 (占量 7.3%)
-[2026-10-21 筹码] 主力机构呈净卖出 (-185 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 263 张 (占量 6.0%)
+[2026-10-22 筹码] 主力机构呈净买入 (+263 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 4990.0</t>
+          <t>NT$ 5070.0</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>2,537 张</t>
+          <t>4,350 张</t>
         </is>
       </c>
     </row>
@@ -991,10 +991,10 @@
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>开盘: 3400.0
-最高: 3450.0
-最低: 3195.0
-收盘: 3235.0</t>
+          <t>开盘: 3285.0
+最高: 3395.0
+最低: 3145.0
+收盘: 3145.0</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -1012,15 +1012,15 @@
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>外资: -1173 张
-投信: +452 张
-[2026-10-21 官方结算] 投信内资买超 (+452 张) 逢低承接，外资高档调节 (-1,173 张)。</t>
+          <t>外资: +69 张
+投信: +212 张
+[2026-10-22 官方结算] 三大法人全线买超 (+283 张)，外资与投信合力加仓。</t>
         </is>
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 847 张 (占量 22.3%)
-[2026-10-21 筹码] 主力机构呈净卖出 (-847 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 283 张 (占量 11.9%)
+[2026-10-22 筹码] 主力机构呈净买入 (+283 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I7" s="15" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="J7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3235.0</t>
+          <t>NT$ 3145.0</t>
         </is>
       </c>
       <c r="K7" s="18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="O7" s="16" t="inlineStr">
         <is>
-          <t>3,802 张</t>
+          <t>2,382 张</t>
         </is>
       </c>
     </row>
@@ -1078,10 +1078,10 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>开盘: 244.5
-最高: 250.0
+          <t>开盘: 249.5
+最高: 250.5
 最低: 244.5
-收盘: 250.0</t>
+收盘: 245.0</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -1099,15 +1099,15 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>外资: +30172 张
-投信: +397 张
-[2026-10-21 官方结算] 外资与投信联手买超 (+27,794 张)，内外部机构共振做多。</t>
+          <t>外资: +1739 张
+投信: -256 张
+[2026-10-22 官方结算] 外资主力大幅回流 (+1,739 张)，投信阶段获利减仓 (-256 张)。</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 27,794 张 (占量 52.1%)
-[2026-10-21 筹码] 主力机构呈净买入 (+27,794 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 1,916 张 (占量 7.4%)
+[2026-10-22 筹码] 主力机构呈净买入 (+1,916 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>NT$ 250.0</t>
+          <t>NT$ 245.0</t>
         </is>
       </c>
       <c r="K8" s="9" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="O8" s="7" t="inlineStr">
         <is>
-          <t>53,380 张</t>
+          <t>25,973 张</t>
         </is>
       </c>
     </row>
@@ -1165,10 +1165,10 @@
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>开盘: 1625.0
-最高: 1660.0
-最低: 1600.0
-收盘: 1625.0</t>
+          <t>开盘: 1640.0
+最高: 1650.0
+最低: 1560.0
+收盘: 1560.0</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -1186,15 +1186,15 @@
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
-          <t>外资: -2536 张
-投信: +353 张
-[2026-10-21 官方结算] 投信内资买超 (+353 张) 逢低承接，外资高档调节 (-2,536 张)。</t>
+          <t>外资: -3209 张
+投信: +76 张
+[2026-10-22 官方结算] 投信内资买超 (+76 张) 逢低承接，外资高档调节 (-3,209 张)。</t>
         </is>
       </c>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 2,336 张 (占量 22.2%)
-[2026-10-21 筹码] 主力机构呈净卖出 (-2,336 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 3,210 张 (占量 38.8%)
+[2026-10-22 筹码] 主力机构呈净卖出 (-3,210 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I9" s="15" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="J9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1625.0</t>
+          <t>NT$ 1560.0</t>
         </is>
       </c>
       <c r="K9" s="18" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="O9" s="16" t="inlineStr">
         <is>
-          <t>10,519 张</t>
+          <t>8,266 张</t>
         </is>
       </c>
     </row>
@@ -1252,10 +1252,10 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>开盘: 2045.0
-最高: 2050.0
-最低: 1805.0
-收盘: 1815.0</t>
+          <t>开盘: 1835.0
+最高: 1880.0
+最低: 1770.0
+收盘: 1775.0</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -1273,15 +1273,15 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>外资: -1544 张
-投信: -121 张
-[2026-10-21 官方结算] 三大法人同步卖超 (-1,864 张)，短线筹码面临清洗。</t>
+          <t>外资: -241 张
+投信: +86 张
+[2026-10-22 官方结算] 投信内资买超 (+86 张) 逢低承接，外资高档调节 (-241 张)。</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 1,864 张 (占量 26.1%)
-[2026-10-21 筹码] 主力机构呈净卖出 (-1,864 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 113 张 (占量 3.5%)
+[2026-10-22 筹码] 主力机构呈净卖出 (-113 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 1815.0</t>
+          <t>NT$ 1775.0</t>
         </is>
       </c>
       <c r="K10" s="9" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>7,140 张</t>
+          <t>3,196 张</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>开盘: 2030.0
-最高: 2095.0
-最低: 1990.0
-收盘: 2010.0</t>
+          <t>开盘: 2090.0
+最高: 2110.0
+最低: 1975.0
+收盘: 1980.0</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
@@ -1360,15 +1360,15 @@
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>外资: -827 张
-投信: +314 张
-[2026-10-21 官方结算] 投信内资买超 (+314 张) 逢低承接，外资高档调节 (-827 张)。</t>
+          <t>外资: -370 张
+投信: +129 张
+[2026-10-22 官方结算] 投信内资买超 (+129 张) 逢低承接，外资高档调节 (-370 张)。</t>
         </is>
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 542 张 (占量 20.9%)
-[2026-10-21 筹码] 主力机构呈净卖出 (-542 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 266 张 (占量 12.3%)
+[2026-10-22 筹码] 主力机构呈净卖出 (-266 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I11" s="15" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="J11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2010.0</t>
+          <t>NT$ 1980.0</t>
         </is>
       </c>
       <c r="K11" s="18" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="O11" s="16" t="inlineStr">
         <is>
-          <t>2,589 张</t>
+          <t>2,170 张</t>
         </is>
       </c>
     </row>
@@ -1426,10 +1426,10 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>开盘: 684.0
-最高: 687.0
-最低: 668.0
-收盘: 684.0</t>
+          <t>开盘: 690.0
+最高: 699.0
+最低: 652.0
+收盘: 654.0</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -1447,15 +1447,15 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>外资: +65 张
-投信: +267 张
-[2026-10-21 官方结算] 三大法人全线买超 (+467 张)，外资与投信合力加仓。</t>
+          <t>外资: -5438 张
+投信: +2251 张
+[2026-10-22 官方结算] 投信内资买超 (+2,251 张) 逢低承接，外资高档调节 (-5,438 张)。</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 467 张 (占量 4.5%)
-[2026-10-21 筹码] 主力机构呈净买入 (+467 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 3,161 张 (占量 18.5%)
+[2026-10-22 筹码] 主力机构呈净卖出 (-3,161 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 684.0</t>
+          <t>NT$ 654.0</t>
         </is>
       </c>
       <c r="K12" s="9" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>10,425 张</t>
+          <t>17,102 张</t>
         </is>
       </c>
     </row>
@@ -1513,10 +1513,10 @@
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>开盘: 4215.0
-最高: 4295.0
-最低: 4095.0
-收盘: 4140.0</t>
+          <t>开盘: 4230.0
+最高: 4230.0
+最低: 4005.0
+收盘: 4010.0</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
@@ -1534,15 +1534,15 @@
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>外资: -1162 张
-投信: +167 张
-[2026-10-21 官方结算] 投信内资买超 (+167 张) 逢低承接，外资高档调节 (-1,162 张)。</t>
+          <t>外资: -1084 张
+投信: +357 张
+[2026-10-22 官方结算] 投信内资买超 (+357 张) 逢低承接，外资高档调节 (-1,084 张)。</t>
         </is>
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 1,646 张 (占量 20.5%)
-[2026-10-21 筹码] 主力机构呈净卖出 (-1,646 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 631 张 (占量 10.7%)
+[2026-10-22 筹码] 主力机构呈净卖出 (-631 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I13" s="15" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="J13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 4140.0</t>
+          <t>NT$ 4010.0</t>
         </is>
       </c>
       <c r="K13" s="18" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="O13" s="16" t="inlineStr">
         <is>
-          <t>8,018 张</t>
+          <t>5,885 张</t>
         </is>
       </c>
     </row>
@@ -1600,10 +1600,10 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>开盘: 6835.0
-最高: 6985.0
-最低: 6500.0
-收盘: 6535.0</t>
+          <t>开盘: 6555.0
+最高: 6675.0
+最低: 5995.0
+收盘: 6070.0</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -1621,15 +1621,15 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>外资: -180 张
-投信: -3 张
-[2026-10-21 官方结算] 三大法人同步卖超 (-224 张)，短线筹码面临清洗。</t>
+          <t>外资: +311 张
+投信: -191 张
+[2026-10-22 官方结算] 外资主力大幅回流 (+311 张)，投信阶段获利减仓 (-191 张)。</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 224 张 (占量 17.6%)
-[2026-10-21 筹码] 主力机构呈净卖出 (-224 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 125 张 (占量 7.6%)
+[2026-10-22 筹码] 主力机构呈净买入 (+125 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>NT$ 6535.0</t>
+          <t>NT$ 6070.0</t>
         </is>
       </c>
       <c r="K14" s="9" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="O14" s="7" t="inlineStr">
         <is>
-          <t>1,271 张</t>
+          <t>1,645 张</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-21 20:09:46 | 策略: 3-3-4 分批建仓</t>
+          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-22 20:13:08 | 策略: 3-3-4 分批建仓</t>
         </is>
       </c>
     </row>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="C4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2425.0</t>
+          <t>NT$ 2435.0</t>
         </is>
       </c>
       <c r="D4" s="24" t="inlineStr">
@@ -1782,12 +1782,12 @@
       </c>
       <c r="E4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2400.0</t>
+          <t>NT$ 2385.0</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2420.0</t>
+          <t>NT$ 2385.0</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
@@ -1819,22 +1819,22 @@
       </c>
       <c r="C5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 10500.0</t>
+          <t>NT$ 10100.0</t>
         </is>
       </c>
       <c r="D5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 10580.0</t>
+          <t>NT$ 10255.0</t>
         </is>
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 9985.0</t>
+          <t>NT$ 9755.0</t>
         </is>
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 10080.0</t>
+          <t>NT$ 9755.0</t>
         </is>
       </c>
       <c r="G5" s="29" t="inlineStr">
@@ -1866,22 +1866,22 @@
       </c>
       <c r="C6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5135.0</t>
+          <t>NT$ 5335.0</t>
         </is>
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5205.0</t>
+          <t>NT$ 5485.0</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 4965.0</t>
+          <t>NT$ 5060.0</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 4990.0</t>
+          <t>NT$ 5070.0</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
@@ -1913,22 +1913,22 @@
       </c>
       <c r="C7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3400.0</t>
+          <t>NT$ 3285.0</t>
         </is>
       </c>
       <c r="D7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3450.0</t>
+          <t>NT$ 3395.0</t>
         </is>
       </c>
       <c r="E7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3195.0</t>
+          <t>NT$ 3145.0</t>
         </is>
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3235.0</t>
+          <t>NT$ 3145.0</t>
         </is>
       </c>
       <c r="G7" s="29" t="inlineStr">
@@ -1960,22 +1960,22 @@
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
+          <t>NT$ 249.5</t>
+        </is>
+      </c>
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>NT$ 250.5</t>
+        </is>
+      </c>
+      <c r="E8" s="24" t="inlineStr">
+        <is>
           <t>NT$ 244.5</t>
         </is>
       </c>
-      <c r="D8" s="24" t="inlineStr">
-        <is>
-          <t>NT$ 250.0</t>
-        </is>
-      </c>
-      <c r="E8" s="24" t="inlineStr">
-        <is>
-          <t>NT$ 244.5</t>
-        </is>
-      </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>NT$ 250.0</t>
+          <t>NT$ 245.0</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
@@ -2007,22 +2007,22 @@
       </c>
       <c r="C9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1625.0</t>
+          <t>NT$ 1640.0</t>
         </is>
       </c>
       <c r="D9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1660.0</t>
+          <t>NT$ 1650.0</t>
         </is>
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1600.0</t>
+          <t>NT$ 1560.0</t>
         </is>
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1625.0</t>
+          <t>NT$ 1560.0</t>
         </is>
       </c>
       <c r="G9" s="29" t="inlineStr">
@@ -2054,22 +2054,22 @@
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2045.0</t>
+          <t>NT$ 1835.0</t>
         </is>
       </c>
       <c r="D10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2050.0</t>
+          <t>NT$ 1880.0</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1805.0</t>
+          <t>NT$ 1770.0</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 1815.0</t>
+          <t>NT$ 1775.0</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
@@ -2101,22 +2101,22 @@
       </c>
       <c r="C11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2030.0</t>
+          <t>NT$ 2090.0</t>
         </is>
       </c>
       <c r="D11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2095.0</t>
+          <t>NT$ 2110.0</t>
         </is>
       </c>
       <c r="E11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1990.0</t>
+          <t>NT$ 1975.0</t>
         </is>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2010.0</t>
+          <t>NT$ 1980.0</t>
         </is>
       </c>
       <c r="G11" s="29" t="inlineStr">
@@ -2148,22 +2148,22 @@
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 684.0</t>
+          <t>NT$ 690.0</t>
         </is>
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 687.0</t>
+          <t>NT$ 699.0</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 668.0</t>
+          <t>NT$ 652.0</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 684.0</t>
+          <t>NT$ 654.0</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
@@ -2195,22 +2195,22 @@
       </c>
       <c r="C13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4215.0</t>
+          <t>NT$ 4230.0</t>
         </is>
       </c>
       <c r="D13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4295.0</t>
+          <t>NT$ 4230.0</t>
         </is>
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4095.0</t>
+          <t>NT$ 4005.0</t>
         </is>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 4140.0</t>
+          <t>NT$ 4010.0</t>
         </is>
       </c>
       <c r="G13" s="29" t="inlineStr">
@@ -2242,22 +2242,22 @@
       </c>
       <c r="C14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 6835.0</t>
+          <t>NT$ 6555.0</t>
         </is>
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 6985.0</t>
+          <t>NT$ 6675.0</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 6500.0</t>
+          <t>NT$ 5995.0</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>NT$ 6535.0</t>
+          <t>NT$ 6070.0</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">

--- a/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
+++ b/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="核心卡位龙头全景深度分析" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="买卖决策速查面板" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="核心卡位龙头全景深度分析" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="买卖决策速查面板" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -631,7 +631,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>定盘时间: 2026-10-22 20:13:08 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
+          <t>定盘时间: 2026-10-23 14:57:17 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-22 20:13:08 | 策略: 3-3-4 分批建仓</t>
+          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-23 14:57:17 | 策略: 3-3-4 分批建仓</t>
         </is>
       </c>
     </row>

--- a/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
+++ b/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="核心卡位龙头全景深度分析" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="买卖决策速查面板" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="核心卡位龙头全景深度分析" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="买卖决策速查面板" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -631,7 +631,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>定盘时间: 2026-10-23 14:57:17 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
+          <t>定盘时间: 2026-10-23 19:54:13 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-23 14:57:17 | 策略: 3-3-4 分批建仓</t>
+          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-23 19:54:13 | 策略: 3-3-4 分批建仓</t>
         </is>
       </c>
     </row>

--- a/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
+++ b/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="核心卡位龙头全景深度分析" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="买卖决策速查面板" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="核心卡位龙头全景深度分析" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="买卖决策速查面板" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
+++ b/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
@@ -631,7 +631,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>定盘时间: 2026-10-23 19:54:13 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
+          <t>定盘时间: 2026-10-26 15:03:33 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-23 19:54:13 | 策略: 3-3-4 分批建仓</t>
+          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-26 15:03:33 | 策略: 3-3-4 分批建仓</t>
         </is>
       </c>
     </row>

--- a/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
+++ b/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="核心卡位龙头全景深度分析" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="买卖决策速查面板" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="核心卡位龙头全景深度分析" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="买卖决策速查面板" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -631,7 +631,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>定盘时间: 2026-10-26 15:03:33 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
+          <t>定盘时间: 2026-10-26 21:25:08 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-26 15:03:33 | 策略: 3-3-4 分批建仓</t>
+          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-26 21:25:08 | 策略: 3-3-4 分批建仓</t>
         </is>
       </c>
     </row>

--- a/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
+++ b/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="核心卡位龙头全景深度分析" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="买卖决策速查面板" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="核心卡位龙头全景深度分析" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="买卖决策速查面板" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -631,7 +631,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>定盘时间: 2026-10-26 21:25:08 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
+          <t>定盘时间: 2026-10-27 15:04:06 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
         </is>
       </c>
     </row>
@@ -730,10 +730,10 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>开盘: 2435.0
-最高: 2435.0
-最低: 2385.0
-收盘: 2385.0</t>
+          <t>开盘: 2380.0
+最高: 2405.0
+最低: 2380.0
+收盘: 2400.0</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2385.0</t>
+          <t>NT$ 2400.0</t>
         </is>
       </c>
       <c r="K4" s="9" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>22,750 张</t>
+          <t>33,882 张</t>
         </is>
       </c>
     </row>
@@ -817,10 +817,10 @@
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>开盘: 10100.0
-最高: 10255.0
-最低: 9755.0
-收盘: 9755.0</t>
+          <t>开盘: 9830.0
+最高: 9890.0
+最低: 9475.0
+收盘: 9810.0</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 9755.0</t>
+          <t>NT$ 9810.0</t>
         </is>
       </c>
       <c r="K5" s="18" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="O5" s="16" t="inlineStr">
         <is>
-          <t>410 张</t>
+          <t>557 张</t>
         </is>
       </c>
     </row>
@@ -904,10 +904,10 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>开盘: 5335.0
-最高: 5485.0
-最低: 5060.0
-收盘: 5070.0</t>
+          <t>开盘: 5200.0
+最高: 5200.0
+最低: 4685.0
+收盘: 4750.0</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 5070.0</t>
+          <t>NT$ 4750.0</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>4,350 张</t>
+          <t>4,438 张</t>
         </is>
       </c>
     </row>
@@ -991,10 +991,10 @@
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>开盘: 3285.0
-最高: 3395.0
-最低: 3145.0
-收盘: 3145.0</t>
+          <t>开盘: 3300.0
+最高: 3320.0
+最低: 3050.0
+收盘: 3130.0</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="J7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3145.0</t>
+          <t>NT$ 3130.0</t>
         </is>
       </c>
       <c r="K7" s="18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="O7" s="16" t="inlineStr">
         <is>
-          <t>2,382 张</t>
+          <t>2,691 张</t>
         </is>
       </c>
     </row>
@@ -1078,10 +1078,10 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>开盘: 249.5
-最高: 250.5
-最低: 244.5
-收盘: 245.0</t>
+          <t>开盘: 246.5
+最高: 248.5
+最低: 244.0
+收盘: 247.5</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>NT$ 245.0</t>
+          <t>NT$ 247.5</t>
         </is>
       </c>
       <c r="K8" s="9" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="O8" s="7" t="inlineStr">
         <is>
-          <t>25,973 张</t>
+          <t>52,096 张</t>
         </is>
       </c>
     </row>
@@ -1165,10 +1165,10 @@
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>开盘: 1640.0
-最高: 1650.0
-最低: 1560.0
-收盘: 1560.0</t>
+          <t>开盘: 1535.0
+最高: 1570.0
+最低: 1490.0
+收盘: 1510.0</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="J9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1560.0</t>
+          <t>NT$ 1510.0</t>
         </is>
       </c>
       <c r="K9" s="18" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="O9" s="16" t="inlineStr">
         <is>
-          <t>8,266 张</t>
+          <t>16,641 张</t>
         </is>
       </c>
     </row>
@@ -1252,10 +1252,10 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>开盘: 1835.0
-最高: 1880.0
-最低: 1770.0
-收盘: 1775.0</t>
+          <t>开盘: 1760.0
+最高: 1805.0
+最低: 1740.0
+收盘: 1760.0</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 1775.0</t>
+          <t>NT$ 1760.0</t>
         </is>
       </c>
       <c r="K10" s="9" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>3,196 张</t>
+          <t>4,243 张</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>开盘: 2090.0
-最高: 2110.0
-最低: 1975.0
-收盘: 1980.0</t>
+          <t>开盘: 1910.0
+最高: 1980.0
+最低: 1905.0
+收盘: 1955.0</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="J11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1980.0</t>
+          <t>NT$ 1955.0</t>
         </is>
       </c>
       <c r="K11" s="18" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="O11" s="16" t="inlineStr">
         <is>
-          <t>2,170 张</t>
+          <t>3,549 张</t>
         </is>
       </c>
     </row>
@@ -1426,10 +1426,10 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>开盘: 690.0
-最高: 699.0
-最低: 652.0
-收盘: 654.0</t>
+          <t>开盘: 654.0
+最高: 668.0
+最低: 642.0
+收盘: 651.0</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 654.0</t>
+          <t>NT$ 651.0</t>
         </is>
       </c>
       <c r="K12" s="9" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>17,102 张</t>
+          <t>25,169 张</t>
         </is>
       </c>
     </row>
@@ -1513,10 +1513,10 @@
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>开盘: 4230.0
-最高: 4230.0
-最低: 4005.0
-收盘: 4010.0</t>
+          <t>开盘: 4035.0
+最高: 4075.0
+最低: 3910.0
+收盘: 3960.0</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="J13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 4010.0</t>
+          <t>NT$ 3960.0</t>
         </is>
       </c>
       <c r="K13" s="18" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="O13" s="16" t="inlineStr">
         <is>
-          <t>5,885 张</t>
+          <t>11,978 张</t>
         </is>
       </c>
     </row>
@@ -1600,10 +1600,10 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>开盘: 6555.0
-最高: 6675.0
-最低: 5995.0
-收盘: 6070.0</t>
+          <t>开盘: 6080.0
+最高: 6095.0
+最低: 5710.0
+收盘: 5860.0</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>NT$ 6070.0</t>
+          <t>NT$ 5860.0</t>
         </is>
       </c>
       <c r="K14" s="9" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="O14" s="7" t="inlineStr">
         <is>
-          <t>1,645 张</t>
+          <t>2,354 张</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-26 21:25:08 | 策略: 3-3-4 分批建仓</t>
+          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-27 15:04:06 | 策略: 3-3-4 分批建仓</t>
         </is>
       </c>
     </row>
@@ -1772,22 +1772,22 @@
       </c>
       <c r="C4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2435.0</t>
+          <t>NT$ 2380.0</t>
         </is>
       </c>
       <c r="D4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2435.0</t>
+          <t>NT$ 2405.0</t>
         </is>
       </c>
       <c r="E4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2385.0</t>
+          <t>NT$ 2380.0</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2385.0</t>
+          <t>NT$ 2400.0</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
@@ -1819,22 +1819,22 @@
       </c>
       <c r="C5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 10100.0</t>
+          <t>NT$ 9830.0</t>
         </is>
       </c>
       <c r="D5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 10255.0</t>
+          <t>NT$ 9890.0</t>
         </is>
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 9755.0</t>
+          <t>NT$ 9475.0</t>
         </is>
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 9755.0</t>
+          <t>NT$ 9810.0</t>
         </is>
       </c>
       <c r="G5" s="29" t="inlineStr">
@@ -1866,22 +1866,22 @@
       </c>
       <c r="C6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5335.0</t>
+          <t>NT$ 5200.0</t>
         </is>
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5485.0</t>
+          <t>NT$ 5200.0</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5060.0</t>
+          <t>NT$ 4685.0</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 5070.0</t>
+          <t>NT$ 4750.0</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
@@ -1913,22 +1913,22 @@
       </c>
       <c r="C7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3285.0</t>
+          <t>NT$ 3300.0</t>
         </is>
       </c>
       <c r="D7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3395.0</t>
+          <t>NT$ 3320.0</t>
         </is>
       </c>
       <c r="E7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3145.0</t>
+          <t>NT$ 3050.0</t>
         </is>
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3145.0</t>
+          <t>NT$ 3130.0</t>
         </is>
       </c>
       <c r="G7" s="29" t="inlineStr">
@@ -1960,22 +1960,22 @@
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 249.5</t>
+          <t>NT$ 246.5</t>
         </is>
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 250.5</t>
+          <t>NT$ 248.5</t>
         </is>
       </c>
       <c r="E8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 244.5</t>
+          <t>NT$ 244.0</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>NT$ 245.0</t>
+          <t>NT$ 247.5</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
@@ -2007,22 +2007,22 @@
       </c>
       <c r="C9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1640.0</t>
+          <t>NT$ 1535.0</t>
         </is>
       </c>
       <c r="D9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1650.0</t>
+          <t>NT$ 1570.0</t>
         </is>
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1560.0</t>
+          <t>NT$ 1490.0</t>
         </is>
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1560.0</t>
+          <t>NT$ 1510.0</t>
         </is>
       </c>
       <c r="G9" s="29" t="inlineStr">
@@ -2054,22 +2054,22 @@
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1835.0</t>
+          <t>NT$ 1760.0</t>
         </is>
       </c>
       <c r="D10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1880.0</t>
+          <t>NT$ 1805.0</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1770.0</t>
+          <t>NT$ 1740.0</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 1775.0</t>
+          <t>NT$ 1760.0</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
@@ -2101,22 +2101,22 @@
       </c>
       <c r="C11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2090.0</t>
+          <t>NT$ 1910.0</t>
         </is>
       </c>
       <c r="D11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2110.0</t>
+          <t>NT$ 1980.0</t>
         </is>
       </c>
       <c r="E11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1975.0</t>
+          <t>NT$ 1905.0</t>
         </is>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1980.0</t>
+          <t>NT$ 1955.0</t>
         </is>
       </c>
       <c r="G11" s="29" t="inlineStr">
@@ -2148,22 +2148,22 @@
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 690.0</t>
+          <t>NT$ 654.0</t>
         </is>
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 699.0</t>
+          <t>NT$ 668.0</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 652.0</t>
+          <t>NT$ 642.0</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 654.0</t>
+          <t>NT$ 651.0</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
@@ -2195,22 +2195,22 @@
       </c>
       <c r="C13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4230.0</t>
+          <t>NT$ 4035.0</t>
         </is>
       </c>
       <c r="D13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4230.0</t>
+          <t>NT$ 4075.0</t>
         </is>
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4005.0</t>
+          <t>NT$ 3910.0</t>
         </is>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 4010.0</t>
+          <t>NT$ 3960.0</t>
         </is>
       </c>
       <c r="G13" s="29" t="inlineStr">
@@ -2242,22 +2242,22 @@
       </c>
       <c r="C14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 6555.0</t>
+          <t>NT$ 6080.0</t>
         </is>
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 6675.0</t>
+          <t>NT$ 6095.0</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5995.0</t>
+          <t>NT$ 5710.0</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>NT$ 6070.0</t>
+          <t>NT$ 5860.0</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">

--- a/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
+++ b/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="核心卡位龙头全景深度分析" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="买卖决策速查面板" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="核心卡位龙头全景深度分析" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="买卖决策速查面板" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -631,7 +631,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>定盘时间: 2026-10-27 15:04:06 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
+          <t>定盘时间: 2026-10-27 20:31:24 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
         </is>
       </c>
     </row>
@@ -751,15 +751,15 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>外资: -12695 张
-投信: +1349 张
-[2026-10-22 官方结算] 投信内资买超 (+1,349 张) 逢低承接，外资高档调节 (-12,695 张)。</t>
+          <t>外资: -1619 张
+投信: +2420 张
+[2026-10-27 官方结算] 投信内资买超 (+2,420 张) 逢低承接，外资高档调节 (-1,619 张)。</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 10,150 张 (占量 44.6%)
-[2026-10-22 筹码] 主力机构呈净卖出 (-10,150 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 2,709 张 (占量 8.0%)
+[2026-10-27 筹码] 主力机构呈净买入 (+2,709 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
@@ -838,15 +838,15 @@
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>外资: +19 张
-投信: +21 张
-[2026-10-22 官方结算] 三大法人全线买超 (+42 张)，外资与投信合力加仓。</t>
+          <t>外资: +64 张
+投信: +32 张
+[2026-10-27 官方结算] 三大法人全线买超 (+108 张)，外资与投信合力加仓。</t>
         </is>
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 42 张 (占量 10.2%)
-[2026-10-22 筹码] 主力机构呈净买入 (+42 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 108 张 (占量 19.4%)
+[2026-10-27 筹码] 主力机构呈净买入 (+108 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -925,15 +925,15 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>外资: +162 张
-投信: +36 张
-[2026-10-22 官方结算] 三大法人全线买超 (+263 张)，外资与投信合力加仓。</t>
+          <t>外资: -1055 张
+投信: +146 张
+[2026-10-27 官方结算] 投信内资买超 (+146 张) 逢低承接，外资高档调节 (-1,055 张)。</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 263 张 (占量 6.0%)
-[2026-10-22 筹码] 主力机构呈净买入 (+263 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 760 张 (占量 17.1%)
+[2026-10-27 筹码] 主力机构呈净卖出 (-760 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
@@ -1012,15 +1012,15 @@
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>外资: +69 张
-投信: +212 张
-[2026-10-22 官方结算] 三大法人全线买超 (+283 张)，外资与投信合力加仓。</t>
+          <t>外资: -247 张
+投信: +375 张
+[2026-10-27 官方结算] 投信内资买超 (+375 张) 逢低承接，外资高档调节 (-247 张)。</t>
         </is>
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 283 张 (占量 11.9%)
-[2026-10-22 筹码] 主力机构呈净买入 (+283 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 126 张 (占量 4.7%)
+[2026-10-27 筹码] 主力机构呈净买入 (+126 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I7" s="15" t="inlineStr">
@@ -1099,15 +1099,15 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>外资: +1739 张
-投信: -256 张
-[2026-10-22 官方结算] 外资主力大幅回流 (+1,739 张)，投信阶段获利减仓 (-256 张)。</t>
+          <t>外资: +4971 张
+投信: +828 张
+[2026-10-27 官方结算] 三大法人全线买超 (+7,123 张)，外资与投信合力加仓。</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 1,916 张 (占量 7.4%)
-[2026-10-22 筹码] 主力机构呈净买入 (+1,916 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 7,123 张 (占量 13.7%)
+[2026-10-27 筹码] 主力机构呈净买入 (+7,123 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -1186,15 +1186,15 @@
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
-          <t>外资: -3209 张
-投信: +76 张
-[2026-10-22 官方结算] 投信内资买超 (+76 张) 逢低承接，外资高档调节 (-3,209 张)。</t>
+          <t>外资: -3334 张
+投信: +7 张
+[2026-10-27 官方结算] 投信内资买超 (+7 张) 逢低承接，外资高档调节 (-3,334 张)。</t>
         </is>
       </c>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 3,210 张 (占量 38.8%)
-[2026-10-22 筹码] 主力机构呈净卖出 (-3,210 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 2,662 张 (占量 16.0%)
+[2026-10-27 筹码] 主力机构呈净卖出 (-2,662 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I9" s="15" t="inlineStr">
@@ -1273,15 +1273,15 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>外资: -241 张
-投信: +86 张
-[2026-10-22 官方结算] 投信内资买超 (+86 张) 逢低承接，外资高档调节 (-241 张)。</t>
+          <t>外资: +475 张
+投信: +21 张
+[2026-10-27 官方结算] 三大法人全线买超 (+552 张)，外资与投信合力加仓。</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 113 张 (占量 3.5%)
-[2026-10-22 筹码] 主力机构呈净卖出 (-113 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 552 张 (占量 13.0%)
+[2026-10-27 筹码] 主力机构呈净买入 (+552 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1360,15 +1360,15 @@
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>外资: -370 张
-投信: +129 张
-[2026-10-22 官方结算] 投信内资买超 (+129 张) 逢低承接，外资高档调节 (-370 张)。</t>
+          <t>外资: -170 张
+投信: +78 张
+[2026-10-27 官方结算] 投信内资买超 (+78 张) 逢低承接，外资高档调节 (-170 张)。</t>
         </is>
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 266 张 (占量 12.3%)
-[2026-10-22 筹码] 主力机构呈净卖出 (-266 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 42 张 (占量 1.2%)
+[2026-10-27 筹码] 主力机构呈净卖出 (-42 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I11" s="15" t="inlineStr">
@@ -1447,15 +1447,15 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>外资: -5438 张
-投信: +2251 张
-[2026-10-22 官方结算] 投信内资买超 (+2,251 张) 逢低承接，外资高档调节 (-5,438 张)。</t>
+          <t>外资: -5281 张
+投信: +3786 张
+[2026-10-27 官方结算] 投信内资买超 (+3,786 张) 逢低承接，外资高档调节 (-5,281 张)。</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 3,161 张 (占量 18.5%)
-[2026-10-22 筹码] 主力机构呈净卖出 (-3,161 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 850 张 (占量 3.4%)
+[2026-10-27 筹码] 主力机构呈净卖出 (-850 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -1534,15 +1534,15 @@
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>外资: -1084 张
-投信: +357 张
-[2026-10-22 官方结算] 投信内资买超 (+357 张) 逢低承接，外资高档调节 (-1,084 张)。</t>
+          <t>外资: -2340 张
+投信: +674 张
+[2026-10-27 官方结算] 投信内资买超 (+674 张) 逢低承接，外资高档调节 (-2,340 张)。</t>
         </is>
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 631 张 (占量 10.7%)
-[2026-10-22 筹码] 主力机构呈净卖出 (-631 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 1,492 张 (占量 12.5%)
+[2026-10-27 筹码] 主力机构呈净卖出 (-1,492 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I13" s="15" t="inlineStr">
@@ -1621,15 +1621,15 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>外资: +311 张
-投信: -191 张
-[2026-10-22 官方结算] 外资主力大幅回流 (+311 张)，投信阶段获利减仓 (-191 张)。</t>
+          <t>外资: +780 张
+投信: +58 张
+[2026-10-27 官方结算] 三大法人全线买超 (+857 张)，外资与投信合力加仓。</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 125 张 (占量 7.6%)
-[2026-10-22 筹码] 主力机构呈净买入 (+125 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 857 张 (占量 36.4%)
+[2026-10-27 筹码] 主力机构呈净买入 (+857 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -1708,7 +1708,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-27 15:04:06 | 策略: 3-3-4 分批建仓</t>
+          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-27 20:31:24 | 策略: 3-3-4 分批建仓</t>
         </is>
       </c>
     </row>

--- a/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
+++ b/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="核心卡位龙头全景深度分析" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="买卖决策速查面板" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="核心卡位龙头全景深度分析" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="买卖决策速查面板" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -631,7 +631,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>定盘时间: 2026-10-27 20:31:24 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
+          <t>定盘时间: 2026-10-28 14:57:18 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
         </is>
       </c>
     </row>
@@ -730,10 +730,10 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>开盘: 2380.0
-最高: 2405.0
-最低: 2380.0
-收盘: 2400.0</t>
+          <t>开盘: 2420.0
+最高: 2430.0
+最低: 2410.0
+收盘: 2425.0</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 2,709 张 (占量 8.0%)
+          <t>法人净买超 2,709 张 (占量 13.6%)
 [2026-10-27 筹码] 主力机构呈净买入 (+2,709 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
@@ -769,7 +769,7 @@
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2400.0</t>
+          <t>NT$ 2425.0</t>
         </is>
       </c>
       <c r="K4" s="9" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>33,882 张</t>
+          <t>19,852 张</t>
         </is>
       </c>
     </row>
@@ -817,10 +817,10 @@
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>开盘: 9830.0
-最高: 9890.0
-最低: 9475.0
-收盘: 9810.0</t>
+          <t>开盘: 10225.0
+最高: 10290.0
+最低: 10015.0
+收盘: 10150.0</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 108 张 (占量 19.4%)
+          <t>法人净买超 108 张 (占量 35.4%)
 [2026-10-27 筹码] 主力机构呈净买入 (+108 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
@@ -856,7 +856,7 @@
       </c>
       <c r="J5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 9810.0</t>
+          <t>NT$ 10150.0</t>
         </is>
       </c>
       <c r="K5" s="18" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="O5" s="16" t="inlineStr">
         <is>
-          <t>557 张</t>
+          <t>305 张</t>
         </is>
       </c>
     </row>
@@ -904,10 +904,10 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>开盘: 5200.0
-最高: 5200.0
-最低: 4685.0
-收盘: 4750.0</t>
+          <t>开盘: 4975.0
+最高: 5065.0
+最低: 4830.0
+收盘: 5025.0</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 760 张 (占量 17.1%)
+          <t>法人净卖超 760 张 (占量 24.3%)
 [2026-10-27 筹码] 主力机构呈净卖出 (-760 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
@@ -943,7 +943,7 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 4750.0</t>
+          <t>NT$ 5025.0</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>4,438 张</t>
+          <t>3,130 张</t>
         </is>
       </c>
     </row>
@@ -991,10 +991,10 @@
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>开盘: 3300.0
-最高: 3320.0
-最低: 3050.0
-收盘: 3130.0</t>
+          <t>开盘: 3230.0
+最高: 3330.0
+最低: 3185.0
+收盘: 3215.0</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 126 张 (占量 4.7%)
+          <t>法人净买超 126 张 (占量 6.2%)
 [2026-10-27 筹码] 主力机构呈净买入 (+126 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="J7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3130.0</t>
+          <t>NT$ 3215.0</t>
         </is>
       </c>
       <c r="K7" s="18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="O7" s="16" t="inlineStr">
         <is>
-          <t>2,691 张</t>
+          <t>2,024 张</t>
         </is>
       </c>
     </row>
@@ -1078,10 +1078,10 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>开盘: 246.5
-最高: 248.5
-最低: 244.0
-收盘: 247.5</t>
+          <t>开盘: 248.0
+最高: 252.0
+最低: 246.5
+收盘: 251.5</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 7,123 张 (占量 13.7%)
+          <t>法人净买超 7,123 张 (占量 17.2%)
 [2026-10-27 筹码] 主力机构呈净买入 (+7,123 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>NT$ 247.5</t>
+          <t>NT$ 251.5</t>
         </is>
       </c>
       <c r="K8" s="9" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="O8" s="7" t="inlineStr">
         <is>
-          <t>52,096 张</t>
+          <t>41,355 张</t>
         </is>
       </c>
     </row>
@@ -1165,10 +1165,10 @@
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>开盘: 1535.0
-最高: 1570.0
-最低: 1490.0
-收盘: 1510.0</t>
+          <t>开盘: 1565.0
+最高: 1575.0
+最低: 1515.0
+收盘: 1550.0</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 2,662 张 (占量 16.0%)
+          <t>法人净卖超 2,662 张 (占量 38.4%)
 [2026-10-27 筹码] 主力机构呈净卖出 (-2,662 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="J9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1510.0</t>
+          <t>NT$ 1550.0</t>
         </is>
       </c>
       <c r="K9" s="18" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="O9" s="16" t="inlineStr">
         <is>
-          <t>16,641 张</t>
+          <t>6,925 张</t>
         </is>
       </c>
     </row>
@@ -1252,10 +1252,10 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>开盘: 1760.0
-最高: 1805.0
-最低: 1740.0
-收盘: 1760.0</t>
+          <t>开盘: 1820.0
+最高: 1830.0
+最低: 1780.0
+收盘: 1815.0</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 552 张 (占量 13.0%)
+          <t>法人净买超 552 张 (占量 19.1%)
 [2026-10-27 筹码] 主力机构呈净买入 (+552 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 1760.0</t>
+          <t>NT$ 1815.0</t>
         </is>
       </c>
       <c r="K10" s="9" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>4,243 张</t>
+          <t>2,889 张</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>开盘: 1910.0
-最高: 1980.0
-最低: 1905.0
-收盘: 1955.0</t>
+          <t>开盘: 1995.0
+最高: 2050.0
+最低: 1995.0
+收盘: 2035.0</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 42 张 (占量 1.2%)
+          <t>法人净卖超 42 张 (占量 1.0%)
 [2026-10-27 筹码] 主力机构呈净卖出 (-42 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="J11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1955.0</t>
+          <t>NT$ 2035.0</t>
         </is>
       </c>
       <c r="K11" s="18" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="O11" s="16" t="inlineStr">
         <is>
-          <t>3,549 张</t>
+          <t>4,050 张</t>
         </is>
       </c>
     </row>
@@ -1426,10 +1426,10 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>开盘: 654.0
-最高: 668.0
-最低: 642.0
-收盘: 651.0</t>
+          <t>开盘: 672.0
+最高: 698.0
+最低: 672.0
+收盘: 695.0</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 850 张 (占量 3.4%)
+          <t>法人净卖超 850 张 (占量 4.5%)
 [2026-10-27 筹码] 主力机构呈净卖出 (-850 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 651.0</t>
+          <t>NT$ 695.0</t>
         </is>
       </c>
       <c r="K12" s="9" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>25,169 张</t>
+          <t>18,912 张</t>
         </is>
       </c>
     </row>
@@ -1513,10 +1513,10 @@
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>开盘: 4035.0
-最高: 4075.0
-最低: 3910.0
-收盘: 3960.0</t>
+          <t>开盘: 4040.0
+最高: 4245.0
+最低: 4040.0
+收盘: 4235.0</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 1,492 张 (占量 12.5%)
+          <t>法人净卖超 1,492 张 (占量 21.5%)
 [2026-10-27 筹码] 主力机构呈净卖出 (-1,492 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="J13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3960.0</t>
+          <t>NT$ 4235.0</t>
         </is>
       </c>
       <c r="K13" s="18" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="O13" s="16" t="inlineStr">
         <is>
-          <t>11,978 张</t>
+          <t>6,953 张</t>
         </is>
       </c>
     </row>
@@ -1600,10 +1600,10 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>开盘: 6080.0
-最高: 6095.0
-最低: 5710.0
-收盘: 5860.0</t>
+          <t>开盘: 6200.0
+最高: 6445.0
+最低: 6055.0
+收盘: 6375.0</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 857 张 (占量 36.4%)
+          <t>法人净买超 857 张 (占量 40.2%)
 [2026-10-27 筹码] 主力机构呈净买入 (+857 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>NT$ 5860.0</t>
+          <t>NT$ 6375.0</t>
         </is>
       </c>
       <c r="K14" s="9" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="O14" s="7" t="inlineStr">
         <is>
-          <t>2,354 张</t>
+          <t>2,130 张</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-27 20:31:24 | 策略: 3-3-4 分批建仓</t>
+          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-28 14:57:18 | 策略: 3-3-4 分批建仓</t>
         </is>
       </c>
     </row>
@@ -1772,22 +1772,22 @@
       </c>
       <c r="C4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2380.0</t>
+          <t>NT$ 2420.0</t>
         </is>
       </c>
       <c r="D4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2405.0</t>
+          <t>NT$ 2430.0</t>
         </is>
       </c>
       <c r="E4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2380.0</t>
+          <t>NT$ 2410.0</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2400.0</t>
+          <t>NT$ 2425.0</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
@@ -1819,22 +1819,22 @@
       </c>
       <c r="C5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 9830.0</t>
+          <t>NT$ 10225.0</t>
         </is>
       </c>
       <c r="D5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 9890.0</t>
+          <t>NT$ 10290.0</t>
         </is>
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 9475.0</t>
+          <t>NT$ 10015.0</t>
         </is>
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 9810.0</t>
+          <t>NT$ 10150.0</t>
         </is>
       </c>
       <c r="G5" s="29" t="inlineStr">
@@ -1866,22 +1866,22 @@
       </c>
       <c r="C6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5200.0</t>
+          <t>NT$ 4975.0</t>
         </is>
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5200.0</t>
+          <t>NT$ 5065.0</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 4685.0</t>
+          <t>NT$ 4830.0</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 4750.0</t>
+          <t>NT$ 5025.0</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
@@ -1913,22 +1913,22 @@
       </c>
       <c r="C7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3300.0</t>
+          <t>NT$ 3230.0</t>
         </is>
       </c>
       <c r="D7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3320.0</t>
+          <t>NT$ 3330.0</t>
         </is>
       </c>
       <c r="E7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3050.0</t>
+          <t>NT$ 3185.0</t>
         </is>
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3130.0</t>
+          <t>NT$ 3215.0</t>
         </is>
       </c>
       <c r="G7" s="29" t="inlineStr">
@@ -1960,22 +1960,22 @@
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
+          <t>NT$ 248.0</t>
+        </is>
+      </c>
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>NT$ 252.0</t>
+        </is>
+      </c>
+      <c r="E8" s="24" t="inlineStr">
+        <is>
           <t>NT$ 246.5</t>
         </is>
       </c>
-      <c r="D8" s="24" t="inlineStr">
-        <is>
-          <t>NT$ 248.5</t>
-        </is>
-      </c>
-      <c r="E8" s="24" t="inlineStr">
-        <is>
-          <t>NT$ 244.0</t>
-        </is>
-      </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>NT$ 247.5</t>
+          <t>NT$ 251.5</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
@@ -2007,22 +2007,22 @@
       </c>
       <c r="C9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1535.0</t>
+          <t>NT$ 1565.0</t>
         </is>
       </c>
       <c r="D9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1570.0</t>
+          <t>NT$ 1575.0</t>
         </is>
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1490.0</t>
+          <t>NT$ 1515.0</t>
         </is>
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1510.0</t>
+          <t>NT$ 1550.0</t>
         </is>
       </c>
       <c r="G9" s="29" t="inlineStr">
@@ -2054,22 +2054,22 @@
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1760.0</t>
+          <t>NT$ 1820.0</t>
         </is>
       </c>
       <c r="D10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1805.0</t>
+          <t>NT$ 1830.0</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1740.0</t>
+          <t>NT$ 1780.0</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 1760.0</t>
+          <t>NT$ 1815.0</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
@@ -2101,22 +2101,22 @@
       </c>
       <c r="C11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1910.0</t>
+          <t>NT$ 1995.0</t>
         </is>
       </c>
       <c r="D11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1980.0</t>
+          <t>NT$ 2050.0</t>
         </is>
       </c>
       <c r="E11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1905.0</t>
+          <t>NT$ 1995.0</t>
         </is>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1955.0</t>
+          <t>NT$ 2035.0</t>
         </is>
       </c>
       <c r="G11" s="29" t="inlineStr">
@@ -2148,22 +2148,22 @@
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 654.0</t>
+          <t>NT$ 672.0</t>
         </is>
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 668.0</t>
+          <t>NT$ 698.0</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 642.0</t>
+          <t>NT$ 672.0</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 651.0</t>
+          <t>NT$ 695.0</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
@@ -2195,22 +2195,22 @@
       </c>
       <c r="C13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4035.0</t>
+          <t>NT$ 4040.0</t>
         </is>
       </c>
       <c r="D13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4075.0</t>
+          <t>NT$ 4245.0</t>
         </is>
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3910.0</t>
+          <t>NT$ 4040.0</t>
         </is>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3960.0</t>
+          <t>NT$ 4235.0</t>
         </is>
       </c>
       <c r="G13" s="29" t="inlineStr">
@@ -2242,22 +2242,22 @@
       </c>
       <c r="C14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 6080.0</t>
+          <t>NT$ 6200.0</t>
         </is>
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 6095.0</t>
+          <t>NT$ 6445.0</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5710.0</t>
+          <t>NT$ 6055.0</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>NT$ 5860.0</t>
+          <t>NT$ 6375.0</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">

--- a/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
+++ b/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="核心卡位龙头全景深度分析" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="买卖决策速查面板" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="核心卡位龙头全景深度分析" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="买卖决策速查面板" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -631,7 +631,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>定盘时间: 2026-10-28 14:57:18 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
+          <t>定盘时间: 2026-10-28 21:19:42 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
         </is>
       </c>
     </row>
@@ -751,15 +751,15 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>外资: -1619 张
-投信: +2420 张
-[2026-10-27 官方结算] 投信内资买超 (+2,420 张) 逢低承接，外资高档调节 (-1,619 张)。</t>
+          <t>外资: -3176 张
+投信: +844 张
+[2026-10-28 官方结算] 投信内资买超 (+844 张) 逢低承接，外资高档调节 (-3,176 张)。</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 2,709 张 (占量 13.6%)
-[2026-10-27 筹码] 主力机构呈净买入 (+2,709 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 2,069 张 (占量 10.4%)
+[2026-10-28 筹码] 主力机构呈净卖出 (-2,069 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
@@ -838,15 +838,15 @@
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>外资: +64 张
-投信: +32 张
-[2026-10-27 官方结算] 三大法人全线买超 (+108 张)，外资与投信合力加仓。</t>
+          <t>外资: +68 张
+投信: +17 张
+[2026-10-28 官方结算] 外资与投信联手买超 (+69 张)，内外部机构共振做多。</t>
         </is>
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 108 张 (占量 35.4%)
-[2026-10-27 筹码] 主力机构呈净买入 (+108 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 69 张 (占量 22.6%)
+[2026-10-28 筹码] 主力机构呈净买入 (+69 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -925,15 +925,15 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>外资: -1055 张
-投信: +146 张
-[2026-10-27 官方结算] 投信内资买超 (+146 张) 逢低承接，外资高档调节 (-1,055 张)。</t>
+          <t>外资: -679 张
+投信: +24 张
+[2026-10-28 官方结算] 投信内资买超 (+24 张) 逢低承接，外资高档调节 (-679 张)。</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 760 张 (占量 24.3%)
-[2026-10-27 筹码] 主力机构呈净卖出 (-760 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 506 张 (占量 16.2%)
+[2026-10-28 筹码] 主力机构呈净卖出 (-506 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
@@ -1012,15 +1012,15 @@
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>外资: -247 张
-投信: +375 张
-[2026-10-27 官方结算] 投信内资买超 (+375 张) 逢低承接，外资高档调节 (-247 张)。</t>
+          <t>外资: -160 张
+投信: +236 张
+[2026-10-28 官方结算] 投信内资买超 (+236 张) 逢低承接，外资高档调节 (-160 张)。</t>
         </is>
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 126 张 (占量 6.2%)
-[2026-10-27 筹码] 主力机构呈净买入 (+126 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 119 张 (占量 5.9%)
+[2026-10-28 筹码] 主力机构呈净买入 (+119 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I7" s="15" t="inlineStr">
@@ -1099,15 +1099,15 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>外资: +4971 张
-投信: +828 张
-[2026-10-27 官方结算] 三大法人全线买超 (+7,123 张)，外资与投信合力加仓。</t>
+          <t>外资: +11299 张
+投信: +216 张
+[2026-10-28 官方结算] 三大法人全线买超 (+12,082 张)，外资与投信合力加仓。</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 7,123 张 (占量 17.2%)
-[2026-10-27 筹码] 主力机构呈净买入 (+7,123 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 12,082 张 (占量 29.2%)
+[2026-10-28 筹码] 主力机构呈净买入 (+12,082 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -1186,15 +1186,15 @@
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
-          <t>外资: -3334 张
-投信: +7 张
-[2026-10-27 官方结算] 投信内资买超 (+7 张) 逢低承接，外资高档调节 (-3,334 张)。</t>
+          <t>外资: +1 张
+投信: -729 张
+[2026-10-28 官方结算] 外资主力大幅回流 (+1 张)，投信阶段获利减仓 (-729 张)。</t>
         </is>
       </c>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 2,662 张 (占量 38.4%)
-[2026-10-27 筹码] 主力机构呈净卖出 (-2,662 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 836 张 (占量 12.1%)
+[2026-10-28 筹码] 主力机构呈净卖出 (-836 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I9" s="15" t="inlineStr">
@@ -1273,15 +1273,15 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>外资: +475 张
-投信: +21 张
-[2026-10-27 官方结算] 三大法人全线买超 (+552 张)，外资与投信合力加仓。</t>
+          <t>外资: +800 张
+投信: -12 张
+[2026-10-28 官方结算] 外资主力大幅回流 (+800 张)，投信阶段获利减仓 (-12 张)。</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 552 张 (占量 19.1%)
-[2026-10-27 筹码] 主力机构呈净买入 (+552 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 811 张 (占量 28.1%)
+[2026-10-28 筹码] 主力机构呈净买入 (+811 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1360,15 +1360,15 @@
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>外资: -170 张
-投信: +78 张
-[2026-10-27 官方结算] 投信内资买超 (+78 张) 逢低承接，外资高档调节 (-170 张)。</t>
+          <t>外资: +382 张
+投信: +3 张
+[2026-10-28 官方结算] 三大法人全线买超 (+474 张)，外资与投信合力加仓。</t>
         </is>
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 42 张 (占量 1.0%)
-[2026-10-27 筹码] 主力机构呈净卖出 (-42 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 474 张 (占量 11.7%)
+[2026-10-28 筹码] 主力机构呈净买入 (+474 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I11" s="15" t="inlineStr">
@@ -1447,15 +1447,15 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>外资: -5281 张
-投信: +3786 张
-[2026-10-27 官方结算] 投信内资买超 (+3,786 张) 逢低承接，外资高档调节 (-5,281 张)。</t>
+          <t>外资: +108 张
+投信: +5189 张
+[2026-10-28 官方结算] 三大法人全线买超 (+5,706 张)，外资与投信合力加仓。</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 850 张 (占量 4.5%)
-[2026-10-27 筹码] 主力机构呈净卖出 (-850 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 5,706 张 (占量 30.2%)
+[2026-10-28 筹码] 主力机构呈净买入 (+5,706 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -1534,15 +1534,15 @@
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>外资: -2340 张
-投信: +674 张
-[2026-10-27 官方结算] 投信内资买超 (+674 张) 逢低承接，外资高档调节 (-2,340 张)。</t>
+          <t>外资: -1037 张
+投信: +551 张
+[2026-10-28 官方结算] 投信内资买超 (+551 张) 逢低承接，外资高档调节 (-1,037 张)。</t>
         </is>
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 1,492 张 (占量 21.5%)
-[2026-10-27 筹码] 主力机构呈净卖出 (-1,492 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 209 张 (占量 3.0%)
+[2026-10-28 筹码] 主力机构呈净卖出 (-209 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I13" s="15" t="inlineStr">
@@ -1621,15 +1621,15 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>外资: +780 张
-投信: +58 张
-[2026-10-27 官方结算] 三大法人全线买超 (+857 张)，外资与投信合力加仓。</t>
+          <t>外资: -376 张
+投信: +112 张
+[2026-10-28 官方结算] 投信内资买超 (+112 张) 逢低承接，外资高档调节 (-376 张)。</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 857 张 (占量 40.2%)
-[2026-10-27 筹码] 主力机构呈净买入 (+857 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 271 张 (占量 12.7%)
+[2026-10-28 筹码] 主力机构呈净卖出 (-271 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -1708,7 +1708,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-28 14:57:18 | 策略: 3-3-4 分批建仓</t>
+          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-28 21:19:42 | 策略: 3-3-4 分批建仓</t>
         </is>
       </c>
     </row>

--- a/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
+++ b/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
@@ -631,7 +631,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>定盘时间: 2026-10-28 21:19:42 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
+          <t>定盘时间: 2026-10-29 21:28:17 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
         </is>
       </c>
     </row>
@@ -731,9 +731,9 @@
       <c r="D4" s="7" t="inlineStr">
         <is>
           <t>开盘: 2420.0
-最高: 2430.0
-最低: 2410.0
-收盘: 2425.0</t>
+最高: 2425.0
+最低: 2390.0
+收盘: 2415.0</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -751,15 +751,15 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>外资: -3176 张
-投信: +844 张
-[2026-10-28 官方结算] 投信内资买超 (+844 张) 逢低承接，外资高档调节 (-3,176 张)。</t>
+          <t>外资: -11 张
+投信: +443 张
+[2026-10-29 官方结算] 投信内资买超 (+443 张) 逢低承接，外资高档调节 (-11 张)。</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 2,069 张 (占量 10.4%)
-[2026-10-28 筹码] 主力机构呈净卖出 (-2,069 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 151 张 (占量 0.9%)
+[2026-10-29 筹码] 主力机构呈净买入 (+151 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2425.0</t>
+          <t>NT$ 2415.0</t>
         </is>
       </c>
       <c r="K4" s="9" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>19,852 张</t>
+          <t>16,833 张</t>
         </is>
       </c>
     </row>
@@ -817,10 +817,10 @@
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>开盘: 10225.0
-最高: 10290.0
-最低: 10015.0
-收盘: 10150.0</t>
+          <t>开盘: 10250.0
+最高: 10250.0
+最低: 9600.0
+收盘: 9880.0</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -838,15 +838,15 @@
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>外资: +68 张
-投信: +17 张
-[2026-10-28 官方结算] 外资与投信联手买超 (+69 张)，内外部机构共振做多。</t>
+          <t>外资: +22 张
+投信: +50 张
+[2026-10-29 官方结算] 外资与投信联手买超 (+57 张)，内外部机构共振做多。</t>
         </is>
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 69 张 (占量 22.6%)
-[2026-10-28 筹码] 主力机构呈净买入 (+69 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 57 张 (占量 11.7%)
+[2026-10-29 筹码] 主力机构呈净买入 (+57 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 10150.0</t>
+          <t>NT$ 9880.0</t>
         </is>
       </c>
       <c r="K5" s="18" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="O5" s="16" t="inlineStr">
         <is>
-          <t>305 张</t>
+          <t>488 张</t>
         </is>
       </c>
     </row>
@@ -904,10 +904,10 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>开盘: 4975.0
-最高: 5065.0
-最低: 4830.0
-收盘: 5025.0</t>
+          <t>开盘: 5200.0
+最高: 5295.0
+最低: 4935.0
+收盘: 5010.0</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -925,15 +925,15 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>外资: -679 张
-投信: +24 张
-[2026-10-28 官方结算] 投信内资买超 (+24 张) 逢低承接，外资高档调节 (-679 张)。</t>
+          <t>外资: +223 张
+投信: +299 张
+[2026-10-29 官方结算] 外资与投信联手买超 (+521 张)，内外部机构共振做多。</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 506 张 (占量 16.2%)
-[2026-10-28 筹码] 主力机构呈净卖出 (-506 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 521 张 (占量 15.1%)
+[2026-10-29 筹码] 主力机构呈净买入 (+521 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 5025.0</t>
+          <t>NT$ 5010.0</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>3,130 张</t>
+          <t>3,450 张</t>
         </is>
       </c>
     </row>
@@ -991,10 +991,10 @@
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>开盘: 3230.0
-最高: 3330.0
-最低: 3185.0
-收盘: 3215.0</t>
+          <t>开盘: 3220.0
+最高: 3260.0
+最低: 3080.0
+收盘: 3105.0</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -1012,15 +1012,15 @@
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>外资: -160 张
-投信: +236 张
-[2026-10-28 官方结算] 投信内资买超 (+236 张) 逢低承接，外资高档调节 (-160 张)。</t>
+          <t>外资: -333 张
+投信: +23 张
+[2026-10-29 官方结算] 投信内资买超 (+23 张) 逢低承接，外资高档调节 (-333 张)。</t>
         </is>
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 119 张 (占量 5.9%)
-[2026-10-28 筹码] 主力机构呈净买入 (+119 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 346 张 (占量 19.4%)
+[2026-10-29 筹码] 主力机构呈净卖出 (-346 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I7" s="15" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="J7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3215.0</t>
+          <t>NT$ 3105.0</t>
         </is>
       </c>
       <c r="K7" s="18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="O7" s="16" t="inlineStr">
         <is>
-          <t>2,024 张</t>
+          <t>1,780 张</t>
         </is>
       </c>
     </row>
@@ -1078,10 +1078,10 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>开盘: 248.0
-最高: 252.0
-最低: 246.5
-收盘: 251.5</t>
+          <t>开盘: 250.0
+最高: 253.5
+最低: 247.0
+收盘: 248.0</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -1099,15 +1099,15 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>外资: +11299 张
-投信: +216 张
-[2026-10-28 官方结算] 三大法人全线买超 (+12,082 张)，外资与投信合力加仓。</t>
+          <t>外资: +3341 张
+投信: +512 张
+[2026-10-29 官方结算] 外资与投信联手买超 (+3,737 张)，内外部机构共振做多。</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 12,082 张 (占量 29.2%)
-[2026-10-28 筹码] 主力机构呈净买入 (+12,082 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 3,737 张 (占量 17.9%)
+[2026-10-29 筹码] 主力机构呈净买入 (+3,737 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>NT$ 251.5</t>
+          <t>NT$ 248.0</t>
         </is>
       </c>
       <c r="K8" s="9" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="O8" s="7" t="inlineStr">
         <is>
-          <t>41,355 张</t>
+          <t>20,873 张</t>
         </is>
       </c>
     </row>
@@ -1165,10 +1165,10 @@
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>开盘: 1565.0
-最高: 1575.0
-最低: 1515.0
-收盘: 1550.0</t>
+          <t>开盘: 1525.0
+最高: 1525.0
+最低: 1430.0
+收盘: 1480.0</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -1186,15 +1186,15 @@
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
-          <t>外资: +1 张
-投信: -729 张
-[2026-10-28 官方结算] 外资主力大幅回流 (+1 张)，投信阶段获利减仓 (-729 张)。</t>
+          <t>外资: -2432 张
+投信: -1534 张
+[2026-10-29 官方结算] 外资与投信偏空调节 (-3,901 张)，机构筹码阶段获利了结。</t>
         </is>
       </c>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 836 张 (占量 12.1%)
-[2026-10-28 筹码] 主力机构呈净卖出 (-836 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 3,901 张 (占量 25.6%)
+[2026-10-29 筹码] 主力机构呈净卖出 (-3,901 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I9" s="15" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="J9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1550.0</t>
+          <t>NT$ 1480.0</t>
         </is>
       </c>
       <c r="K9" s="18" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="O9" s="16" t="inlineStr">
         <is>
-          <t>6,925 张</t>
+          <t>15,211 张</t>
         </is>
       </c>
     </row>
@@ -1252,10 +1252,10 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>开盘: 1820.0
-最高: 1830.0
-最低: 1780.0
-收盘: 1815.0</t>
+          <t>开盘: 1845.0
+最高: 1875.0
+最低: 1740.0
+收盘: 1755.0</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -1273,15 +1273,15 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>外资: +800 张
-投信: -12 张
-[2026-10-28 官方结算] 外资主力大幅回流 (+800 张)，投信阶段获利减仓 (-12 张)。</t>
+          <t>外资: -35 张
+投信: -175 张
+[2026-10-29 官方结算] 外资与投信偏空调节 (-175 张)，机构筹码阶段获利了结。</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 811 张 (占量 28.1%)
-[2026-10-28 筹码] 主力机构呈净买入 (+811 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 175 张 (占量 5.1%)
+[2026-10-29 筹码] 主力机构呈净卖出 (-175 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 1815.0</t>
+          <t>NT$ 1755.0</t>
         </is>
       </c>
       <c r="K10" s="9" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>2,889 张</t>
+          <t>3,444 张</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>开盘: 1995.0
-最高: 2050.0
-最低: 1995.0
-收盘: 2035.0</t>
+          <t>开盘: 2045.0
+最高: 2070.0
+最低: 1910.0
+收盘: 1945.0</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
@@ -1360,15 +1360,15 @@
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>外资: +382 张
-投信: +3 张
-[2026-10-28 官方结算] 三大法人全线买超 (+474 张)，外资与投信合力加仓。</t>
+          <t>外资: -152 张
+投信: -106 张
+[2026-10-29 官方结算] 三大法人同步卖超 (-260 张)，短线筹码面临清洗。</t>
         </is>
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 474 张 (占量 11.7%)
-[2026-10-28 筹码] 主力机构呈净买入 (+474 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 260 张 (占量 9.0%)
+[2026-10-29 筹码] 主力机构呈净卖出 (-260 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I11" s="15" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="J11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2035.0</t>
+          <t>NT$ 1945.0</t>
         </is>
       </c>
       <c r="K11" s="18" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="O11" s="16" t="inlineStr">
         <is>
-          <t>4,050 张</t>
+          <t>2,892 张</t>
         </is>
       </c>
     </row>
@@ -1426,10 +1426,10 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>开盘: 672.0
-最高: 698.0
-最低: 672.0
-收盘: 695.0</t>
+          <t>开盘: 709.0
+最高: 709.0
+最低: 676.0
+收盘: 683.0</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -1447,15 +1447,15 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>外资: +108 张
-投信: +5189 张
-[2026-10-28 官方结算] 三大法人全线买超 (+5,706 张)，外资与投信合力加仓。</t>
+          <t>外资: -3504 张
+投信: +1141 张
+[2026-10-29 官方结算] 投信内资买超 (+1,141 张) 逢低承接，外资高档调节 (-3,504 张)。</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 5,706 张 (占量 30.2%)
-[2026-10-28 筹码] 主力机构呈净买入 (+5,706 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 2,138 张 (占量 16.8%)
+[2026-10-29 筹码] 主力机构呈净卖出 (-2,138 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 695.0</t>
+          <t>NT$ 683.0</t>
         </is>
       </c>
       <c r="K12" s="9" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>18,912 张</t>
+          <t>12,752 张</t>
         </is>
       </c>
     </row>
@@ -1513,10 +1513,10 @@
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>开盘: 4040.0
-最高: 4245.0
-最低: 4040.0
-收盘: 4235.0</t>
+          <t>开盘: 4205.0
+最高: 4225.0
+最低: 4000.0
+收盘: 4045.0</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
@@ -1534,15 +1534,15 @@
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>外资: -1037 张
-投信: +551 张
-[2026-10-28 官方结算] 投信内资买超 (+551 张) 逢低承接，外资高档调节 (-1,037 张)。</t>
+          <t>外资: -1683 张
+投信: +366 张
+[2026-10-29 官方结算] 投信内资买超 (+366 张) 逢低承接，外资高档调节 (-1,683 张)。</t>
         </is>
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 209 张 (占量 3.0%)
-[2026-10-28 筹码] 主力机构呈净卖出 (-209 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 1,223 张 (占量 20.0%)
+[2026-10-29 筹码] 主力机构呈净卖出 (-1,223 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I13" s="15" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="J13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 4235.0</t>
+          <t>NT$ 4045.0</t>
         </is>
       </c>
       <c r="K13" s="18" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="O13" s="16" t="inlineStr">
         <is>
-          <t>6,953 张</t>
+          <t>6,113 张</t>
         </is>
       </c>
     </row>
@@ -1600,10 +1600,10 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>开盘: 6200.0
-最高: 6445.0
-最低: 6055.0
-收盘: 6375.0</t>
+          <t>开盘: 6500.0
+最高: 6655.0
+最低: 6230.0
+收盘: 6405.0</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -1621,15 +1621,15 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>外资: -376 张
-投信: +112 张
-[2026-10-28 官方结算] 投信内资买超 (+112 张) 逢低承接，外资高档调节 (-376 张)。</t>
+          <t>外资: -517 张
+投信: +88 张
+[2026-10-29 官方结算] 投信内资买超 (+88 张) 逢低承接，外资高档调节 (-517 张)。</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 271 张 (占量 12.7%)
-[2026-10-28 筹码] 主力机构呈净卖出 (-271 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 431 张 (占量 22.4%)
+[2026-10-29 筹码] 主力机构呈净卖出 (-431 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>NT$ 6375.0</t>
+          <t>NT$ 6405.0</t>
         </is>
       </c>
       <c r="K14" s="9" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="O14" s="7" t="inlineStr">
         <is>
-          <t>2,130 张</t>
+          <t>1,923 张</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-28 21:19:42 | 策略: 3-3-4 分批建仓</t>
+          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-29 21:28:17 | 策略: 3-3-4 分批建仓</t>
         </is>
       </c>
     </row>
@@ -1777,17 +1777,17 @@
       </c>
       <c r="D4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2430.0</t>
+          <t>NT$ 2425.0</t>
         </is>
       </c>
       <c r="E4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2410.0</t>
+          <t>NT$ 2390.0</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2425.0</t>
+          <t>NT$ 2415.0</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
@@ -1819,22 +1819,22 @@
       </c>
       <c r="C5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 10225.0</t>
+          <t>NT$ 10250.0</t>
         </is>
       </c>
       <c r="D5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 10290.0</t>
+          <t>NT$ 10250.0</t>
         </is>
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 10015.0</t>
+          <t>NT$ 9600.0</t>
         </is>
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 10150.0</t>
+          <t>NT$ 9880.0</t>
         </is>
       </c>
       <c r="G5" s="29" t="inlineStr">
@@ -1866,22 +1866,22 @@
       </c>
       <c r="C6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 4975.0</t>
+          <t>NT$ 5200.0</t>
         </is>
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5065.0</t>
+          <t>NT$ 5295.0</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 4830.0</t>
+          <t>NT$ 4935.0</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 5025.0</t>
+          <t>NT$ 5010.0</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
@@ -1913,22 +1913,22 @@
       </c>
       <c r="C7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3230.0</t>
+          <t>NT$ 3220.0</t>
         </is>
       </c>
       <c r="D7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3330.0</t>
+          <t>NT$ 3260.0</t>
         </is>
       </c>
       <c r="E7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3185.0</t>
+          <t>NT$ 3080.0</t>
         </is>
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3215.0</t>
+          <t>NT$ 3105.0</t>
         </is>
       </c>
       <c r="G7" s="29" t="inlineStr">
@@ -1960,22 +1960,22 @@
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
+          <t>NT$ 250.0</t>
+        </is>
+      </c>
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>NT$ 253.5</t>
+        </is>
+      </c>
+      <c r="E8" s="24" t="inlineStr">
+        <is>
+          <t>NT$ 247.0</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
           <t>NT$ 248.0</t>
-        </is>
-      </c>
-      <c r="D8" s="24" t="inlineStr">
-        <is>
-          <t>NT$ 252.0</t>
-        </is>
-      </c>
-      <c r="E8" s="24" t="inlineStr">
-        <is>
-          <t>NT$ 246.5</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>NT$ 251.5</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
@@ -2007,22 +2007,22 @@
       </c>
       <c r="C9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1565.0</t>
+          <t>NT$ 1525.0</t>
         </is>
       </c>
       <c r="D9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1575.0</t>
+          <t>NT$ 1525.0</t>
         </is>
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1515.0</t>
+          <t>NT$ 1430.0</t>
         </is>
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1550.0</t>
+          <t>NT$ 1480.0</t>
         </is>
       </c>
       <c r="G9" s="29" t="inlineStr">
@@ -2054,22 +2054,22 @@
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1820.0</t>
+          <t>NT$ 1845.0</t>
         </is>
       </c>
       <c r="D10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1830.0</t>
+          <t>NT$ 1875.0</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1780.0</t>
+          <t>NT$ 1740.0</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 1815.0</t>
+          <t>NT$ 1755.0</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
@@ -2101,22 +2101,22 @@
       </c>
       <c r="C11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1995.0</t>
+          <t>NT$ 2045.0</t>
         </is>
       </c>
       <c r="D11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2050.0</t>
+          <t>NT$ 2070.0</t>
         </is>
       </c>
       <c r="E11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1995.0</t>
+          <t>NT$ 1910.0</t>
         </is>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 2035.0</t>
+          <t>NT$ 1945.0</t>
         </is>
       </c>
       <c r="G11" s="29" t="inlineStr">
@@ -2148,22 +2148,22 @@
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 672.0</t>
+          <t>NT$ 709.0</t>
         </is>
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 698.0</t>
+          <t>NT$ 709.0</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 672.0</t>
+          <t>NT$ 676.0</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 695.0</t>
+          <t>NT$ 683.0</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
@@ -2195,22 +2195,22 @@
       </c>
       <c r="C13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4040.0</t>
+          <t>NT$ 4205.0</t>
         </is>
       </c>
       <c r="D13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4245.0</t>
+          <t>NT$ 4225.0</t>
         </is>
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4040.0</t>
+          <t>NT$ 4000.0</t>
         </is>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 4235.0</t>
+          <t>NT$ 4045.0</t>
         </is>
       </c>
       <c r="G13" s="29" t="inlineStr">
@@ -2242,22 +2242,22 @@
       </c>
       <c r="C14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 6200.0</t>
+          <t>NT$ 6500.0</t>
         </is>
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 6445.0</t>
+          <t>NT$ 6655.0</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 6055.0</t>
+          <t>NT$ 6230.0</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>NT$ 6375.0</t>
+          <t>NT$ 6405.0</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">

--- a/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
+++ b/台股 5 大 AI 核心卡位龙头深度投资与买卖点筹码量化分析表.xlsx
@@ -631,7 +631,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>定盘时间: 2026-10-29 21:28:17 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
+          <t>定盘时间: 2026-10-30 21:16:57 | 数据源: Shioaji Snapshot (primary) + TWSE MIS cross-check | 包含三大法人买卖超、财报发布日及主力资金分析</t>
         </is>
       </c>
     </row>
@@ -730,10 +730,10 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>开盘: 2420.0
-最高: 2425.0
-最低: 2390.0
-收盘: 2415.0</t>
+          <t>开盘: 2380.0
+最高: 2380.0
+最低: 2360.0
+收盘: 2370.0</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -751,15 +751,15 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>外资: -11 张
-投信: +443 张
-[2026-10-29 官方结算] 投信内资买超 (+443 张) 逢低承接，外资高档调节 (-11 张)。</t>
+          <t>外资: -8633 张
+投信: +1854 张
+[2026-10-30 官方结算] 投信内资买超 (+1,854 张) 逢低承接，外资高档调节 (-8,633 张)。</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 151 张 (占量 0.9%)
-[2026-10-29 筹码] 主力机构呈净买入 (+151 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 5,857 张 (占量 19.8%)
+[2026-10-30 筹码] 主力机构呈净卖出 (-5,857 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2415.0</t>
+          <t>NT$ 2370.0</t>
         </is>
       </c>
       <c r="K4" s="9" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>16,833 张</t>
+          <t>29,595 张</t>
         </is>
       </c>
     </row>
@@ -817,10 +817,10 @@
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>开盘: 10250.0
-最高: 10250.0
-最低: 9600.0
-收盘: 9880.0</t>
+          <t>开盘: 9415.0
+最高: 9840.0
+最低: 9345.0
+收盘: 9650.0</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -838,15 +838,15 @@
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>外资: +22 张
-投信: +50 张
-[2026-10-29 官方结算] 外资与投信联手买超 (+57 张)，内外部机构共振做多。</t>
+          <t>外资: -16 张
+投信: +37 张
+[2026-10-30 官方结算] 投信内资买超 (+37 张) 逢低承接，外资高档调节 (-16 张)。</t>
         </is>
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>法人净买超 57 张 (占量 11.7%)
-[2026-10-29 筹码] 主力机构呈净买入 (+57 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净买超 21 张 (占量 5.2%)
+[2026-10-30 筹码] 主力机构呈净买入 (+21 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 9880.0</t>
+          <t>NT$ 9650.0</t>
         </is>
       </c>
       <c r="K5" s="18" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="O5" s="16" t="inlineStr">
         <is>
-          <t>488 张</t>
+          <t>401 张</t>
         </is>
       </c>
     </row>
@@ -904,10 +904,10 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>开盘: 5200.0
-最高: 5295.0
-最低: 4935.0
-收盘: 5010.0</t>
+          <t>开盘: 4570.0
+最高: 4760.0
+最低: 4560.0
+收盘: 4675.0</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -920,20 +920,20 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>2026-10-29 (26Q3 财报) | 每月 10 日发布营收</t>
+          <t>2026-10-29 (26Q3 財報已舉行)；下一次財報/法說會日期待公司公告 | 每月 10 日发布营收</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>外资: +223 张
-投信: +299 张
-[2026-10-29 官方结算] 外资与投信联手买超 (+521 张)，内外部机构共振做多。</t>
+          <t>外资: -697 张
+投信: +310 张
+[2026-10-30 官方结算] 投信内资买超 (+310 张) 逢低承接，外资高档调节 (-697 张)。</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 521 张 (占量 15.1%)
-[2026-10-29 筹码] 主力机构呈净买入 (+521 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 485 张 (占量 14.1%)
+[2026-10-30 筹码] 主力机构呈净卖出 (-485 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 5010.0</t>
+          <t>NT$ 4675.0</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>3,450 张</t>
+          <t>3,437 张</t>
         </is>
       </c>
     </row>
@@ -991,10 +991,10 @@
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>开盘: 3220.0
-最高: 3260.0
-最低: 3080.0
-收盘: 3105.0</t>
+          <t>开盘: 2890.0
+最高: 3150.0
+最低: 2885.0
+收盘: 3095.0</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -1012,15 +1012,15 @@
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>外资: -333 张
-投信: +23 张
-[2026-10-29 官方结算] 投信内资买超 (+23 张) 逢低承接，外资高档调节 (-333 张)。</t>
+          <t>外资: -400 张
+投信: +477 张
+[2026-10-30 官方结算] 投信内资买超 (+477 张) 逢低承接，外资高档调节 (-400 张)。</t>
         </is>
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 346 张 (占量 19.4%)
-[2026-10-29 筹码] 主力机构呈净卖出 (-346 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 118 张 (占量 4.4%)
+[2026-10-30 筹码] 主力机构呈净买入 (+118 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I7" s="15" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="J7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3105.0</t>
+          <t>NT$ 3095.0</t>
         </is>
       </c>
       <c r="K7" s="18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="O7" s="16" t="inlineStr">
         <is>
-          <t>1,780 张</t>
+          <t>2,661 张</t>
         </is>
       </c>
     </row>
@@ -1078,10 +1078,10 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>开盘: 250.0
-最高: 253.5
-最低: 247.0
-收盘: 248.0</t>
+          <t>开盘: 245.0
+最高: 246.0
+最低: 240.0
+收盘: 245.5</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -1099,15 +1099,15 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>外资: +3341 张
-投信: +512 张
-[2026-10-29 官方结算] 外资与投信联手买超 (+3,737 张)，内外部机构共振做多。</t>
+          <t>外资: -3393 张
+投信: +1373 张
+[2026-10-30 官方结算] 投信内资买超 (+1,373 张) 逢低承接，外资高档调节 (-3,393 张)。</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>法人净买超 3,737 张 (占量 17.9%)
-[2026-10-29 筹码] 主力机构呈净买入 (+3,737 张)，筹码向法人端汇聚沉淀。</t>
+          <t>法人净卖超 1,895 张 (占量 5.8%)
+[2026-10-30 筹码] 主力机构呈净卖出 (-1,895 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>NT$ 248.0</t>
+          <t>NT$ 245.5</t>
         </is>
       </c>
       <c r="K8" s="9" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="O8" s="7" t="inlineStr">
         <is>
-          <t>20,873 张</t>
+          <t>32,633 张</t>
         </is>
       </c>
     </row>
@@ -1165,10 +1165,10 @@
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>开盘: 1525.0
-最高: 1525.0
-最低: 1430.0
-收盘: 1480.0</t>
+          <t>开盘: 1365.0
+最高: 1395.0
+最低: 1335.0
+收盘: 1335.0</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -1186,15 +1186,15 @@
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
-          <t>外资: -2432 张
-投信: -1534 张
-[2026-10-29 官方结算] 外资与投信偏空调节 (-3,901 张)，机构筹码阶段获利了结。</t>
+          <t>外资: -10954 张
+投信: -465 张
+[2026-10-30 官方结算] 外资与投信偏空调节 (-11,385 张)，机构筹码阶段获利了结。</t>
         </is>
       </c>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 3,901 张 (占量 25.6%)
-[2026-10-29 筹码] 主力机构呈净卖出 (-3,901 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 11,385 张 (占量 62.3%)
+[2026-10-30 筹码] 主力机构呈净卖出 (-11,385 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I9" s="15" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="J9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1480.0</t>
+          <t>NT$ 1335.0</t>
         </is>
       </c>
       <c r="K9" s="18" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="O9" s="16" t="inlineStr">
         <is>
-          <t>15,211 张</t>
+          <t>18,275 张</t>
         </is>
       </c>
     </row>
@@ -1252,10 +1252,10 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>开盘: 1845.0
-最高: 1875.0
-最低: 1740.0
-收盘: 1755.0</t>
+          <t>开盘: 1680.0
+最高: 1685.0
+最低: 1580.0
+收盘: 1615.0</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -1273,15 +1273,15 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>外资: -35 张
-投信: -175 张
-[2026-10-29 官方结算] 外资与投信偏空调节 (-175 张)，机构筹码阶段获利了结。</t>
+          <t>外资: +360 张
+投信: -129 张
+[2026-10-30 官方结算] 外资主力大幅回流 (+360 张)，投信阶段获利减仓 (-129 张)。</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 175 张 (占量 5.1%)
-[2026-10-29 筹码] 主力机构呈净卖出 (-175 张)，散户承接，筹码短期发散。</t>
+          <t>法人净买超 258 张 (占量 5.4%)
+[2026-10-30 筹码] 主力机构呈净买入 (+258 张)，筹码向法人端汇聚沉淀。</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 1755.0</t>
+          <t>NT$ 1615.0</t>
         </is>
       </c>
       <c r="K10" s="9" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>3,444 张</t>
+          <t>4,813 张</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>开盘: 2045.0
-最高: 2070.0
-最低: 1910.0
-收盘: 1945.0</t>
+          <t>开盘: 1770.0
+最高: 1800.0
+最低: 1755.0
+收盘: 1755.0</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
@@ -1360,15 +1360,15 @@
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>外资: -152 张
-投信: -106 张
-[2026-10-29 官方结算] 三大法人同步卖超 (-260 张)，短线筹码面临清洗。</t>
+          <t>外资: -157 张
+投信: -48 张
+[2026-10-30 官方结算] 三大法人同步卖超 (-280 张)，短线筹码面临清洗。</t>
         </is>
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 260 张 (占量 9.0%)
-[2026-10-29 筹码] 主力机构呈净卖出 (-260 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 280 张 (占量 16.6%)
+[2026-10-30 筹码] 主力机构呈净卖出 (-280 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I11" s="15" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="J11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1945.0</t>
+          <t>NT$ 1755.0</t>
         </is>
       </c>
       <c r="K11" s="18" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="O11" s="16" t="inlineStr">
         <is>
-          <t>2,892 张</t>
+          <t>1,686 张</t>
         </is>
       </c>
     </row>
@@ -1426,10 +1426,10 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>开盘: 709.0
-最高: 709.0
-最低: 676.0
-收盘: 683.0</t>
+          <t>开盘: 654.0
+最高: 675.0
+最低: 624.0
+收盘: 668.0</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -1447,15 +1447,15 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>外资: -3504 张
-投信: +1141 张
-[2026-10-29 官方结算] 投信内资买超 (+1,141 张) 逢低承接，外资高档调节 (-3,504 张)。</t>
+          <t>外资: -12157 张
+投信: +7173 张
+[2026-10-30 官方结算] 投信内资买超 (+7,173 张) 逢低承接，外资高档调节 (-12,157 张)。</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 2,138 张 (占量 16.8%)
-[2026-10-29 筹码] 主力机构呈净卖出 (-2,138 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 5,055 张 (占量 16.0%)
+[2026-10-30 筹码] 主力机构呈净卖出 (-5,055 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 683.0</t>
+          <t>NT$ 668.0</t>
         </is>
       </c>
       <c r="K12" s="9" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>12,752 张</t>
+          <t>31,510 张</t>
         </is>
       </c>
     </row>
@@ -1513,10 +1513,10 @@
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>开盘: 4205.0
-最高: 4225.0
-最低: 4000.0
-收盘: 4045.0</t>
+          <t>开盘: 3820.0
+最高: 3990.0
+最低: 3805.0
+收盘: 3915.0</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
@@ -1534,15 +1534,15 @@
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>外资: -1683 张
-投信: +366 张
-[2026-10-29 官方结算] 投信内资买超 (+366 张) 逢低承接，外资高档调节 (-1,683 张)。</t>
+          <t>外资: -2954 张
+投信: +673 张
+[2026-10-30 官方结算] 投信内资买超 (+673 张) 逢低承接，外资高档调节 (-2,954 张)。</t>
         </is>
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>法人净卖超 1,223 张 (占量 20.0%)
-[2026-10-29 筹码] 主力机构呈净卖出 (-1,223 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 2,188 张 (占量 19.4%)
+[2026-10-30 筹码] 主力机构呈净卖出 (-2,188 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I13" s="15" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="J13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 4045.0</t>
+          <t>NT$ 3915.0</t>
         </is>
       </c>
       <c r="K13" s="18" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="O13" s="16" t="inlineStr">
         <is>
-          <t>6,113 张</t>
+          <t>11,302 张</t>
         </is>
       </c>
     </row>
@@ -1600,10 +1600,10 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>开盘: 6500.0
-最高: 6655.0
-最低: 6230.0
-收盘: 6405.0</t>
+          <t>开盘: 6010.0
+最高: 6525.0
+最低: 5995.0
+收盘: 6315.0</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -1621,15 +1621,15 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>外资: -517 张
-投信: +88 张
-[2026-10-29 官方结算] 投信内资买超 (+88 张) 逢低承接，外资高档调节 (-517 张)。</t>
+          <t>外资: -234 张
+投信: +126 张
+[2026-10-30 官方结算] 投信内资买超 (+126 张) 逢低承接，外资高档调节 (-234 张)。</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>法人净卖超 431 张 (占量 22.4%)
-[2026-10-29 筹码] 主力机构呈净卖出 (-431 张)，散户承接，筹码短期发散。</t>
+          <t>法人净卖超 97 张 (占量 6.7%)
+[2026-10-30 筹码] 主力机构呈净卖出 (-97 张)，散户承接，筹码短期发散。</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>NT$ 6405.0</t>
+          <t>NT$ 6315.0</t>
         </is>
       </c>
       <c r="K14" s="9" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="O14" s="7" t="inlineStr">
         <is>
-          <t>1,923 张</t>
+          <t>1,454 张</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-29 21:28:17 | 策略: 3-3-4 分批建仓</t>
+          <t>数据源: 永丰金 Shioaji 实时盘口 | 定盘时间: 2026-10-30 21:16:57 | 策略: 3-3-4 分批建仓</t>
         </is>
       </c>
     </row>
@@ -1772,22 +1772,22 @@
       </c>
       <c r="C4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2420.0</t>
+          <t>NT$ 2380.0</t>
         </is>
       </c>
       <c r="D4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2425.0</t>
+          <t>NT$ 2380.0</t>
         </is>
       </c>
       <c r="E4" s="24" t="inlineStr">
         <is>
-          <t>NT$ 2390.0</t>
+          <t>NT$ 2360.0</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>NT$ 2415.0</t>
+          <t>NT$ 2370.0</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
@@ -1819,22 +1819,22 @@
       </c>
       <c r="C5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 10250.0</t>
+          <t>NT$ 9415.0</t>
         </is>
       </c>
       <c r="D5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 10250.0</t>
+          <t>NT$ 9840.0</t>
         </is>
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>NT$ 9600.0</t>
+          <t>NT$ 9345.0</t>
         </is>
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>NT$ 9880.0</t>
+          <t>NT$ 9650.0</t>
         </is>
       </c>
       <c r="G5" s="29" t="inlineStr">
@@ -1866,22 +1866,22 @@
       </c>
       <c r="C6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5200.0</t>
+          <t>NT$ 4570.0</t>
         </is>
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 5295.0</t>
+          <t>NT$ 4760.0</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t>NT$ 4935.0</t>
+          <t>NT$ 4560.0</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>NT$ 5010.0</t>
+          <t>NT$ 4675.0</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
@@ -1913,22 +1913,22 @@
       </c>
       <c r="C7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3220.0</t>
+          <t>NT$ 2890.0</t>
         </is>
       </c>
       <c r="D7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3260.0</t>
+          <t>NT$ 3150.0</t>
         </is>
       </c>
       <c r="E7" s="28" t="inlineStr">
         <is>
-          <t>NT$ 3080.0</t>
+          <t>NT$ 2885.0</t>
         </is>
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t>NT$ 3105.0</t>
+          <t>NT$ 3095.0</t>
         </is>
       </c>
       <c r="G7" s="29" t="inlineStr">
@@ -1960,22 +1960,22 @@
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 250.0</t>
+          <t>NT$ 245.0</t>
         </is>
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 253.5</t>
+          <t>NT$ 246.0</t>
         </is>
       </c>
       <c r="E8" s="24" t="inlineStr">
         <is>
-          <t>NT$ 247.0</t>
+          <t>NT$ 240.0</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>NT$ 248.0</t>
+          <t>NT$ 245.5</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
@@ -2007,22 +2007,22 @@
       </c>
       <c r="C9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1525.0</t>
+          <t>NT$ 1365.0</t>
         </is>
       </c>
       <c r="D9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1525.0</t>
+          <t>NT$ 1395.0</t>
         </is>
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1430.0</t>
+          <t>NT$ 1335.0</t>
         </is>
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1480.0</t>
+          <t>NT$ 1335.0</t>
         </is>
       </c>
       <c r="G9" s="29" t="inlineStr">
@@ -2054,22 +2054,22 @@
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1845.0</t>
+          <t>NT$ 1680.0</t>
         </is>
       </c>
       <c r="D10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1875.0</t>
+          <t>NT$ 1685.0</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
         <is>
-          <t>NT$ 1740.0</t>
+          <t>NT$ 1580.0</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>NT$ 1755.0</t>
+          <t>NT$ 1615.0</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
@@ -2101,22 +2101,22 @@
       </c>
       <c r="C11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2045.0</t>
+          <t>NT$ 1770.0</t>
         </is>
       </c>
       <c r="D11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 2070.0</t>
+          <t>NT$ 1800.0</t>
         </is>
       </c>
       <c r="E11" s="28" t="inlineStr">
         <is>
-          <t>NT$ 1910.0</t>
+          <t>NT$ 1755.0</t>
         </is>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>NT$ 1945.0</t>
+          <t>NT$ 1755.0</t>
         </is>
       </c>
       <c r="G11" s="29" t="inlineStr">
@@ -2148,22 +2148,22 @@
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 709.0</t>
+          <t>NT$ 654.0</t>
         </is>
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 709.0</t>
+          <t>NT$ 675.0</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
         <is>
-          <t>NT$ 676.0</t>
+          <t>NT$ 624.0</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>NT$ 683.0</t>
+          <t>NT$ 668.0</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
@@ -2195,22 +2195,22 @@
       </c>
       <c r="C13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4205.0</t>
+          <t>NT$ 3820.0</t>
         </is>
       </c>
       <c r="D13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4225.0</t>
+          <t>NT$ 3990.0</t>
         </is>
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
-          <t>NT$ 4000.0</t>
+          <t>NT$ 3805.0</t>
         </is>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>NT$ 4045.0</t>
+          <t>NT$ 3915.0</t>
         </is>
       </c>
       <c r="G13" s="29" t="inlineStr">
@@ -2242,22 +2242,22 @@
       </c>
       <c r="C14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 6500.0</t>
+          <t>NT$ 6010.0</t>
         </is>
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 6655.0</t>
+          <t>NT$ 6525.0</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
         <is>
-          <t>NT$ 6230.0</t>
+          <t>NT$ 5995.0</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>NT$ 6405.0</t>
+          <t>NT$ 6315.0</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">
